--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -101,13 +101,13 @@
     <t>labStatusC4RetiredL1</t>
   </si>
   <si>
-    <t>eduHighestC4MediumL1</t>
+    <t>eduHighestC4Medium</t>
   </si>
   <si>
-    <t>eduHighestC4LowL1</t>
+    <t>eduHighestC4Low</t>
   </si>
   <si>
-    <t>eduHighestC4NaL1</t>
+    <t>eduHighestC4Na</t>
   </si>
   <si>
     <t>healthPhysicalPcsL1</t>
@@ -167,7 +167,7 @@
     <t>demRgnUKN</t>
   </si>
   <si>
-    <t>demYear</t>
+    <t>demYearTransformed</t>
   </si>
   <si>
     <t>demYear2020</t>
@@ -446,13 +446,13 @@
         <v>58</v>
       </c>
       <c r="B4">
-        <v>0.83524119546708253</v>
+        <v>0.83992117533369515</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
       </c>
       <c r="F4">
-        <v>51090.033764007196</v>
+        <v>47316.641588067927</v>
       </c>
     </row>
     <row r="5">
@@ -460,13 +460,13 @@
         <v>59</v>
       </c>
       <c r="B5">
-        <v>233443</v>
+        <v>213401</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
       </c>
       <c r="F5">
-        <v>-18415612.279833592</v>
+        <v>-16535415.356220428</v>
       </c>
     </row>
   </sheetData>
@@ -617,133 +617,133 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>0.016668924122770979</v>
+        <v>-0.0028496657586431257</v>
       </c>
       <c r="C2">
-        <v>0.00024946416133241837</v>
+        <v>0.00027999834837959329</v>
       </c>
       <c r="D2">
-        <v>2.0459208001701848e-006</v>
+        <v>1.3782281936627096e-006</v>
       </c>
       <c r="E2">
-        <v>-1.5550178594630384e-008</v>
+        <v>-5.278398467618439e-009</v>
       </c>
       <c r="F2">
-        <v>3.3901820258437487e-005</v>
+        <v>4.3829754142323266e-005</v>
       </c>
       <c r="G2">
-        <v>-3.3680900706662889e-005</v>
+        <v>-3.0047062924649634e-005</v>
       </c>
       <c r="H2">
-        <v>-3.850975774006604e-006</v>
+        <v>-1.9110215114272185e-005</v>
       </c>
       <c r="I2">
-        <v>-4.9209175106712356e-005</v>
+        <v>-6.2288857945440437e-005</v>
       </c>
       <c r="J2">
-        <v>-4.2558917069926808e-005</v>
+        <v>-4.1743773505625406e-005</v>
       </c>
       <c r="K2">
-        <v>4.7997248387685069e-005</v>
+        <v>5.7119741304956337e-005</v>
       </c>
       <c r="L2">
-        <v>0.00012425441362667937</v>
+        <v>0.00014079346106052565</v>
       </c>
       <c r="M2">
-        <v>1.0454088520370902e-005</v>
+        <v>-2.1015395207162641e-005</v>
       </c>
       <c r="N2">
-        <v>-3.2781057766288542e-005</v>
+        <v>-5.6043360543491884e-005</v>
       </c>
       <c r="O2">
-        <v>-1.2332377886831896e-005</v>
+        <v>-3.6913905125721386e-005</v>
       </c>
       <c r="P2">
-        <v>-1.3012607956397454e-005</v>
+        <v>-2.5296856216310698e-005</v>
       </c>
       <c r="Q2">
-        <v>-8.997480077545465e-006</v>
+        <v>-2.4638573741358446e-005</v>
       </c>
       <c r="R2">
-        <v>-9.1059760296681505e-006</v>
+        <v>-2.3444387672616781e-005</v>
       </c>
       <c r="S2">
-        <v>-5.8801654824418215e-007</v>
+        <v>-5.2859634024004762e-007</v>
       </c>
       <c r="T2">
-        <v>-1.8045790402083797e-006</v>
+        <v>-2.111075240515896e-006</v>
       </c>
       <c r="U2">
-        <v>-9.1072915680786029e-006</v>
+        <v>-4.1802062486350442e-005</v>
       </c>
       <c r="V2">
-        <v>-1.1725445409026655e-005</v>
+        <v>-4.226846860645582e-005</v>
       </c>
       <c r="W2">
-        <v>-1.5541816134238613e-005</v>
+        <v>-5.0666231693518638e-005</v>
       </c>
       <c r="X2">
-        <v>-3.6493476949137944e-005</v>
+        <v>-6.7680688689462028e-005</v>
       </c>
       <c r="Y2">
-        <v>1.0736937851375664e-006</v>
+        <v>1.9172472073785821e-006</v>
       </c>
       <c r="Z2">
-        <v>3.8632667670828027e-006</v>
+        <v>4.9133748646457759e-006</v>
       </c>
       <c r="AA2">
-        <v>4.9919296051714422e-006</v>
+        <v>1.4586778808205605e-005</v>
       </c>
       <c r="AB2">
-        <v>2.7658233922800067e-005</v>
+        <v>4.8348325666041706e-005</v>
       </c>
       <c r="AC2">
-        <v>-1.6923119529012594e-005</v>
+        <v>4.1662813292447448e-006</v>
       </c>
       <c r="AD2">
-        <v>1.4568062109066573e-006</v>
+        <v>1.7452870443351564e-005</v>
       </c>
       <c r="AE2">
-        <v>-9.2876138578380972e-006</v>
+        <v>6.6743433041048662e-006</v>
       </c>
       <c r="AF2">
-        <v>-1.0983052572330539e-005</v>
+        <v>-9.2457802703926466e-007</v>
       </c>
       <c r="AG2">
-        <v>7.7371514324512604e-006</v>
+        <v>1.4919103126229899e-005</v>
       </c>
       <c r="AH2">
-        <v>3.6322757539457999e-006</v>
+        <v>1.3612597189542542e-005</v>
       </c>
       <c r="AI2">
-        <v>2.8292457749533129e-005</v>
+        <v>5.8301133889744733e-005</v>
       </c>
       <c r="AJ2">
-        <v>2.8452559341954198e-005</v>
+        <v>5.0434960393527338e-005</v>
       </c>
       <c r="AK2">
-        <v>6.671488782523622e-006</v>
+        <v>1.4316850098585939e-005</v>
       </c>
       <c r="AL2">
-        <v>-1.1535714025177435e-007</v>
+        <v>6.9577425603410914e-007</v>
       </c>
       <c r="AM2">
-        <v>9.3452281720407482e-006</v>
+        <v>2.3552594679521088e-006</v>
       </c>
       <c r="AN2">
-        <v>-1.8436763278969418e-006</v>
+        <v>-4.6263798001906424e-006</v>
       </c>
       <c r="AO2">
-        <v>-1.4204625822098928e-005</v>
+        <v>-1.5382763588456706e-005</v>
       </c>
       <c r="AP2">
-        <v>8.6600509173494103e-005</v>
+        <v>8.8093084096739987e-005</v>
       </c>
       <c r="AQ2">
-        <v>-2.9853831091504644e-005</v>
+        <v>-3.256565125021845e-005</v>
       </c>
       <c r="AR2">
-        <v>-7.9450841302348879e-005</v>
+        <v>-6.9261250709546818e-005</v>
       </c>
     </row>
     <row r="3">
@@ -751,133 +751,133 @@
         <v>16</v>
       </c>
       <c r="B3">
-        <v>0.0015281749718158515</v>
+        <v>0.00050998341665666391</v>
       </c>
       <c r="C3">
-        <v>2.0459208001701848e-006</v>
+        <v>1.3782281936627096e-006</v>
       </c>
       <c r="D3">
-        <v>5.669909420668594e-006</v>
+        <v>5.9666242853704266e-006</v>
       </c>
       <c r="E3">
-        <v>-5.5034953043935372e-008</v>
+        <v>-5.7015500433933747e-008</v>
       </c>
       <c r="F3">
-        <v>1.2567113612562531e-005</v>
+        <v>1.4283732594481991e-005</v>
       </c>
       <c r="G3">
-        <v>1.6725374888219033e-007</v>
+        <v>2.1852599867218376e-006</v>
       </c>
       <c r="H3">
-        <v>-2.5320924643905979e-007</v>
+        <v>-5.0654465609007045e-008</v>
       </c>
       <c r="I3">
-        <v>-6.9354187667552411e-007</v>
+        <v>3.186356349573391e-006</v>
       </c>
       <c r="J3">
-        <v>-4.0546867947657649e-006</v>
+        <v>-4.9463363931125027e-006</v>
       </c>
       <c r="K3">
-        <v>8.4145238114080562e-006</v>
+        <v>7.8714309045590841e-006</v>
       </c>
       <c r="L3">
-        <v>5.8958247429164953e-007</v>
+        <v>4.5199294331551765e-007</v>
       </c>
       <c r="M3">
-        <v>3.7359074584324833e-005</v>
+        <v>3.1221000919189724e-005</v>
       </c>
       <c r="N3">
-        <v>1.9802450601060897e-006</v>
+        <v>-4.8451324346025912e-006</v>
       </c>
       <c r="O3">
-        <v>1.3192013234090597e-005</v>
+        <v>8.3856789702572369e-006</v>
       </c>
       <c r="P3">
-        <v>1.9702723944720058e-006</v>
+        <v>7.679434612894412e-007</v>
       </c>
       <c r="Q3">
-        <v>4.4942725883523771e-006</v>
+        <v>2.0142446136799905e-006</v>
       </c>
       <c r="R3">
-        <v>3.733618546458085e-006</v>
+        <v>-2.3064223972200535e-007</v>
       </c>
       <c r="S3">
-        <v>8.6283539050876427e-008</v>
+        <v>1.5294151081129712e-007</v>
       </c>
       <c r="T3">
-        <v>6.575578767759628e-008</v>
+        <v>8.1297443753781934e-008</v>
       </c>
       <c r="U3">
-        <v>7.0204829550340042e-006</v>
+        <v>9.1431235299073356e-008</v>
       </c>
       <c r="V3">
-        <v>4.1230766851864239e-006</v>
+        <v>-4.1640705650681992e-006</v>
       </c>
       <c r="W3">
-        <v>-7.6218967627988119e-007</v>
+        <v>-1.1421700110895525e-005</v>
       </c>
       <c r="X3">
-        <v>-3.3611388591390891e-006</v>
+        <v>-1.4565289128997498e-005</v>
       </c>
       <c r="Y3">
-        <v>-5.499356484356939e-007</v>
+        <v>-4.0173526973749299e-007</v>
       </c>
       <c r="Z3">
-        <v>1.0170225143241933e-006</v>
+        <v>1.6528686182612116e-006</v>
       </c>
       <c r="AA3">
-        <v>-6.2496400249413236e-007</v>
+        <v>1.1045635412607635e-006</v>
       </c>
       <c r="AB3">
-        <v>1.0889288606136084e-006</v>
+        <v>1.9078451432136867e-006</v>
       </c>
       <c r="AC3">
-        <v>-4.2552124166550009e-006</v>
+        <v>-1.5330894462409858e-006</v>
       </c>
       <c r="AD3">
-        <v>1.1252972455124169e-006</v>
+        <v>1.6505894576776775e-006</v>
       </c>
       <c r="AE3">
-        <v>-1.4378485627170886e-006</v>
+        <v>-1.7110537181407257e-006</v>
       </c>
       <c r="AF3">
-        <v>-7.1017926504283113e-007</v>
+        <v>-7.9883507211689906e-008</v>
       </c>
       <c r="AG3">
-        <v>9.4106940662763486e-007</v>
+        <v>-7.8844860095415302e-007</v>
       </c>
       <c r="AH3">
-        <v>1.2825810163173493e-006</v>
+        <v>2.2295222118078913e-006</v>
       </c>
       <c r="AI3">
-        <v>1.8700772625263708e-006</v>
+        <v>3.5810226884147745e-007</v>
       </c>
       <c r="AJ3">
-        <v>-3.0038078623486962e-006</v>
+        <v>-2.3689269384005123e-006</v>
       </c>
       <c r="AK3">
-        <v>6.476161654871452e-007</v>
+        <v>1.3747387937357601e-006</v>
       </c>
       <c r="AL3">
-        <v>-1.2690632868808265e-007</v>
+        <v>-1.2111370772023238e-007</v>
       </c>
       <c r="AM3">
-        <v>-5.4242521893380373e-007</v>
+        <v>-1.4510760285588929e-006</v>
       </c>
       <c r="AN3">
-        <v>-2.5125921005398887e-006</v>
+        <v>-4.1721003046750409e-006</v>
       </c>
       <c r="AO3">
-        <v>3.1794096558238958e-006</v>
+        <v>4.3760362831400668e-006</v>
       </c>
       <c r="AP3">
-        <v>-1.503287740570827e-006</v>
+        <v>-1.2946571286714252e-006</v>
       </c>
       <c r="AQ3">
-        <v>1.3586438275875595e-006</v>
+        <v>2.9664197279297112e-006</v>
       </c>
       <c r="AR3">
-        <v>-0.00014555706351228976</v>
+        <v>-0.00014875875697339168</v>
       </c>
     </row>
     <row r="4">
@@ -885,133 +885,133 @@
         <v>17</v>
       </c>
       <c r="B4">
-        <v>2.4648916519208202e-005</v>
+        <v>3.0993893055359874e-005</v>
       </c>
       <c r="C4">
-        <v>-1.5550178594630384e-008</v>
+        <v>-5.278398467618439e-009</v>
       </c>
       <c r="D4">
-        <v>-5.5034953043935372e-008</v>
+        <v>-5.7015500433933747e-008</v>
       </c>
       <c r="E4">
-        <v>5.8334679559462007e-010</v>
+        <v>5.9600342963523226e-010</v>
       </c>
       <c r="F4">
-        <v>-9.4543794659512502e-008</v>
+        <v>-1.074422395605e-007</v>
       </c>
       <c r="G4">
-        <v>-6.053496792081295e-009</v>
+        <v>-3.4322673133571372e-008</v>
       </c>
       <c r="H4">
-        <v>2.6604706425439408e-008</v>
+        <v>2.7106495169775076e-008</v>
       </c>
       <c r="I4">
-        <v>2.4750982618384684e-008</v>
+        <v>8.0513292386083072e-009</v>
       </c>
       <c r="J4">
-        <v>6.3210557346510806e-008</v>
+        <v>7.0411545695360501e-008</v>
       </c>
       <c r="K4">
-        <v>-7.5866770990633526e-008</v>
+        <v>-6.9200346870263668e-008</v>
       </c>
       <c r="L4">
-        <v>2.1722356103211847e-008</v>
+        <v>2.599409488113338e-008</v>
       </c>
       <c r="M4">
-        <v>-2.6741189618656613e-007</v>
+        <v>-1.9242184619714848e-007</v>
       </c>
       <c r="N4">
-        <v>9.9688596928060811e-009</v>
+        <v>8.3548624238436732e-008</v>
       </c>
       <c r="O4">
-        <v>-2.2492481164605253e-007</v>
+        <v>-1.7869038228465474e-007</v>
       </c>
       <c r="P4">
-        <v>-2.8885721244888692e-008</v>
+        <v>-1.270894148361265e-008</v>
       </c>
       <c r="Q4">
-        <v>-8.9650775135490984e-008</v>
+        <v>-6.2086123423845401e-008</v>
       </c>
       <c r="R4">
-        <v>-4.5345779074856702e-008</v>
+        <v>-2.2778854145536958e-009</v>
       </c>
       <c r="S4">
-        <v>4.0452023652442571e-010</v>
+        <v>-3.0239205225700207e-010</v>
       </c>
       <c r="T4">
-        <v>-1.2053311925375307e-009</v>
+        <v>-1.4676985848761628e-009</v>
       </c>
       <c r="U4">
-        <v>-5.9831280507467376e-008</v>
+        <v>1.8363534191056456e-008</v>
       </c>
       <c r="V4">
-        <v>-1.9221771838733098e-008</v>
+        <v>7.5860138125306047e-008</v>
       </c>
       <c r="W4">
-        <v>1.646685843589255e-008</v>
+        <v>1.2814808475640945e-007</v>
       </c>
       <c r="X4">
-        <v>3.1033188124340523e-008</v>
+        <v>1.4559625400088673e-007</v>
       </c>
       <c r="Y4">
-        <v>-5.3778849829135753e-011</v>
+        <v>-1.8348439949019265e-009</v>
       </c>
       <c r="Z4">
-        <v>-2.552668159549023e-008</v>
+        <v>-3.1040478989826164e-008</v>
       </c>
       <c r="AA4">
-        <v>8.9551859007246444e-009</v>
+        <v>-5.1573874919431026e-009</v>
       </c>
       <c r="AB4">
-        <v>-1.2534074504177438e-008</v>
+        <v>-2.1319695933760214e-008</v>
       </c>
       <c r="AC4">
-        <v>5.5355775858361458e-008</v>
+        <v>2.0522970470851614e-008</v>
       </c>
       <c r="AD4">
-        <v>-5.3275426812384167e-009</v>
+        <v>-1.163196309365136e-008</v>
       </c>
       <c r="AE4">
-        <v>2.7698618000959086e-008</v>
+        <v>3.1711804310644824e-008</v>
       </c>
       <c r="AF4">
-        <v>8.052277936034005e-009</v>
+        <v>3.714190287959945e-009</v>
       </c>
       <c r="AG4">
-        <v>-5.6684974704174004e-009</v>
+        <v>4.3192795793339746e-009</v>
       </c>
       <c r="AH4">
-        <v>-1.6521739648338824e-008</v>
+        <v>-2.6741717379863864e-008</v>
       </c>
       <c r="AI4">
-        <v>-1.2082130474813329e-008</v>
+        <v>-2.2986567658487526e-009</v>
       </c>
       <c r="AJ4">
-        <v>2.7935207484647161e-008</v>
+        <v>2.0044812961463735e-008</v>
       </c>
       <c r="AK4">
-        <v>-4.3129974628508136e-009</v>
+        <v>-1.1317478305566059e-008</v>
       </c>
       <c r="AL4">
-        <v>7.5620018810960088e-010</v>
+        <v>-2.9702376529953202e-011</v>
       </c>
       <c r="AM4">
-        <v>-1.7504791653671584e-009</v>
+        <v>1.2819615368578351e-008</v>
       </c>
       <c r="AN4">
-        <v>1.7383427903372448e-008</v>
+        <v>3.7193788054851373e-008</v>
       </c>
       <c r="AO4">
-        <v>-2.7910049670628022e-008</v>
+        <v>-3.1435677844151087e-008</v>
       </c>
       <c r="AP4">
-        <v>-7.060185963541953e-009</v>
+        <v>-4.4613305539511652e-009</v>
       </c>
       <c r="AQ4">
-        <v>-1.1482967124046874e-008</v>
+        <v>-1.9718864686090522e-008</v>
       </c>
       <c r="AR4">
-        <v>1.2758208535263078e-006</v>
+        <v>1.2858923047636232e-006</v>
       </c>
     </row>
     <row r="5">
@@ -1019,133 +1019,133 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>-0.18758349087358833</v>
+        <v>-0.18117423902097704</v>
       </c>
       <c r="C5">
-        <v>3.3901820258437487e-005</v>
+        <v>4.3829754142323266e-005</v>
       </c>
       <c r="D5">
-        <v>1.2567113612562531e-005</v>
+        <v>1.4283732594481991e-005</v>
       </c>
       <c r="E5">
-        <v>-9.4543794659512502e-008</v>
+        <v>-1.074422395605e-007</v>
       </c>
       <c r="F5">
-        <v>0.021453292698302619</v>
+        <v>0.023575673551016793</v>
       </c>
       <c r="G5">
-        <v>0.00071971261806389093</v>
+        <v>0.0008925819892052039</v>
       </c>
       <c r="H5">
-        <v>0.00069771045070756354</v>
+        <v>0.00085818404736183115</v>
       </c>
       <c r="I5">
-        <v>0.00082730398384166259</v>
+        <v>0.00097166672394532756</v>
       </c>
       <c r="J5">
-        <v>0.00076474441725547316</v>
+        <v>0.00094351453921162241</v>
       </c>
       <c r="K5">
-        <v>0.00076272835448843856</v>
+        <v>0.00092851519052453732</v>
       </c>
       <c r="L5">
-        <v>0.00078007941643748696</v>
+        <v>0.00095200092260827466</v>
       </c>
       <c r="M5">
-        <v>-0.00033698037716075506</v>
+        <v>-0.00024001513471835423</v>
       </c>
       <c r="N5">
-        <v>1.9991056765056894e-005</v>
+        <v>-6.4290986453170934e-005</v>
       </c>
       <c r="O5">
-        <v>-1.564908908936475e-005</v>
+        <v>-7.2448380436126701e-005</v>
       </c>
       <c r="P5">
-        <v>0.00018630272666383846</v>
+        <v>0.0001973315521787865</v>
       </c>
       <c r="Q5">
-        <v>0.00017379683436849692</v>
+        <v>0.0001761194141308896</v>
       </c>
       <c r="R5">
-        <v>0.00044698455126123066</v>
+        <v>0.00034406786427301512</v>
       </c>
       <c r="S5">
-        <v>-8.8758017466262801e-007</v>
+        <v>-1.8289953009510864e-006</v>
       </c>
       <c r="T5">
-        <v>2.0472830417760267e-006</v>
+        <v>2.5130255296876655e-006</v>
       </c>
       <c r="U5">
-        <v>-7.2107721958023725e-005</v>
+        <v>-0.00013568252562926625</v>
       </c>
       <c r="V5">
-        <v>-2.16697000946717e-005</v>
+        <v>-0.0001106587141544848</v>
       </c>
       <c r="W5">
-        <v>2.8972836161941817e-005</v>
+        <v>-5.5988895563068345e-005</v>
       </c>
       <c r="X5">
-        <v>0.0002853464376080234</v>
+        <v>0.00028316271886620701</v>
       </c>
       <c r="Y5">
-        <v>-2.2519425623303467e-006</v>
+        <v>3.8247655731721304e-006</v>
       </c>
       <c r="Z5">
-        <v>7.2623294855599964e-005</v>
+        <v>7.7175228406035532e-005</v>
       </c>
       <c r="AA5">
-        <v>-4.8467977757201967e-005</v>
+        <v>-2.09485669032236e-005</v>
       </c>
       <c r="AB5">
-        <v>3.450724360467975e-005</v>
+        <v>7.4816698394393651e-005</v>
       </c>
       <c r="AC5">
-        <v>5.1066092595635683e-005</v>
+        <v>7.9931594919426674e-005</v>
       </c>
       <c r="AD5">
-        <v>8.8653499255903552e-005</v>
+        <v>0.00013480050484371357</v>
       </c>
       <c r="AE5">
-        <v>0.00012732946475200812</v>
+        <v>0.00015314337615946578</v>
       </c>
       <c r="AF5">
-        <v>2.0776887963205033e-005</v>
+        <v>5.7110204037460566e-005</v>
       </c>
       <c r="AG5">
-        <v>4.1186073895733033e-005</v>
+        <v>8.7040917421662192e-005</v>
       </c>
       <c r="AH5">
-        <v>6.1418462199559903e-005</v>
+        <v>0.00010997163232206887</v>
       </c>
       <c r="AI5">
-        <v>6.0786325587824615e-005</v>
+        <v>8.963330669920557e-005</v>
       </c>
       <c r="AJ5">
-        <v>-1.5433493991132193e-005</v>
+        <v>2.0457253425828246e-005</v>
       </c>
       <c r="AK5">
-        <v>9.7340831935838375e-005</v>
+        <v>0.0001295253426587838</v>
       </c>
       <c r="AL5">
-        <v>3.5092277268555577e-007</v>
+        <v>2.454494799653033e-006</v>
       </c>
       <c r="AM5">
-        <v>2.5486789082202106e-005</v>
+        <v>3.8627978727757322e-005</v>
       </c>
       <c r="AN5">
-        <v>1.1380626673533774e-005</v>
+        <v>-5.2194278313286786e-006</v>
       </c>
       <c r="AO5">
-        <v>8.7384479165576794e-005</v>
+        <v>0.00010029161839558622</v>
       </c>
       <c r="AP5">
-        <v>0.00010780617953720152</v>
+        <v>0.00016719960752428005</v>
       </c>
       <c r="AQ5">
-        <v>0.00030916124864551419</v>
+        <v>0.00039851319441228247</v>
       </c>
       <c r="AR5">
-        <v>-0.0014299568639463463</v>
+        <v>-0.001642070453253288</v>
       </c>
     </row>
     <row r="6">
@@ -1153,133 +1153,133 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>-0.0116413186584332</v>
+        <v>-0.033338916422106325</v>
       </c>
       <c r="C6">
-        <v>-3.3680900706662889e-005</v>
+        <v>-3.0047062924649634e-005</v>
       </c>
       <c r="D6">
-        <v>1.6725374888219033e-007</v>
+        <v>2.1852599867218376e-006</v>
       </c>
       <c r="E6">
-        <v>-6.053496792081295e-009</v>
+        <v>-3.4322673133571372e-008</v>
       </c>
       <c r="F6">
-        <v>0.00071971261806389093</v>
+        <v>0.0008925819892052039</v>
       </c>
       <c r="G6">
-        <v>0.0011328445694659399</v>
+        <v>0.0013198079712772837</v>
       </c>
       <c r="H6">
-        <v>0.0006072551246029199</v>
+        <v>0.0007597631061267813</v>
       </c>
       <c r="I6">
-        <v>0.00072363655162960131</v>
+        <v>0.00087727131993849399</v>
       </c>
       <c r="J6">
-        <v>0.00070399304085531846</v>
+        <v>0.00087949587512627678</v>
       </c>
       <c r="K6">
-        <v>0.00075301920162832846</v>
+        <v>0.00093465699626598883</v>
       </c>
       <c r="L6">
-        <v>0.00072179481580191115</v>
+        <v>0.0009025298862893929</v>
       </c>
       <c r="M6">
-        <v>-6.0156336492201397e-005</v>
+        <v>-4.2371897196805881e-005</v>
       </c>
       <c r="N6">
-        <v>-2.3471714481097122e-005</v>
+        <v>-4.96573528976194e-005</v>
       </c>
       <c r="O6">
-        <v>-6.4162644009880241e-005</v>
+        <v>-4.8942203627644646e-005</v>
       </c>
       <c r="P6">
-        <v>1.8948614685013144e-005</v>
+        <v>2.5948394020186381e-005</v>
       </c>
       <c r="Q6">
-        <v>1.169176914098878e-005</v>
+        <v>3.6032988772732931e-005</v>
       </c>
       <c r="R6">
-        <v>-8.9862655802493596e-006</v>
+        <v>7.7544270617507923e-005</v>
       </c>
       <c r="S6">
-        <v>1.8299571693418365e-007</v>
+        <v>-9.2089538807322488e-007</v>
       </c>
       <c r="T6">
-        <v>-3.8395399446019663e-008</v>
+        <v>-6.63481251449356e-007</v>
       </c>
       <c r="U6">
-        <v>-3.9698931242686783e-005</v>
+        <v>-2.6616280561899129e-005</v>
       </c>
       <c r="V6">
-        <v>1.424422101243714e-005</v>
+        <v>3.3974872992910529e-005</v>
       </c>
       <c r="W6">
-        <v>0.00012326112717946775</v>
+        <v>0.00015747990045400582</v>
       </c>
       <c r="X6">
-        <v>0.00025613763376659067</v>
+        <v>0.00037065696543726846</v>
       </c>
       <c r="Y6">
-        <v>-9.7176991831581803e-006</v>
+        <v>-7.8086964854894302e-006</v>
       </c>
       <c r="Z6">
-        <v>-4.2109259147220067e-005</v>
+        <v>-3.9563504319354832e-005</v>
       </c>
       <c r="AA6">
-        <v>-7.043881872992166e-006</v>
+        <v>2.1099303147705569e-005</v>
       </c>
       <c r="AB6">
-        <v>3.4943920739572077e-005</v>
+        <v>5.8517165327780555e-005</v>
       </c>
       <c r="AC6">
-        <v>6.605026595133602e-005</v>
+        <v>6.1187453167548282e-005</v>
       </c>
       <c r="AD6">
-        <v>2.6523328342246719e-005</v>
+        <v>6.5405406941513786e-005</v>
       </c>
       <c r="AE6">
-        <v>-2.3277222436022198e-005</v>
+        <v>-2.4563141838224883e-005</v>
       </c>
       <c r="AF6">
-        <v>1.0989969644485526e-005</v>
+        <v>4.3059488357400921e-005</v>
       </c>
       <c r="AG6">
-        <v>2.5876128595239913e-005</v>
+        <v>6.2684186318883307e-005</v>
       </c>
       <c r="AH6">
-        <v>1.5088431674196048e-005</v>
+        <v>5.2049254081877014e-005</v>
       </c>
       <c r="AI6">
-        <v>3.3337337161404647e-005</v>
+        <v>7.8461982076474362e-005</v>
       </c>
       <c r="AJ6">
-        <v>-2.791904447079386e-005</v>
+        <v>-1.1715212806015348e-005</v>
       </c>
       <c r="AK6">
-        <v>1.2850658976226818e-005</v>
+        <v>3.7137573823124481e-005</v>
       </c>
       <c r="AL6">
-        <v>-2.5181911651032769e-006</v>
+        <v>-2.5129145492207836e-006</v>
       </c>
       <c r="AM6">
-        <v>5.3702259389035297e-006</v>
+        <v>1.5017072349810152e-005</v>
       </c>
       <c r="AN6">
-        <v>3.3310426357166672e-005</v>
+        <v>1.8928164114159063e-005</v>
       </c>
       <c r="AO6">
-        <v>4.75949310102105e-005</v>
+        <v>6.1895639545434694e-005</v>
       </c>
       <c r="AP6">
-        <v>3.5863422703233139e-005</v>
+        <v>7.8146814757587942e-005</v>
       </c>
       <c r="AQ6">
-        <v>-1.0840675277494903e-005</v>
+        <v>-1.7705123841352098e-005</v>
       </c>
       <c r="AR6">
-        <v>-0.00067504910860638034</v>
+        <v>-0.00085379951980207804</v>
       </c>
     </row>
     <row r="7">
@@ -1287,133 +1287,133 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-0.012975849927207274</v>
+        <v>0.012414359701786516</v>
       </c>
       <c r="C7">
-        <v>-3.850975774006604e-006</v>
+        <v>-1.9110215114272185e-005</v>
       </c>
       <c r="D7">
-        <v>-2.5320924643905979e-007</v>
+        <v>-5.0654465609007045e-008</v>
       </c>
       <c r="E7">
-        <v>2.6604706425439408e-008</v>
+        <v>2.7106495169775076e-008</v>
       </c>
       <c r="F7">
-        <v>0.00069771045070756354</v>
+        <v>0.00085818404736183115</v>
       </c>
       <c r="G7">
-        <v>0.0006072551246029199</v>
+        <v>0.0007597631061267813</v>
       </c>
       <c r="H7">
-        <v>0.0012930652858738202</v>
+        <v>0.0016770422236972282</v>
       </c>
       <c r="I7">
-        <v>0.00069270680670465855</v>
+        <v>0.00078821475415920197</v>
       </c>
       <c r="J7">
-        <v>0.00065772669431125581</v>
+        <v>0.00082766250663657336</v>
       </c>
       <c r="K7">
-        <v>0.0006120767924409781</v>
+        <v>0.00076439104703266379</v>
       </c>
       <c r="L7">
-        <v>0.00062645046947880747</v>
+        <v>0.00077525916244256823</v>
       </c>
       <c r="M7">
-        <v>0.00013105196288250363</v>
+        <v>9.4830053936788411e-005</v>
       </c>
       <c r="N7">
-        <v>7.7305366078437332e-005</v>
+        <v>4.0645165692777256e-005</v>
       </c>
       <c r="O7">
-        <v>-1.2204477443889403e-005</v>
+        <v>-4.8580811496723205e-005</v>
       </c>
       <c r="P7">
-        <v>7.5402891280150399e-006</v>
+        <v>-4.6168277448304263e-006</v>
       </c>
       <c r="Q7">
-        <v>1.8173315610157817e-005</v>
+        <v>1.8229716450658245e-005</v>
       </c>
       <c r="R7">
-        <v>-3.8641978202873912e-005</v>
+        <v>2.8842976648460516e-005</v>
       </c>
       <c r="S7">
-        <v>9.2428653871472117e-007</v>
+        <v>5.0390719465660914e-007</v>
       </c>
       <c r="T7">
-        <v>-8.5542673223008388e-007</v>
+        <v>-1.3200867165801667e-006</v>
       </c>
       <c r="U7">
-        <v>-6.9683695691212893e-006</v>
+        <v>-4.4419594255488008e-005</v>
       </c>
       <c r="V7">
-        <v>-8.7433403924377684e-006</v>
+        <v>-3.9700452207297517e-005</v>
       </c>
       <c r="W7">
-        <v>3.8594232514448399e-005</v>
+        <v>-2.4618417597373687e-006</v>
       </c>
       <c r="X7">
-        <v>0.00017521196185679049</v>
+        <v>0.00021564468405084914</v>
       </c>
       <c r="Y7">
-        <v>5.6575211164803647e-006</v>
+        <v>1.1453377564667509e-005</v>
       </c>
       <c r="Z7">
-        <v>-4.9061241805649678e-005</v>
+        <v>-5.1553080450806416e-005</v>
       </c>
       <c r="AA7">
-        <v>-3.9345163549354937e-005</v>
+        <v>-3.0852490993212906e-005</v>
       </c>
       <c r="AB7">
-        <v>-1.7931724332668038e-005</v>
+        <v>-7.1957525722399739e-006</v>
       </c>
       <c r="AC7">
-        <v>5.541971389223609e-006</v>
+        <v>1.1450031033868049e-005</v>
       </c>
       <c r="AD7">
-        <v>4.4134205847152347e-006</v>
+        <v>1.4892552454762322e-005</v>
       </c>
       <c r="AE7">
-        <v>-5.2557039161334743e-006</v>
+        <v>7.7127984679595263e-006</v>
       </c>
       <c r="AF7">
-        <v>-2.2499949623952684e-005</v>
+        <v>-2.2166076240639593e-006</v>
       </c>
       <c r="AG7">
-        <v>-6.5846223941549962e-006</v>
+        <v>8.2950318306736807e-006</v>
       </c>
       <c r="AH7">
-        <v>-1.4421251890911568e-005</v>
+        <v>1.7039702809658626e-005</v>
       </c>
       <c r="AI7">
-        <v>4.334419083304099e-005</v>
+        <v>7.3917316703664762e-005</v>
       </c>
       <c r="AJ7">
-        <v>-4.8322758346642043e-005</v>
+        <v>-5.2956930014984375e-005</v>
       </c>
       <c r="AK7">
-        <v>5.9094566025350655e-006</v>
+        <v>8.9075732955111897e-006</v>
       </c>
       <c r="AL7">
-        <v>3.1387519070449102e-006</v>
+        <v>5.3365881955915622e-006</v>
       </c>
       <c r="AM7">
-        <v>-8.2957948803577845e-008</v>
+        <v>-3.2755924613270802e-006</v>
       </c>
       <c r="AN7">
-        <v>1.0148412724088668e-005</v>
+        <v>-2.3311382286742011e-005</v>
       </c>
       <c r="AO7">
-        <v>-5.8842545785034826e-005</v>
+        <v>-7.9006280705703699e-005</v>
       </c>
       <c r="AP7">
-        <v>0.0003492775354372567</v>
+        <v>0.00048721441514155874</v>
       </c>
       <c r="AQ7">
-        <v>-2.9366031038672476e-005</v>
+        <v>-2.1844161501035204e-005</v>
       </c>
       <c r="AR7">
-        <v>-0.00076262092031300472</v>
+        <v>-0.00089514177615652828</v>
       </c>
     </row>
     <row r="8">
@@ -1421,133 +1421,133 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>-0.052438262204534881</v>
+        <v>-0.2264272683971198</v>
       </c>
       <c r="C8">
-        <v>-4.9209175106712356e-005</v>
+        <v>-6.2288857945440437e-005</v>
       </c>
       <c r="D8">
-        <v>-6.9354187667552411e-007</v>
+        <v>3.186356349573391e-006</v>
       </c>
       <c r="E8">
-        <v>2.4750982618384684e-008</v>
+        <v>8.0513292386083072e-009</v>
       </c>
       <c r="F8">
-        <v>0.00082730398384166259</v>
+        <v>0.00097166672394532756</v>
       </c>
       <c r="G8">
-        <v>0.00072363655162960131</v>
+        <v>0.00087727131993849399</v>
       </c>
       <c r="H8">
-        <v>0.00069270680670465855</v>
+        <v>0.00078821475415920197</v>
       </c>
       <c r="I8">
-        <v>0.018726040782018033</v>
+        <v>0.023989217829248261</v>
       </c>
       <c r="J8">
-        <v>0.00080554557891886148</v>
+        <v>0.00098388636142415927</v>
       </c>
       <c r="K8">
-        <v>0.00072492533676426119</v>
+        <v>0.0008828953847017549</v>
       </c>
       <c r="L8">
-        <v>0.00081600234751671075</v>
+        <v>0.00096970569210961784</v>
       </c>
       <c r="M8">
-        <v>-9.1238969566159411e-005</v>
+        <v>0.00019825386725749576</v>
       </c>
       <c r="N8">
-        <v>0.00020687300724792803</v>
+        <v>0.00014575623749065256</v>
       </c>
       <c r="O8">
-        <v>8.0546627164334488e-005</v>
+        <v>3.0273762155107641e-005</v>
       </c>
       <c r="P8">
-        <v>8.9896841271704759e-005</v>
+        <v>0.00010510891435513628</v>
       </c>
       <c r="Q8">
-        <v>0.00014504377653912228</v>
+        <v>0.00011701139869537612</v>
       </c>
       <c r="R8">
-        <v>0.0002854267663048609</v>
+        <v>0.00019329162416323298</v>
       </c>
       <c r="S8">
-        <v>4.7445277405104249e-007</v>
+        <v>5.3943887649995809e-007</v>
       </c>
       <c r="T8">
-        <v>1.0929233605987388e-006</v>
+        <v>1.4953105196428771e-006</v>
       </c>
       <c r="U8">
-        <v>2.5999592982125716e-005</v>
+        <v>-6.0305337685957077e-005</v>
       </c>
       <c r="V8">
-        <v>9.3598298992700845e-005</v>
+        <v>3.0375240113230724e-005</v>
       </c>
       <c r="W8">
-        <v>0.00027936603332839817</v>
+        <v>0.00025648664510740732</v>
       </c>
       <c r="X8">
-        <v>0.0004886531114818792</v>
+        <v>0.00055756887930067658</v>
       </c>
       <c r="Y8">
-        <v>-2.7585878730862785e-006</v>
+        <v>5.334721430239551e-006</v>
       </c>
       <c r="Z8">
-        <v>2.8352229360092539e-005</v>
+        <v>-2.1069270456002345e-005</v>
       </c>
       <c r="AA8">
-        <v>-4.9004460596212721e-005</v>
+        <v>-3.8454813066869875e-005</v>
       </c>
       <c r="AB8">
-        <v>-1.3380512365986021e-005</v>
+        <v>-1.7163599744755864e-005</v>
       </c>
       <c r="AC8">
-        <v>0.00010916740218480557</v>
+        <v>9.8732372083621119e-005</v>
       </c>
       <c r="AD8">
-        <v>2.896481767935846e-005</v>
+        <v>0.00019982728928884206</v>
       </c>
       <c r="AE8">
-        <v>-5.3213363051345829e-005</v>
+        <v>-1.7878381275420043e-005</v>
       </c>
       <c r="AF8">
-        <v>5.2671460004574482e-005</v>
+        <v>3.4066532533534111e-005</v>
       </c>
       <c r="AG8">
-        <v>1.9420977007738005e-005</v>
+        <v>2.9277263107849511e-005</v>
       </c>
       <c r="AH8">
-        <v>3.0815336267243802e-005</v>
+        <v>7.0805307919838198e-005</v>
       </c>
       <c r="AI8">
-        <v>4.3619398935583627e-006</v>
+        <v>3.4602105039228893e-005</v>
       </c>
       <c r="AJ8">
-        <v>-7.5132049609409149e-005</v>
+        <v>-4.7534915596808612e-005</v>
       </c>
       <c r="AK8">
-        <v>2.9490277286494835e-005</v>
+        <v>5.601103958479401e-005</v>
       </c>
       <c r="AL8">
-        <v>-9.5605678684841254e-007</v>
+        <v>6.0198201151925109e-007</v>
       </c>
       <c r="AM8">
-        <v>-2.2551947215774181e-005</v>
+        <v>-2.4857347083338994e-005</v>
       </c>
       <c r="AN8">
-        <v>5.1251596970826167e-005</v>
+        <v>1.6333941158872402e-005</v>
       </c>
       <c r="AO8">
-        <v>-1.7766040377709645e-005</v>
+        <v>-4.2336294477487665e-005</v>
       </c>
       <c r="AP8">
-        <v>-0.00031482890878425208</v>
+        <v>-0.00031563404324402215</v>
       </c>
       <c r="AQ8">
-        <v>6.1191314515677273e-005</v>
+        <v>9.3065147360806531e-005</v>
       </c>
       <c r="AR8">
-        <v>-0.0010778048533915895</v>
+        <v>-0.0013819365227629179</v>
       </c>
     </row>
     <row r="9">
@@ -1555,133 +1555,133 @@
         <v>22</v>
       </c>
       <c r="B9">
-        <v>-0.1930010101027311</v>
+        <v>-0.16850602105957024</v>
       </c>
       <c r="C9">
-        <v>-4.2558917069926808e-005</v>
+        <v>-4.1743773505625406e-005</v>
       </c>
       <c r="D9">
-        <v>-4.0546867947657649e-006</v>
+        <v>-4.9463363931125027e-006</v>
       </c>
       <c r="E9">
-        <v>6.3210557346510806e-008</v>
+        <v>7.0411545695360501e-008</v>
       </c>
       <c r="F9">
-        <v>0.00076474441725547316</v>
+        <v>0.00094351453921162241</v>
       </c>
       <c r="G9">
-        <v>0.00070399304085531846</v>
+        <v>0.00087949587512627678</v>
       </c>
       <c r="H9">
-        <v>0.00065772669431125581</v>
+        <v>0.00082766250663657336</v>
       </c>
       <c r="I9">
-        <v>0.00080554557891886148</v>
+        <v>0.00098388636142415927</v>
       </c>
       <c r="J9">
-        <v>0.0016778957207360873</v>
+        <v>0.0019820990701685751</v>
       </c>
       <c r="K9">
-        <v>0.00069917283472343888</v>
+        <v>0.00088083670407906748</v>
       </c>
       <c r="L9">
-        <v>0.00075633417231647587</v>
+        <v>0.00096664489063724712</v>
       </c>
       <c r="M9">
-        <v>0.00010773732930988759</v>
+        <v>0.00017306320451280366</v>
       </c>
       <c r="N9">
-        <v>0.00011798497895133384</v>
+        <v>9.8447465793736089e-005</v>
       </c>
       <c r="O9">
-        <v>6.9176422847610079e-005</v>
+        <v>7.5955953665694741e-005</v>
       </c>
       <c r="P9">
-        <v>2.7145765677405632e-005</v>
+        <v>3.0591208644005019e-005</v>
       </c>
       <c r="Q9">
-        <v>1.8669708884215671e-005</v>
+        <v>3.1416036478610807e-005</v>
       </c>
       <c r="R9">
-        <v>3.727138739077605e-005</v>
+        <v>9.9815567753607209e-005</v>
       </c>
       <c r="S9">
-        <v>1.0330813284656474e-007</v>
+        <v>-6.3318059620109478e-007</v>
       </c>
       <c r="T9">
-        <v>-5.1381582036962406e-007</v>
+        <v>-1.1332049925488468e-006</v>
       </c>
       <c r="U9">
-        <v>-1.8088146721284787e-005</v>
+        <v>-2.5999556811430208e-005</v>
       </c>
       <c r="V9">
-        <v>6.7057250079301009e-005</v>
+        <v>6.3707855740123353e-005</v>
       </c>
       <c r="W9">
-        <v>0.00024588971889155236</v>
+        <v>0.00029381187277655962</v>
       </c>
       <c r="X9">
-        <v>0.00041494499568498134</v>
+        <v>0.00053990245059271037</v>
       </c>
       <c r="Y9">
-        <v>-2.2304105266666879e-007</v>
+        <v>2.8737524549438014e-006</v>
       </c>
       <c r="Z9">
-        <v>-2.8701241675033184e-005</v>
+        <v>-2.9279214136346786e-005</v>
       </c>
       <c r="AA9">
-        <v>5.2585453892579553e-006</v>
+        <v>2.8316877733636889e-005</v>
       </c>
       <c r="AB9">
-        <v>-3.0288749601091192e-005</v>
+        <v>-2.4321333586669518e-005</v>
       </c>
       <c r="AC9">
-        <v>6.9362526257207168e-005</v>
+        <v>8.7419944024424398e-005</v>
       </c>
       <c r="AD9">
-        <v>4.2868266510759408e-005</v>
+        <v>8.5762330607335748e-005</v>
       </c>
       <c r="AE9">
-        <v>3.2356629745811799e-005</v>
+        <v>4.6440425210770724e-005</v>
       </c>
       <c r="AF9">
-        <v>4.1847794395830524e-005</v>
+        <v>7.8426301734844681e-005</v>
       </c>
       <c r="AG9">
-        <v>2.2515925083977395e-005</v>
+        <v>6.6898236795609375e-005</v>
       </c>
       <c r="AH9">
-        <v>5.2864224098164437e-005</v>
+        <v>9.3364765904528245e-005</v>
       </c>
       <c r="AI9">
-        <v>4.7758379338087254e-005</v>
+        <v>8.0771753064403008e-005</v>
       </c>
       <c r="AJ9">
-        <v>-1.1182780678062562e-005</v>
+        <v>4.7496736955574955e-006</v>
       </c>
       <c r="AK9">
-        <v>2.893025999202179e-005</v>
+        <v>4.4931155737837401e-005</v>
       </c>
       <c r="AL9">
-        <v>-3.0913615097126154e-006</v>
+        <v>-2.1481505128037657e-006</v>
       </c>
       <c r="AM9">
-        <v>3.869224932268373e-005</v>
+        <v>4.9999387739772805e-005</v>
       </c>
       <c r="AN9">
-        <v>5.0491794858513117e-005</v>
+        <v>3.2302692425942542e-005</v>
       </c>
       <c r="AO9">
-        <v>-9.6767174759019502e-005</v>
+        <v>-0.0001402046376901985</v>
       </c>
       <c r="AP9">
-        <v>2.8346627682554969e-005</v>
+        <v>4.9981873358811508e-005</v>
       </c>
       <c r="AQ9">
-        <v>-9.6307066173570758e-006</v>
+        <v>-1.9265200884426091e-005</v>
       </c>
       <c r="AR9">
-        <v>-0.00076307716696935243</v>
+        <v>-0.0009244285236165294</v>
       </c>
     </row>
     <row r="10">
@@ -1689,133 +1689,133 @@
         <v>23</v>
       </c>
       <c r="B10">
-        <v>-0.20202506349138113</v>
+        <v>-0.23309014993139543</v>
       </c>
       <c r="C10">
-        <v>4.7997248387685069e-005</v>
+        <v>5.7119741304956337e-005</v>
       </c>
       <c r="D10">
-        <v>8.4145238114080562e-006</v>
+        <v>7.8714309045590841e-006</v>
       </c>
       <c r="E10">
-        <v>-7.5866770990633526e-008</v>
+        <v>-6.9200346870263668e-008</v>
       </c>
       <c r="F10">
-        <v>0.00076272835448843856</v>
+        <v>0.00092851519052453732</v>
       </c>
       <c r="G10">
-        <v>0.00075301920162832846</v>
+        <v>0.00093465699626598883</v>
       </c>
       <c r="H10">
-        <v>0.0006120767924409781</v>
+        <v>0.00076439104703266379</v>
       </c>
       <c r="I10">
-        <v>0.00072492533676426119</v>
+        <v>0.0008828953847017549</v>
       </c>
       <c r="J10">
-        <v>0.00069917283472343888</v>
+        <v>0.00088083670407906748</v>
       </c>
       <c r="K10">
-        <v>0.0008710269821525958</v>
+        <v>0.001054228864298862</v>
       </c>
       <c r="L10">
-        <v>0.00077897912019362693</v>
+        <v>0.00096731272085377957</v>
       </c>
       <c r="M10">
-        <v>-2.5739091256947859e-005</v>
+        <v>-3.9133337825911308e-005</v>
       </c>
       <c r="N10">
-        <v>-5.4305956768161215e-006</v>
+        <v>-4.8176425429376129e-005</v>
       </c>
       <c r="O10">
-        <v>-3.7879992251757045e-005</v>
+        <v>-6.677903870580838e-005</v>
       </c>
       <c r="P10">
-        <v>3.2904065454284349e-005</v>
+        <v>2.4550854414299593e-005</v>
       </c>
       <c r="Q10">
-        <v>4.5667103065209953e-005</v>
+        <v>4.2911078734865656e-005</v>
       </c>
       <c r="R10">
-        <v>-1.3104223290601289e-005</v>
+        <v>5.4183267296301378e-005</v>
       </c>
       <c r="S10">
-        <v>3.1303772616247708e-007</v>
+        <v>7.1070514033530672e-008</v>
       </c>
       <c r="T10">
-        <v>8.5517705544683208e-007</v>
+        <v>6.5177634143807304e-007</v>
       </c>
       <c r="U10">
-        <v>4.2258043145662513e-005</v>
+        <v>4.0904890860921788e-006</v>
       </c>
       <c r="V10">
-        <v>7.7709603315361005e-005</v>
+        <v>4.7744001122612537e-005</v>
       </c>
       <c r="W10">
-        <v>0.00017615584213518092</v>
+        <v>0.00016013198282030923</v>
       </c>
       <c r="X10">
-        <v>0.00028939289149326985</v>
+        <v>0.00034642341845914537</v>
       </c>
       <c r="Y10">
-        <v>-4.156649014962588e-006</v>
+        <v>-4.8224622873501432e-007</v>
       </c>
       <c r="Z10">
-        <v>-2.802475643151099e-005</v>
+        <v>-3.4067901259253897e-005</v>
       </c>
       <c r="AA10">
-        <v>7.4395120156806076e-006</v>
+        <v>5.4067773522827763e-005</v>
       </c>
       <c r="AB10">
-        <v>4.5771244717234005e-005</v>
+        <v>7.6244204832872503e-005</v>
       </c>
       <c r="AC10">
-        <v>5.9435937056824797e-005</v>
+        <v>0.0001075158168526052</v>
       </c>
       <c r="AD10">
-        <v>4.5539398515967207e-005</v>
+        <v>9.6352853455409658e-005</v>
       </c>
       <c r="AE10">
-        <v>3.8544863051353476e-005</v>
+        <v>6.154551878967922e-005</v>
       </c>
       <c r="AF10">
-        <v>2.9183820655782962e-005</v>
+        <v>7.5388672424806392e-005</v>
       </c>
       <c r="AG10">
-        <v>2.8527622475749243e-005</v>
+        <v>7.6854999545582188e-005</v>
       </c>
       <c r="AH10">
-        <v>3.7984069541432218e-005</v>
+        <v>8.7393877995467327e-005</v>
       </c>
       <c r="AI10">
-        <v>6.4728098202022856e-005</v>
+        <v>0.00012436222096174531</v>
       </c>
       <c r="AJ10">
-        <v>-4.4397882672252254e-006</v>
+        <v>2.3603331651853174e-005</v>
       </c>
       <c r="AK10">
-        <v>2.1220832550911367e-005</v>
+        <v>4.8177857676390951e-005</v>
       </c>
       <c r="AL10">
-        <v>-1.3538825561573047e-006</v>
+        <v>1.4487326934295051e-006</v>
       </c>
       <c r="AM10">
-        <v>9.1952183886822832e-007</v>
+        <v>-4.5809783189185117e-006</v>
       </c>
       <c r="AN10">
-        <v>3.1295935031665163e-005</v>
+        <v>3.1529328078946472e-006</v>
       </c>
       <c r="AO10">
-        <v>5.4315215191140715e-005</v>
+        <v>5.1034847559638941e-005</v>
       </c>
       <c r="AP10">
-        <v>-7.4172390560937277e-006</v>
+        <v>2.6819045759125467e-005</v>
       </c>
       <c r="AQ10">
-        <v>-2.5683171753813e-005</v>
+        <v>-3.3611662745310089e-005</v>
       </c>
       <c r="AR10">
-        <v>-0.0011191812380152615</v>
+        <v>-0.0013257180498786228</v>
       </c>
     </row>
     <row r="11">
@@ -1823,133 +1823,133 @@
         <v>24</v>
       </c>
       <c r="B11">
-        <v>-0.28333850166326818</v>
+        <v>-0.30553247476495521</v>
       </c>
       <c r="C11">
-        <v>0.00012425441362667937</v>
+        <v>0.00014079346106052565</v>
       </c>
       <c r="D11">
-        <v>5.8958247429164953e-007</v>
+        <v>4.5199294331551765e-007</v>
       </c>
       <c r="E11">
-        <v>2.1722356103211847e-008</v>
+        <v>2.599409488113338e-008</v>
       </c>
       <c r="F11">
-        <v>0.00078007941643748696</v>
+        <v>0.00095200092260827466</v>
       </c>
       <c r="G11">
-        <v>0.00072179481580191115</v>
+        <v>0.0009025298862893929</v>
       </c>
       <c r="H11">
-        <v>0.00062645046947880747</v>
+        <v>0.00077525916244256823</v>
       </c>
       <c r="I11">
-        <v>0.00081600234751671075</v>
+        <v>0.00096970569210961784</v>
       </c>
       <c r="J11">
-        <v>0.00075633417231647587</v>
+        <v>0.00096664489063724712</v>
       </c>
       <c r="K11">
-        <v>0.00077897912019362693</v>
+        <v>0.00096731272085377957</v>
       </c>
       <c r="L11">
-        <v>0.001780087333649152</v>
+        <v>0.0019971724888173071</v>
       </c>
       <c r="M11">
-        <v>2.4797206420860588e-005</v>
+        <v>0.00010595274845782678</v>
       </c>
       <c r="N11">
-        <v>4.334301167074485e-005</v>
+        <v>9.486593289753504e-006</v>
       </c>
       <c r="O11">
-        <v>9.6818211103805125e-005</v>
+        <v>8.9400994553342952e-005</v>
       </c>
       <c r="P11">
-        <v>-6.0210486450192622e-006</v>
+        <v>-1.3276604256051282e-005</v>
       </c>
       <c r="Q11">
-        <v>7.1020851827182882e-006</v>
+        <v>7.4329532209340223e-006</v>
       </c>
       <c r="R11">
-        <v>8.5535378192221816e-005</v>
+        <v>0.00013607179998894052</v>
       </c>
       <c r="S11">
-        <v>5.0028220700627444e-007</v>
+        <v>1.787361506892389e-009</v>
       </c>
       <c r="T11">
-        <v>4.2342652135527104e-008</v>
+        <v>-2.3101791425125704e-007</v>
       </c>
       <c r="U11">
-        <v>1.0861564075975168e-005</v>
+        <v>-1.330778390749244e-005</v>
       </c>
       <c r="V11">
-        <v>0.00017288810916693293</v>
+        <v>0.00017941140256331299</v>
       </c>
       <c r="W11">
-        <v>0.00028707091216008949</v>
+        <v>0.00031256187880037832</v>
       </c>
       <c r="X11">
-        <v>0.00042471603685718197</v>
+        <v>0.00053061406795338717</v>
       </c>
       <c r="Y11">
-        <v>-1.7437623491682887e-005</v>
+        <v>-1.5698585313602546e-005</v>
       </c>
       <c r="Z11">
-        <v>8.6419694683554618e-006</v>
+        <v>9.4514353176459185e-006</v>
       </c>
       <c r="AA11">
-        <v>-5.7920386536971879e-006</v>
+        <v>2.8939937073308044e-005</v>
       </c>
       <c r="AB11">
-        <v>9.9785747238746161e-006</v>
+        <v>3.6558440500630341e-005</v>
       </c>
       <c r="AC11">
-        <v>2.2422144470807899e-005</v>
+        <v>5.2709697111056895e-005</v>
       </c>
       <c r="AD11">
-        <v>6.6042232922931975e-005</v>
+        <v>0.00011795259458065728</v>
       </c>
       <c r="AE11">
-        <v>-1.8421843753382611e-005</v>
+        <v>1.3167178215708593e-007</v>
       </c>
       <c r="AF11">
-        <v>5.3644210220699101e-005</v>
+        <v>0.00010383663614040038</v>
       </c>
       <c r="AG11">
-        <v>1.2482435849904094e-005</v>
+        <v>5.4381361092423086e-005</v>
       </c>
       <c r="AH11">
-        <v>1.3733613124281006e-005</v>
+        <v>5.7208549644156969e-005</v>
       </c>
       <c r="AI11">
-        <v>2.7598608568576706e-005</v>
+        <v>8.0325162247492243e-005</v>
       </c>
       <c r="AJ11">
-        <v>-3.7952161317652736e-005</v>
+        <v>-1.3812228128396513e-005</v>
       </c>
       <c r="AK11">
-        <v>-8.2522317011030077e-006</v>
+        <v>1.2930378904404786e-005</v>
       </c>
       <c r="AL11">
-        <v>7.5412286701169006e-007</v>
+        <v>3.6238143179959982e-006</v>
       </c>
       <c r="AM11">
-        <v>2.7187844071529653e-005</v>
+        <v>2.688945968248158e-005</v>
       </c>
       <c r="AN11">
-        <v>4.0787884889321026e-005</v>
+        <v>1.6892956007167486e-005</v>
       </c>
       <c r="AO11">
-        <v>-4.3524527080902604e-005</v>
+        <v>-6.3235109826288336e-005</v>
       </c>
       <c r="AP11">
-        <v>-0.00012865556881364897</v>
+        <v>-0.00012291969029934509</v>
       </c>
       <c r="AQ11">
-        <v>-9.9899726318818241e-005</v>
+        <v>-0.00010893720246602911</v>
       </c>
       <c r="AR11">
-        <v>-0.0011197535362246493</v>
+        <v>-0.0013669345585731907</v>
       </c>
     </row>
     <row r="12">
@@ -1957,133 +1957,133 @@
         <v>25</v>
       </c>
       <c r="B12">
-        <v>0.16688440119470538</v>
+        <v>0.16220851386968813</v>
       </c>
       <c r="C12">
-        <v>1.0454088520370902e-005</v>
+        <v>-2.1015395207162641e-005</v>
       </c>
       <c r="D12">
-        <v>3.7359074584324833e-005</v>
+        <v>3.1221000919189724e-005</v>
       </c>
       <c r="E12">
-        <v>-2.6741189618656613e-007</v>
+        <v>-1.9242184619714848e-007</v>
       </c>
       <c r="F12">
-        <v>-0.00033698037716075506</v>
+        <v>-0.00024001513471835423</v>
       </c>
       <c r="G12">
-        <v>-6.0156336492201397e-005</v>
+        <v>-4.2371897196805881e-005</v>
       </c>
       <c r="H12">
-        <v>0.00013105196288250363</v>
+        <v>9.4830053936788411e-005</v>
       </c>
       <c r="I12">
-        <v>-9.1238969566159411e-005</v>
+        <v>0.00019825386725749576</v>
       </c>
       <c r="J12">
-        <v>0.00010773732930988759</v>
+        <v>0.00017306320451280366</v>
       </c>
       <c r="K12">
-        <v>-2.5739091256947859e-005</v>
+        <v>-3.9133337825911308e-005</v>
       </c>
       <c r="L12">
-        <v>2.4797206420860588e-005</v>
+        <v>0.00010595274845782678</v>
       </c>
       <c r="M12">
-        <v>0.0049156913620749124</v>
+        <v>0.0042349404892102968</v>
       </c>
       <c r="N12">
-        <v>0.00056838386912298148</v>
+        <v>0.0011525240865150673</v>
       </c>
       <c r="O12">
-        <v>0.00039580897591942209</v>
+        <v>0.00074301703871835914</v>
       </c>
       <c r="P12">
-        <v>-4.388590890549212e-005</v>
+        <v>5.299914436657574e-005</v>
       </c>
       <c r="Q12">
-        <v>-2.0697280462731891e-005</v>
+        <v>8.1600316665843102e-005</v>
       </c>
       <c r="R12">
-        <v>-0.0039341093119958145</v>
+        <v>-0.0027479995940856016</v>
       </c>
       <c r="S12">
-        <v>-6.4201954834072337e-007</v>
+        <v>7.6559243139081178e-007</v>
       </c>
       <c r="T12">
-        <v>-7.8026880292941461e-007</v>
+        <v>-4.8698238867935072e-007</v>
       </c>
       <c r="U12">
-        <v>0.00044899586266481913</v>
+        <v>0.00073880584348539734</v>
       </c>
       <c r="V12">
-        <v>0.00067437557096458774</v>
+        <v>0.0012232715306503108</v>
       </c>
       <c r="W12">
-        <v>0.00068638645399832427</v>
+        <v>0.001244540787666532</v>
       </c>
       <c r="X12">
-        <v>0.00060459516710758892</v>
+        <v>0.0012435844642963705</v>
       </c>
       <c r="Y12">
-        <v>-4.8263989154144534e-005</v>
+        <v>-7.7535588980698084e-005</v>
       </c>
       <c r="Z12">
-        <v>-0.00010453867013011226</v>
+        <v>-0.0001127040533805369</v>
       </c>
       <c r="AA12">
-        <v>2.8371905887127346e-005</v>
+        <v>-4.5786824760092062e-005</v>
       </c>
       <c r="AB12">
-        <v>1.4875480513473977e-005</v>
+        <v>-7.5309339545896032e-005</v>
       </c>
       <c r="AC12">
-        <v>-2.6634179705862512e-005</v>
+        <v>-2.1817353218621572e-005</v>
       </c>
       <c r="AD12">
-        <v>-1.2779151844084677e-005</v>
+        <v>-2.2707777568890011e-005</v>
       </c>
       <c r="AE12">
-        <v>-7.8284291509899523e-006</v>
+        <v>-1.5651849468180466e-005</v>
       </c>
       <c r="AF12">
-        <v>-9.2529558582061025e-006</v>
+        <v>-5.1192621658569003e-005</v>
       </c>
       <c r="AG12">
-        <v>8.0744857456591134e-006</v>
+        <v>-6.4028010656713336e-005</v>
       </c>
       <c r="AH12">
-        <v>-1.5710430887543714e-005</v>
+        <v>-5.1584734982397039e-005</v>
       </c>
       <c r="AI12">
-        <v>1.6980297160309478e-005</v>
+        <v>-6.5751063532627009e-005</v>
       </c>
       <c r="AJ12">
-        <v>-8.5387699983922335e-005</v>
+        <v>-0.00012834369175097082</v>
       </c>
       <c r="AK12">
-        <v>5.7974636795026023e-005</v>
+        <v>-8.5507285691666579e-006</v>
       </c>
       <c r="AL12">
-        <v>-4.1214757251409719e-006</v>
+        <v>-3.0699328490907461e-006</v>
       </c>
       <c r="AM12">
-        <v>-8.558915722435903e-006</v>
+        <v>-1.0022660543728161e-005</v>
       </c>
       <c r="AN12">
-        <v>3.7357891695974723e-005</v>
+        <v>4.3089916938325568e-005</v>
       </c>
       <c r="AO12">
-        <v>-5.8412913859671729e-005</v>
+        <v>-0.00010603247255646357</v>
       </c>
       <c r="AP12">
-        <v>-0.00011146349452775687</v>
+        <v>-0.00017162079197778911</v>
       </c>
       <c r="AQ12">
-        <v>-3.986919141736714e-005</v>
+        <v>1.1566786474190099e-005</v>
       </c>
       <c r="AR12">
-        <v>-0.0015773779337714912</v>
+        <v>-0.0021289784604977893</v>
       </c>
     </row>
     <row r="13">
@@ -2091,133 +2091,133 @@
         <v>26</v>
       </c>
       <c r="B13">
-        <v>-0.11231406340547266</v>
+        <v>-0.02378683159474285</v>
       </c>
       <c r="C13">
-        <v>-3.2781057766288542e-005</v>
+        <v>-5.6043360543491884e-005</v>
       </c>
       <c r="D13">
-        <v>1.9802450601060897e-006</v>
+        <v>-4.8451324346025912e-006</v>
       </c>
       <c r="E13">
-        <v>9.9688596928060811e-009</v>
+        <v>8.3548624238436732e-008</v>
       </c>
       <c r="F13">
-        <v>1.9991056765056894e-005</v>
+        <v>-6.4290986453170934e-005</v>
       </c>
       <c r="G13">
-        <v>-2.3471714481097122e-005</v>
+        <v>-4.96573528976194e-005</v>
       </c>
       <c r="H13">
-        <v>7.7305366078437332e-005</v>
+        <v>4.0645165692777256e-005</v>
       </c>
       <c r="I13">
-        <v>0.00020687300724792803</v>
+        <v>0.00014575623749065256</v>
       </c>
       <c r="J13">
-        <v>0.00011798497895133384</v>
+        <v>9.8447465793736089e-005</v>
       </c>
       <c r="K13">
-        <v>-5.4305956768161215e-006</v>
+        <v>-4.8176425429376129e-005</v>
       </c>
       <c r="L13">
-        <v>4.334301167074485e-005</v>
+        <v>9.486593289753504e-006</v>
       </c>
       <c r="M13">
-        <v>0.00056838386912298148</v>
+        <v>0.0011525240865150673</v>
       </c>
       <c r="N13">
-        <v>0.0011728488848412192</v>
+        <v>0.00154101564131226</v>
       </c>
       <c r="O13">
-        <v>0.0005868262495193193</v>
+        <v>0.00084420989299218362</v>
       </c>
       <c r="P13">
-        <v>-3.6584873864488245e-006</v>
+        <v>3.5294004281916569e-005</v>
       </c>
       <c r="Q13">
-        <v>2.9595876905782461e-006</v>
+        <v>3.6156786155918546e-005</v>
       </c>
       <c r="R13">
-        <v>8.2474185954300593e-005</v>
+        <v>7.1267337531774524e-006</v>
       </c>
       <c r="S13">
-        <v>2.9652451486910559e-006</v>
+        <v>3.1652204422735849e-006</v>
       </c>
       <c r="T13">
-        <v>1.3425435305749641e-006</v>
+        <v>2.5271800298096919e-006</v>
       </c>
       <c r="U13">
-        <v>0.00043689289239818083</v>
+        <v>0.00068206398847657946</v>
       </c>
       <c r="V13">
-        <v>0.00073374082258449789</v>
+        <v>0.0011391809011316698</v>
       </c>
       <c r="W13">
-        <v>0.00080236299359988535</v>
+        <v>0.0012113199633241381</v>
       </c>
       <c r="X13">
-        <v>0.00082892632638236852</v>
+        <v>0.0012343293384560815</v>
       </c>
       <c r="Y13">
-        <v>-4.3093164585602338e-005</v>
+        <v>-7.2422524511325288e-005</v>
       </c>
       <c r="Z13">
-        <v>-8.9714795900230557e-006</v>
+        <v>-1.5189057460102194e-005</v>
       </c>
       <c r="AA13">
-        <v>2.3917894514836709e-005</v>
+        <v>-2.381389980264713e-005</v>
       </c>
       <c r="AB13">
-        <v>-4.4716938946902146e-005</v>
+        <v>-6.7511640797502e-005</v>
       </c>
       <c r="AC13">
-        <v>3.7485144180460618e-006</v>
+        <v>2.4144081687174011e-005</v>
       </c>
       <c r="AD13">
-        <v>-9.4553784114425991e-006</v>
+        <v>-6.8561985376150185e-006</v>
       </c>
       <c r="AE13">
-        <v>3.6530063503372704e-005</v>
+        <v>5.0829659946405098e-005</v>
       </c>
       <c r="AF13">
-        <v>-1.7995507338083063e-005</v>
+        <v>-3.0389947216074046e-005</v>
       </c>
       <c r="AG13">
-        <v>1.8168709011991038e-005</v>
+        <v>3.3971703979008487e-006</v>
       </c>
       <c r="AH13">
-        <v>1.3805711962802794e-005</v>
+        <v>1.3344986052519672e-005</v>
       </c>
       <c r="AI13">
-        <v>-9.725978033740671e-006</v>
+        <v>-3.5526186225770751e-005</v>
       </c>
       <c r="AJ13">
-        <v>-2.0725216027190239e-005</v>
+        <v>-4.2131290468233024e-005</v>
       </c>
       <c r="AK13">
-        <v>-2.2490583635362813e-005</v>
+        <v>-3.932946520510724e-005</v>
       </c>
       <c r="AL13">
-        <v>-2.7648575358676626e-006</v>
+        <v>-2.8486466540738318e-006</v>
       </c>
       <c r="AM13">
-        <v>2.1431832186185338e-005</v>
+        <v>-8.9782770100952898e-006</v>
       </c>
       <c r="AN13">
-        <v>2.5851085616417459e-005</v>
+        <v>2.8764268275706362e-005</v>
       </c>
       <c r="AO13">
-        <v>-3.7940244664105496e-005</v>
+        <v>-5.4573577878855588e-005</v>
       </c>
       <c r="AP13">
-        <v>-4.6895061999656471e-005</v>
+        <v>-7.8984974460211783e-005</v>
       </c>
       <c r="AQ13">
-        <v>6.7056466161502265e-005</v>
+        <v>0.00011508895384840147</v>
       </c>
       <c r="AR13">
-        <v>-0.0010996729323705498</v>
+        <v>-0.0013618450006663604</v>
       </c>
     </row>
     <row r="14">
@@ -2225,133 +2225,133 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>0.080146717590037886</v>
+        <v>0.13362879746806683</v>
       </c>
       <c r="C14">
-        <v>-1.2332377886831896e-005</v>
+        <v>-3.6913905125721386e-005</v>
       </c>
       <c r="D14">
-        <v>1.3192013234090597e-005</v>
+        <v>8.3856789702572369e-006</v>
       </c>
       <c r="E14">
-        <v>-2.2492481164605253e-007</v>
+        <v>-1.7869038228465474e-007</v>
       </c>
       <c r="F14">
-        <v>-1.564908908936475e-005</v>
+        <v>-7.2448380436126701e-005</v>
       </c>
       <c r="G14">
-        <v>-6.4162644009880241e-005</v>
+        <v>-4.8942203627644646e-005</v>
       </c>
       <c r="H14">
-        <v>-1.2204477443889403e-005</v>
+        <v>-4.8580811496723205e-005</v>
       </c>
       <c r="I14">
-        <v>8.0546627164334488e-005</v>
+        <v>3.0273762155107641e-005</v>
       </c>
       <c r="J14">
-        <v>6.9176422847610079e-005</v>
+        <v>7.5955953665694741e-005</v>
       </c>
       <c r="K14">
-        <v>-3.7879992251757045e-005</v>
+        <v>-6.677903870580838e-005</v>
       </c>
       <c r="L14">
-        <v>9.6818211103805125e-005</v>
+        <v>8.9400994553342952e-005</v>
       </c>
       <c r="M14">
-        <v>0.00039580897591942209</v>
+        <v>0.00074301703871835914</v>
       </c>
       <c r="N14">
-        <v>0.0005868262495193193</v>
+        <v>0.00084420989299218362</v>
       </c>
       <c r="O14">
-        <v>0.0011571080833799421</v>
+        <v>0.0013841823088598683</v>
       </c>
       <c r="P14">
-        <v>3.4000946265196476e-005</v>
+        <v>5.9570786866506957e-005</v>
       </c>
       <c r="Q14">
-        <v>3.4068662095751217e-005</v>
+        <v>5.8382311306116028e-005</v>
       </c>
       <c r="R14">
-        <v>2.7307092927135023e-005</v>
+        <v>8.6535164948743355e-005</v>
       </c>
       <c r="S14">
-        <v>1.132600628345244e-006</v>
+        <v>1.3109694415009711e-006</v>
       </c>
       <c r="T14">
-        <v>-1.1541809518803255e-006</v>
+        <v>-7.5551999660274686e-007</v>
       </c>
       <c r="U14">
-        <v>0.00031306394996420911</v>
+        <v>0.00048116415972502646</v>
       </c>
       <c r="V14">
-        <v>0.00054660533126663741</v>
+        <v>0.00083688150539680084</v>
       </c>
       <c r="W14">
-        <v>0.00066072389110351302</v>
+        <v>0.00098183880766435929</v>
       </c>
       <c r="X14">
-        <v>0.00069599738424238429</v>
+        <v>0.0010281791198004781</v>
       </c>
       <c r="Y14">
-        <v>-5.9789770551377431e-005</v>
+        <v>-8.3327383696171092e-005</v>
       </c>
       <c r="Z14">
-        <v>6.3922222322539504e-006</v>
+        <v>1.1081674890348709e-005</v>
       </c>
       <c r="AA14">
-        <v>-2.8053505016801839e-005</v>
+        <v>-6.393419503143149e-005</v>
       </c>
       <c r="AB14">
-        <v>-6.3320116264522488e-005</v>
+        <v>-8.0433865819956455e-005</v>
       </c>
       <c r="AC14">
-        <v>-4.7082137800893737e-005</v>
+        <v>-2.6517319736276779e-005</v>
       </c>
       <c r="AD14">
-        <v>-1.7031096058253325e-005</v>
+        <v>-5.4597090472370632e-006</v>
       </c>
       <c r="AE14">
-        <v>-1.5585977240371992e-005</v>
+        <v>-1.6961982026322906e-005</v>
       </c>
       <c r="AF14">
-        <v>-3.3664256515412977e-005</v>
+        <v>-4.8780497296978476e-005</v>
       </c>
       <c r="AG14">
-        <v>3.5614431227369922e-006</v>
+        <v>-6.374754304186153e-006</v>
       </c>
       <c r="AH14">
-        <v>1.1466332426809768e-005</v>
+        <v>1.7637862802154376e-005</v>
       </c>
       <c r="AI14">
-        <v>-2.9930942522931291e-005</v>
+        <v>-3.6003823550613231e-005</v>
       </c>
       <c r="AJ14">
-        <v>-6.9791533030363293e-005</v>
+        <v>-7.8927664947620185e-005</v>
       </c>
       <c r="AK14">
-        <v>-1.2048022267360499e-005</v>
+        <v>-2.2218754609247874e-005</v>
       </c>
       <c r="AL14">
-        <v>2.7311700451492513e-008</v>
+        <v>1.7658887970857962e-006</v>
       </c>
       <c r="AM14">
-        <v>-1.2597984353376304e-006</v>
+        <v>-3.0443866844916275e-005</v>
       </c>
       <c r="AN14">
-        <v>-1.5569390147192764e-008</v>
+        <v>-5.4718112438425582e-006</v>
       </c>
       <c r="AO14">
-        <v>-3.9989143034873889e-005</v>
+        <v>-8.0930963355587522e-005</v>
       </c>
       <c r="AP14">
-        <v>8.1378506141577657e-005</v>
+        <v>5.6097868507115959e-005</v>
       </c>
       <c r="AQ14">
-        <v>-3.3865779494024397e-005</v>
+        <v>-2.9974449459499724e-005</v>
       </c>
       <c r="AR14">
-        <v>-0.00073451033445564033</v>
+        <v>-0.00093452285064598022</v>
       </c>
     </row>
     <row r="15">
@@ -2359,133 +2359,133 @@
         <v>28</v>
       </c>
       <c r="B15">
-        <v>-0.16786519111010387</v>
+        <v>-0.16466634537223668</v>
       </c>
       <c r="C15">
-        <v>-1.3012607956397454e-005</v>
+        <v>-2.5296856216310698e-005</v>
       </c>
       <c r="D15">
-        <v>1.9702723944720058e-006</v>
+        <v>7.679434612894412e-007</v>
       </c>
       <c r="E15">
-        <v>-2.8885721244888692e-008</v>
+        <v>-1.270894148361265e-008</v>
       </c>
       <c r="F15">
-        <v>0.00018630272666383846</v>
+        <v>0.0001973315521787865</v>
       </c>
       <c r="G15">
-        <v>1.8948614685013144e-005</v>
+        <v>2.5948394020186381e-005</v>
       </c>
       <c r="H15">
-        <v>7.5402891280150399e-006</v>
+        <v>-4.6168277448304263e-006</v>
       </c>
       <c r="I15">
-        <v>8.9896841271704759e-005</v>
+        <v>0.00010510891435513628</v>
       </c>
       <c r="J15">
-        <v>2.7145765677405632e-005</v>
+        <v>3.0591208644005019e-005</v>
       </c>
       <c r="K15">
-        <v>3.2904065454284349e-005</v>
+        <v>2.4550854414299593e-005</v>
       </c>
       <c r="L15">
-        <v>-6.0210486450192622e-006</v>
+        <v>-1.3276604256051282e-005</v>
       </c>
       <c r="M15">
-        <v>-4.388590890549212e-005</v>
+        <v>5.299914436657574e-005</v>
       </c>
       <c r="N15">
-        <v>-3.6584873864488245e-006</v>
+        <v>3.5294004281916569e-005</v>
       </c>
       <c r="O15">
-        <v>3.4000946265196476e-005</v>
+        <v>5.9570786866506957e-005</v>
       </c>
       <c r="P15">
-        <v>0.00043604425066138863</v>
+        <v>0.00046160590175671739</v>
       </c>
       <c r="Q15">
-        <v>0.00034974188223331861</v>
+        <v>0.00035950621854139949</v>
       </c>
       <c r="R15">
-        <v>0.00037099188895872986</v>
+        <v>0.0003452210129737648</v>
       </c>
       <c r="S15">
-        <v>1.6453860819674325e-007</v>
+        <v>5.4188540166182362e-007</v>
       </c>
       <c r="T15">
-        <v>-3.5363448432731263e-007</v>
+        <v>3.0913841740410465e-008</v>
       </c>
       <c r="U15">
-        <v>1.0036636651174681e-005</v>
+        <v>3.0494360210134313e-005</v>
       </c>
       <c r="V15">
-        <v>-2.7066096083603538e-006</v>
+        <v>2.829871391237196e-005</v>
       </c>
       <c r="W15">
-        <v>6.1233488376941211e-005</v>
+        <v>0.00010391853954084038</v>
       </c>
       <c r="X15">
-        <v>0.0001244167354179503</v>
+        <v>0.00016776162462602139</v>
       </c>
       <c r="Y15">
-        <v>2.8463343521252781e-006</v>
+        <v>-5.759060063784046e-007</v>
       </c>
       <c r="Z15">
-        <v>-2.0145298515756715e-006</v>
+        <v>-3.0115007396594559e-006</v>
       </c>
       <c r="AA15">
-        <v>-2.4570342923778678e-005</v>
+        <v>-2.799545736193258e-005</v>
       </c>
       <c r="AB15">
-        <v>-2.277922762833043e-005</v>
+        <v>-3.5894578389401049e-005</v>
       </c>
       <c r="AC15">
-        <v>-2.7875408808096163e-005</v>
+        <v>-2.113688565160433e-005</v>
       </c>
       <c r="AD15">
-        <v>-3.3908035623789632e-005</v>
+        <v>-4.7830291953542181e-005</v>
       </c>
       <c r="AE15">
-        <v>-2.5186920921054617e-005</v>
+        <v>-3.3215351931366393e-005</v>
       </c>
       <c r="AF15">
-        <v>-3.4561000594923128e-005</v>
+        <v>-4.4925466177820861e-005</v>
       </c>
       <c r="AG15">
-        <v>-4.1272511123606934e-005</v>
+        <v>-2.7841507683270559e-005</v>
       </c>
       <c r="AH15">
-        <v>-1.7694268842343671e-005</v>
+        <v>-3.1691635280815236e-005</v>
       </c>
       <c r="AI15">
-        <v>-4.5990781099885644e-005</v>
+        <v>-7.7012783928613973e-005</v>
       </c>
       <c r="AJ15">
-        <v>-3.7038990804816481e-005</v>
+        <v>-5.3016544937652357e-005</v>
       </c>
       <c r="AK15">
-        <v>-5.0558213503038897e-006</v>
+        <v>-8.4943755631748826e-006</v>
       </c>
       <c r="AL15">
-        <v>-1.4803834540635789e-006</v>
+        <v>-7.0892045033260566e-007</v>
       </c>
       <c r="AM15">
-        <v>7.0981289341343979e-007</v>
+        <v>-1.7533332889775854e-005</v>
       </c>
       <c r="AN15">
-        <v>3.9077910141636622e-005</v>
+        <v>4.0653882754113316e-005</v>
       </c>
       <c r="AO15">
-        <v>0.00011525909412599361</v>
+        <v>0.00012373135501357198</v>
       </c>
       <c r="AP15">
-        <v>-3.8727182285099799e-005</v>
+        <v>-4.9457782564098861e-005</v>
       </c>
       <c r="AQ15">
-        <v>5.010353978806996e-005</v>
+        <v>2.7124900873592216e-005</v>
       </c>
       <c r="AR15">
-        <v>-0.00034835238235100135</v>
+        <v>-0.00041412722166980738</v>
       </c>
     </row>
     <row r="16">
@@ -2493,133 +2493,133 @@
         <v>29</v>
       </c>
       <c r="B16">
-        <v>-0.30937038307457937</v>
+        <v>-0.29662049717465033</v>
       </c>
       <c r="C16">
-        <v>-8.997480077545465e-006</v>
+        <v>-2.4638573741358446e-005</v>
       </c>
       <c r="D16">
-        <v>4.4942725883523771e-006</v>
+        <v>2.0142446136799905e-006</v>
       </c>
       <c r="E16">
-        <v>-8.9650775135490984e-008</v>
+        <v>-6.2086123423845401e-008</v>
       </c>
       <c r="F16">
-        <v>0.00017379683436849692</v>
+        <v>0.0001761194141308896</v>
       </c>
       <c r="G16">
-        <v>1.169176914098878e-005</v>
+        <v>3.6032988772732931e-005</v>
       </c>
       <c r="H16">
-        <v>1.8173315610157817e-005</v>
+        <v>1.8229716450658245e-005</v>
       </c>
       <c r="I16">
-        <v>0.00014504377653912228</v>
+        <v>0.00011701139869537612</v>
       </c>
       <c r="J16">
-        <v>1.8669708884215671e-005</v>
+        <v>3.1416036478610807e-005</v>
       </c>
       <c r="K16">
-        <v>4.5667103065209953e-005</v>
+        <v>4.2911078734865656e-005</v>
       </c>
       <c r="L16">
-        <v>7.1020851827182882e-006</v>
+        <v>7.4329532209340223e-006</v>
       </c>
       <c r="M16">
-        <v>-2.0697280462731891e-005</v>
+        <v>8.1600316665843102e-005</v>
       </c>
       <c r="N16">
-        <v>2.9595876905782461e-006</v>
+        <v>3.6156786155918546e-005</v>
       </c>
       <c r="O16">
-        <v>3.4068662095751217e-005</v>
+        <v>5.8382311306116028e-005</v>
       </c>
       <c r="P16">
-        <v>0.00034974188223331861</v>
+        <v>0.00035950621854139949</v>
       </c>
       <c r="Q16">
-        <v>0.00062094129000162608</v>
+        <v>0.0006398669833342041</v>
       </c>
       <c r="R16">
-        <v>0.00031729788697603832</v>
+        <v>0.00028052649422890662</v>
       </c>
       <c r="S16">
-        <v>7.8686661769910411e-007</v>
+        <v>1.5764463137921975e-006</v>
       </c>
       <c r="T16">
-        <v>-3.063432327969994e-007</v>
+        <v>2.3245001786483499e-007</v>
       </c>
       <c r="U16">
-        <v>2.6484390600387815e-005</v>
+        <v>3.2004572896313668e-005</v>
       </c>
       <c r="V16">
-        <v>5.3189475717644336e-005</v>
+        <v>7.6224857291609969e-005</v>
       </c>
       <c r="W16">
-        <v>0.00010243757590374968</v>
+        <v>0.0001373108598322086</v>
       </c>
       <c r="X16">
-        <v>0.00018937289710298003</v>
+        <v>0.00023342728825639616</v>
       </c>
       <c r="Y16">
-        <v>1.0951415106172347e-005</v>
+        <v>7.5993245916347912e-006</v>
       </c>
       <c r="Z16">
-        <v>2.3796591476535014e-005</v>
+        <v>1.9829827945221025e-005</v>
       </c>
       <c r="AA16">
-        <v>-8.4201781252286282e-007</v>
+        <v>-1.4529425622065881e-006</v>
       </c>
       <c r="AB16">
-        <v>-1.838687861698926e-005</v>
+        <v>-3.1162968217501695e-005</v>
       </c>
       <c r="AC16">
-        <v>-5.3632916983847596e-005</v>
+        <v>-3.374909157595717e-005</v>
       </c>
       <c r="AD16">
-        <v>-4.4694368098089833e-005</v>
+        <v>-5.8310482600679141e-005</v>
       </c>
       <c r="AE16">
-        <v>2.5991419842010281e-007</v>
+        <v>-3.6232512181531211e-006</v>
       </c>
       <c r="AF16">
-        <v>-2.6748372990485336e-005</v>
+        <v>-3.3158693346604675e-005</v>
       </c>
       <c r="AG16">
-        <v>-3.6699206240433357e-005</v>
+        <v>-1.8845789235205042e-005</v>
       </c>
       <c r="AH16">
-        <v>7.9598417998092681e-006</v>
+        <v>-6.8509161631558018e-006</v>
       </c>
       <c r="AI16">
-        <v>-4.0167247408948902e-005</v>
+        <v>-6.0803425415086148e-005</v>
       </c>
       <c r="AJ16">
-        <v>-2.1109648320352211e-005</v>
+        <v>-3.6247264831092393e-005</v>
       </c>
       <c r="AK16">
-        <v>-2.3012665814294123e-005</v>
+        <v>-2.9757842378926318e-005</v>
       </c>
       <c r="AL16">
-        <v>1.7652598805730695e-006</v>
+        <v>3.6657020293479569e-006</v>
       </c>
       <c r="AM16">
-        <v>-1.9778177244917825e-006</v>
+        <v>-2.6417359465770262e-005</v>
       </c>
       <c r="AN16">
-        <v>4.8972409429167156e-005</v>
+        <v>4.794313342363256e-005</v>
       </c>
       <c r="AO16">
-        <v>7.1003728473824663e-005</v>
+        <v>6.4535690093456695e-005</v>
       </c>
       <c r="AP16">
-        <v>3.4691242641461824e-005</v>
+        <v>1.312708388221305e-005</v>
       </c>
       <c r="AQ16">
-        <v>7.6542786129071507e-005</v>
+        <v>6.0124255663574305e-005</v>
       </c>
       <c r="AR16">
-        <v>-0.00048754231826059771</v>
+        <v>-0.00056085186551675008</v>
       </c>
     </row>
     <row r="17">
@@ -2627,133 +2627,133 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>-0.26031661679370438</v>
+        <v>-0.12765543741736268</v>
       </c>
       <c r="C17">
-        <v>-9.1059760296681505e-006</v>
+        <v>-2.3444387672616781e-005</v>
       </c>
       <c r="D17">
-        <v>3.733618546458085e-006</v>
+        <v>-2.3064223972200535e-007</v>
       </c>
       <c r="E17">
-        <v>-4.5345779074856702e-008</v>
+        <v>-2.2778854145536958e-009</v>
       </c>
       <c r="F17">
-        <v>0.00044698455126123066</v>
+        <v>0.00034406786427301512</v>
       </c>
       <c r="G17">
-        <v>-8.9862655802493596e-006</v>
+        <v>7.7544270617507923e-005</v>
       </c>
       <c r="H17">
-        <v>-3.8641978202873912e-005</v>
+        <v>2.8842976648460516e-005</v>
       </c>
       <c r="I17">
-        <v>0.0002854267663048609</v>
+        <v>0.00019329162416323298</v>
       </c>
       <c r="J17">
-        <v>3.727138739077605e-005</v>
+        <v>9.9815567753607209e-005</v>
       </c>
       <c r="K17">
-        <v>-1.3104223290601289e-005</v>
+        <v>5.4183267296301378e-005</v>
       </c>
       <c r="L17">
-        <v>8.5535378192221816e-005</v>
+        <v>0.00013607179998894052</v>
       </c>
       <c r="M17">
-        <v>-0.0039341093119958145</v>
+        <v>-0.0027479995940856016</v>
       </c>
       <c r="N17">
-        <v>8.2474185954300593e-005</v>
+        <v>7.1267337531774524e-006</v>
       </c>
       <c r="O17">
-        <v>2.7307092927135023e-005</v>
+        <v>8.6535164948743355e-005</v>
       </c>
       <c r="P17">
-        <v>0.00037099188895872986</v>
+        <v>0.0003452210129737648</v>
       </c>
       <c r="Q17">
-        <v>0.00031729788697603832</v>
+        <v>0.00028052649422890662</v>
       </c>
       <c r="R17">
-        <v>0.0051869947491330433</v>
+        <v>0.005430014561984677</v>
       </c>
       <c r="S17">
-        <v>1.4676030856041168e-006</v>
+        <v>3.573773554275586e-008</v>
       </c>
       <c r="T17">
-        <v>-1.8609953741164372e-006</v>
+        <v>-2.5801178212606264e-006</v>
       </c>
       <c r="U17">
-        <v>-4.3531404292793498e-005</v>
+        <v>3.8415631755004705e-005</v>
       </c>
       <c r="V17">
-        <v>-2.7908340380019456e-005</v>
+        <v>6.4316863125706458e-005</v>
       </c>
       <c r="W17">
-        <v>1.425793739530047e-005</v>
+        <v>0.00014302277872261276</v>
       </c>
       <c r="X17">
-        <v>0.00010074541004779155</v>
+        <v>0.00019563666315527669</v>
       </c>
       <c r="Y17">
-        <v>1.185429778187645e-005</v>
+        <v>-9.6685720339629898e-006</v>
       </c>
       <c r="Z17">
-        <v>1.3190672542102793e-005</v>
+        <v>4.6467771264812718e-006</v>
       </c>
       <c r="AA17">
-        <v>-1.2364235595923689e-005</v>
+        <v>4.2708286761512158e-007</v>
       </c>
       <c r="AB17">
-        <v>-8.8603271498986384e-005</v>
+        <v>1.5711229592522443e-005</v>
       </c>
       <c r="AC17">
-        <v>-4.3934063515557725e-005</v>
+        <v>-2.1759828669103873e-005</v>
       </c>
       <c r="AD17">
-        <v>-2.0145822864561728e-005</v>
+        <v>-1.7816854081849041e-005</v>
       </c>
       <c r="AE17">
-        <v>-2.7473614082384497e-005</v>
+        <v>-4.9939853678547934e-005</v>
       </c>
       <c r="AF17">
-        <v>-5.8214685573740683e-005</v>
+        <v>-2.3288915060881721e-005</v>
       </c>
       <c r="AG17">
-        <v>-5.1719909536976351e-005</v>
+        <v>7.9766340056744047e-006</v>
       </c>
       <c r="AH17">
-        <v>-5.3685925061198715e-006</v>
+        <v>1.4208835870225412e-005</v>
       </c>
       <c r="AI17">
-        <v>-4.6911389359856502e-005</v>
+        <v>2.8726732420323639e-005</v>
       </c>
       <c r="AJ17">
-        <v>-6.8064019435743295e-006</v>
+        <v>1.416153316204855e-005</v>
       </c>
       <c r="AK17">
-        <v>-0.00010119897594843482</v>
+        <v>-4.5502479570227658e-005</v>
       </c>
       <c r="AL17">
-        <v>1.7210229087900579e-006</v>
+        <v>3.1260469260903907e-006</v>
       </c>
       <c r="AM17">
-        <v>-1.6811122165266929e-006</v>
+        <v>-8.740134791834287e-005</v>
       </c>
       <c r="AN17">
-        <v>-1.2975361294483118e-005</v>
+        <v>-2.6548707415788414e-005</v>
       </c>
       <c r="AO17">
-        <v>-2.1388941329578582e-005</v>
+        <v>-3.5504609063952509e-005</v>
       </c>
       <c r="AP17">
-        <v>8.2308327370232429e-005</v>
+        <v>1.6338125590001227e-005</v>
       </c>
       <c r="AQ17">
-        <v>0.00018379794660937143</v>
+        <v>0.00031194683469120505</v>
       </c>
       <c r="AR17">
-        <v>-0.0003356768476641236</v>
+        <v>-0.00028553703677698086</v>
       </c>
     </row>
     <row r="18">
@@ -2761,133 +2761,133 @@
         <v>31</v>
       </c>
       <c r="B18">
-        <v>0.0068762743629800626</v>
+        <v>0.0065675531684875662</v>
       </c>
       <c r="C18">
-        <v>-5.8801654824418215e-007</v>
+        <v>-5.2859634024004762e-007</v>
       </c>
       <c r="D18">
-        <v>8.6283539050876427e-008</v>
+        <v>1.5294151081129712e-007</v>
       </c>
       <c r="E18">
-        <v>4.0452023652442571e-010</v>
+        <v>-3.0239205225700207e-010</v>
       </c>
       <c r="F18">
-        <v>-8.8758017466262801e-007</v>
+        <v>-1.8289953009510864e-006</v>
       </c>
       <c r="G18">
-        <v>1.8299571693418365e-007</v>
+        <v>-9.2089538807322488e-007</v>
       </c>
       <c r="H18">
-        <v>9.2428653871472117e-007</v>
+        <v>5.0390719465660914e-007</v>
       </c>
       <c r="I18">
-        <v>4.7445277405104249e-007</v>
+        <v>5.3943887649995809e-007</v>
       </c>
       <c r="J18">
-        <v>1.0330813284656474e-007</v>
+        <v>-6.3318059620109478e-007</v>
       </c>
       <c r="K18">
-        <v>3.1303772616247708e-007</v>
+        <v>7.1070514033530672e-008</v>
       </c>
       <c r="L18">
-        <v>5.0028220700627444e-007</v>
+        <v>1.787361506892389e-009</v>
       </c>
       <c r="M18">
-        <v>-6.4201954834072337e-007</v>
+        <v>7.6559243139081178e-007</v>
       </c>
       <c r="N18">
-        <v>2.9652451486910559e-006</v>
+        <v>3.1652204422735849e-006</v>
       </c>
       <c r="O18">
-        <v>1.132600628345244e-006</v>
+        <v>1.3109694415009711e-006</v>
       </c>
       <c r="P18">
-        <v>1.6453860819674325e-007</v>
+        <v>5.4188540166182362e-007</v>
       </c>
       <c r="Q18">
-        <v>7.8686661769910411e-007</v>
+        <v>1.5764463137921975e-006</v>
       </c>
       <c r="R18">
-        <v>1.4676030856041168e-006</v>
+        <v>3.573773554275586e-008</v>
       </c>
       <c r="S18">
-        <v>5.0487484867291649e-007</v>
+        <v>5.4062229809190631e-007</v>
       </c>
       <c r="T18">
-        <v>-3.7614746655066682e-009</v>
+        <v>-2.7093950796788721e-009</v>
       </c>
       <c r="U18">
-        <v>2.1644202927660883e-007</v>
+        <v>8.0835086648017708e-007</v>
       </c>
       <c r="V18">
-        <v>-1.3058318352165235e-006</v>
+        <v>-8.8829618239509296e-007</v>
       </c>
       <c r="W18">
-        <v>-1.3235927714713896e-006</v>
+        <v>-1.2560250109220201e-006</v>
       </c>
       <c r="X18">
-        <v>-1.2502282646431542e-006</v>
+        <v>-1.457738535931683e-006</v>
       </c>
       <c r="Y18">
-        <v>-5.1392670570253004e-008</v>
+        <v>-2.6198855942942262e-008</v>
       </c>
       <c r="Z18">
-        <v>-6.8123807194000929e-007</v>
+        <v>-7.2403600792762224e-007</v>
       </c>
       <c r="AA18">
-        <v>1.6263743121030536e-006</v>
+        <v>1.9879628997550427e-006</v>
       </c>
       <c r="AB18">
-        <v>5.8501440745486238e-007</v>
+        <v>4.7712506940220115e-007</v>
       </c>
       <c r="AC18">
-        <v>1.8761626655150252e-006</v>
+        <v>1.3741449696128293e-006</v>
       </c>
       <c r="AD18">
-        <v>1.2574698949771415e-006</v>
+        <v>1.3792963263199738e-006</v>
       </c>
       <c r="AE18">
-        <v>2.7485368047185941e-006</v>
+        <v>3.005024940018818e-006</v>
       </c>
       <c r="AF18">
-        <v>9.0978379837808464e-007</v>
+        <v>1.1013059060450647e-006</v>
       </c>
       <c r="AG18">
-        <v>1.1384125971795166e-006</v>
+        <v>9.1854783113393936e-007</v>
       </c>
       <c r="AH18">
-        <v>1.1374378148736754e-006</v>
+        <v>1.9811368500926468e-006</v>
       </c>
       <c r="AI18">
-        <v>1.941276287368735e-006</v>
+        <v>1.872351147270361e-006</v>
       </c>
       <c r="AJ18">
-        <v>9.7241617733335524e-007</v>
+        <v>1.1257162621809847e-006</v>
       </c>
       <c r="AK18">
-        <v>1.6276734925956061e-006</v>
+        <v>1.8739130171534807e-006</v>
       </c>
       <c r="AL18">
-        <v>1.2780953898564263e-007</v>
+        <v>1.0809047784141537e-007</v>
       </c>
       <c r="AM18">
-        <v>-2.9121498596975902e-007</v>
+        <v>-4.3537703964380468e-007</v>
       </c>
       <c r="AN18">
-        <v>-1.0712565992968563e-006</v>
+        <v>-8.5843833960773721e-007</v>
       </c>
       <c r="AO18">
-        <v>8.3875680710881582e-007</v>
+        <v>1.1665665695757725e-006</v>
       </c>
       <c r="AP18">
-        <v>3.2586043201149949e-007</v>
+        <v>1.1815582784634849e-006</v>
       </c>
       <c r="AQ18">
-        <v>5.0501977913672393e-007</v>
+        <v>5.7822382418539757e-007</v>
       </c>
       <c r="AR18">
-        <v>-3.2983725265745666e-005</v>
+        <v>-3.6233586246106934e-005</v>
       </c>
     </row>
     <row r="19">
@@ -2895,133 +2895,133 @@
         <v>32</v>
       </c>
       <c r="B19">
-        <v>0.0036767699376115954</v>
+        <v>0.0035464628721402439</v>
       </c>
       <c r="C19">
-        <v>-1.8045790402083797e-006</v>
+        <v>-2.111075240515896e-006</v>
       </c>
       <c r="D19">
-        <v>6.575578767759628e-008</v>
+        <v>8.1297443753781934e-008</v>
       </c>
       <c r="E19">
-        <v>-1.2053311925375307e-009</v>
+        <v>-1.4676985848761628e-009</v>
       </c>
       <c r="F19">
-        <v>2.0472830417760267e-006</v>
+        <v>2.5130255296876655e-006</v>
       </c>
       <c r="G19">
-        <v>-3.8395399446019663e-008</v>
+        <v>-6.63481251449356e-007</v>
       </c>
       <c r="H19">
-        <v>-8.5542673223008388e-007</v>
+        <v>-1.3200867165801667e-006</v>
       </c>
       <c r="I19">
-        <v>1.0929233605987388e-006</v>
+        <v>1.4953105196428771e-006</v>
       </c>
       <c r="J19">
-        <v>-5.1381582036962406e-007</v>
+        <v>-1.1332049925488468e-006</v>
       </c>
       <c r="K19">
-        <v>8.5517705544683208e-007</v>
+        <v>6.5177634143807304e-007</v>
       </c>
       <c r="L19">
-        <v>4.2342652135527104e-008</v>
+        <v>-2.3101791425125704e-007</v>
       </c>
       <c r="M19">
-        <v>-7.8026880292941461e-007</v>
+        <v>-4.8698238867935072e-007</v>
       </c>
       <c r="N19">
-        <v>1.3425435305749641e-006</v>
+        <v>2.5271800298096919e-006</v>
       </c>
       <c r="O19">
-        <v>-1.1541809518803255e-006</v>
+        <v>-7.5551999660274686e-007</v>
       </c>
       <c r="P19">
-        <v>-3.5363448432731263e-007</v>
+        <v>3.0913841740410465e-008</v>
       </c>
       <c r="Q19">
-        <v>-3.063432327969994e-007</v>
+        <v>2.3245001786483499e-007</v>
       </c>
       <c r="R19">
-        <v>-1.8609953741164372e-006</v>
+        <v>-2.5801178212606264e-006</v>
       </c>
       <c r="S19">
-        <v>-3.7614746655066682e-009</v>
+        <v>-2.7093950796788721e-009</v>
       </c>
       <c r="T19">
-        <v>6.0651811307528936e-007</v>
+        <v>6.8947674577144812e-007</v>
       </c>
       <c r="U19">
-        <v>-9.9303249461532453e-008</v>
+        <v>3.8428482826233996e-007</v>
       </c>
       <c r="V19">
-        <v>-1.794660128682704e-006</v>
+        <v>-1.1354298054468393e-006</v>
       </c>
       <c r="W19">
-        <v>-2.2357054536265696e-006</v>
+        <v>-1.7398437729270858e-006</v>
       </c>
       <c r="X19">
-        <v>-2.4719830364674378e-006</v>
+        <v>-1.9782017643194653e-006</v>
       </c>
       <c r="Y19">
-        <v>4.9570348641423301e-008</v>
+        <v>4.9522192939229459e-008</v>
       </c>
       <c r="Z19">
-        <v>-3.2664595383561887e-007</v>
+        <v>-4.0966996353986499e-007</v>
       </c>
       <c r="AA19">
-        <v>1.2233373175113052e-006</v>
+        <v>1.5652263061771817e-006</v>
       </c>
       <c r="AB19">
-        <v>1.5520074841212529e-006</v>
+        <v>1.8042953125036854e-006</v>
       </c>
       <c r="AC19">
-        <v>1.7490863628047759e-006</v>
+        <v>1.7997576982976277e-006</v>
       </c>
       <c r="AD19">
-        <v>9.8522883859277706e-007</v>
+        <v>9.7846385221225734e-007</v>
       </c>
       <c r="AE19">
-        <v>1.8310178728618793e-006</v>
+        <v>2.2906799369046227e-006</v>
       </c>
       <c r="AF19">
-        <v>1.31624259368367e-006</v>
+        <v>1.6814927442265341e-006</v>
       </c>
       <c r="AG19">
-        <v>8.1195392537847175e-007</v>
+        <v>1.3992193814255076e-006</v>
       </c>
       <c r="AH19">
-        <v>2.3122322589005658e-007</v>
+        <v>2.7700938297861094e-007</v>
       </c>
       <c r="AI19">
-        <v>6.8966310783656917e-007</v>
+        <v>-9.0919938225552548e-008</v>
       </c>
       <c r="AJ19">
-        <v>5.3884604295419614e-007</v>
+        <v>6.5432913302823684e-007</v>
       </c>
       <c r="AK19">
-        <v>5.5771612317680025e-007</v>
+        <v>6.7862422894459416e-007</v>
       </c>
       <c r="AL19">
-        <v>1.5799231672027583e-007</v>
+        <v>1.7875692451641683e-007</v>
       </c>
       <c r="AM19">
-        <v>3.2559255936529875e-007</v>
+        <v>4.588815820395906e-007</v>
       </c>
       <c r="AN19">
-        <v>1.2821756331147944e-006</v>
+        <v>1.6034020641304969e-006</v>
       </c>
       <c r="AO19">
-        <v>3.3868228428815622e-006</v>
+        <v>4.3872289432178702e-006</v>
       </c>
       <c r="AP19">
-        <v>-2.9013074395084985e-006</v>
+        <v>-3.4976686572818025e-006</v>
       </c>
       <c r="AQ19">
-        <v>1.4767093594554237e-006</v>
+        <v>1.7125742510849635e-006</v>
       </c>
       <c r="AR19">
-        <v>-3.0329957970758059e-005</v>
+        <v>-3.5586229727230072e-005</v>
       </c>
     </row>
     <row r="20">
@@ -3029,133 +3029,133 @@
         <v>33</v>
       </c>
       <c r="B20">
-        <v>0.041821259939029548</v>
+        <v>0.077809490571521533</v>
       </c>
       <c r="C20">
-        <v>-9.1072915680786029e-006</v>
+        <v>-4.1802062486350442e-005</v>
       </c>
       <c r="D20">
-        <v>7.0204829550340042e-006</v>
+        <v>9.1431235299073356e-008</v>
       </c>
       <c r="E20">
-        <v>-5.9831280507467376e-008</v>
+        <v>1.8363534191056456e-008</v>
       </c>
       <c r="F20">
-        <v>-7.2107721958023725e-005</v>
+        <v>-0.00013568252562926625</v>
       </c>
       <c r="G20">
-        <v>-3.9698931242686783e-005</v>
+        <v>-2.6616280561899129e-005</v>
       </c>
       <c r="H20">
-        <v>-6.9683695691212893e-006</v>
+        <v>-4.4419594255488008e-005</v>
       </c>
       <c r="I20">
-        <v>2.5999592982125716e-005</v>
+        <v>-6.0305337685957077e-005</v>
       </c>
       <c r="J20">
-        <v>-1.8088146721284787e-005</v>
+        <v>-2.5999556811430208e-005</v>
       </c>
       <c r="K20">
-        <v>4.2258043145662513e-005</v>
+        <v>4.0904890860921788e-006</v>
       </c>
       <c r="L20">
-        <v>1.0861564075975168e-005</v>
+        <v>-1.330778390749244e-005</v>
       </c>
       <c r="M20">
-        <v>0.00044899586266481913</v>
+        <v>0.00073880584348539734</v>
       </c>
       <c r="N20">
-        <v>0.00043689289239818083</v>
+        <v>0.00068206398847657946</v>
       </c>
       <c r="O20">
-        <v>0.00031306394996420911</v>
+        <v>0.00048116415972502646</v>
       </c>
       <c r="P20">
-        <v>1.0036636651174681e-005</v>
+        <v>3.0494360210134313e-005</v>
       </c>
       <c r="Q20">
-        <v>2.6484390600387815e-005</v>
+        <v>3.2004572896313668e-005</v>
       </c>
       <c r="R20">
-        <v>-4.3531404292793498e-005</v>
+        <v>3.8415631755004705e-005</v>
       </c>
       <c r="S20">
-        <v>2.1644202927660883e-007</v>
+        <v>8.0835086648017708e-007</v>
       </c>
       <c r="T20">
-        <v>-9.9303249461532453e-008</v>
+        <v>3.8428482826233996e-007</v>
       </c>
       <c r="U20">
-        <v>0.00076675385320341591</v>
+        <v>0.0009583411319834252</v>
       </c>
       <c r="V20">
-        <v>0.00065649275947177741</v>
+        <v>0.00093366656729831346</v>
       </c>
       <c r="W20">
-        <v>0.00065979760412394092</v>
+        <v>0.00093434169697037832</v>
       </c>
       <c r="X20">
-        <v>0.00061927698327147226</v>
+        <v>0.00090304424419730732</v>
       </c>
       <c r="Y20">
-        <v>-5.3703166632165379e-005</v>
+        <v>-7.9295951572697855e-005</v>
       </c>
       <c r="Z20">
-        <v>-1.6816515901543554e-005</v>
+        <v>-2.483725332290659e-005</v>
       </c>
       <c r="AA20">
-        <v>1.5171756706226129e-006</v>
+        <v>-3.076897877102392e-005</v>
       </c>
       <c r="AB20">
-        <v>-2.0912221383999612e-005</v>
+        <v>-2.4992711963683965e-005</v>
       </c>
       <c r="AC20">
-        <v>-3.7736126974272059e-005</v>
+        <v>6.0764066150467282e-006</v>
       </c>
       <c r="AD20">
-        <v>-2.6679572799916676e-005</v>
+        <v>-2.2832336034873248e-005</v>
       </c>
       <c r="AE20">
-        <v>1.8418900332821072e-005</v>
+        <v>2.7210759183189572e-005</v>
       </c>
       <c r="AF20">
-        <v>-4.0028278059515737e-005</v>
+        <v>-4.9719309572991146e-005</v>
       </c>
       <c r="AG20">
-        <v>3.0808817222595266e-006</v>
+        <v>-3.7684588234171212e-006</v>
       </c>
       <c r="AH20">
-        <v>-2.5766383757899628e-005</v>
+        <v>-4.0022951393980047e-005</v>
       </c>
       <c r="AI20">
-        <v>-3.2630267389363734e-005</v>
+        <v>-3.9412224871447141e-005</v>
       </c>
       <c r="AJ20">
-        <v>-3.3337085446458112e-005</v>
+        <v>-4.861101136781027e-005</v>
       </c>
       <c r="AK20">
-        <v>-1.0940284810062226e-005</v>
+        <v>-2.237748137005717e-005</v>
       </c>
       <c r="AL20">
-        <v>1.3169132184540625e-006</v>
+        <v>4.2542319785726667e-006</v>
       </c>
       <c r="AM20">
-        <v>-2.274446115493791e-005</v>
+        <v>-6.2428407644931814e-005</v>
       </c>
       <c r="AN20">
-        <v>-1.5538076929352753e-005</v>
+        <v>-3.197922235086267e-005</v>
       </c>
       <c r="AO20">
-        <v>4.3517345419745158e-005</v>
+        <v>3.8012649383127161e-005</v>
       </c>
       <c r="AP20">
-        <v>-5.1230759610730445e-005</v>
+        <v>-6.4855753695447336e-005</v>
       </c>
       <c r="AQ20">
-        <v>2.4595279634770178e-005</v>
+        <v>4.4192741894875313e-005</v>
       </c>
       <c r="AR20">
-        <v>-0.00082412723064898322</v>
+        <v>-0.0010013012718396745</v>
       </c>
     </row>
     <row r="21">
@@ -3163,133 +3163,133 @@
         <v>34</v>
       </c>
       <c r="B21">
-        <v>0.16895605719581233</v>
+        <v>0.23735009390516218</v>
       </c>
       <c r="C21">
-        <v>-1.1725445409026655e-005</v>
+        <v>-4.226846860645582e-005</v>
       </c>
       <c r="D21">
-        <v>4.1230766851864239e-006</v>
+        <v>-4.1640705650681992e-006</v>
       </c>
       <c r="E21">
-        <v>-1.9221771838733098e-008</v>
+        <v>7.5860138125306047e-008</v>
       </c>
       <c r="F21">
-        <v>-2.16697000946717e-005</v>
+        <v>-0.0001106587141544848</v>
       </c>
       <c r="G21">
-        <v>1.424422101243714e-005</v>
+        <v>3.3974872992910529e-005</v>
       </c>
       <c r="H21">
-        <v>-8.7433403924377684e-006</v>
+        <v>-3.9700452207297517e-005</v>
       </c>
       <c r="I21">
-        <v>9.3598298992700845e-005</v>
+        <v>3.0375240113230724e-005</v>
       </c>
       <c r="J21">
-        <v>6.7057250079301009e-005</v>
+        <v>6.3707855740123353e-005</v>
       </c>
       <c r="K21">
-        <v>7.7709603315361005e-005</v>
+        <v>4.7744001122612537e-005</v>
       </c>
       <c r="L21">
-        <v>0.00017288810916693293</v>
+        <v>0.00017941140256331299</v>
       </c>
       <c r="M21">
-        <v>0.00067437557096458774</v>
+        <v>0.0012232715306503108</v>
       </c>
       <c r="N21">
-        <v>0.00073374082258449789</v>
+        <v>0.0011391809011316698</v>
       </c>
       <c r="O21">
-        <v>0.00054660533126663741</v>
+        <v>0.00083688150539680084</v>
       </c>
       <c r="P21">
-        <v>-2.7066096083603538e-006</v>
+        <v>2.829871391237196e-005</v>
       </c>
       <c r="Q21">
-        <v>5.3189475717644336e-005</v>
+        <v>7.6224857291609969e-005</v>
       </c>
       <c r="R21">
-        <v>-2.7908340380019456e-005</v>
+        <v>6.4316863125706458e-005</v>
       </c>
       <c r="S21">
-        <v>-1.3058318352165235e-006</v>
+        <v>-8.8829618239509296e-007</v>
       </c>
       <c r="T21">
-        <v>-1.794660128682704e-006</v>
+        <v>-1.1354298054468393e-006</v>
       </c>
       <c r="U21">
-        <v>0.00065649275947177741</v>
+        <v>0.00093366656729831346</v>
       </c>
       <c r="V21">
-        <v>0.0011407380215080359</v>
+        <v>0.0016262165864250561</v>
       </c>
       <c r="W21">
-        <v>0.00096157558582373316</v>
+        <v>0.0014253922371825095</v>
       </c>
       <c r="X21">
-        <v>0.00095762363059621761</v>
+        <v>0.001438249099318946</v>
       </c>
       <c r="Y21">
-        <v>-6.5992547738548719e-005</v>
+        <v>-0.00010321457883615811</v>
       </c>
       <c r="Z21">
-        <v>-2.2787525922815196e-005</v>
+        <v>-3.2659898003095807e-005</v>
       </c>
       <c r="AA21">
-        <v>2.9245033515769596e-006</v>
+        <v>-4.288569286322138e-005</v>
       </c>
       <c r="AB21">
-        <v>-5.5626315530184851e-005</v>
+        <v>-7.0892266513092978e-005</v>
       </c>
       <c r="AC21">
-        <v>-4.9691836658977609e-005</v>
+        <v>-1.0337927216232375e-005</v>
       </c>
       <c r="AD21">
-        <v>-3.0192516035786901e-005</v>
+        <v>-2.4616680539874497e-005</v>
       </c>
       <c r="AE21">
-        <v>-7.8550287322711994e-006</v>
+        <v>-1.2420097785560322e-005</v>
       </c>
       <c r="AF21">
-        <v>-5.4022103131555791e-005</v>
+        <v>-6.7972506729304749e-005</v>
       </c>
       <c r="AG21">
-        <v>-1.5698463657213261e-005</v>
+        <v>-3.6431199264291717e-005</v>
       </c>
       <c r="AH21">
-        <v>-1.9033411027798229e-005</v>
+        <v>-4.3945520463039664e-005</v>
       </c>
       <c r="AI21">
-        <v>-4.6149880784336248e-005</v>
+        <v>-6.192092835186396e-005</v>
       </c>
       <c r="AJ21">
-        <v>-5.4378512471950875e-005</v>
+        <v>-8.5252838608095932e-005</v>
       </c>
       <c r="AK21">
-        <v>-2.5809870252953043e-005</v>
+        <v>-4.6697600736223953e-005</v>
       </c>
       <c r="AL21">
-        <v>-3.6114845905076305e-006</v>
+        <v>-1.6294092022376403e-006</v>
       </c>
       <c r="AM21">
-        <v>1.0048196464664547e-006</v>
+        <v>-3.0082986885877992e-005</v>
       </c>
       <c r="AN21">
-        <v>3.7290284315279751e-005</v>
+        <v>3.1343774996907443e-005</v>
       </c>
       <c r="AO21">
-        <v>1.0082114372973131e-005</v>
+        <v>-7.1002114972978209e-006</v>
       </c>
       <c r="AP21">
-        <v>-7.1762802134276381e-005</v>
+        <v>-0.00012735181070724398</v>
       </c>
       <c r="AQ21">
-        <v>3.4102191292039114e-005</v>
+        <v>6.7146047269941132e-005</v>
       </c>
       <c r="AR21">
-        <v>-0.00086799851914626702</v>
+        <v>-0.0011898007594459165</v>
       </c>
     </row>
     <row r="22">
@@ -3297,133 +3297,133 @@
         <v>35</v>
       </c>
       <c r="B22">
-        <v>0.25398178301999508</v>
+        <v>0.33836189777750852</v>
       </c>
       <c r="C22">
-        <v>-1.5541816134238613e-005</v>
+        <v>-5.0666231693518638e-005</v>
       </c>
       <c r="D22">
-        <v>-7.6218967627988119e-007</v>
+        <v>-1.1421700110895525e-005</v>
       </c>
       <c r="E22">
-        <v>1.646685843589255e-008</v>
+        <v>1.2814808475640945e-007</v>
       </c>
       <c r="F22">
-        <v>2.8972836161941817e-005</v>
+        <v>-5.5988895563068345e-005</v>
       </c>
       <c r="G22">
-        <v>0.00012326112717946775</v>
+        <v>0.00015747990045400582</v>
       </c>
       <c r="H22">
-        <v>3.8594232514448399e-005</v>
+        <v>-2.4618417597373687e-006</v>
       </c>
       <c r="I22">
-        <v>0.00027936603332839817</v>
+        <v>0.00025648664510740732</v>
       </c>
       <c r="J22">
-        <v>0.00024588971889155236</v>
+        <v>0.00029381187277655962</v>
       </c>
       <c r="K22">
-        <v>0.00017615584213518092</v>
+        <v>0.00016013198282030923</v>
       </c>
       <c r="L22">
-        <v>0.00028707091216008949</v>
+        <v>0.00031256187880037832</v>
       </c>
       <c r="M22">
-        <v>0.00068638645399832427</v>
+        <v>0.001244540787666532</v>
       </c>
       <c r="N22">
-        <v>0.00080236299359988535</v>
+        <v>0.0012113199633241381</v>
       </c>
       <c r="O22">
-        <v>0.00066072389110351302</v>
+        <v>0.00098183880766435929</v>
       </c>
       <c r="P22">
-        <v>6.1233488376941211e-005</v>
+        <v>0.00010391853954084038</v>
       </c>
       <c r="Q22">
-        <v>0.00010243757590374968</v>
+        <v>0.0001373108598322086</v>
       </c>
       <c r="R22">
-        <v>1.425793739530047e-005</v>
+        <v>0.00014302277872261276</v>
       </c>
       <c r="S22">
-        <v>-1.3235927714713896e-006</v>
+        <v>-1.2560250109220201e-006</v>
       </c>
       <c r="T22">
-        <v>-2.2357054536265696e-006</v>
+        <v>-1.7398437729270858e-006</v>
       </c>
       <c r="U22">
-        <v>0.00065979760412394092</v>
+        <v>0.00093434169697037832</v>
       </c>
       <c r="V22">
-        <v>0.00096157558582373316</v>
+        <v>0.0014253922371825095</v>
       </c>
       <c r="W22">
-        <v>0.0013692974214337902</v>
+        <v>0.0019145285500977293</v>
       </c>
       <c r="X22">
-        <v>0.0010968903426359939</v>
+        <v>0.0016191610611042309</v>
       </c>
       <c r="Y22">
-        <v>-6.3265297089636934e-005</v>
+        <v>-9.9254478770523832e-005</v>
       </c>
       <c r="Z22">
-        <v>-3.2905415992433491e-005</v>
+        <v>-3.994251917640722e-005</v>
       </c>
       <c r="AA22">
-        <v>3.9933575660626642e-005</v>
+        <v>7.6307758992014488e-008</v>
       </c>
       <c r="AB22">
-        <v>1.2939583623873085e-006</v>
+        <v>-4.2100027117227077e-006</v>
       </c>
       <c r="AC22">
-        <v>7.6165782903686108e-006</v>
+        <v>5.5323966355177572e-005</v>
       </c>
       <c r="AD22">
-        <v>-4.7607900552067712e-006</v>
+        <v>4.1041610294057716e-006</v>
       </c>
       <c r="AE22">
-        <v>3.3577920639451901e-005</v>
+        <v>3.5000378968972398e-005</v>
       </c>
       <c r="AF22">
-        <v>-1.7032245439057989e-005</v>
+        <v>-3.2886693973134529e-005</v>
       </c>
       <c r="AG22">
-        <v>3.23332139067824e-005</v>
+        <v>1.6235610702650704e-005</v>
       </c>
       <c r="AH22">
-        <v>1.5878163546745055e-005</v>
+        <v>-3.6662179746308565e-006</v>
       </c>
       <c r="AI22">
-        <v>1.5908721903990495e-006</v>
+        <v>1.3189982189747e-007</v>
       </c>
       <c r="AJ22">
-        <v>-3.6660565095516948e-005</v>
+        <v>-6.4705955962645644e-005</v>
       </c>
       <c r="AK22">
-        <v>3.3815551894529183e-005</v>
+        <v>2.5606344078588821e-005</v>
       </c>
       <c r="AL22">
-        <v>-1.6589537495092501e-006</v>
+        <v>1.223786904663973e-006</v>
       </c>
       <c r="AM22">
-        <v>2.3949861344967245e-006</v>
+        <v>-3.3545968427638596e-005</v>
       </c>
       <c r="AN22">
-        <v>4.3464041864935512e-005</v>
+        <v>2.479204403048709e-005</v>
       </c>
       <c r="AO22">
-        <v>3.5758038089570281e-005</v>
+        <v>7.7262241716620278e-006</v>
       </c>
       <c r="AP22">
-        <v>-0.00012217240604241484</v>
+        <v>-0.0001907798999700902</v>
       </c>
       <c r="AQ22">
-        <v>2.6635442568804417e-005</v>
+        <v>5.9091613669990414e-005</v>
       </c>
       <c r="AR22">
-        <v>-0.0010128521456368141</v>
+        <v>-0.0013060491489696115</v>
       </c>
     </row>
     <row r="23">
@@ -3431,133 +3431,133 @@
         <v>36</v>
       </c>
       <c r="B23">
-        <v>0.47398630339657288</v>
+        <v>0.57821775478908677</v>
       </c>
       <c r="C23">
-        <v>-3.6493476949137944e-005</v>
+        <v>-6.7680688689462028e-005</v>
       </c>
       <c r="D23">
-        <v>-3.3611388591390891e-006</v>
+        <v>-1.4565289128997498e-005</v>
       </c>
       <c r="E23">
-        <v>3.1033188124340523e-008</v>
+        <v>1.4559625400088673e-007</v>
       </c>
       <c r="F23">
-        <v>0.0002853464376080234</v>
+        <v>0.00028316271886620701</v>
       </c>
       <c r="G23">
-        <v>0.00025613763376659067</v>
+        <v>0.00037065696543726846</v>
       </c>
       <c r="H23">
-        <v>0.00017521196185679049</v>
+        <v>0.00021564468405084914</v>
       </c>
       <c r="I23">
-        <v>0.0004886531114818792</v>
+        <v>0.00055756887930067658</v>
       </c>
       <c r="J23">
-        <v>0.00041494499568498134</v>
+        <v>0.00053990245059271037</v>
       </c>
       <c r="K23">
-        <v>0.00028939289149326985</v>
+        <v>0.00034642341845914537</v>
       </c>
       <c r="L23">
-        <v>0.00042471603685718197</v>
+        <v>0.00053061406795338717</v>
       </c>
       <c r="M23">
-        <v>0.00060459516710758892</v>
+        <v>0.0012435844642963705</v>
       </c>
       <c r="N23">
-        <v>0.00082892632638236852</v>
+        <v>0.0012343293384560815</v>
       </c>
       <c r="O23">
-        <v>0.00069599738424238429</v>
+        <v>0.0010281791198004781</v>
       </c>
       <c r="P23">
-        <v>0.0001244167354179503</v>
+        <v>0.00016776162462602139</v>
       </c>
       <c r="Q23">
-        <v>0.00018937289710298003</v>
+        <v>0.00023342728825639616</v>
       </c>
       <c r="R23">
-        <v>0.00010074541004779155</v>
+        <v>0.00019563666315527669</v>
       </c>
       <c r="S23">
-        <v>-1.2502282646431542e-006</v>
+        <v>-1.457738535931683e-006</v>
       </c>
       <c r="T23">
-        <v>-2.4719830364674378e-006</v>
+        <v>-1.9782017643194653e-006</v>
       </c>
       <c r="U23">
-        <v>0.00061927698327147226</v>
+        <v>0.00090304424419730732</v>
       </c>
       <c r="V23">
-        <v>0.00095762363059621761</v>
+        <v>0.001438249099318946</v>
       </c>
       <c r="W23">
-        <v>0.0010968903426359939</v>
+        <v>0.0016191610611042309</v>
       </c>
       <c r="X23">
-        <v>0.0016097787199780874</v>
+        <v>0.0022590495903486267</v>
       </c>
       <c r="Y23">
-        <v>-5.6360536731869828e-005</v>
+        <v>-9.2499615380287224e-005</v>
       </c>
       <c r="Z23">
-        <v>-2.0767756289942116e-005</v>
+        <v>-1.9718108388979707e-005</v>
       </c>
       <c r="AA23">
-        <v>5.4727184869604074e-005</v>
+        <v>2.7106839798559084e-005</v>
       </c>
       <c r="AB23">
-        <v>-9.2327657897180648e-006</v>
+        <v>-1.9083401742996217e-005</v>
       </c>
       <c r="AC23">
-        <v>2.1006373226300107e-005</v>
+        <v>8.0001062442423501e-005</v>
       </c>
       <c r="AD23">
-        <v>2.7869249853123326e-005</v>
+        <v>6.6266146997782997e-005</v>
       </c>
       <c r="AE23">
-        <v>5.3708705553035397e-005</v>
+        <v>6.3438348941717289e-005</v>
       </c>
       <c r="AF23">
-        <v>1.8785977616310527e-005</v>
+        <v>3.0704801696259721e-005</v>
       </c>
       <c r="AG23">
-        <v>5.5213051653421288e-005</v>
+        <v>6.1770233905072218e-005</v>
       </c>
       <c r="AH23">
-        <v>5.2945592962918596e-005</v>
+        <v>7.2494043269069968e-005</v>
       </c>
       <c r="AI23">
-        <v>3.0681426331698934e-005</v>
+        <v>5.9057308561918869e-005</v>
       </c>
       <c r="AJ23">
-        <v>-2.0048983944776291e-005</v>
+        <v>-3.990600052266723e-005</v>
       </c>
       <c r="AK23">
-        <v>6.3369757640363285e-005</v>
+        <v>6.1921404085622648e-005</v>
       </c>
       <c r="AL23">
-        <v>-8.092324873794441e-007</v>
+        <v>3.233796564268025e-006</v>
       </c>
       <c r="AM23">
-        <v>1.2172442310589594e-006</v>
+        <v>-3.6071372926431856e-005</v>
       </c>
       <c r="AN23">
-        <v>3.2950879794847233e-005</v>
+        <v>3.1095124272513151e-005</v>
       </c>
       <c r="AO23">
-        <v>4.5807146495905606e-005</v>
+        <v>3.6381671166443971e-006</v>
       </c>
       <c r="AP23">
-        <v>0.0001422823147644082</v>
+        <v>0.00011680430192955864</v>
       </c>
       <c r="AQ23">
-        <v>4.7202699598200104e-006</v>
+        <v>1.847634351199339e-005</v>
       </c>
       <c r="AR23">
-        <v>-0.0011496104685229536</v>
+        <v>-0.0015469890464635779</v>
       </c>
     </row>
     <row r="24">
@@ -3565,133 +3565,133 @@
         <v>37</v>
       </c>
       <c r="B24">
-        <v>0.025221581784877985</v>
+        <v>0.025332245207594532</v>
       </c>
       <c r="C24">
-        <v>1.0736937851375664e-006</v>
+        <v>1.9172472073785821e-006</v>
       </c>
       <c r="D24">
-        <v>-5.499356484356939e-007</v>
+        <v>-4.0173526973749299e-007</v>
       </c>
       <c r="E24">
-        <v>-5.3778849829135753e-011</v>
+        <v>-1.8348439949019265e-009</v>
       </c>
       <c r="F24">
-        <v>-2.2519425623303467e-006</v>
+        <v>3.8247655731721304e-006</v>
       </c>
       <c r="G24">
-        <v>-9.7176991831581803e-006</v>
+        <v>-7.8086964854894302e-006</v>
       </c>
       <c r="H24">
-        <v>5.6575211164803647e-006</v>
+        <v>1.1453377564667509e-005</v>
       </c>
       <c r="I24">
-        <v>-2.7585878730862785e-006</v>
+        <v>5.334721430239551e-006</v>
       </c>
       <c r="J24">
-        <v>-2.2304105266666879e-007</v>
+        <v>2.8737524549438014e-006</v>
       </c>
       <c r="K24">
-        <v>-4.156649014962588e-006</v>
+        <v>-4.8224622873501432e-007</v>
       </c>
       <c r="L24">
-        <v>-1.7437623491682887e-005</v>
+        <v>-1.5698585313602546e-005</v>
       </c>
       <c r="M24">
-        <v>-4.8263989154144534e-005</v>
+        <v>-7.7535588980698084e-005</v>
       </c>
       <c r="N24">
-        <v>-4.3093164585602338e-005</v>
+        <v>-7.2422524511325288e-005</v>
       </c>
       <c r="O24">
-        <v>-5.9789770551377431e-005</v>
+        <v>-8.3327383696171092e-005</v>
       </c>
       <c r="P24">
-        <v>2.8463343521252781e-006</v>
+        <v>-5.759060063784046e-007</v>
       </c>
       <c r="Q24">
-        <v>1.0951415106172347e-005</v>
+        <v>7.5993245916347912e-006</v>
       </c>
       <c r="R24">
-        <v>1.185429778187645e-005</v>
+        <v>-9.6685720339629898e-006</v>
       </c>
       <c r="S24">
-        <v>-5.1392670570253004e-008</v>
+        <v>-2.6198855942942262e-008</v>
       </c>
       <c r="T24">
-        <v>4.9570348641423301e-008</v>
+        <v>4.9522192939229459e-008</v>
       </c>
       <c r="U24">
-        <v>-5.3703166632165379e-005</v>
+        <v>-7.9295951572697855e-005</v>
       </c>
       <c r="V24">
-        <v>-6.5992547738548719e-005</v>
+        <v>-0.00010321457883615811</v>
       </c>
       <c r="W24">
-        <v>-6.3265297089636934e-005</v>
+        <v>-9.9254478770523832e-005</v>
       </c>
       <c r="X24">
-        <v>-5.6360536731869828e-005</v>
+        <v>-9.2499615380287224e-005</v>
       </c>
       <c r="Y24">
-        <v>1.5248662504811043e-005</v>
+        <v>1.8384296100941413e-005</v>
       </c>
       <c r="Z24">
-        <v>-3.1902130174293674e-006</v>
+        <v>-3.8476829746095646e-006</v>
       </c>
       <c r="AA24">
-        <v>3.6835541923056735e-006</v>
+        <v>5.492820011553154e-006</v>
       </c>
       <c r="AB24">
-        <v>5.373758368500831e-006</v>
+        <v>6.3134423785058351e-006</v>
       </c>
       <c r="AC24">
-        <v>2.1150063819015847e-007</v>
+        <v>1.8377217868794636e-006</v>
       </c>
       <c r="AD24">
-        <v>2.4246350945414608e-006</v>
+        <v>1.6504408618961196e-006</v>
       </c>
       <c r="AE24">
-        <v>5.3141280559835419e-006</v>
+        <v>5.0821490929837811e-006</v>
       </c>
       <c r="AF24">
-        <v>5.910953883521034e-006</v>
+        <v>6.9324461777779794e-006</v>
       </c>
       <c r="AG24">
-        <v>-1.3335409566129502e-006</v>
+        <v>9.4406532682533979e-007</v>
       </c>
       <c r="AH24">
-        <v>1.8602886005732109e-006</v>
+        <v>2.543888677239866e-006</v>
       </c>
       <c r="AI24">
-        <v>4.2954688641642587e-006</v>
+        <v>5.5325639065215473e-006</v>
       </c>
       <c r="AJ24">
-        <v>6.8825686854774799e-006</v>
+        <v>7.6531177090155907e-006</v>
       </c>
       <c r="AK24">
-        <v>7.8360982931844616e-006</v>
+        <v>9.3274257843658481e-006</v>
       </c>
       <c r="AL24">
-        <v>8.9451254721847559e-008</v>
+        <v>8.1572801357504765e-008</v>
       </c>
       <c r="AM24">
-        <v>4.7184293760651032e-006</v>
+        <v>6.7178253239322673e-006</v>
       </c>
       <c r="AN24">
-        <v>3.1818560463067259e-006</v>
+        <v>3.1385165109328633e-006</v>
       </c>
       <c r="AO24">
-        <v>2.7631707915406007e-006</v>
+        <v>2.6593975610107229e-006</v>
       </c>
       <c r="AP24">
-        <v>1.0003287084237739e-005</v>
+        <v>9.2676325506488142e-006</v>
       </c>
       <c r="AQ24">
-        <v>1.5247869565932259e-005</v>
+        <v>1.4885622350689095e-005</v>
       </c>
       <c r="AR24">
-        <v>6.9545374660529664e-005</v>
+        <v>9.6391757175422248e-005</v>
       </c>
     </row>
     <row r="25">
@@ -3699,133 +3699,133 @@
         <v>38</v>
       </c>
       <c r="B25">
-        <v>3.7359929106782239</v>
+        <v>3.7629327198538025</v>
       </c>
       <c r="C25">
-        <v>3.8632667670828027e-006</v>
+        <v>4.9133748646457759e-006</v>
       </c>
       <c r="D25">
-        <v>1.0170225143241933e-006</v>
+        <v>1.6528686182612116e-006</v>
       </c>
       <c r="E25">
-        <v>-2.552668159549023e-008</v>
+        <v>-3.1040478989826164e-008</v>
       </c>
       <c r="F25">
-        <v>7.2623294855599964e-005</v>
+        <v>7.7175228406035532e-005</v>
       </c>
       <c r="G25">
-        <v>-4.2109259147220067e-005</v>
+        <v>-3.9563504319354832e-005</v>
       </c>
       <c r="H25">
-        <v>-4.9061241805649678e-005</v>
+        <v>-5.1553080450806416e-005</v>
       </c>
       <c r="I25">
-        <v>2.8352229360092539e-005</v>
+        <v>-2.1069270456002345e-005</v>
       </c>
       <c r="J25">
-        <v>-2.8701241675033184e-005</v>
+        <v>-2.9279214136346786e-005</v>
       </c>
       <c r="K25">
-        <v>-2.802475643151099e-005</v>
+        <v>-3.4067901259253897e-005</v>
       </c>
       <c r="L25">
-        <v>8.6419694683554618e-006</v>
+        <v>9.4514353176459185e-006</v>
       </c>
       <c r="M25">
-        <v>-0.00010453867013011226</v>
+        <v>-0.0001127040533805369</v>
       </c>
       <c r="N25">
-        <v>-8.9714795900230557e-006</v>
+        <v>-1.5189057460102194e-005</v>
       </c>
       <c r="O25">
-        <v>6.3922222322539504e-006</v>
+        <v>1.1081674890348709e-005</v>
       </c>
       <c r="P25">
-        <v>-2.0145298515756715e-006</v>
+        <v>-3.0115007396594559e-006</v>
       </c>
       <c r="Q25">
-        <v>2.3796591476535014e-005</v>
+        <v>1.9829827945221025e-005</v>
       </c>
       <c r="R25">
-        <v>1.3190672542102793e-005</v>
+        <v>4.6467771264812718e-006</v>
       </c>
       <c r="S25">
-        <v>-6.8123807194000929e-007</v>
+        <v>-7.2403600792762224e-007</v>
       </c>
       <c r="T25">
-        <v>-3.2664595383561887e-007</v>
+        <v>-4.0966996353986499e-007</v>
       </c>
       <c r="U25">
-        <v>-1.6816515901543554e-005</v>
+        <v>-2.483725332290659e-005</v>
       </c>
       <c r="V25">
-        <v>-2.2787525922815196e-005</v>
+        <v>-3.2659898003095807e-005</v>
       </c>
       <c r="W25">
-        <v>-3.2905415992433491e-005</v>
+        <v>-3.994251917640722e-005</v>
       </c>
       <c r="X25">
-        <v>-2.0767756289942116e-005</v>
+        <v>-1.9718108388979707e-005</v>
       </c>
       <c r="Y25">
-        <v>-3.1902130174293674e-006</v>
+        <v>-3.8476829746095646e-006</v>
       </c>
       <c r="Z25">
-        <v>0.00033326184451792798</v>
+        <v>0.00036115170827494958</v>
       </c>
       <c r="AA25">
-        <v>8.8479286341839391e-006</v>
+        <v>1.8867667497290179e-005</v>
       </c>
       <c r="AB25">
-        <v>2.5137999717867585e-005</v>
+        <v>3.2410306295986387e-005</v>
       </c>
       <c r="AC25">
-        <v>2.7678084023200529e-007</v>
+        <v>1.2464750887375996e-005</v>
       </c>
       <c r="AD25">
-        <v>-1.3492602416699446e-005</v>
+        <v>-3.8485784119720351e-006</v>
       </c>
       <c r="AE25">
-        <v>-1.8650286154376622e-005</v>
+        <v>-1.4497062607255772e-005</v>
       </c>
       <c r="AF25">
-        <v>1.2260936122236334e-005</v>
+        <v>1.8674528758030312e-005</v>
       </c>
       <c r="AG25">
-        <v>9.1560773110160757e-006</v>
+        <v>1.0898978086052061e-005</v>
       </c>
       <c r="AH25">
-        <v>1.739880310280001e-005</v>
+        <v>3.6729566786976938e-005</v>
       </c>
       <c r="AI25">
-        <v>2.3539982962205941e-006</v>
+        <v>1.1208741863025789e-005</v>
       </c>
       <c r="AJ25">
-        <v>2.2620832609368221e-005</v>
+        <v>2.7192284001170244e-005</v>
       </c>
       <c r="AK25">
-        <v>2.4682039530958024e-005</v>
+        <v>3.8810514857990052e-005</v>
       </c>
       <c r="AL25">
-        <v>-2.3954864016779782e-006</v>
+        <v>-2.2410219462174139e-006</v>
       </c>
       <c r="AM25">
-        <v>1.8321008126630678e-005</v>
+        <v>2.0566109562185455e-005</v>
       </c>
       <c r="AN25">
-        <v>2.0709937472939272e-005</v>
+        <v>8.5543599476870262e-006</v>
       </c>
       <c r="AO25">
-        <v>2.2584203542119543e-005</v>
+        <v>1.7994488680800379e-005</v>
       </c>
       <c r="AP25">
-        <v>3.4339578234846572e-005</v>
+        <v>5.6032212269172835e-005</v>
       </c>
       <c r="AQ25">
-        <v>1.833381811899894e-006</v>
+        <v>3.2310732276846345e-006</v>
       </c>
       <c r="AR25">
-        <v>-3.9696038262219755e-005</v>
+        <v>-6.246885734528862e-005</v>
       </c>
     </row>
     <row r="26">
@@ -3833,133 +3833,133 @@
         <v>39</v>
       </c>
       <c r="B26">
-        <v>0.099469406099229052</v>
+        <v>0.12817871214002283</v>
       </c>
       <c r="C26">
-        <v>4.9919296051714422e-006</v>
+        <v>1.4586778808205605e-005</v>
       </c>
       <c r="D26">
-        <v>-6.2496400249413236e-007</v>
+        <v>1.1045635412607635e-006</v>
       </c>
       <c r="E26">
-        <v>8.9551859007246444e-009</v>
+        <v>-5.1573874919431026e-009</v>
       </c>
       <c r="F26">
-        <v>-4.8467977757201967e-005</v>
+        <v>-2.09485669032236e-005</v>
       </c>
       <c r="G26">
-        <v>-7.043881872992166e-006</v>
+        <v>2.1099303147705569e-005</v>
       </c>
       <c r="H26">
-        <v>-3.9345163549354937e-005</v>
+        <v>-3.0852490993212906e-005</v>
       </c>
       <c r="I26">
-        <v>-4.9004460596212721e-005</v>
+        <v>-3.8454813066869875e-005</v>
       </c>
       <c r="J26">
-        <v>5.2585453892579553e-006</v>
+        <v>2.8316877733636889e-005</v>
       </c>
       <c r="K26">
-        <v>7.4395120156806076e-006</v>
+        <v>5.4067773522827763e-005</v>
       </c>
       <c r="L26">
-        <v>-5.7920386536971879e-006</v>
+        <v>2.8939937073308044e-005</v>
       </c>
       <c r="M26">
-        <v>2.8371905887127346e-005</v>
+        <v>-4.5786824760092062e-005</v>
       </c>
       <c r="N26">
-        <v>2.3917894514836709e-005</v>
+        <v>-2.381389980264713e-005</v>
       </c>
       <c r="O26">
-        <v>-2.8053505016801839e-005</v>
+        <v>-6.393419503143149e-005</v>
       </c>
       <c r="P26">
-        <v>-2.4570342923778678e-005</v>
+        <v>-2.799545736193258e-005</v>
       </c>
       <c r="Q26">
-        <v>-8.4201781252286282e-007</v>
+        <v>-1.4529425622065881e-006</v>
       </c>
       <c r="R26">
-        <v>-1.2364235595923689e-005</v>
+        <v>4.2708286761512158e-007</v>
       </c>
       <c r="S26">
-        <v>1.6263743121030536e-006</v>
+        <v>1.9879628997550427e-006</v>
       </c>
       <c r="T26">
-        <v>1.2233373175113052e-006</v>
+        <v>1.5652263061771817e-006</v>
       </c>
       <c r="U26">
-        <v>1.5171756706226129e-006</v>
+        <v>-3.076897877102392e-005</v>
       </c>
       <c r="V26">
-        <v>2.9245033515769596e-006</v>
+        <v>-4.288569286322138e-005</v>
       </c>
       <c r="W26">
-        <v>3.9933575660626642e-005</v>
+        <v>7.6307758992014488e-008</v>
       </c>
       <c r="X26">
-        <v>5.4727184869604074e-005</v>
+        <v>2.7106839798559084e-005</v>
       </c>
       <c r="Y26">
-        <v>3.6835541923056735e-006</v>
+        <v>5.492820011553154e-006</v>
       </c>
       <c r="Z26">
-        <v>8.8479286341839391e-006</v>
+        <v>1.8867667497290179e-005</v>
       </c>
       <c r="AA26">
-        <v>0.0016563484694491961</v>
+        <v>0.0017520960258131846</v>
       </c>
       <c r="AB26">
-        <v>0.00069585605019522494</v>
+        <v>0.00076582610333398042</v>
       </c>
       <c r="AC26">
-        <v>0.00067358666873452869</v>
+        <v>0.0007416764676055485</v>
       </c>
       <c r="AD26">
-        <v>0.00068244090518800797</v>
+        <v>0.00074161030818948844</v>
       </c>
       <c r="AE26">
-        <v>0.00065154166127628964</v>
+        <v>0.00071419180411844835</v>
       </c>
       <c r="AF26">
-        <v>0.00068578998808925616</v>
+        <v>0.0007538483389272657</v>
       </c>
       <c r="AG26">
-        <v>0.00070232558595874741</v>
+        <v>0.00077345142835916268</v>
       </c>
       <c r="AH26">
-        <v>0.00068653732181760173</v>
+        <v>0.00076783116940227374</v>
       </c>
       <c r="AI26">
-        <v>0.00068144453949511386</v>
+        <v>0.00075508385658314625</v>
       </c>
       <c r="AJ26">
-        <v>0.00068719379599146773</v>
+        <v>0.0007535264710489748</v>
       </c>
       <c r="AK26">
-        <v>0.0006966720097199892</v>
+        <v>0.00076262389974661329</v>
       </c>
       <c r="AL26">
-        <v>5.6910552416185138e-007</v>
+        <v>-4.185880501603325e-007</v>
       </c>
       <c r="AM26">
-        <v>5.7986871772275296e-006</v>
+        <v>1.0153964018569367e-005</v>
       </c>
       <c r="AN26">
-        <v>-4.6708153033118337e-005</v>
+        <v>-2.9249240436185031e-005</v>
       </c>
       <c r="AO26">
-        <v>0.00034625239569195806</v>
+        <v>0.00040667310985996778</v>
       </c>
       <c r="AP26">
-        <v>0.00045606386192649073</v>
+        <v>0.00042653613757206023</v>
       </c>
       <c r="AQ26">
-        <v>0.00015679943667678889</v>
+        <v>0.0001801290143543884</v>
       </c>
       <c r="AR26">
-        <v>-0.00084337222398017089</v>
+        <v>-0.00097135406621512844</v>
       </c>
     </row>
     <row r="27">
@@ -3967,133 +3967,133 @@
         <v>40</v>
       </c>
       <c r="B27">
-        <v>0.20543235087343747</v>
+        <v>0.21540611465986548</v>
       </c>
       <c r="C27">
-        <v>2.7658233922800067e-005</v>
+        <v>4.8348325666041706e-005</v>
       </c>
       <c r="D27">
-        <v>1.0889288606136084e-006</v>
+        <v>1.9078451432136867e-006</v>
       </c>
       <c r="E27">
-        <v>-1.2534074504177438e-008</v>
+        <v>-2.1319695933760214e-008</v>
       </c>
       <c r="F27">
-        <v>3.450724360467975e-005</v>
+        <v>7.4816698394393651e-005</v>
       </c>
       <c r="G27">
-        <v>3.4943920739572077e-005</v>
+        <v>5.8517165327780555e-005</v>
       </c>
       <c r="H27">
-        <v>-1.7931724332668038e-005</v>
+        <v>-7.1957525722399739e-006</v>
       </c>
       <c r="I27">
-        <v>-1.3380512365986021e-005</v>
+        <v>-1.7163599744755864e-005</v>
       </c>
       <c r="J27">
-        <v>-3.0288749601091192e-005</v>
+        <v>-2.4321333586669518e-005</v>
       </c>
       <c r="K27">
-        <v>4.5771244717234005e-005</v>
+        <v>7.6244204832872503e-005</v>
       </c>
       <c r="L27">
-        <v>9.9785747238746161e-006</v>
+        <v>3.6558440500630341e-005</v>
       </c>
       <c r="M27">
-        <v>1.4875480513473977e-005</v>
+        <v>-7.5309339545896032e-005</v>
       </c>
       <c r="N27">
-        <v>-4.4716938946902146e-005</v>
+        <v>-6.7511640797502e-005</v>
       </c>
       <c r="O27">
-        <v>-6.3320116264522488e-005</v>
+        <v>-8.0433865819956455e-005</v>
       </c>
       <c r="P27">
-        <v>-2.277922762833043e-005</v>
+        <v>-3.5894578389401049e-005</v>
       </c>
       <c r="Q27">
-        <v>-1.838687861698926e-005</v>
+        <v>-3.1162968217501695e-005</v>
       </c>
       <c r="R27">
-        <v>-8.8603271498986384e-005</v>
+        <v>1.5711229592522443e-005</v>
       </c>
       <c r="S27">
-        <v>5.8501440745486238e-007</v>
+        <v>4.7712506940220115e-007</v>
       </c>
       <c r="T27">
-        <v>1.5520074841212529e-006</v>
+        <v>1.8042953125036854e-006</v>
       </c>
       <c r="U27">
-        <v>-2.0912221383999612e-005</v>
+        <v>-2.4992711963683965e-005</v>
       </c>
       <c r="V27">
-        <v>-5.5626315530184851e-005</v>
+        <v>-7.0892266513092978e-005</v>
       </c>
       <c r="W27">
-        <v>1.2939583623873085e-006</v>
+        <v>-4.2100027117227077e-006</v>
       </c>
       <c r="X27">
-        <v>-9.2327657897180648e-006</v>
+        <v>-1.9083401742996217e-005</v>
       </c>
       <c r="Y27">
-        <v>5.373758368500831e-006</v>
+        <v>6.3134423785058351e-006</v>
       </c>
       <c r="Z27">
-        <v>2.5137999717867585e-005</v>
+        <v>3.2410306295986387e-005</v>
       </c>
       <c r="AA27">
-        <v>0.00069585605019522494</v>
+        <v>0.00076582610333398042</v>
       </c>
       <c r="AB27">
-        <v>0.0012896184358892474</v>
+        <v>0.0014817686315319303</v>
       </c>
       <c r="AC27">
-        <v>0.00067329030952174179</v>
+        <v>0.00074430609589742241</v>
       </c>
       <c r="AD27">
-        <v>0.0006847065960271431</v>
+        <v>0.00075207796468486202</v>
       </c>
       <c r="AE27">
-        <v>0.00064502989637527466</v>
+        <v>0.0007105221784815337</v>
       </c>
       <c r="AF27">
-        <v>0.00069237294302422795</v>
+        <v>0.0007629490986268265</v>
       </c>
       <c r="AG27">
-        <v>0.00069644340451890886</v>
+        <v>0.00077085599380908307</v>
       </c>
       <c r="AH27">
-        <v>0.00069005587690615226</v>
+        <v>0.00077824357656879723</v>
       </c>
       <c r="AI27">
-        <v>0.00068386397236017236</v>
+        <v>0.00076365159117512628</v>
       </c>
       <c r="AJ27">
-        <v>0.0006807792292058577</v>
+        <v>0.00075392067678132406</v>
       </c>
       <c r="AK27">
-        <v>0.00069094269961033781</v>
+        <v>0.00076775634214041276</v>
       </c>
       <c r="AL27">
-        <v>7.2697627449898366e-006</v>
+        <v>8.2812427561535824e-006</v>
       </c>
       <c r="AM27">
-        <v>2.034791693589146e-006</v>
+        <v>-2.7424139002368332e-006</v>
       </c>
       <c r="AN27">
-        <v>-4.0369927433161795e-005</v>
+        <v>-3.7753771744656071e-005</v>
       </c>
       <c r="AO27">
-        <v>0.00047547721163142227</v>
+        <v>0.00056897941243370031</v>
       </c>
       <c r="AP27">
-        <v>0.00032385066478538775</v>
+        <v>0.00034086033844387586</v>
       </c>
       <c r="AQ27">
-        <v>0.00017284238330720681</v>
+        <v>0.00019285211886811151</v>
       </c>
       <c r="AR27">
-        <v>-0.0009463620560112015</v>
+        <v>-0.0010810131861802076</v>
       </c>
     </row>
     <row r="28">
@@ -4101,133 +4101,133 @@
         <v>41</v>
       </c>
       <c r="B28">
-        <v>0.1755134776737266</v>
+        <v>0.18614353591487351</v>
       </c>
       <c r="C28">
-        <v>-1.6923119529012594e-005</v>
+        <v>4.1662813292447448e-006</v>
       </c>
       <c r="D28">
-        <v>-4.2552124166550009e-006</v>
+        <v>-1.5330894462409858e-006</v>
       </c>
       <c r="E28">
-        <v>5.5355775858361458e-008</v>
+        <v>2.0522970470851614e-008</v>
       </c>
       <c r="F28">
-        <v>5.1066092595635683e-005</v>
+        <v>7.9931594919426674e-005</v>
       </c>
       <c r="G28">
-        <v>6.605026595133602e-005</v>
+        <v>6.1187453167548282e-005</v>
       </c>
       <c r="H28">
-        <v>5.541971389223609e-006</v>
+        <v>1.1450031033868049e-005</v>
       </c>
       <c r="I28">
-        <v>0.00010916740218480557</v>
+        <v>9.8732372083621119e-005</v>
       </c>
       <c r="J28">
-        <v>6.9362526257207168e-005</v>
+        <v>8.7419944024424398e-005</v>
       </c>
       <c r="K28">
-        <v>5.9435937056824797e-005</v>
+        <v>0.0001075158168526052</v>
       </c>
       <c r="L28">
-        <v>2.2422144470807899e-005</v>
+        <v>5.2709697111056895e-005</v>
       </c>
       <c r="M28">
-        <v>-2.6634179705862512e-005</v>
+        <v>-2.1817353218621572e-005</v>
       </c>
       <c r="N28">
-        <v>3.7485144180460618e-006</v>
+        <v>2.4144081687174011e-005</v>
       </c>
       <c r="O28">
-        <v>-4.7082137800893737e-005</v>
+        <v>-2.6517319736276779e-005</v>
       </c>
       <c r="P28">
-        <v>-2.7875408808096163e-005</v>
+        <v>-2.113688565160433e-005</v>
       </c>
       <c r="Q28">
-        <v>-5.3632916983847596e-005</v>
+        <v>-3.374909157595717e-005</v>
       </c>
       <c r="R28">
-        <v>-4.3934063515557725e-005</v>
+        <v>-2.1759828669103873e-005</v>
       </c>
       <c r="S28">
-        <v>1.8761626655150252e-006</v>
+        <v>1.3741449696128293e-006</v>
       </c>
       <c r="T28">
-        <v>1.7490863628047759e-006</v>
+        <v>1.7997576982976277e-006</v>
       </c>
       <c r="U28">
-        <v>-3.7736126974272059e-005</v>
+        <v>6.0764066150467282e-006</v>
       </c>
       <c r="V28">
-        <v>-4.9691836658977609e-005</v>
+        <v>-1.0337927216232375e-005</v>
       </c>
       <c r="W28">
-        <v>7.6165782903686108e-006</v>
+        <v>5.5323966355177572e-005</v>
       </c>
       <c r="X28">
-        <v>2.1006373226300107e-005</v>
+        <v>8.0001062442423501e-005</v>
       </c>
       <c r="Y28">
-        <v>2.1150063819015847e-007</v>
+        <v>1.8377217868794636e-006</v>
       </c>
       <c r="Z28">
-        <v>2.7678084023200529e-007</v>
+        <v>1.2464750887375996e-005</v>
       </c>
       <c r="AA28">
-        <v>0.00067358666873452869</v>
+        <v>0.0007416764676055485</v>
       </c>
       <c r="AB28">
-        <v>0.00067329030952174179</v>
+        <v>0.00074430609589742241</v>
       </c>
       <c r="AC28">
-        <v>0.0013158962994416425</v>
+        <v>0.0014255880896480672</v>
       </c>
       <c r="AD28">
-        <v>0.00067438622716039717</v>
+        <v>0.00073421016262355818</v>
       </c>
       <c r="AE28">
-        <v>0.00063772197763787989</v>
+        <v>0.00070152838912274085</v>
       </c>
       <c r="AF28">
-        <v>0.00067652558207601746</v>
+        <v>0.00074112676630128224</v>
       </c>
       <c r="AG28">
-        <v>0.00068507848671234424</v>
+        <v>0.00075674723407687875</v>
       </c>
       <c r="AH28">
-        <v>0.00067223962469098474</v>
+        <v>0.00075773118476117531</v>
       </c>
       <c r="AI28">
-        <v>0.00067516449665185713</v>
+        <v>0.00075415647031044268</v>
       </c>
       <c r="AJ28">
-        <v>0.00066406858941643696</v>
+        <v>0.00073417708710036113</v>
       </c>
       <c r="AK28">
-        <v>0.00067672324313192568</v>
+        <v>0.00074810463871088516</v>
       </c>
       <c r="AL28">
-        <v>1.7398932839757383e-006</v>
+        <v>-1.3054637036469474e-006</v>
       </c>
       <c r="AM28">
-        <v>4.1726784370255419e-005</v>
+        <v>6.3257219955537448e-005</v>
       </c>
       <c r="AN28">
-        <v>-3.3144436351797014e-006</v>
+        <v>3.9561312607833414e-005</v>
       </c>
       <c r="AO28">
-        <v>0.00030755465578035653</v>
+        <v>0.00036911767534070157</v>
       </c>
       <c r="AP28">
-        <v>0.00032796529678440504</v>
+        <v>0.0003493078803809193</v>
       </c>
       <c r="AQ28">
-        <v>0.00012984242396120107</v>
+        <v>0.00014827495259978966</v>
       </c>
       <c r="AR28">
-        <v>-0.00081244812388351858</v>
+        <v>-0.00095530970503672149</v>
       </c>
     </row>
     <row r="29">
@@ -4235,133 +4235,133 @@
         <v>42</v>
       </c>
       <c r="B29">
-        <v>0.22446663231642017</v>
+        <v>0.2343467889093348</v>
       </c>
       <c r="C29">
-        <v>1.4568062109066573e-006</v>
+        <v>1.7452870443351564e-005</v>
       </c>
       <c r="D29">
-        <v>1.1252972455124169e-006</v>
+        <v>1.6505894576776775e-006</v>
       </c>
       <c r="E29">
-        <v>-5.3275426812384167e-009</v>
+        <v>-1.163196309365136e-008</v>
       </c>
       <c r="F29">
-        <v>8.8653499255903552e-005</v>
+        <v>0.00013480050484371357</v>
       </c>
       <c r="G29">
-        <v>2.6523328342246719e-005</v>
+        <v>6.5405406941513786e-005</v>
       </c>
       <c r="H29">
-        <v>4.4134205847152347e-006</v>
+        <v>1.4892552454762322e-005</v>
       </c>
       <c r="I29">
-        <v>2.896481767935846e-005</v>
+        <v>0.00019982728928884206</v>
       </c>
       <c r="J29">
-        <v>4.2868266510759408e-005</v>
+        <v>8.5762330607335748e-005</v>
       </c>
       <c r="K29">
-        <v>4.5539398515967207e-005</v>
+        <v>9.6352853455409658e-005</v>
       </c>
       <c r="L29">
-        <v>6.6042232922931975e-005</v>
+        <v>0.00011795259458065728</v>
       </c>
       <c r="M29">
-        <v>-1.2779151844084677e-005</v>
+        <v>-2.2707777568890011e-005</v>
       </c>
       <c r="N29">
-        <v>-9.4553784114425991e-006</v>
+        <v>-6.8561985376150185e-006</v>
       </c>
       <c r="O29">
-        <v>-1.7031096058253325e-005</v>
+        <v>-5.4597090472370632e-006</v>
       </c>
       <c r="P29">
-        <v>-3.3908035623789632e-005</v>
+        <v>-4.7830291953542181e-005</v>
       </c>
       <c r="Q29">
-        <v>-4.4694368098089833e-005</v>
+        <v>-5.8310482600679141e-005</v>
       </c>
       <c r="R29">
-        <v>-2.0145822864561728e-005</v>
+        <v>-1.7816854081849041e-005</v>
       </c>
       <c r="S29">
-        <v>1.2574698949771415e-006</v>
+        <v>1.3792963263199738e-006</v>
       </c>
       <c r="T29">
-        <v>9.8522883859277706e-007</v>
+        <v>9.7846385221225734e-007</v>
       </c>
       <c r="U29">
-        <v>-2.6679572799916676e-005</v>
+        <v>-2.2832336034873248e-005</v>
       </c>
       <c r="V29">
-        <v>-3.0192516035786901e-005</v>
+        <v>-2.4616680539874497e-005</v>
       </c>
       <c r="W29">
-        <v>-4.7607900552067712e-006</v>
+        <v>4.1041610294057716e-006</v>
       </c>
       <c r="X29">
-        <v>2.7869249853123326e-005</v>
+        <v>6.6266146997782997e-005</v>
       </c>
       <c r="Y29">
-        <v>2.4246350945414608e-006</v>
+        <v>1.6504408618961196e-006</v>
       </c>
       <c r="Z29">
-        <v>-1.3492602416699446e-005</v>
+        <v>-3.8485784119720351e-006</v>
       </c>
       <c r="AA29">
-        <v>0.00068244090518800797</v>
+        <v>0.00074161030818948844</v>
       </c>
       <c r="AB29">
-        <v>0.0006847065960271431</v>
+        <v>0.00075207796468486202</v>
       </c>
       <c r="AC29">
-        <v>0.00067438622716039717</v>
+        <v>0.00073421016262355818</v>
       </c>
       <c r="AD29">
-        <v>0.0013330635966773508</v>
+        <v>0.0014781135402534521</v>
       </c>
       <c r="AE29">
-        <v>0.00064358755169237813</v>
+        <v>0.00070369050325878326</v>
       </c>
       <c r="AF29">
-        <v>0.00067632480718764329</v>
+        <v>0.00073306539195586444</v>
       </c>
       <c r="AG29">
-        <v>0.00069218446652036226</v>
+        <v>0.0007549982872926609</v>
       </c>
       <c r="AH29">
-        <v>0.00067530070810414985</v>
+        <v>0.00075190355026618445</v>
       </c>
       <c r="AI29">
-        <v>0.00068223286505812838</v>
+        <v>0.00075452145079943692</v>
       </c>
       <c r="AJ29">
-        <v>0.00066578822256154759</v>
+        <v>0.00072410759392834572</v>
       </c>
       <c r="AK29">
-        <v>0.00068334560606015185</v>
+        <v>0.00074700902868599886</v>
       </c>
       <c r="AL29">
-        <v>1.055768868937731e-006</v>
+        <v>-2.0205520996701917e-007</v>
       </c>
       <c r="AM29">
-        <v>3.6530697835527432e-005</v>
+        <v>3.8669777341555943e-005</v>
       </c>
       <c r="AN29">
-        <v>-4.3282254485336324e-005</v>
+        <v>-1.3648641224538855e-006</v>
       </c>
       <c r="AO29">
-        <v>0.0002972152685853544</v>
+        <v>0.00034527432085628524</v>
       </c>
       <c r="AP29">
-        <v>0.00033421090781490966</v>
+        <v>0.00035063666474183312</v>
       </c>
       <c r="AQ29">
-        <v>0.00011865249555428333</v>
+        <v>0.00013240843373502206</v>
       </c>
       <c r="AR29">
-        <v>-0.00083425548594079346</v>
+        <v>-0.00094956294404000907</v>
       </c>
     </row>
     <row r="30">
@@ -4369,133 +4369,133 @@
         <v>43</v>
       </c>
       <c r="B30">
-        <v>0.24248121377421164</v>
+        <v>0.25168116116828909</v>
       </c>
       <c r="C30">
-        <v>-9.2876138578380972e-006</v>
+        <v>6.6743433041048662e-006</v>
       </c>
       <c r="D30">
-        <v>-1.4378485627170886e-006</v>
+        <v>-1.7110537181407257e-006</v>
       </c>
       <c r="E30">
-        <v>2.7698618000959086e-008</v>
+        <v>3.1711804310644824e-008</v>
       </c>
       <c r="F30">
-        <v>0.00012732946475200812</v>
+        <v>0.00015314337615946578</v>
       </c>
       <c r="G30">
-        <v>-2.3277222436022198e-005</v>
+        <v>-2.4563141838224883e-005</v>
       </c>
       <c r="H30">
-        <v>-5.2557039161334743e-006</v>
+        <v>7.7127984679595263e-006</v>
       </c>
       <c r="I30">
-        <v>-5.3213363051345829e-005</v>
+        <v>-1.7878381275420043e-005</v>
       </c>
       <c r="J30">
-        <v>3.2356629745811799e-005</v>
+        <v>4.6440425210770724e-005</v>
       </c>
       <c r="K30">
-        <v>3.8544863051353476e-005</v>
+        <v>6.154551878967922e-005</v>
       </c>
       <c r="L30">
-        <v>-1.8421843753382611e-005</v>
+        <v>1.3167178215708593e-007</v>
       </c>
       <c r="M30">
-        <v>-7.8284291509899523e-006</v>
+        <v>-1.5651849468180466e-005</v>
       </c>
       <c r="N30">
-        <v>3.6530063503372704e-005</v>
+        <v>5.0829659946405098e-005</v>
       </c>
       <c r="O30">
-        <v>-1.5585977240371992e-005</v>
+        <v>-1.6961982026322906e-005</v>
       </c>
       <c r="P30">
-        <v>-2.5186920921054617e-005</v>
+        <v>-3.3215351931366393e-005</v>
       </c>
       <c r="Q30">
-        <v>2.5991419842010281e-007</v>
+        <v>-3.6232512181531211e-006</v>
       </c>
       <c r="R30">
-        <v>-2.7473614082384497e-005</v>
+        <v>-4.9939853678547934e-005</v>
       </c>
       <c r="S30">
-        <v>2.7485368047185941e-006</v>
+        <v>3.005024940018818e-006</v>
       </c>
       <c r="T30">
-        <v>1.8310178728618793e-006</v>
+        <v>2.2906799369046227e-006</v>
       </c>
       <c r="U30">
-        <v>1.8418900332821072e-005</v>
+        <v>2.7210759183189572e-005</v>
       </c>
       <c r="V30">
-        <v>-7.8550287322711994e-006</v>
+        <v>-1.2420097785560322e-005</v>
       </c>
       <c r="W30">
-        <v>3.3577920639451901e-005</v>
+        <v>3.5000378968972398e-005</v>
       </c>
       <c r="X30">
-        <v>5.3708705553035397e-005</v>
+        <v>6.3438348941717289e-005</v>
       </c>
       <c r="Y30">
-        <v>5.3141280559835419e-006</v>
+        <v>5.0821490929837811e-006</v>
       </c>
       <c r="Z30">
-        <v>-1.8650286154376622e-005</v>
+        <v>-1.4497062607255772e-005</v>
       </c>
       <c r="AA30">
-        <v>0.00065154166127628964</v>
+        <v>0.00071419180411844835</v>
       </c>
       <c r="AB30">
-        <v>0.00064502989637527466</v>
+        <v>0.0007105221784815337</v>
       </c>
       <c r="AC30">
-        <v>0.00063772197763787989</v>
+        <v>0.00070152838912274085</v>
       </c>
       <c r="AD30">
-        <v>0.00064358755169237813</v>
+        <v>0.00070369050325878326</v>
       </c>
       <c r="AE30">
-        <v>0.0014407312320830813</v>
+        <v>0.0015812673054742107</v>
       </c>
       <c r="AF30">
-        <v>0.00064767329444408454</v>
+        <v>0.00071016430929977232</v>
       </c>
       <c r="AG30">
-        <v>0.00065638794125717314</v>
+        <v>0.00072391009447585338</v>
       </c>
       <c r="AH30">
-        <v>0.00063915390964863988</v>
+        <v>0.00071948789598513276</v>
       </c>
       <c r="AI30">
-        <v>0.00064919137358499489</v>
+        <v>0.00072592186689537464</v>
       </c>
       <c r="AJ30">
-        <v>0.00063817121074017042</v>
+        <v>0.00070256217106079574</v>
       </c>
       <c r="AK30">
-        <v>0.00065104703239814306</v>
+        <v>0.00071566647326955527</v>
       </c>
       <c r="AL30">
-        <v>4.6871989733391047e-006</v>
+        <v>5.2159778893596945e-006</v>
       </c>
       <c r="AM30">
-        <v>6.5291188244552306e-006</v>
+        <v>1.9976263603420775e-005</v>
       </c>
       <c r="AN30">
-        <v>-2.7336358460504942e-005</v>
+        <v>-1.3142188213072952e-005</v>
       </c>
       <c r="AO30">
-        <v>0.00021540578163028432</v>
+        <v>0.00025121291813554785</v>
       </c>
       <c r="AP30">
-        <v>0.00023724922766060641</v>
+        <v>0.00025745556175778983</v>
       </c>
       <c r="AQ30">
-        <v>8.5640388843538965e-005</v>
+        <v>9.7964694079839826e-005</v>
       </c>
       <c r="AR30">
-        <v>-0.00097246846857259293</v>
+        <v>-0.0011091362621227568</v>
       </c>
     </row>
     <row r="31">
@@ -4503,133 +4503,133 @@
         <v>44</v>
       </c>
       <c r="B31">
-        <v>0.18283614605390777</v>
+        <v>0.17543179604188527</v>
       </c>
       <c r="C31">
-        <v>-1.0983052572330539e-005</v>
+        <v>-9.2457802703926466e-007</v>
       </c>
       <c r="D31">
-        <v>-7.1017926504283113e-007</v>
+        <v>-7.9883507211689906e-008</v>
       </c>
       <c r="E31">
-        <v>8.052277936034005e-009</v>
+        <v>3.714190287959945e-009</v>
       </c>
       <c r="F31">
-        <v>2.0776887963205033e-005</v>
+        <v>5.7110204037460566e-005</v>
       </c>
       <c r="G31">
-        <v>1.0989969644485526e-005</v>
+        <v>4.3059488357400921e-005</v>
       </c>
       <c r="H31">
-        <v>-2.2499949623952684e-005</v>
+        <v>-2.2166076240639593e-006</v>
       </c>
       <c r="I31">
-        <v>5.2671460004574482e-005</v>
+        <v>3.4066532533534111e-005</v>
       </c>
       <c r="J31">
-        <v>4.1847794395830524e-005</v>
+        <v>7.8426301734844681e-005</v>
       </c>
       <c r="K31">
-        <v>2.9183820655782962e-005</v>
+        <v>7.5388672424806392e-005</v>
       </c>
       <c r="L31">
-        <v>5.3644210220699101e-005</v>
+        <v>0.00010383663614040038</v>
       </c>
       <c r="M31">
-        <v>-9.2529558582061025e-006</v>
+        <v>-5.1192621658569003e-005</v>
       </c>
       <c r="N31">
-        <v>-1.7995507338083063e-005</v>
+        <v>-3.0389947216074046e-005</v>
       </c>
       <c r="O31">
-        <v>-3.3664256515412977e-005</v>
+        <v>-4.8780497296978476e-005</v>
       </c>
       <c r="P31">
-        <v>-3.4561000594923128e-005</v>
+        <v>-4.4925466177820861e-005</v>
       </c>
       <c r="Q31">
-        <v>-2.6748372990485336e-005</v>
+        <v>-3.3158693346604675e-005</v>
       </c>
       <c r="R31">
-        <v>-5.8214685573740683e-005</v>
+        <v>-2.3288915060881721e-005</v>
       </c>
       <c r="S31">
-        <v>9.0978379837808464e-007</v>
+        <v>1.1013059060450647e-006</v>
       </c>
       <c r="T31">
-        <v>1.31624259368367e-006</v>
+        <v>1.6814927442265341e-006</v>
       </c>
       <c r="U31">
-        <v>-4.0028278059515737e-005</v>
+        <v>-4.9719309572991146e-005</v>
       </c>
       <c r="V31">
-        <v>-5.4022103131555791e-005</v>
+        <v>-6.7972506729304749e-005</v>
       </c>
       <c r="W31">
-        <v>-1.7032245439057989e-005</v>
+        <v>-3.2886693973134529e-005</v>
       </c>
       <c r="X31">
-        <v>1.8785977616310527e-005</v>
+        <v>3.0704801696259721e-005</v>
       </c>
       <c r="Y31">
-        <v>5.910953883521034e-006</v>
+        <v>6.9324461777779794e-006</v>
       </c>
       <c r="Z31">
-        <v>1.2260936122236334e-005</v>
+        <v>1.8674528758030312e-005</v>
       </c>
       <c r="AA31">
-        <v>0.00068578998808925616</v>
+        <v>0.0007538483389272657</v>
       </c>
       <c r="AB31">
-        <v>0.00069237294302422795</v>
+        <v>0.0007629490986268265</v>
       </c>
       <c r="AC31">
-        <v>0.00067652558207601746</v>
+        <v>0.00074112676630128224</v>
       </c>
       <c r="AD31">
-        <v>0.00067632480718764329</v>
+        <v>0.00073306539195586444</v>
       </c>
       <c r="AE31">
-        <v>0.00064767329444408454</v>
+        <v>0.00071016430929977232</v>
       </c>
       <c r="AF31">
-        <v>0.0012216089374670999</v>
+        <v>0.0013251436527656631</v>
       </c>
       <c r="AG31">
-        <v>0.00069733978834818594</v>
+        <v>0.00076759852390409153</v>
       </c>
       <c r="AH31">
-        <v>0.00068475310181464598</v>
+        <v>0.00076497387433915182</v>
       </c>
       <c r="AI31">
-        <v>0.00068455491975494146</v>
+        <v>0.00075925104225068023</v>
       </c>
       <c r="AJ31">
-        <v>0.00067873460619821777</v>
+        <v>0.0007458866854992204</v>
       </c>
       <c r="AK31">
-        <v>0.00068976260931781995</v>
+        <v>0.00075799814901674454</v>
       </c>
       <c r="AL31">
-        <v>-3.4408798431670673e-007</v>
+        <v>-1.7176370339405016e-006</v>
       </c>
       <c r="AM31">
-        <v>3.5825742213308896e-005</v>
+        <v>2.8469741865013473e-005</v>
       </c>
       <c r="AN31">
-        <v>-9.6520469735784237e-006</v>
+        <v>6.804480587293307e-006</v>
       </c>
       <c r="AO31">
-        <v>0.00032992005705753864</v>
+        <v>0.00038515508749997448</v>
       </c>
       <c r="AP31">
-        <v>0.0003070246790552114</v>
+        <v>0.00033555524927157611</v>
       </c>
       <c r="AQ31">
-        <v>6.7341297920779915e-005</v>
+        <v>8.1334805588733787e-005</v>
       </c>
       <c r="AR31">
-        <v>-0.00075095060483252067</v>
+        <v>-0.0008715863496420365</v>
       </c>
     </row>
     <row r="32">
@@ -4637,133 +4637,133 @@
         <v>45</v>
       </c>
       <c r="B32">
-        <v>0.16012060346024687</v>
+        <v>0.17901918267980349</v>
       </c>
       <c r="C32">
-        <v>7.7371514324512604e-006</v>
+        <v>1.4919103126229899e-005</v>
       </c>
       <c r="D32">
-        <v>9.4106940662763486e-007</v>
+        <v>-7.8844860095415302e-007</v>
       </c>
       <c r="E32">
-        <v>-5.6684974704174004e-009</v>
+        <v>4.3192795793339746e-009</v>
       </c>
       <c r="F32">
-        <v>4.1186073895733033e-005</v>
+        <v>8.7040917421662192e-005</v>
       </c>
       <c r="G32">
-        <v>2.5876128595239913e-005</v>
+        <v>6.2684186318883307e-005</v>
       </c>
       <c r="H32">
-        <v>-6.5846223941549962e-006</v>
+        <v>8.2950318306736807e-006</v>
       </c>
       <c r="I32">
-        <v>1.9420977007738005e-005</v>
+        <v>2.9277263107849511e-005</v>
       </c>
       <c r="J32">
-        <v>2.2515925083977395e-005</v>
+        <v>6.6898236795609375e-005</v>
       </c>
       <c r="K32">
-        <v>2.8527622475749243e-005</v>
+        <v>7.6854999545582188e-005</v>
       </c>
       <c r="L32">
-        <v>1.2482435849904094e-005</v>
+        <v>5.4381361092423086e-005</v>
       </c>
       <c r="M32">
-        <v>8.0744857456591134e-006</v>
+        <v>-6.4028010656713336e-005</v>
       </c>
       <c r="N32">
-        <v>1.8168709011991038e-005</v>
+        <v>3.3971703979008487e-006</v>
       </c>
       <c r="O32">
-        <v>3.5614431227369922e-006</v>
+        <v>-6.374754304186153e-006</v>
       </c>
       <c r="P32">
-        <v>-4.1272511123606934e-005</v>
+        <v>-2.7841507683270559e-005</v>
       </c>
       <c r="Q32">
-        <v>-3.6699206240433357e-005</v>
+        <v>-1.8845789235205042e-005</v>
       </c>
       <c r="R32">
-        <v>-5.1719909536976351e-005</v>
+        <v>7.9766340056744047e-006</v>
       </c>
       <c r="S32">
-        <v>1.1384125971795166e-006</v>
+        <v>9.1854783113393936e-007</v>
       </c>
       <c r="T32">
-        <v>8.1195392537847175e-007</v>
+        <v>1.3992193814255076e-006</v>
       </c>
       <c r="U32">
-        <v>3.0808817222595266e-006</v>
+        <v>-3.7684588234171212e-006</v>
       </c>
       <c r="V32">
-        <v>-1.5698463657213261e-005</v>
+        <v>-3.6431199264291717e-005</v>
       </c>
       <c r="W32">
-        <v>3.23332139067824e-005</v>
+        <v>1.6235610702650704e-005</v>
       </c>
       <c r="X32">
-        <v>5.5213051653421288e-005</v>
+        <v>6.1770233905072218e-005</v>
       </c>
       <c r="Y32">
-        <v>-1.3335409566129502e-006</v>
+        <v>9.4406532682533979e-007</v>
       </c>
       <c r="Z32">
-        <v>9.1560773110160757e-006</v>
+        <v>1.0898978086052061e-005</v>
       </c>
       <c r="AA32">
-        <v>0.00070232558595874741</v>
+        <v>0.00077345142835916268</v>
       </c>
       <c r="AB32">
-        <v>0.00069644340451890886</v>
+        <v>0.00077085599380908307</v>
       </c>
       <c r="AC32">
-        <v>0.00068507848671234424</v>
+        <v>0.00075674723407687875</v>
       </c>
       <c r="AD32">
-        <v>0.00069218446652036226</v>
+        <v>0.0007549982872926609</v>
       </c>
       <c r="AE32">
-        <v>0.00065638794125717314</v>
+        <v>0.00072391009447585338</v>
       </c>
       <c r="AF32">
-        <v>0.00069733978834818594</v>
+        <v>0.00076759852390409153</v>
       </c>
       <c r="AG32">
-        <v>0.0011570601399936438</v>
+        <v>0.0012522381586096861</v>
       </c>
       <c r="AH32">
-        <v>0.00069364615868296197</v>
+        <v>0.00077917967158550809</v>
       </c>
       <c r="AI32">
-        <v>0.00069666115240712945</v>
+        <v>0.0007748577284809122</v>
       </c>
       <c r="AJ32">
-        <v>0.00068710441450951407</v>
+        <v>0.00075931960699552529</v>
       </c>
       <c r="AK32">
-        <v>0.00070121879336255055</v>
+        <v>0.00077346783161252419</v>
       </c>
       <c r="AL32">
-        <v>1.6509670226000296e-006</v>
+        <v>-3.6478814823989421e-007</v>
       </c>
       <c r="AM32">
-        <v>6.1780198984726477e-006</v>
+        <v>1.2150099578316103e-005</v>
       </c>
       <c r="AN32">
-        <v>-2.6267984352743533e-005</v>
+        <v>-3.153996104924661e-006</v>
       </c>
       <c r="AO32">
-        <v>0.00033102985002223353</v>
+        <v>0.0004016707033665921</v>
       </c>
       <c r="AP32">
-        <v>0.00040433809938117957</v>
+        <v>0.00043844491449865309</v>
       </c>
       <c r="AQ32">
-        <v>0.00011028588477638462</v>
+        <v>0.00013302587577027587</v>
       </c>
       <c r="AR32">
-        <v>-0.00086337050717419069</v>
+        <v>-0.00090903362570042296</v>
       </c>
     </row>
     <row r="33">
@@ -4771,133 +4771,133 @@
         <v>46</v>
       </c>
       <c r="B33">
-        <v>0.17208011990454108</v>
+        <v>0.17682617604489581</v>
       </c>
       <c r="C33">
-        <v>3.6322757539457999e-006</v>
+        <v>1.3612597189542542e-005</v>
       </c>
       <c r="D33">
-        <v>1.2825810163173493e-006</v>
+        <v>2.2295222118078913e-006</v>
       </c>
       <c r="E33">
-        <v>-1.6521739648338824e-008</v>
+        <v>-2.6741717379863864e-008</v>
       </c>
       <c r="F33">
-        <v>6.1418462199559903e-005</v>
+        <v>0.00010997163232206887</v>
       </c>
       <c r="G33">
-        <v>1.5088431674196048e-005</v>
+        <v>5.2049254081877014e-005</v>
       </c>
       <c r="H33">
-        <v>-1.4421251890911568e-005</v>
+        <v>1.7039702809658626e-005</v>
       </c>
       <c r="I33">
-        <v>3.0815336267243802e-005</v>
+        <v>7.0805307919838198e-005</v>
       </c>
       <c r="J33">
-        <v>5.2864224098164437e-005</v>
+        <v>9.3364765904528245e-005</v>
       </c>
       <c r="K33">
-        <v>3.7984069541432218e-005</v>
+        <v>8.7393877995467327e-005</v>
       </c>
       <c r="L33">
-        <v>1.3733613124281006e-005</v>
+        <v>5.7208549644156969e-005</v>
       </c>
       <c r="M33">
-        <v>-1.5710430887543714e-005</v>
+        <v>-5.1584734982397039e-005</v>
       </c>
       <c r="N33">
-        <v>1.3805711962802794e-005</v>
+        <v>1.3344986052519672e-005</v>
       </c>
       <c r="O33">
-        <v>1.1466332426809768e-005</v>
+        <v>1.7637862802154376e-005</v>
       </c>
       <c r="P33">
-        <v>-1.7694268842343671e-005</v>
+        <v>-3.1691635280815236e-005</v>
       </c>
       <c r="Q33">
-        <v>7.9598417998092681e-006</v>
+        <v>-6.8509161631558018e-006</v>
       </c>
       <c r="R33">
-        <v>-5.3685925061198715e-006</v>
+        <v>1.4208835870225412e-005</v>
       </c>
       <c r="S33">
-        <v>1.1374378148736754e-006</v>
+        <v>1.9811368500926468e-006</v>
       </c>
       <c r="T33">
-        <v>2.3122322589005658e-007</v>
+        <v>2.7700938297861094e-007</v>
       </c>
       <c r="U33">
-        <v>-2.5766383757899628e-005</v>
+        <v>-4.0022951393980047e-005</v>
       </c>
       <c r="V33">
-        <v>-1.9033411027798229e-005</v>
+        <v>-4.3945520463039664e-005</v>
       </c>
       <c r="W33">
-        <v>1.5878163546745055e-005</v>
+        <v>-3.6662179746308565e-006</v>
       </c>
       <c r="X33">
-        <v>5.2945592962918596e-005</v>
+        <v>7.2494043269069968e-005</v>
       </c>
       <c r="Y33">
-        <v>1.8602886005732109e-006</v>
+        <v>2.543888677239866e-006</v>
       </c>
       <c r="Z33">
-        <v>1.739880310280001e-005</v>
+        <v>3.6729566786976938e-005</v>
       </c>
       <c r="AA33">
-        <v>0.00068653732181760173</v>
+        <v>0.00076783116940227374</v>
       </c>
       <c r="AB33">
-        <v>0.00069005587690615226</v>
+        <v>0.00077824357656879723</v>
       </c>
       <c r="AC33">
-        <v>0.00067223962469098474</v>
+        <v>0.00075773118476117531</v>
       </c>
       <c r="AD33">
-        <v>0.00067530070810414985</v>
+        <v>0.00075190355026618445</v>
       </c>
       <c r="AE33">
-        <v>0.00063915390964863988</v>
+        <v>0.00071948789598513276</v>
       </c>
       <c r="AF33">
-        <v>0.00068475310181464598</v>
+        <v>0.00076497387433915182</v>
       </c>
       <c r="AG33">
-        <v>0.00069364615868296197</v>
+        <v>0.00077917967158550809</v>
       </c>
       <c r="AH33">
-        <v>0.0012499812957202684</v>
+        <v>0.0014557699200025346</v>
       </c>
       <c r="AI33">
-        <v>0.00067715985571140938</v>
+        <v>0.00076899962649758897</v>
       </c>
       <c r="AJ33">
-        <v>0.00067275349360048514</v>
+        <v>0.00075920868665692233</v>
       </c>
       <c r="AK33">
-        <v>0.00068878519018399878</v>
+        <v>0.00077569916809100403</v>
       </c>
       <c r="AL33">
-        <v>6.0929773009878803e-007</v>
+        <v>1.1857755812136285e-006</v>
       </c>
       <c r="AM33">
-        <v>3.8418489417236037e-005</v>
+        <v>3.5195521248497454e-005</v>
       </c>
       <c r="AN33">
-        <v>9.7404579013808733e-007</v>
+        <v>7.249235149254233e-006</v>
       </c>
       <c r="AO33">
-        <v>0.0003540340035062531</v>
+        <v>0.0004122811006228266</v>
       </c>
       <c r="AP33">
-        <v>0.00038401008036990068</v>
+        <v>0.00040746498305542402</v>
       </c>
       <c r="AQ33">
-        <v>0.00014618276502644962</v>
+        <v>0.00016470006754011466</v>
       </c>
       <c r="AR33">
-        <v>-0.00081821065788280085</v>
+        <v>-0.0010129733688989428</v>
       </c>
     </row>
     <row r="34">
@@ -4905,133 +4905,133 @@
         <v>47</v>
       </c>
       <c r="B34">
-        <v>0.2166741122772145</v>
+        <v>0.23917005253266202</v>
       </c>
       <c r="C34">
-        <v>2.8292457749533129e-005</v>
+        <v>5.8301133889744733e-005</v>
       </c>
       <c r="D34">
-        <v>1.8700772625263708e-006</v>
+        <v>3.5810226884147745e-007</v>
       </c>
       <c r="E34">
-        <v>-1.2082130474813329e-008</v>
+        <v>-2.2986567658487526e-009</v>
       </c>
       <c r="F34">
-        <v>6.0786325587824615e-005</v>
+        <v>8.963330669920557e-005</v>
       </c>
       <c r="G34">
-        <v>3.3337337161404647e-005</v>
+        <v>7.8461982076474362e-005</v>
       </c>
       <c r="H34">
-        <v>4.334419083304099e-005</v>
+        <v>7.3917316703664762e-005</v>
       </c>
       <c r="I34">
-        <v>4.3619398935583627e-006</v>
+        <v>3.4602105039228893e-005</v>
       </c>
       <c r="J34">
-        <v>4.7758379338087254e-005</v>
+        <v>8.0771753064403008e-005</v>
       </c>
       <c r="K34">
-        <v>6.4728098202022856e-005</v>
+        <v>0.00012436222096174531</v>
       </c>
       <c r="L34">
-        <v>2.7598608568576706e-005</v>
+        <v>8.0325162247492243e-005</v>
       </c>
       <c r="M34">
-        <v>1.6980297160309478e-005</v>
+        <v>-6.5751063532627009e-005</v>
       </c>
       <c r="N34">
-        <v>-9.725978033740671e-006</v>
+        <v>-3.5526186225770751e-005</v>
       </c>
       <c r="O34">
-        <v>-2.9930942522931291e-005</v>
+        <v>-3.6003823550613231e-005</v>
       </c>
       <c r="P34">
-        <v>-4.5990781099885644e-005</v>
+        <v>-7.7012783928613973e-005</v>
       </c>
       <c r="Q34">
-        <v>-4.0167247408948902e-005</v>
+        <v>-6.0803425415086148e-005</v>
       </c>
       <c r="R34">
-        <v>-4.6911389359856502e-005</v>
+        <v>2.8726732420323639e-005</v>
       </c>
       <c r="S34">
-        <v>1.941276287368735e-006</v>
+        <v>1.872351147270361e-006</v>
       </c>
       <c r="T34">
-        <v>6.8966310783656917e-007</v>
+        <v>-9.0919938225552548e-008</v>
       </c>
       <c r="U34">
-        <v>-3.2630267389363734e-005</v>
+        <v>-3.9412224871447141e-005</v>
       </c>
       <c r="V34">
-        <v>-4.6149880784336248e-005</v>
+        <v>-6.192092835186396e-005</v>
       </c>
       <c r="W34">
-        <v>1.5908721903990495e-006</v>
+        <v>1.3189982189747e-007</v>
       </c>
       <c r="X34">
-        <v>3.0681426331698934e-005</v>
+        <v>5.9057308561918869e-005</v>
       </c>
       <c r="Y34">
-        <v>4.2954688641642587e-006</v>
+        <v>5.5325639065215473e-006</v>
       </c>
       <c r="Z34">
-        <v>2.3539982962205941e-006</v>
+        <v>1.1208741863025789e-005</v>
       </c>
       <c r="AA34">
-        <v>0.00068144453949511386</v>
+        <v>0.00075508385658314625</v>
       </c>
       <c r="AB34">
-        <v>0.00068386397236017236</v>
+        <v>0.00076365159117512628</v>
       </c>
       <c r="AC34">
-        <v>0.00067516449665185713</v>
+        <v>0.00075415647031044268</v>
       </c>
       <c r="AD34">
-        <v>0.00068223286505812838</v>
+        <v>0.00075452145079943692</v>
       </c>
       <c r="AE34">
-        <v>0.00064919137358499489</v>
+        <v>0.00072592186689537464</v>
       </c>
       <c r="AF34">
-        <v>0.00068455491975494146</v>
+        <v>0.00075925104225068023</v>
       </c>
       <c r="AG34">
-        <v>0.00069666115240712945</v>
+        <v>0.0007748577284809122</v>
       </c>
       <c r="AH34">
-        <v>0.00067715985571140938</v>
+        <v>0.00076899962649758897</v>
       </c>
       <c r="AI34">
-        <v>0.0015091572056749243</v>
+        <v>0.0018150990965600607</v>
       </c>
       <c r="AJ34">
-        <v>0.00067844298282802959</v>
+        <v>0.00075580073571676469</v>
       </c>
       <c r="AK34">
-        <v>0.00069562522791092013</v>
+        <v>0.00078004191764674655</v>
       </c>
       <c r="AL34">
-        <v>2.3138725280044269e-006</v>
+        <v>3.9421135921308836e-006</v>
       </c>
       <c r="AM34">
-        <v>1.1509480802379966e-005</v>
+        <v>-7.0821478250976465e-007</v>
       </c>
       <c r="AN34">
-        <v>-3.9208441362080233e-005</v>
+        <v>-4.0288353086371614e-005</v>
       </c>
       <c r="AO34">
-        <v>0.00032862238633554915</v>
+        <v>0.00037346088621774333</v>
       </c>
       <c r="AP34">
-        <v>0.00037940474563385394</v>
+        <v>0.00040064684333281704</v>
       </c>
       <c r="AQ34">
-        <v>0.00012559078748121272</v>
+        <v>0.0001333008981011423</v>
       </c>
       <c r="AR34">
-        <v>-0.00092809557796094309</v>
+        <v>-0.000991779301602816</v>
       </c>
     </row>
     <row r="35">
@@ -5039,133 +5039,133 @@
         <v>48</v>
       </c>
       <c r="B35">
-        <v>0.13317581800677716</v>
+        <v>0.15030017715138966</v>
       </c>
       <c r="C35">
-        <v>2.8452559341954198e-005</v>
+        <v>5.0434960393527338e-005</v>
       </c>
       <c r="D35">
-        <v>-3.0038078623486962e-006</v>
+        <v>-2.3689269384005123e-006</v>
       </c>
       <c r="E35">
-        <v>2.7935207484647161e-008</v>
+        <v>2.0044812961463735e-008</v>
       </c>
       <c r="F35">
-        <v>-1.5433493991132193e-005</v>
+        <v>2.0457253425828246e-005</v>
       </c>
       <c r="G35">
-        <v>-2.791904447079386e-005</v>
+        <v>-1.1715212806015348e-005</v>
       </c>
       <c r="H35">
-        <v>-4.8322758346642043e-005</v>
+        <v>-5.2956930014984375e-005</v>
       </c>
       <c r="I35">
-        <v>-7.5132049609409149e-005</v>
+        <v>-4.7534915596808612e-005</v>
       </c>
       <c r="J35">
-        <v>-1.1182780678062562e-005</v>
+        <v>4.7496736955574955e-006</v>
       </c>
       <c r="K35">
-        <v>-4.4397882672252254e-006</v>
+        <v>2.3603331651853174e-005</v>
       </c>
       <c r="L35">
-        <v>-3.7952161317652736e-005</v>
+        <v>-1.3812228128396513e-005</v>
       </c>
       <c r="M35">
-        <v>-8.5387699983922335e-005</v>
+        <v>-0.00012834369175097082</v>
       </c>
       <c r="N35">
-        <v>-2.0725216027190239e-005</v>
+        <v>-4.2131290468233024e-005</v>
       </c>
       <c r="O35">
-        <v>-6.9791533030363293e-005</v>
+        <v>-7.8927664947620185e-005</v>
       </c>
       <c r="P35">
-        <v>-3.7038990804816481e-005</v>
+        <v>-5.3016544937652357e-005</v>
       </c>
       <c r="Q35">
-        <v>-2.1109648320352211e-005</v>
+        <v>-3.6247264831092393e-005</v>
       </c>
       <c r="R35">
-        <v>-6.8064019435743295e-006</v>
+        <v>1.416153316204855e-005</v>
       </c>
       <c r="S35">
-        <v>9.7241617733335524e-007</v>
+        <v>1.1257162621809847e-006</v>
       </c>
       <c r="T35">
-        <v>5.3884604295419614e-007</v>
+        <v>6.5432913302823684e-007</v>
       </c>
       <c r="U35">
-        <v>-3.3337085446458112e-005</v>
+        <v>-4.861101136781027e-005</v>
       </c>
       <c r="V35">
-        <v>-5.4378512471950875e-005</v>
+        <v>-8.5252838608095932e-005</v>
       </c>
       <c r="W35">
-        <v>-3.6660565095516948e-005</v>
+        <v>-6.4705955962645644e-005</v>
       </c>
       <c r="X35">
-        <v>-2.0048983944776291e-005</v>
+        <v>-3.990600052266723e-005</v>
       </c>
       <c r="Y35">
-        <v>6.8825686854774799e-006</v>
+        <v>7.6531177090155907e-006</v>
       </c>
       <c r="Z35">
-        <v>2.2620832609368221e-005</v>
+        <v>2.7192284001170244e-005</v>
       </c>
       <c r="AA35">
-        <v>0.00068719379599146773</v>
+        <v>0.0007535264710489748</v>
       </c>
       <c r="AB35">
-        <v>0.0006807792292058577</v>
+        <v>0.00075392067678132406</v>
       </c>
       <c r="AC35">
-        <v>0.00066406858941643696</v>
+        <v>0.00073417708710036113</v>
       </c>
       <c r="AD35">
-        <v>0.00066578822256154759</v>
+        <v>0.00072410759392834572</v>
       </c>
       <c r="AE35">
-        <v>0.00063817121074017042</v>
+        <v>0.00070256217106079574</v>
       </c>
       <c r="AF35">
-        <v>0.00067873460619821777</v>
+        <v>0.0007458866854992204</v>
       </c>
       <c r="AG35">
-        <v>0.00068710441450951407</v>
+        <v>0.00075931960699552529</v>
       </c>
       <c r="AH35">
-        <v>0.00067275349360048514</v>
+        <v>0.00075920868665692233</v>
       </c>
       <c r="AI35">
-        <v>0.00067844298282802959</v>
+        <v>0.00075580073571676469</v>
       </c>
       <c r="AJ35">
-        <v>0.001232983507919391</v>
+        <v>0.0013554452834347794</v>
       </c>
       <c r="AK35">
-        <v>0.00068437578606983854</v>
+        <v>0.0007556620152195764</v>
       </c>
       <c r="AL35">
-        <v>1.7470790429749533e-006</v>
+        <v>2.6997776408038785e-007</v>
       </c>
       <c r="AM35">
-        <v>1.1356176633436384e-005</v>
+        <v>2.1656733642858348e-005</v>
       </c>
       <c r="AN35">
-        <v>-4.0701627739962905e-005</v>
+        <v>-2.1057852117538313e-005</v>
       </c>
       <c r="AO35">
-        <v>0.00032906654604927858</v>
+        <v>0.00038026104349897245</v>
       </c>
       <c r="AP35">
-        <v>0.00034834092666768718</v>
+        <v>0.00036953671517060899</v>
       </c>
       <c r="AQ35">
-        <v>0.00014609613356185794</v>
+        <v>0.00015484823302541241</v>
       </c>
       <c r="AR35">
-        <v>-0.00065509772358266177</v>
+        <v>-0.00072346021065076169</v>
       </c>
     </row>
     <row r="36">
@@ -5173,133 +5173,133 @@
         <v>49</v>
       </c>
       <c r="B36">
-        <v>0.27710413224489727</v>
+        <v>0.31709786514647736</v>
       </c>
       <c r="C36">
-        <v>6.671488782523622e-006</v>
+        <v>1.4316850098585939e-005</v>
       </c>
       <c r="D36">
-        <v>6.476161654871452e-007</v>
+        <v>1.3747387937357601e-006</v>
       </c>
       <c r="E36">
-        <v>-4.3129974628508136e-009</v>
+        <v>-1.1317478305566059e-008</v>
       </c>
       <c r="F36">
-        <v>9.7340831935838375e-005</v>
+        <v>0.0001295253426587838</v>
       </c>
       <c r="G36">
-        <v>1.2850658976226818e-005</v>
+        <v>3.7137573823124481e-005</v>
       </c>
       <c r="H36">
-        <v>5.9094566025350655e-006</v>
+        <v>8.9075732955111897e-006</v>
       </c>
       <c r="I36">
-        <v>2.9490277286494835e-005</v>
+        <v>5.601103958479401e-005</v>
       </c>
       <c r="J36">
-        <v>2.893025999202179e-005</v>
+        <v>4.4931155737837401e-005</v>
       </c>
       <c r="K36">
-        <v>2.1220832550911367e-005</v>
+        <v>4.8177857676390951e-005</v>
       </c>
       <c r="L36">
-        <v>-8.2522317011030077e-006</v>
+        <v>1.2930378904404786e-005</v>
       </c>
       <c r="M36">
-        <v>5.7974636795026023e-005</v>
+        <v>-8.5507285691666579e-006</v>
       </c>
       <c r="N36">
-        <v>-2.2490583635362813e-005</v>
+        <v>-3.932946520510724e-005</v>
       </c>
       <c r="O36">
-        <v>-1.2048022267360499e-005</v>
+        <v>-2.2218754609247874e-005</v>
       </c>
       <c r="P36">
-        <v>-5.0558213503038897e-006</v>
+        <v>-8.4943755631748826e-006</v>
       </c>
       <c r="Q36">
-        <v>-2.3012665814294123e-005</v>
+        <v>-2.9757842378926318e-005</v>
       </c>
       <c r="R36">
-        <v>-0.00010119897594843482</v>
+        <v>-4.5502479570227658e-005</v>
       </c>
       <c r="S36">
-        <v>1.6276734925956061e-006</v>
+        <v>1.8739130171534807e-006</v>
       </c>
       <c r="T36">
-        <v>5.5771612317680025e-007</v>
+        <v>6.7862422894459416e-007</v>
       </c>
       <c r="U36">
-        <v>-1.0940284810062226e-005</v>
+        <v>-2.237748137005717e-005</v>
       </c>
       <c r="V36">
-        <v>-2.5809870252953043e-005</v>
+        <v>-4.6697600736223953e-005</v>
       </c>
       <c r="W36">
-        <v>3.3815551894529183e-005</v>
+        <v>2.5606344078588821e-005</v>
       </c>
       <c r="X36">
-        <v>6.3369757640363285e-005</v>
+        <v>6.1921404085622648e-005</v>
       </c>
       <c r="Y36">
-        <v>7.8360982931844616e-006</v>
+        <v>9.3274257843658481e-006</v>
       </c>
       <c r="Z36">
-        <v>2.4682039530958024e-005</v>
+        <v>3.8810514857990052e-005</v>
       </c>
       <c r="AA36">
-        <v>0.0006966720097199892</v>
+        <v>0.00076262389974661329</v>
       </c>
       <c r="AB36">
-        <v>0.00069094269961033781</v>
+        <v>0.00076775634214041276</v>
       </c>
       <c r="AC36">
-        <v>0.00067672324313192568</v>
+        <v>0.00074810463871088516</v>
       </c>
       <c r="AD36">
-        <v>0.00068334560606015185</v>
+        <v>0.00074700902868599886</v>
       </c>
       <c r="AE36">
-        <v>0.00065104703239814306</v>
+        <v>0.00071566647326955527</v>
       </c>
       <c r="AF36">
-        <v>0.00068976260931781995</v>
+        <v>0.00075799814901674454</v>
       </c>
       <c r="AG36">
-        <v>0.00070121879336255055</v>
+        <v>0.00077346783161252419</v>
       </c>
       <c r="AH36">
-        <v>0.00068878519018399878</v>
+        <v>0.00077569916809100403</v>
       </c>
       <c r="AI36">
-        <v>0.00069562522791092013</v>
+        <v>0.00078004191764674655</v>
       </c>
       <c r="AJ36">
-        <v>0.00068437578606983854</v>
+        <v>0.0007556620152195764</v>
       </c>
       <c r="AK36">
-        <v>0.0015719344205440554</v>
+        <v>0.0017035240196553196</v>
       </c>
       <c r="AL36">
-        <v>4.4352339165971998e-007</v>
+        <v>-4.1361853284710372e-007</v>
       </c>
       <c r="AM36">
-        <v>2.5882291728958502e-005</v>
+        <v>2.2917204746696876e-005</v>
       </c>
       <c r="AN36">
-        <v>-4.6113126984487104e-005</v>
+        <v>-3.5590691236426743e-005</v>
       </c>
       <c r="AO36">
-        <v>0.00043457738567994589</v>
+        <v>0.00050836871260555761</v>
       </c>
       <c r="AP36">
-        <v>0.00040052508338801616</v>
+        <v>0.00043259280791338786</v>
       </c>
       <c r="AQ36">
-        <v>0.00016109453152884831</v>
+        <v>0.00018508197948161365</v>
       </c>
       <c r="AR36">
-        <v>-0.00086353170123420336</v>
+        <v>-0.00097377242397340264</v>
       </c>
     </row>
     <row r="37">
@@ -5307,133 +5307,133 @@
         <v>50</v>
       </c>
       <c r="B37">
-        <v>0.0091100744629305629</v>
+        <v>0.0094379697399259582</v>
       </c>
       <c r="C37">
-        <v>-1.1535714025177435e-007</v>
+        <v>6.9577425603410914e-007</v>
       </c>
       <c r="D37">
-        <v>-1.2690632868808265e-007</v>
+        <v>-1.2111370772023238e-007</v>
       </c>
       <c r="E37">
-        <v>7.5620018810960088e-010</v>
+        <v>-2.9702376529953202e-011</v>
       </c>
       <c r="F37">
-        <v>3.5092277268555577e-007</v>
+        <v>2.454494799653033e-006</v>
       </c>
       <c r="G37">
-        <v>-2.5181911651032769e-006</v>
+        <v>-2.5129145492207836e-006</v>
       </c>
       <c r="H37">
-        <v>3.1387519070449102e-006</v>
+        <v>5.3365881955915622e-006</v>
       </c>
       <c r="I37">
-        <v>-9.5605678684841254e-007</v>
+        <v>6.0198201151925109e-007</v>
       </c>
       <c r="J37">
-        <v>-3.0913615097126154e-006</v>
+        <v>-2.1481505128037657e-006</v>
       </c>
       <c r="K37">
-        <v>-1.3538825561573047e-006</v>
+        <v>1.4487326934295051e-006</v>
       </c>
       <c r="L37">
-        <v>7.5412286701169006e-007</v>
+        <v>3.6238143179959982e-006</v>
       </c>
       <c r="M37">
-        <v>-4.1214757251409719e-006</v>
+        <v>-3.0699328490907461e-006</v>
       </c>
       <c r="N37">
-        <v>-2.7648575358676626e-006</v>
+        <v>-2.8486466540738318e-006</v>
       </c>
       <c r="O37">
-        <v>2.7311700451492513e-008</v>
+        <v>1.7658887970857962e-006</v>
       </c>
       <c r="P37">
-        <v>-1.4803834540635789e-006</v>
+        <v>-7.0892045033260566e-007</v>
       </c>
       <c r="Q37">
-        <v>1.7652598805730695e-006</v>
+        <v>3.6657020293479569e-006</v>
       </c>
       <c r="R37">
-        <v>1.7210229087900579e-006</v>
+        <v>3.1260469260903907e-006</v>
       </c>
       <c r="S37">
-        <v>1.2780953898564263e-007</v>
+        <v>1.0809047784141537e-007</v>
       </c>
       <c r="T37">
-        <v>1.5799231672027583e-007</v>
+        <v>1.7875692451641683e-007</v>
       </c>
       <c r="U37">
-        <v>1.3169132184540625e-006</v>
+        <v>4.2542319785726667e-006</v>
       </c>
       <c r="V37">
-        <v>-3.6114845905076305e-006</v>
+        <v>-1.6294092022376403e-006</v>
       </c>
       <c r="W37">
-        <v>-1.6589537495092501e-006</v>
+        <v>1.223786904663973e-006</v>
       </c>
       <c r="X37">
-        <v>-8.092324873794441e-007</v>
+        <v>3.233796564268025e-006</v>
       </c>
       <c r="Y37">
-        <v>8.9451254721847559e-008</v>
+        <v>8.1572801357504765e-008</v>
       </c>
       <c r="Z37">
-        <v>-2.3954864016779782e-006</v>
+        <v>-2.2410219462174139e-006</v>
       </c>
       <c r="AA37">
-        <v>5.6910552416185138e-007</v>
+        <v>-4.185880501603325e-007</v>
       </c>
       <c r="AB37">
-        <v>7.2697627449898366e-006</v>
+        <v>8.2812427561535824e-006</v>
       </c>
       <c r="AC37">
-        <v>1.7398932839757383e-006</v>
+        <v>-1.3054637036469474e-006</v>
       </c>
       <c r="AD37">
-        <v>1.055768868937731e-006</v>
+        <v>-2.0205520996701917e-007</v>
       </c>
       <c r="AE37">
-        <v>4.6871989733391047e-006</v>
+        <v>5.2159778893596945e-006</v>
       </c>
       <c r="AF37">
-        <v>-3.4408798431670673e-007</v>
+        <v>-1.7176370339405016e-006</v>
       </c>
       <c r="AG37">
-        <v>1.6509670226000296e-006</v>
+        <v>-3.6478814823989421e-007</v>
       </c>
       <c r="AH37">
-        <v>6.0929773009878803e-007</v>
+        <v>1.1857755812136285e-006</v>
       </c>
       <c r="AI37">
-        <v>2.3138725280044269e-006</v>
+        <v>3.9421135921308836e-006</v>
       </c>
       <c r="AJ37">
-        <v>1.7470790429749533e-006</v>
+        <v>2.6997776408038785e-007</v>
       </c>
       <c r="AK37">
-        <v>4.4352339165971998e-007</v>
+        <v>-4.1361853284710372e-007</v>
       </c>
       <c r="AL37">
-        <v>4.6399146647799235e-006</v>
+        <v>5.2557270910892523e-006</v>
       </c>
       <c r="AM37">
-        <v>-2.1708913701458711e-005</v>
+        <v>-2.5447366411689566e-005</v>
       </c>
       <c r="AN37">
-        <v>-2.5379281559476691e-005</v>
+        <v>-2.7346966961911284e-005</v>
       </c>
       <c r="AO37">
-        <v>8.3143018422219784e-006</v>
+        <v>1.0737892507111869e-005</v>
       </c>
       <c r="AP37">
-        <v>1.2134805427321862e-005</v>
+        <v>1.1331890824418911e-005</v>
       </c>
       <c r="AQ37">
-        <v>-3.0573299661988664e-006</v>
+        <v>-4.8508973518122782e-006</v>
       </c>
       <c r="AR37">
-        <v>-8.1144206722909157e-005</v>
+        <v>-9.4484547373245226e-005</v>
       </c>
     </row>
     <row r="38">
@@ -5441,133 +5441,133 @@
         <v>51</v>
       </c>
       <c r="B38">
-        <v>0.030161087773254831</v>
+        <v>0.021556552585683102</v>
       </c>
       <c r="C38">
-        <v>9.3452281720407482e-006</v>
+        <v>2.3552594679521088e-006</v>
       </c>
       <c r="D38">
-        <v>-5.4242521893380373e-007</v>
+        <v>-1.4510760285588929e-006</v>
       </c>
       <c r="E38">
-        <v>-1.7504791653671584e-009</v>
+        <v>1.2819615368578351e-008</v>
       </c>
       <c r="F38">
-        <v>2.5486789082202106e-005</v>
+        <v>3.8627978727757322e-005</v>
       </c>
       <c r="G38">
-        <v>5.3702259389035297e-006</v>
+        <v>1.5017072349810152e-005</v>
       </c>
       <c r="H38">
-        <v>-8.2957948803577845e-008</v>
+        <v>-3.2755924613270802e-006</v>
       </c>
       <c r="I38">
-        <v>-2.2551947215774181e-005</v>
+        <v>-2.4857347083338994e-005</v>
       </c>
       <c r="J38">
-        <v>3.869224932268373e-005</v>
+        <v>4.9999387739772805e-005</v>
       </c>
       <c r="K38">
-        <v>9.1952183886822832e-007</v>
+        <v>-4.5809783189185117e-006</v>
       </c>
       <c r="L38">
-        <v>2.7187844071529653e-005</v>
+        <v>2.688945968248158e-005</v>
       </c>
       <c r="M38">
-        <v>-8.558915722435903e-006</v>
+        <v>-1.0022660543728161e-005</v>
       </c>
       <c r="N38">
-        <v>2.1431832186185338e-005</v>
+        <v>-8.9782770100952898e-006</v>
       </c>
       <c r="O38">
-        <v>-1.2597984353376304e-006</v>
+        <v>-3.0443866844916275e-005</v>
       </c>
       <c r="P38">
-        <v>7.0981289341343979e-007</v>
+        <v>-1.7533332889775854e-005</v>
       </c>
       <c r="Q38">
-        <v>-1.9778177244917825e-006</v>
+        <v>-2.6417359465770262e-005</v>
       </c>
       <c r="R38">
-        <v>-1.6811122165266929e-006</v>
+        <v>-8.740134791834287e-005</v>
       </c>
       <c r="S38">
-        <v>-2.9121498596975902e-007</v>
+        <v>-4.3537703964380468e-007</v>
       </c>
       <c r="T38">
-        <v>3.2559255936529875e-007</v>
+        <v>4.588815820395906e-007</v>
       </c>
       <c r="U38">
-        <v>-2.274446115493791e-005</v>
+        <v>-6.2428407644931814e-005</v>
       </c>
       <c r="V38">
-        <v>1.0048196464664547e-006</v>
+        <v>-3.0082986885877992e-005</v>
       </c>
       <c r="W38">
-        <v>2.3949861344967245e-006</v>
+        <v>-3.3545968427638596e-005</v>
       </c>
       <c r="X38">
-        <v>1.2172442310589594e-006</v>
+        <v>-3.6071372926431856e-005</v>
       </c>
       <c r="Y38">
-        <v>4.7184293760651032e-006</v>
+        <v>6.7178253239322673e-006</v>
       </c>
       <c r="Z38">
-        <v>1.8321008126630678e-005</v>
+        <v>2.0566109562185455e-005</v>
       </c>
       <c r="AA38">
-        <v>5.7986871772275296e-006</v>
+        <v>1.0153964018569367e-005</v>
       </c>
       <c r="AB38">
-        <v>2.034791693589146e-006</v>
+        <v>-2.7424139002368332e-006</v>
       </c>
       <c r="AC38">
-        <v>4.1726784370255419e-005</v>
+        <v>6.3257219955537448e-005</v>
       </c>
       <c r="AD38">
-        <v>3.6530697835527432e-005</v>
+        <v>3.8669777341555943e-005</v>
       </c>
       <c r="AE38">
-        <v>6.5291188244552306e-006</v>
+        <v>1.9976263603420775e-005</v>
       </c>
       <c r="AF38">
-        <v>3.5825742213308896e-005</v>
+        <v>2.8469741865013473e-005</v>
       </c>
       <c r="AG38">
-        <v>6.1780198984726477e-006</v>
+        <v>1.2150099578316103e-005</v>
       </c>
       <c r="AH38">
-        <v>3.8418489417236037e-005</v>
+        <v>3.5195521248497454e-005</v>
       </c>
       <c r="AI38">
-        <v>1.1509480802379966e-005</v>
+        <v>-7.0821478250976465e-007</v>
       </c>
       <c r="AJ38">
-        <v>1.1356176633436384e-005</v>
+        <v>2.1656733642858348e-005</v>
       </c>
       <c r="AK38">
-        <v>2.5882291728958502e-005</v>
+        <v>2.2917204746696876e-005</v>
       </c>
       <c r="AL38">
-        <v>-2.1708913701458711e-005</v>
+        <v>-2.5447366411689566e-005</v>
       </c>
       <c r="AM38">
-        <v>0.00089862313286534349</v>
+        <v>0.0010128292213331396</v>
       </c>
       <c r="AN38">
-        <v>0.0001193654518040392</v>
+        <v>0.00012717129607673562</v>
       </c>
       <c r="AO38">
-        <v>-5.1667975644205459e-005</v>
+        <v>-6.405161412790436e-005</v>
       </c>
       <c r="AP38">
-        <v>-4.7764547992832324e-005</v>
+        <v>-3.3860108883625265e-005</v>
       </c>
       <c r="AQ38">
-        <v>6.9566571328999265e-006</v>
+        <v>7.3037320864195699e-006</v>
       </c>
       <c r="AR38">
-        <v>0.00028141595745595748</v>
+        <v>0.0003942342501973724</v>
       </c>
     </row>
     <row r="39">
@@ -5575,133 +5575,133 @@
         <v>52</v>
       </c>
       <c r="B39">
-        <v>-0.0040669580400411005</v>
+        <v>-0.022453996442778876</v>
       </c>
       <c r="C39">
-        <v>-1.8436763278969418e-006</v>
+        <v>-4.6263798001906424e-006</v>
       </c>
       <c r="D39">
-        <v>-2.5125921005398887e-006</v>
+        <v>-4.1721003046750409e-006</v>
       </c>
       <c r="E39">
-        <v>1.7383427903372448e-008</v>
+        <v>3.7193788054851373e-008</v>
       </c>
       <c r="F39">
-        <v>1.1380626673533774e-005</v>
+        <v>-5.2194278313286786e-006</v>
       </c>
       <c r="G39">
-        <v>3.3310426357166672e-005</v>
+        <v>1.8928164114159063e-005</v>
       </c>
       <c r="H39">
-        <v>1.0148412724088668e-005</v>
+        <v>-2.3311382286742011e-005</v>
       </c>
       <c r="I39">
-        <v>5.1251596970826167e-005</v>
+        <v>1.6333941158872402e-005</v>
       </c>
       <c r="J39">
-        <v>5.0491794858513117e-005</v>
+        <v>3.2302692425942542e-005</v>
       </c>
       <c r="K39">
-        <v>3.1295935031665163e-005</v>
+        <v>3.1529328078946472e-006</v>
       </c>
       <c r="L39">
-        <v>4.0787884889321026e-005</v>
+        <v>1.6892956007167486e-005</v>
       </c>
       <c r="M39">
-        <v>3.7357891695974723e-005</v>
+        <v>4.3089916938325568e-005</v>
       </c>
       <c r="N39">
-        <v>2.5851085616417459e-005</v>
+        <v>2.8764268275706362e-005</v>
       </c>
       <c r="O39">
-        <v>-1.5569390147192764e-008</v>
+        <v>-5.4718112438425582e-006</v>
       </c>
       <c r="P39">
-        <v>3.9077910141636622e-005</v>
+        <v>4.0653882754113316e-005</v>
       </c>
       <c r="Q39">
-        <v>4.8972409429167156e-005</v>
+        <v>4.794313342363256e-005</v>
       </c>
       <c r="R39">
-        <v>-1.2975361294483118e-005</v>
+        <v>-2.6548707415788414e-005</v>
       </c>
       <c r="S39">
-        <v>-1.0712565992968563e-006</v>
+        <v>-8.5843833960773721e-007</v>
       </c>
       <c r="T39">
-        <v>1.2821756331147944e-006</v>
+        <v>1.6034020641304969e-006</v>
       </c>
       <c r="U39">
-        <v>-1.5538076929352753e-005</v>
+        <v>-3.197922235086267e-005</v>
       </c>
       <c r="V39">
-        <v>3.7290284315279751e-005</v>
+        <v>3.1343774996907443e-005</v>
       </c>
       <c r="W39">
-        <v>4.3464041864935512e-005</v>
+        <v>2.479204403048709e-005</v>
       </c>
       <c r="X39">
-        <v>3.2950879794847233e-005</v>
+        <v>3.1095124272513151e-005</v>
       </c>
       <c r="Y39">
-        <v>3.1818560463067259e-006</v>
+        <v>3.1385165109328633e-006</v>
       </c>
       <c r="Z39">
-        <v>2.0709937472939272e-005</v>
+        <v>8.5543599476870262e-006</v>
       </c>
       <c r="AA39">
-        <v>-4.6708153033118337e-005</v>
+        <v>-2.9249240436185031e-005</v>
       </c>
       <c r="AB39">
-        <v>-4.0369927433161795e-005</v>
+        <v>-3.7753771744656071e-005</v>
       </c>
       <c r="AC39">
-        <v>-3.3144436351797014e-006</v>
+        <v>3.9561312607833414e-005</v>
       </c>
       <c r="AD39">
-        <v>-4.3282254485336324e-005</v>
+        <v>-1.3648641224538855e-006</v>
       </c>
       <c r="AE39">
-        <v>-2.7336358460504942e-005</v>
+        <v>-1.3142188213072952e-005</v>
       </c>
       <c r="AF39">
-        <v>-9.6520469735784237e-006</v>
+        <v>6.804480587293307e-006</v>
       </c>
       <c r="AG39">
-        <v>-2.6267984352743533e-005</v>
+        <v>-3.153996104924661e-006</v>
       </c>
       <c r="AH39">
-        <v>9.7404579013808733e-007</v>
+        <v>7.249235149254233e-006</v>
       </c>
       <c r="AI39">
-        <v>-3.9208441362080233e-005</v>
+        <v>-4.0288353086371614e-005</v>
       </c>
       <c r="AJ39">
-        <v>-4.0701627739962905e-005</v>
+        <v>-2.1057852117538313e-005</v>
       </c>
       <c r="AK39">
-        <v>-4.6113126984487104e-005</v>
+        <v>-3.5590691236426743e-005</v>
       </c>
       <c r="AL39">
-        <v>-2.5379281559476691e-005</v>
+        <v>-2.7346966961911284e-005</v>
       </c>
       <c r="AM39">
-        <v>0.0001193654518040392</v>
+        <v>0.00012717129607673562</v>
       </c>
       <c r="AN39">
-        <v>0.0010070612901237482</v>
+        <v>0.0010914491018651341</v>
       </c>
       <c r="AO39">
-        <v>-7.6683268233654659e-005</v>
+        <v>-9.4842263013269459e-005</v>
       </c>
       <c r="AP39">
-        <v>-8.870764060941922e-005</v>
+        <v>-8.2896844308442808e-005</v>
       </c>
       <c r="AQ39">
-        <v>-1.6965470058798469e-006</v>
+        <v>-2.0048302954905257e-005</v>
       </c>
       <c r="AR39">
-        <v>0.00034807606700237669</v>
+        <v>0.00040090222642198009</v>
       </c>
     </row>
     <row r="40">
@@ -5709,133 +5709,133 @@
         <v>53</v>
       </c>
       <c r="B40">
-        <v>0.15208110299751612</v>
+        <v>0.13590542833970337</v>
       </c>
       <c r="C40">
-        <v>-1.4204625822098928e-005</v>
+        <v>-1.5382763588456706e-005</v>
       </c>
       <c r="D40">
-        <v>3.1794096558238958e-006</v>
+        <v>4.3760362831400668e-006</v>
       </c>
       <c r="E40">
-        <v>-2.7910049670628022e-008</v>
+        <v>-3.1435677844151087e-008</v>
       </c>
       <c r="F40">
-        <v>8.7384479165576794e-005</v>
+        <v>0.00010029161839558622</v>
       </c>
       <c r="G40">
-        <v>4.75949310102105e-005</v>
+        <v>6.1895639545434694e-005</v>
       </c>
       <c r="H40">
-        <v>-5.8842545785034826e-005</v>
+        <v>-7.9006280705703699e-005</v>
       </c>
       <c r="I40">
-        <v>-1.7766040377709645e-005</v>
+        <v>-4.2336294477487665e-005</v>
       </c>
       <c r="J40">
-        <v>-9.6767174759019502e-005</v>
+        <v>-0.0001402046376901985</v>
       </c>
       <c r="K40">
-        <v>5.4315215191140715e-005</v>
+        <v>5.1034847559638941e-005</v>
       </c>
       <c r="L40">
-        <v>-4.3524527080902604e-005</v>
+        <v>-6.3235109826288336e-005</v>
       </c>
       <c r="M40">
-        <v>-5.8412913859671729e-005</v>
+        <v>-0.00010603247255646357</v>
       </c>
       <c r="N40">
-        <v>-3.7940244664105496e-005</v>
+        <v>-5.4573577878855588e-005</v>
       </c>
       <c r="O40">
-        <v>-3.9989143034873889e-005</v>
+        <v>-8.0930963355587522e-005</v>
       </c>
       <c r="P40">
-        <v>0.00011525909412599361</v>
+        <v>0.00012373135501357198</v>
       </c>
       <c r="Q40">
-        <v>7.1003728473824663e-005</v>
+        <v>6.4535690093456695e-005</v>
       </c>
       <c r="R40">
-        <v>-2.1388941329578582e-005</v>
+        <v>-3.5504609063952509e-005</v>
       </c>
       <c r="S40">
-        <v>8.3875680710881582e-007</v>
+        <v>1.1665665695757725e-006</v>
       </c>
       <c r="T40">
-        <v>3.3868228428815622e-006</v>
+        <v>4.3872289432178702e-006</v>
       </c>
       <c r="U40">
-        <v>4.3517345419745158e-005</v>
+        <v>3.8012649383127161e-005</v>
       </c>
       <c r="V40">
-        <v>1.0082114372973131e-005</v>
+        <v>-7.1002114972978209e-006</v>
       </c>
       <c r="W40">
-        <v>3.5758038089570281e-005</v>
+        <v>7.7262241716620278e-006</v>
       </c>
       <c r="X40">
-        <v>4.5807146495905606e-005</v>
+        <v>3.6381671166443971e-006</v>
       </c>
       <c r="Y40">
-        <v>2.7631707915406007e-006</v>
+        <v>2.6593975610107229e-006</v>
       </c>
       <c r="Z40">
-        <v>2.2584203542119543e-005</v>
+        <v>1.7994488680800379e-005</v>
       </c>
       <c r="AA40">
-        <v>0.00034625239569195806</v>
+        <v>0.00040667310985996778</v>
       </c>
       <c r="AB40">
-        <v>0.00047547721163142227</v>
+        <v>0.00056897941243370031</v>
       </c>
       <c r="AC40">
-        <v>0.00030755465578035653</v>
+        <v>0.00036911767534070157</v>
       </c>
       <c r="AD40">
-        <v>0.0002972152685853544</v>
+        <v>0.00034527432085628524</v>
       </c>
       <c r="AE40">
-        <v>0.00021540578163028432</v>
+        <v>0.00025121291813554785</v>
       </c>
       <c r="AF40">
-        <v>0.00032992005705753864</v>
+        <v>0.00038515508749997448</v>
       </c>
       <c r="AG40">
-        <v>0.00033102985002223353</v>
+        <v>0.0004016707033665921</v>
       </c>
       <c r="AH40">
-        <v>0.0003540340035062531</v>
+        <v>0.0004122811006228266</v>
       </c>
       <c r="AI40">
-        <v>0.00032862238633554915</v>
+        <v>0.00037346088621774333</v>
       </c>
       <c r="AJ40">
-        <v>0.00032906654604927858</v>
+        <v>0.00038026104349897245</v>
       </c>
       <c r="AK40">
-        <v>0.00043457738567994589</v>
+        <v>0.00050836871260555761</v>
       </c>
       <c r="AL40">
-        <v>8.3143018422219784e-006</v>
+        <v>1.0737892507111869e-005</v>
       </c>
       <c r="AM40">
-        <v>-5.1667975644205459e-005</v>
+        <v>-6.405161412790436e-005</v>
       </c>
       <c r="AN40">
-        <v>-7.6683268233654659e-005</v>
+        <v>-9.4842263013269459e-005</v>
       </c>
       <c r="AO40">
-        <v>0.0017595724077621689</v>
+        <v>0.0020467706838353883</v>
       </c>
       <c r="AP40">
-        <v>0.00016067109441889537</v>
+        <v>0.00017511916118460944</v>
       </c>
       <c r="AQ40">
-        <v>0.00015503243756071069</v>
+        <v>0.00017546481009309901</v>
       </c>
       <c r="AR40">
-        <v>-0.00091471807646520506</v>
+        <v>-0.0010999821206434924</v>
       </c>
     </row>
     <row r="41">
@@ -5843,133 +5843,133 @@
         <v>54</v>
       </c>
       <c r="B41">
-        <v>-0.14820533464230745</v>
+        <v>-0.098354706674296799</v>
       </c>
       <c r="C41">
-        <v>8.6600509173494103e-005</v>
+        <v>8.8093084096739987e-005</v>
       </c>
       <c r="D41">
-        <v>-1.503287740570827e-006</v>
+        <v>-1.2946571286714252e-006</v>
       </c>
       <c r="E41">
-        <v>-7.060185963541953e-009</v>
+        <v>-4.4613305539511652e-009</v>
       </c>
       <c r="F41">
-        <v>0.00010780617953720152</v>
+        <v>0.00016719960752428005</v>
       </c>
       <c r="G41">
-        <v>3.5863422703233139e-005</v>
+        <v>7.8146814757587942e-005</v>
       </c>
       <c r="H41">
-        <v>0.0003492775354372567</v>
+        <v>0.00048721441514155874</v>
       </c>
       <c r="I41">
-        <v>-0.00031482890878425208</v>
+        <v>-0.00031563404324402215</v>
       </c>
       <c r="J41">
-        <v>2.8346627682554969e-005</v>
+        <v>4.9981873358811508e-005</v>
       </c>
       <c r="K41">
-        <v>-7.4172390560937277e-006</v>
+        <v>2.6819045759125467e-005</v>
       </c>
       <c r="L41">
-        <v>-0.00012865556881364897</v>
+        <v>-0.00012291969029934509</v>
       </c>
       <c r="M41">
-        <v>-0.00011146349452775687</v>
+        <v>-0.00017162079197778911</v>
       </c>
       <c r="N41">
-        <v>-4.6895061999656471e-005</v>
+        <v>-7.8984974460211783e-005</v>
       </c>
       <c r="O41">
-        <v>8.1378506141577657e-005</v>
+        <v>5.6097868507115959e-005</v>
       </c>
       <c r="P41">
-        <v>-3.8727182285099799e-005</v>
+        <v>-4.9457782564098861e-005</v>
       </c>
       <c r="Q41">
-        <v>3.4691242641461824e-005</v>
+        <v>1.312708388221305e-005</v>
       </c>
       <c r="R41">
-        <v>8.2308327370232429e-005</v>
+        <v>1.6338125590001227e-005</v>
       </c>
       <c r="S41">
-        <v>3.2586043201149949e-007</v>
+        <v>1.1815582784634849e-006</v>
       </c>
       <c r="T41">
-        <v>-2.9013074395084985e-006</v>
+        <v>-3.4976686572818025e-006</v>
       </c>
       <c r="U41">
-        <v>-5.1230759610730445e-005</v>
+        <v>-6.4855753695447336e-005</v>
       </c>
       <c r="V41">
-        <v>-7.1762802134276381e-005</v>
+        <v>-0.00012735181070724398</v>
       </c>
       <c r="W41">
-        <v>-0.00012217240604241484</v>
+        <v>-0.0001907798999700902</v>
       </c>
       <c r="X41">
-        <v>0.0001422823147644082</v>
+        <v>0.00011680430192955864</v>
       </c>
       <c r="Y41">
-        <v>1.0003287084237739e-005</v>
+        <v>9.2676325506488142e-006</v>
       </c>
       <c r="Z41">
-        <v>3.4339578234846572e-005</v>
+        <v>5.6032212269172835e-005</v>
       </c>
       <c r="AA41">
-        <v>0.00045606386192649073</v>
+        <v>0.00042653613757206023</v>
       </c>
       <c r="AB41">
-        <v>0.00032385066478538775</v>
+        <v>0.00034086033844387586</v>
       </c>
       <c r="AC41">
-        <v>0.00032796529678440504</v>
+        <v>0.0003493078803809193</v>
       </c>
       <c r="AD41">
-        <v>0.00033421090781490966</v>
+        <v>0.00035063666474183312</v>
       </c>
       <c r="AE41">
-        <v>0.00023724922766060641</v>
+        <v>0.00025745556175778983</v>
       </c>
       <c r="AF41">
-        <v>0.0003070246790552114</v>
+        <v>0.00033555524927157611</v>
       </c>
       <c r="AG41">
-        <v>0.00040433809938117957</v>
+        <v>0.00043844491449865309</v>
       </c>
       <c r="AH41">
-        <v>0.00038401008036990068</v>
+        <v>0.00040746498305542402</v>
       </c>
       <c r="AI41">
-        <v>0.00037940474563385394</v>
+        <v>0.00040064684333281704</v>
       </c>
       <c r="AJ41">
-        <v>0.00034834092666768718</v>
+        <v>0.00036953671517060899</v>
       </c>
       <c r="AK41">
-        <v>0.00040052508338801616</v>
+        <v>0.00043259280791338786</v>
       </c>
       <c r="AL41">
-        <v>1.2134805427321862e-005</v>
+        <v>1.1331890824418911e-005</v>
       </c>
       <c r="AM41">
-        <v>-4.7764547992832324e-005</v>
+        <v>-3.3860108883625265e-005</v>
       </c>
       <c r="AN41">
-        <v>-8.870764060941922e-005</v>
+        <v>-8.2896844308442808e-005</v>
       </c>
       <c r="AO41">
-        <v>0.00016067109441889537</v>
+        <v>0.00017511916118460944</v>
       </c>
       <c r="AP41">
-        <v>0.0039275309304730357</v>
+        <v>0.004091670375793389</v>
       </c>
       <c r="AQ41">
-        <v>0.00012451052888328348</v>
+        <v>0.00013001197998526646</v>
       </c>
       <c r="AR41">
-        <v>-0.00046333549332143231</v>
+        <v>-0.00049472177749748127</v>
       </c>
     </row>
     <row r="42">
@@ -5977,133 +5977,133 @@
         <v>55</v>
       </c>
       <c r="B42">
-        <v>-0.036496439624344568</v>
+        <v>-0.040950088925950673</v>
       </c>
       <c r="C42">
-        <v>-2.9853831091504644e-005</v>
+        <v>-3.256565125021845e-005</v>
       </c>
       <c r="D42">
-        <v>1.3586438275875595e-006</v>
+        <v>2.9664197279297112e-006</v>
       </c>
       <c r="E42">
-        <v>-1.1482967124046874e-008</v>
+        <v>-1.9718864686090522e-008</v>
       </c>
       <c r="F42">
-        <v>0.00030916124864551419</v>
+        <v>0.00039851319441228247</v>
       </c>
       <c r="G42">
-        <v>-1.0840675277494903e-005</v>
+        <v>-1.7705123841352098e-005</v>
       </c>
       <c r="H42">
-        <v>-2.9366031038672476e-005</v>
+        <v>-2.1844161501035204e-005</v>
       </c>
       <c r="I42">
-        <v>6.1191314515677273e-005</v>
+        <v>9.3065147360806531e-005</v>
       </c>
       <c r="J42">
-        <v>-9.6307066173570758e-006</v>
+        <v>-1.9265200884426091e-005</v>
       </c>
       <c r="K42">
-        <v>-2.5683171753813e-005</v>
+        <v>-3.3611662745310089e-005</v>
       </c>
       <c r="L42">
-        <v>-9.9899726318818241e-005</v>
+        <v>-0.00010893720246602911</v>
       </c>
       <c r="M42">
-        <v>-3.986919141736714e-005</v>
+        <v>1.1566786474190099e-005</v>
       </c>
       <c r="N42">
-        <v>6.7056466161502265e-005</v>
+        <v>0.00011508895384840147</v>
       </c>
       <c r="O42">
-        <v>-3.3865779494024397e-005</v>
+        <v>-2.9974449459499724e-005</v>
       </c>
       <c r="P42">
-        <v>5.010353978806996e-005</v>
+        <v>2.7124900873592216e-005</v>
       </c>
       <c r="Q42">
-        <v>7.6542786129071507e-005</v>
+        <v>6.0124255663574305e-005</v>
       </c>
       <c r="R42">
-        <v>0.00018379794660937143</v>
+        <v>0.00031194683469120505</v>
       </c>
       <c r="S42">
-        <v>5.0501977913672393e-007</v>
+        <v>5.7822382418539757e-007</v>
       </c>
       <c r="T42">
-        <v>1.4767093594554237e-006</v>
+        <v>1.7125742510849635e-006</v>
       </c>
       <c r="U42">
-        <v>2.4595279634770178e-005</v>
+        <v>4.4192741894875313e-005</v>
       </c>
       <c r="V42">
-        <v>3.4102191292039114e-005</v>
+        <v>6.7146047269941132e-005</v>
       </c>
       <c r="W42">
-        <v>2.6635442568804417e-005</v>
+        <v>5.9091613669990414e-005</v>
       </c>
       <c r="X42">
-        <v>4.7202699598200104e-006</v>
+        <v>1.847634351199339e-005</v>
       </c>
       <c r="Y42">
-        <v>1.5247869565932259e-005</v>
+        <v>1.4885622350689095e-005</v>
       </c>
       <c r="Z42">
-        <v>1.833381811899894e-006</v>
+        <v>3.2310732276846345e-006</v>
       </c>
       <c r="AA42">
-        <v>0.00015679943667678889</v>
+        <v>0.0001801290143543884</v>
       </c>
       <c r="AB42">
-        <v>0.00017284238330720681</v>
+        <v>0.00019285211886811151</v>
       </c>
       <c r="AC42">
-        <v>0.00012984242396120107</v>
+        <v>0.00014827495259978966</v>
       </c>
       <c r="AD42">
-        <v>0.00011865249555428333</v>
+        <v>0.00013240843373502206</v>
       </c>
       <c r="AE42">
-        <v>8.5640388843538965e-005</v>
+        <v>9.7964694079839826e-005</v>
       </c>
       <c r="AF42">
-        <v>6.7341297920779915e-005</v>
+        <v>8.1334805588733787e-005</v>
       </c>
       <c r="AG42">
-        <v>0.00011028588477638462</v>
+        <v>0.00013302587577027587</v>
       </c>
       <c r="AH42">
-        <v>0.00014618276502644962</v>
+        <v>0.00016470006754011466</v>
       </c>
       <c r="AI42">
-        <v>0.00012559078748121272</v>
+        <v>0.0001333008981011423</v>
       </c>
       <c r="AJ42">
-        <v>0.00014609613356185794</v>
+        <v>0.00015484823302541241</v>
       </c>
       <c r="AK42">
-        <v>0.00016109453152884831</v>
+        <v>0.00018508197948161365</v>
       </c>
       <c r="AL42">
-        <v>-3.0573299661988664e-006</v>
+        <v>-4.8508973518122782e-006</v>
       </c>
       <c r="AM42">
-        <v>6.9566571328999265e-006</v>
+        <v>7.3037320864195699e-006</v>
       </c>
       <c r="AN42">
-        <v>-1.6965470058798469e-006</v>
+        <v>-2.0048302954905257e-005</v>
       </c>
       <c r="AO42">
-        <v>0.00015503243756071069</v>
+        <v>0.00017546481009309901</v>
       </c>
       <c r="AP42">
-        <v>0.00012451052888328348</v>
+        <v>0.00013001197998526646</v>
       </c>
       <c r="AQ42">
-        <v>0.0021732424702782561</v>
+        <v>0.0023562015541280161</v>
       </c>
       <c r="AR42">
-        <v>-0.00031909147846374613</v>
+        <v>-0.00039015444207898229</v>
       </c>
     </row>
     <row r="43">
@@ -6111,133 +6111,133 @@
         <v>56</v>
       </c>
       <c r="B43">
-        <v>-2.6102864413392708</v>
+        <v>-2.6415002227624624</v>
       </c>
       <c r="C43">
-        <v>-7.9450841302348879e-005</v>
+        <v>-6.9261250709546818e-005</v>
       </c>
       <c r="D43">
-        <v>-0.00014555706351228976</v>
+        <v>-0.00014875875697339168</v>
       </c>
       <c r="E43">
-        <v>1.2758208535263078e-006</v>
+        <v>1.2858923047636232e-006</v>
       </c>
       <c r="F43">
-        <v>-0.0014299568639463463</v>
+        <v>-0.001642070453253288</v>
       </c>
       <c r="G43">
-        <v>-0.00067504910860638034</v>
+        <v>-0.00085379951980207804</v>
       </c>
       <c r="H43">
-        <v>-0.00076262092031300472</v>
+        <v>-0.00089514177615652828</v>
       </c>
       <c r="I43">
-        <v>-0.0010778048533915895</v>
+        <v>-0.0013819365227629179</v>
       </c>
       <c r="J43">
-        <v>-0.00076307716696935243</v>
+        <v>-0.0009244285236165294</v>
       </c>
       <c r="K43">
-        <v>-0.0011191812380152615</v>
+        <v>-0.0013257180498786228</v>
       </c>
       <c r="L43">
-        <v>-0.0011197535362246493</v>
+        <v>-0.0013669345585731907</v>
       </c>
       <c r="M43">
-        <v>-0.0015773779337714912</v>
+        <v>-0.0021289784604977893</v>
       </c>
       <c r="N43">
-        <v>-0.0010996729323705498</v>
+        <v>-0.0013618450006663604</v>
       </c>
       <c r="O43">
-        <v>-0.00073451033445564033</v>
+        <v>-0.00093452285064598022</v>
       </c>
       <c r="P43">
-        <v>-0.00034835238235100135</v>
+        <v>-0.00041412722166980738</v>
       </c>
       <c r="Q43">
-        <v>-0.00048754231826059771</v>
+        <v>-0.00056085186551675008</v>
       </c>
       <c r="R43">
-        <v>-0.0003356768476641236</v>
+        <v>-0.00028553703677698086</v>
       </c>
       <c r="S43">
-        <v>-3.2983725265745666e-005</v>
+        <v>-3.6233586246106934e-005</v>
       </c>
       <c r="T43">
-        <v>-3.0329957970758059e-005</v>
+        <v>-3.5586229727230072e-005</v>
       </c>
       <c r="U43">
-        <v>-0.00082412723064898322</v>
+        <v>-0.0010013012718396745</v>
       </c>
       <c r="V43">
-        <v>-0.00086799851914626702</v>
+        <v>-0.0011898007594459165</v>
       </c>
       <c r="W43">
-        <v>-0.0010128521456368141</v>
+        <v>-0.0013060491489696115</v>
       </c>
       <c r="X43">
-        <v>-0.0011496104685229536</v>
+        <v>-0.0015469890464635779</v>
       </c>
       <c r="Y43">
-        <v>6.9545374660529664e-005</v>
+        <v>9.6391757175422248e-005</v>
       </c>
       <c r="Z43">
-        <v>-3.9696038262219755e-005</v>
+        <v>-6.246885734528862e-005</v>
       </c>
       <c r="AA43">
-        <v>-0.00084337222398017089</v>
+        <v>-0.00097135406621512844</v>
       </c>
       <c r="AB43">
-        <v>-0.0009463620560112015</v>
+        <v>-0.0010810131861802076</v>
       </c>
       <c r="AC43">
-        <v>-0.00081244812388351858</v>
+        <v>-0.00095530970503672149</v>
       </c>
       <c r="AD43">
-        <v>-0.00083425548594079346</v>
+        <v>-0.00094956294404000907</v>
       </c>
       <c r="AE43">
-        <v>-0.00097246846857259293</v>
+        <v>-0.0011091362621227568</v>
       </c>
       <c r="AF43">
-        <v>-0.00075095060483252067</v>
+        <v>-0.0008715863496420365</v>
       </c>
       <c r="AG43">
-        <v>-0.00086337050717419069</v>
+        <v>-0.00090903362570042296</v>
       </c>
       <c r="AH43">
-        <v>-0.00081821065788280085</v>
+        <v>-0.0010129733688989428</v>
       </c>
       <c r="AI43">
-        <v>-0.00092809557796094309</v>
+        <v>-0.000991779301602816</v>
       </c>
       <c r="AJ43">
-        <v>-0.00065509772358266177</v>
+        <v>-0.00072346021065076169</v>
       </c>
       <c r="AK43">
-        <v>-0.00086353170123420336</v>
+        <v>-0.00097377242397340264</v>
       </c>
       <c r="AL43">
-        <v>-8.1144206722909157e-005</v>
+        <v>-9.4484547373245226e-005</v>
       </c>
       <c r="AM43">
-        <v>0.00028141595745595748</v>
+        <v>0.0003942342501973724</v>
       </c>
       <c r="AN43">
-        <v>0.00034807606700237669</v>
+        <v>0.00040090222642198009</v>
       </c>
       <c r="AO43">
-        <v>-0.00091471807646520506</v>
+        <v>-0.0010999821206434924</v>
       </c>
       <c r="AP43">
-        <v>-0.00046333549332143231</v>
+        <v>-0.00049472177749748127</v>
       </c>
       <c r="AQ43">
-        <v>-0.00031909147846374613</v>
+        <v>-0.00039015444207898229</v>
       </c>
       <c r="AR43">
-        <v>0.011167486877849495</v>
+        <v>0.012569363274011472</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_home_ownership.xlsx
+++ b/input/reg_home_ownership.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="62">
   <si>
     <t>Description:</t>
   </si>
@@ -207,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -266,6 +266,66 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -275,7 +335,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -325,11 +385,53 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -355,6 +457,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -368,7 +494,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -389,10 +515,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -405,7 +531,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
@@ -432,12 +558,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -452,7 +578,7 @@
         <v>60</v>
       </c>
       <c r="F4">
-        <v>47316.641588067927</v>
+        <v>47316.641588065271</v>
       </c>
     </row>
     <row r="5">
@@ -623,127 +749,127 @@
         <v>0.00027999834837959329</v>
       </c>
       <c r="D2">
-        <v>1.3782281936627096e-006</v>
+        <v>1.3782281936626274e-006</v>
       </c>
       <c r="E2">
-        <v>-5.278398467618439e-009</v>
+        <v>-5.2783984676178699e-009</v>
       </c>
       <c r="F2">
-        <v>4.3829754142323266e-005</v>
+        <v>4.38297541423233e-005</v>
       </c>
       <c r="G2">
-        <v>-3.0047062924649634e-005</v>
+        <v>-3.0047062924649746e-005</v>
       </c>
       <c r="H2">
-        <v>-1.9110215114272185e-005</v>
+        <v>-1.9110215114272259e-005</v>
       </c>
       <c r="I2">
-        <v>-6.2288857945440437e-005</v>
+        <v>-6.228885794544064e-005</v>
       </c>
       <c r="J2">
-        <v>-4.1743773505625406e-005</v>
+        <v>-4.1743773505625596e-005</v>
       </c>
       <c r="K2">
-        <v>5.7119741304956337e-005</v>
+        <v>5.7119741304956229e-005</v>
       </c>
       <c r="L2">
-        <v>0.00014079346106052565</v>
+        <v>0.00014079346106052486</v>
       </c>
       <c r="M2">
-        <v>-2.1015395207162641e-005</v>
+        <v>-2.1015395207162895e-005</v>
       </c>
       <c r="N2">
-        <v>-5.6043360543491884e-005</v>
+        <v>-5.6043360543492277e-005</v>
       </c>
       <c r="O2">
-        <v>-3.6913905125721386e-005</v>
+        <v>-3.6913905125722748e-005</v>
       </c>
       <c r="P2">
-        <v>-2.5296856216310698e-005</v>
+        <v>-2.529685621631081e-005</v>
       </c>
       <c r="Q2">
-        <v>-2.4638573741358446e-005</v>
+        <v>-2.4638573741358636e-005</v>
       </c>
       <c r="R2">
-        <v>-2.3444387672616781e-005</v>
+        <v>-2.3444387672616835e-005</v>
       </c>
       <c r="S2">
-        <v>-5.2859634024004762e-007</v>
+        <v>-5.2859634024005546e-007</v>
       </c>
       <c r="T2">
-        <v>-2.111075240515896e-006</v>
+        <v>-2.1110752405158985e-006</v>
       </c>
       <c r="U2">
-        <v>-4.1802062486350442e-005</v>
+        <v>-4.1802062486350557e-005</v>
       </c>
       <c r="V2">
-        <v>-4.226846860645582e-005</v>
+        <v>-4.2268468606455867e-005</v>
       </c>
       <c r="W2">
-        <v>-5.0666231693518638e-005</v>
+        <v>-5.0666231693519519e-005</v>
       </c>
       <c r="X2">
-        <v>-6.7680688689462028e-005</v>
+        <v>-6.7680688689462909e-005</v>
       </c>
       <c r="Y2">
-        <v>1.9172472073785821e-006</v>
+        <v>1.917247207378602e-006</v>
       </c>
       <c r="Z2">
-        <v>4.9133748646457759e-006</v>
+        <v>4.9133748646456811e-006</v>
       </c>
       <c r="AA2">
-        <v>1.4586778808205605e-005</v>
+        <v>1.4586778808205727e-005</v>
       </c>
       <c r="AB2">
-        <v>4.8348325666041706e-005</v>
+        <v>4.8348325666041652e-005</v>
       </c>
       <c r="AC2">
-        <v>4.1662813292447448e-006</v>
+        <v>4.1662813292441722e-006</v>
       </c>
       <c r="AD2">
-        <v>1.7452870443351564e-005</v>
+        <v>1.7452870443351544e-005</v>
       </c>
       <c r="AE2">
-        <v>6.6743433041048662e-006</v>
+        <v>6.6743433041047443e-006</v>
       </c>
       <c r="AF2">
-        <v>-9.2457802703926466e-007</v>
+        <v>-9.2457802703931549e-007</v>
       </c>
       <c r="AG2">
-        <v>1.4919103126229899e-005</v>
+        <v>1.4919103126229465e-005</v>
       </c>
       <c r="AH2">
-        <v>1.3612597189542542e-005</v>
+        <v>1.3612597189542371e-005</v>
       </c>
       <c r="AI2">
-        <v>5.8301133889744733e-005</v>
+        <v>5.8301133889744801e-005</v>
       </c>
       <c r="AJ2">
-        <v>5.0434960393527338e-005</v>
+        <v>5.0434960393527263e-005</v>
       </c>
       <c r="AK2">
-        <v>1.4316850098585939e-005</v>
+        <v>1.431685009858595e-005</v>
       </c>
       <c r="AL2">
-        <v>6.9577425603410914e-007</v>
+        <v>6.9577425603409474e-007</v>
       </c>
       <c r="AM2">
-        <v>2.3552594679521088e-006</v>
+        <v>2.355259467952119e-006</v>
       </c>
       <c r="AN2">
-        <v>-4.6263798001906424e-006</v>
+        <v>-4.6263798001905069e-006</v>
       </c>
       <c r="AO2">
-        <v>-1.5382763588456706e-005</v>
+        <v>-1.5382763588456804e-005</v>
       </c>
       <c r="AP2">
-        <v>8.8093084096739987e-005</v>
+        <v>8.809308409673996e-005</v>
       </c>
       <c r="AQ2">
-        <v>-3.256565125021845e-005</v>
+        <v>-3.2565651250218376e-005</v>
       </c>
       <c r="AR2">
-        <v>-6.9261250709546818e-005</v>
+        <v>-6.9261250709543417e-005</v>
       </c>
     </row>
     <row r="3">
@@ -754,130 +880,130 @@
         <v>0.00050998341665666391</v>
       </c>
       <c r="C3">
-        <v>1.3782281936627096e-006</v>
+        <v>1.3782281936626274e-006</v>
       </c>
       <c r="D3">
-        <v>5.9666242853704266e-006</v>
+        <v>5.966624285370801e-006</v>
       </c>
       <c r="E3">
-        <v>-5.7015500433933747e-008</v>
+        <v>-5.7015500433934203e-008</v>
       </c>
       <c r="F3">
         <v>1.4283732594481991e-005</v>
       </c>
       <c r="G3">
-        <v>2.1852599867218376e-006</v>
+        <v>2.1852599867222154e-006</v>
       </c>
       <c r="H3">
-        <v>-5.0654465609007045e-008</v>
+        <v>-5.0654465608383629e-008</v>
       </c>
       <c r="I3">
-        <v>3.186356349573391e-006</v>
+        <v>3.1863563495735485e-006</v>
       </c>
       <c r="J3">
-        <v>-4.9463363931125027e-006</v>
+        <v>-4.9463363931119656e-006</v>
       </c>
       <c r="K3">
-        <v>7.8714309045590841e-006</v>
+        <v>7.8714309045609815e-006</v>
       </c>
       <c r="L3">
-        <v>4.5199294331551765e-007</v>
+        <v>4.5199294331752681e-007</v>
       </c>
       <c r="M3">
-        <v>3.1221000919189724e-005</v>
+        <v>3.1221000919193119e-005</v>
       </c>
       <c r="N3">
-        <v>-4.8451324346025912e-006</v>
+        <v>-4.8451324346013546e-006</v>
       </c>
       <c r="O3">
-        <v>8.3856789702572369e-006</v>
+        <v>8.3856789702581483e-006</v>
       </c>
       <c r="P3">
-        <v>7.679434612894412e-007</v>
+        <v>7.6794346128919726e-007</v>
       </c>
       <c r="Q3">
-        <v>2.0142446136799905e-006</v>
+        <v>2.0142446136804784e-006</v>
       </c>
       <c r="R3">
-        <v>-2.3064223972200535e-007</v>
+        <v>-2.3064223972178851e-007</v>
       </c>
       <c r="S3">
-        <v>1.5294151081129712e-007</v>
+        <v>1.5294151081130877e-007</v>
       </c>
       <c r="T3">
-        <v>8.1297443753781934e-008</v>
+        <v>8.1297443753801257e-008</v>
       </c>
       <c r="U3">
-        <v>9.1431235299073356e-008</v>
+        <v>9.1431235300760646e-008</v>
       </c>
       <c r="V3">
-        <v>-4.1640705650681992e-006</v>
+        <v>-4.164070565066024e-006</v>
       </c>
       <c r="W3">
-        <v>-1.1421700110895525e-005</v>
+        <v>-1.1421700110894563e-005</v>
       </c>
       <c r="X3">
-        <v>-1.4565289128997498e-005</v>
+        <v>-1.4565289128993405e-005</v>
       </c>
       <c r="Y3">
-        <v>-4.0173526973749299e-007</v>
+        <v>-4.017352697375687e-007</v>
       </c>
       <c r="Z3">
-        <v>1.6528686182612116e-006</v>
+        <v>1.6528686182612793e-006</v>
       </c>
       <c r="AA3">
-        <v>1.1045635412607635e-006</v>
+        <v>1.1045635412611802e-006</v>
       </c>
       <c r="AB3">
-        <v>1.9078451432136867e-006</v>
+        <v>1.9078451432141203e-006</v>
       </c>
       <c r="AC3">
-        <v>-1.5330894462409858e-006</v>
+        <v>-1.533089446239556e-006</v>
       </c>
       <c r="AD3">
-        <v>1.6505894576776775e-006</v>
+        <v>1.6505894576770522e-006</v>
       </c>
       <c r="AE3">
-        <v>-1.7110537181407257e-006</v>
+        <v>-1.7110537181401226e-006</v>
       </c>
       <c r="AF3">
-        <v>-7.9883507211689906e-008</v>
+        <v>-7.9883507211378198e-008</v>
       </c>
       <c r="AG3">
-        <v>-7.8844860095415302e-007</v>
+        <v>-7.8844860095354485e-007</v>
       </c>
       <c r="AH3">
-        <v>2.2295222118078913e-006</v>
+        <v>2.229522211807871e-006</v>
       </c>
       <c r="AI3">
-        <v>3.5810226884147745e-007</v>
+        <v>3.5810226884189927e-007</v>
       </c>
       <c r="AJ3">
-        <v>-2.3689269384005123e-006</v>
+        <v>-2.368926938400453e-006</v>
       </c>
       <c r="AK3">
-        <v>1.3747387937357601e-006</v>
+        <v>1.3747387937359905e-006</v>
       </c>
       <c r="AL3">
-        <v>-1.2111370772023238e-007</v>
+        <v>-1.211137077203137e-007</v>
       </c>
       <c r="AM3">
-        <v>-1.4510760285588929e-006</v>
+        <v>-1.45107602855871e-006</v>
       </c>
       <c r="AN3">
-        <v>-4.1721003046750409e-006</v>
+        <v>-4.172100304674885e-006</v>
       </c>
       <c r="AO3">
-        <v>4.3760362831400668e-006</v>
+        <v>4.3760362831398635e-006</v>
       </c>
       <c r="AP3">
-        <v>-1.2946571286714252e-006</v>
+        <v>-1.2946571286715336e-006</v>
       </c>
       <c r="AQ3">
-        <v>2.9664197279297112e-006</v>
+        <v>2.9664197279297925e-006</v>
       </c>
       <c r="AR3">
-        <v>-0.00014875875697339168</v>
+        <v>-0.0001487587569733977</v>
       </c>
     </row>
     <row r="4">
@@ -888,130 +1014,130 @@
         <v>3.0993893055359874e-005</v>
       </c>
       <c r="C4">
-        <v>-5.278398467618439e-009</v>
+        <v>-5.2783984676178699e-009</v>
       </c>
       <c r="D4">
-        <v>-5.7015500433933747e-008</v>
+        <v>-5.7015500433934203e-008</v>
       </c>
       <c r="E4">
-        <v>5.9600342963523226e-010</v>
+        <v>5.9600342963523577e-010</v>
       </c>
       <c r="F4">
         <v>-1.074422395605e-007</v>
       </c>
       <c r="G4">
-        <v>-3.4322673133571372e-008</v>
+        <v>-3.4322673133575376e-008</v>
       </c>
       <c r="H4">
-        <v>2.7106495169775076e-008</v>
+        <v>2.7106495169768829e-008</v>
       </c>
       <c r="I4">
-        <v>8.0513292386083072e-009</v>
+        <v>8.0513292386062293e-009</v>
       </c>
       <c r="J4">
-        <v>7.0411545695360501e-008</v>
+        <v>7.0411545695354214e-008</v>
       </c>
       <c r="K4">
-        <v>-6.9200346870263668e-008</v>
+        <v>-6.9200346870282197e-008</v>
       </c>
       <c r="L4">
-        <v>2.599409488113338e-008</v>
+        <v>2.5994094881113011e-008</v>
       </c>
       <c r="M4">
-        <v>-1.9242184619714848e-007</v>
+        <v>-1.9242184619718053e-007</v>
       </c>
       <c r="N4">
-        <v>8.3548624238436732e-008</v>
+        <v>8.3548624238424848e-008</v>
       </c>
       <c r="O4">
-        <v>-1.7869038228465474e-007</v>
+        <v>-1.7869038228466205e-007</v>
       </c>
       <c r="P4">
-        <v>-1.270894148361265e-008</v>
+        <v>-1.2708941483610426e-008</v>
       </c>
       <c r="Q4">
-        <v>-6.2086123423845401e-008</v>
+        <v>-6.2086123423850218e-008</v>
       </c>
       <c r="R4">
-        <v>-2.2778854145536958e-009</v>
+        <v>-2.2778854145554957e-009</v>
       </c>
       <c r="S4">
-        <v>-3.0239205225700207e-010</v>
+        <v>-3.0239205225712532e-010</v>
       </c>
       <c r="T4">
-        <v>-1.4676985848761628e-009</v>
+        <v>-1.4676985848763547e-009</v>
       </c>
       <c r="U4">
-        <v>1.8363534191056456e-008</v>
+        <v>1.8363534191040468e-008</v>
       </c>
       <c r="V4">
-        <v>7.5860138125306047e-008</v>
+        <v>7.586013812528601e-008</v>
       </c>
       <c r="W4">
-        <v>1.2814808475640945e-007</v>
+        <v>1.2814808475640156e-007</v>
       </c>
       <c r="X4">
-        <v>1.4559625400088673e-007</v>
+        <v>1.4559625400084534e-007</v>
       </c>
       <c r="Y4">
-        <v>-1.8348439949019265e-009</v>
+        <v>-1.8348439949012003e-009</v>
       </c>
       <c r="Z4">
-        <v>-3.1040478989826164e-008</v>
+        <v>-3.1040478989826905e-008</v>
       </c>
       <c r="AA4">
-        <v>-5.1573874919431026e-009</v>
+        <v>-5.1573874919470466e-009</v>
       </c>
       <c r="AB4">
-        <v>-2.1319695933760214e-008</v>
+        <v>-2.1319695933764132e-008</v>
       </c>
       <c r="AC4">
-        <v>2.0522970470851614e-008</v>
+        <v>2.052297047083744e-008</v>
       </c>
       <c r="AD4">
-        <v>-1.163196309365136e-008</v>
+        <v>-1.1631963093645107e-008</v>
       </c>
       <c r="AE4">
-        <v>3.1711804310644824e-008</v>
+        <v>3.1711804310638842e-008</v>
       </c>
       <c r="AF4">
-        <v>3.714190287959945e-009</v>
+        <v>3.7141902879569274e-009</v>
       </c>
       <c r="AG4">
-        <v>4.3192795793339746e-009</v>
+        <v>4.3192795793279792e-009</v>
       </c>
       <c r="AH4">
-        <v>-2.6741717379863864e-008</v>
+        <v>-2.6741717379863639e-008</v>
       </c>
       <c r="AI4">
-        <v>-2.2986567658487526e-009</v>
+        <v>-2.2986567658527628e-009</v>
       </c>
       <c r="AJ4">
-        <v>2.0044812961463735e-008</v>
+        <v>2.0044812961462967e-008</v>
       </c>
       <c r="AK4">
-        <v>-1.1317478305566059e-008</v>
+        <v>-1.1317478305567859e-008</v>
       </c>
       <c r="AL4">
-        <v>-2.9702376529953202e-011</v>
+        <v>-2.9702376529185578e-011</v>
       </c>
       <c r="AM4">
-        <v>1.2819615368578351e-008</v>
+        <v>1.2819615368576234e-008</v>
       </c>
       <c r="AN4">
-        <v>3.7193788054851373e-008</v>
+        <v>3.7193788054849785e-008</v>
       </c>
       <c r="AO4">
-        <v>-3.1435677844151087e-008</v>
+        <v>-3.1435677844148917e-008</v>
       </c>
       <c r="AP4">
-        <v>-4.4613305539511652e-009</v>
+        <v>-4.4613305539501064e-009</v>
       </c>
       <c r="AQ4">
-        <v>-1.9718864686090522e-008</v>
+        <v>-1.971886468609084e-008</v>
       </c>
       <c r="AR4">
-        <v>1.2858923047636232e-006</v>
+        <v>1.2858923047636871e-006</v>
       </c>
     </row>
     <row r="5">
@@ -1022,7 +1148,7 @@
         <v>-0.18117423902097704</v>
       </c>
       <c r="C5">
-        <v>4.3829754142323266e-005</v>
+        <v>4.38297541423233e-005</v>
       </c>
       <c r="D5">
         <v>1.4283732594481991e-005</v>
@@ -1031,121 +1157,121 @@
         <v>-1.074422395605e-007</v>
       </c>
       <c r="F5">
-        <v>0.023575673551016793</v>
+        <v>0.023575673551016797</v>
       </c>
       <c r="G5">
-        <v>0.0008925819892052039</v>
+        <v>0.00089258198920520336</v>
       </c>
       <c r="H5">
-        <v>0.00085818404736183115</v>
+        <v>0.00085818404736183332</v>
       </c>
       <c r="I5">
-        <v>0.00097166672394532756</v>
+        <v>0.00097166672394532431</v>
       </c>
       <c r="J5">
-        <v>0.00094351453921162241</v>
+        <v>0.00094351453921161937</v>
       </c>
       <c r="K5">
-        <v>0.00092851519052453732</v>
+        <v>0.0009285151905245397</v>
       </c>
       <c r="L5">
-        <v>0.00095200092260827466</v>
+        <v>0.00095200092260827422</v>
       </c>
       <c r="M5">
-        <v>-0.00024001513471835423</v>
+        <v>-0.00024001513471834761</v>
       </c>
       <c r="N5">
-        <v>-6.4290986453170934e-005</v>
+        <v>-6.4290986453171802e-005</v>
       </c>
       <c r="O5">
-        <v>-7.2448380436126701e-005</v>
+        <v>-7.2448380436126485e-005</v>
       </c>
       <c r="P5">
-        <v>0.0001973315521787865</v>
+        <v>0.000197331552178784</v>
       </c>
       <c r="Q5">
-        <v>0.0001761194141308896</v>
+        <v>0.00017611941413088987</v>
       </c>
       <c r="R5">
-        <v>0.00034406786427301512</v>
+        <v>0.00034406786427301658</v>
       </c>
       <c r="S5">
-        <v>-1.8289953009510864e-006</v>
+        <v>-1.8289953009511215e-006</v>
       </c>
       <c r="T5">
-        <v>2.5130255296876655e-006</v>
+        <v>2.5130255296876511e-006</v>
       </c>
       <c r="U5">
-        <v>-0.00013568252562926625</v>
+        <v>-0.00013568252562926153</v>
       </c>
       <c r="V5">
-        <v>-0.0001106587141544848</v>
+        <v>-0.00011065871415447729</v>
       </c>
       <c r="W5">
-        <v>-5.5988895563068345e-005</v>
+        <v>-5.5988895563060105e-005</v>
       </c>
       <c r="X5">
-        <v>0.00028316271886620701</v>
+        <v>0.00028316271886621048</v>
       </c>
       <c r="Y5">
-        <v>3.8247655731721304e-006</v>
+        <v>3.8247655731720796e-006</v>
       </c>
       <c r="Z5">
-        <v>7.7175228406035532e-005</v>
+        <v>7.7175228406035478e-005</v>
       </c>
       <c r="AA5">
-        <v>-2.09485669032236e-005</v>
+        <v>-2.0948566903222733e-005</v>
       </c>
       <c r="AB5">
-        <v>7.4816698394393651e-005</v>
+        <v>7.4816698394393976e-005</v>
       </c>
       <c r="AC5">
-        <v>7.9931594919426674e-005</v>
+        <v>7.993159491942662e-005</v>
       </c>
       <c r="AD5">
-        <v>0.00013480050484371357</v>
+        <v>0.00013480050484371132</v>
       </c>
       <c r="AE5">
-        <v>0.00015314337615946578</v>
+        <v>0.00015314337615946654</v>
       </c>
       <c r="AF5">
-        <v>5.7110204037460566e-005</v>
+        <v>5.7110204037459875e-005</v>
       </c>
       <c r="AG5">
-        <v>8.7040917421662192e-005</v>
+        <v>8.7040917421663222e-005</v>
       </c>
       <c r="AH5">
-        <v>0.00010997163232206887</v>
+        <v>0.0001099716323220667</v>
       </c>
       <c r="AI5">
-        <v>8.963330669920557e-005</v>
+        <v>8.963330669920599e-005</v>
       </c>
       <c r="AJ5">
-        <v>2.0457253425828246e-005</v>
+        <v>2.0457253425826186e-005</v>
       </c>
       <c r="AK5">
-        <v>0.0001295253426587838</v>
+        <v>0.00012952534265878396</v>
       </c>
       <c r="AL5">
-        <v>2.454494799653033e-006</v>
+        <v>2.4544947996529246e-006</v>
       </c>
       <c r="AM5">
-        <v>3.8627978727757322e-005</v>
+        <v>3.8627978727757051e-005</v>
       </c>
       <c r="AN5">
-        <v>-5.2194278313286786e-006</v>
+        <v>-5.2194278313278113e-006</v>
       </c>
       <c r="AO5">
-        <v>0.00010029161839558622</v>
+        <v>0.00010029161839558601</v>
       </c>
       <c r="AP5">
-        <v>0.00016719960752428005</v>
+        <v>0.00016719960752427902</v>
       </c>
       <c r="AQ5">
-        <v>0.00039851319441228247</v>
+        <v>0.0003985131944122829</v>
       </c>
       <c r="AR5">
-        <v>-0.001642070453253288</v>
+        <v>-0.0016420704532532754</v>
       </c>
     </row>
     <row r="6">
@@ -1156,130 +1282,130 @@
         <v>-0.033338916422106325</v>
       </c>
       <c r="C6">
-        <v>-3.0047062924649634e-005</v>
+        <v>-3.0047062924649746e-005</v>
       </c>
       <c r="D6">
-        <v>2.1852599867218376e-006</v>
+        <v>2.1852599867222154e-006</v>
       </c>
       <c r="E6">
-        <v>-3.4322673133571372e-008</v>
+        <v>-3.4322673133575376e-008</v>
       </c>
       <c r="F6">
-        <v>0.0008925819892052039</v>
+        <v>0.00089258198920520336</v>
       </c>
       <c r="G6">
-        <v>0.0013198079712772837</v>
+        <v>0.0013198079712772833</v>
       </c>
       <c r="H6">
-        <v>0.0007597631061267813</v>
+        <v>0.00075976310612678195</v>
       </c>
       <c r="I6">
-        <v>0.00087727131993849399</v>
+        <v>0.00087727131993849084</v>
       </c>
       <c r="J6">
-        <v>0.00087949587512627678</v>
+        <v>0.00087949587512627353</v>
       </c>
       <c r="K6">
-        <v>0.00093465699626598883</v>
+        <v>0.00093465699626598731</v>
       </c>
       <c r="L6">
-        <v>0.0009025298862893929</v>
+        <v>0.00090252988628938802</v>
       </c>
       <c r="M6">
-        <v>-4.2371897196805881e-005</v>
+        <v>-4.2371897196808524e-005</v>
       </c>
       <c r="N6">
-        <v>-4.96573528976194e-005</v>
+        <v>-4.9657352897623452e-005</v>
       </c>
       <c r="O6">
-        <v>-4.8942203627644646e-005</v>
+        <v>-4.8942203627647296e-005</v>
       </c>
       <c r="P6">
-        <v>2.5948394020186381e-005</v>
+        <v>2.5948394020184674e-005</v>
       </c>
       <c r="Q6">
-        <v>3.6032988772732931e-005</v>
+        <v>3.6032988772732226e-005</v>
       </c>
       <c r="R6">
-        <v>7.7544270617507923e-005</v>
+        <v>7.7544270617508737e-005</v>
       </c>
       <c r="S6">
-        <v>-9.2089538807322488e-007</v>
+        <v>-9.2089538807325622e-007</v>
       </c>
       <c r="T6">
-        <v>-6.63481251449356e-007</v>
+        <v>-6.6348125144941911e-007</v>
       </c>
       <c r="U6">
-        <v>-2.6616280561899129e-005</v>
+        <v>-2.6616280561899563e-005</v>
       </c>
       <c r="V6">
-        <v>3.3974872992910529e-005</v>
+        <v>3.3974872992911695e-005</v>
       </c>
       <c r="W6">
-        <v>0.00015747990045400582</v>
+        <v>0.00015747990045401059</v>
       </c>
       <c r="X6">
-        <v>0.00037065696543726846</v>
+        <v>0.00037065696543726379</v>
       </c>
       <c r="Y6">
-        <v>-7.8086964854894302e-006</v>
+        <v>-7.8086964854892676e-006</v>
       </c>
       <c r="Z6">
-        <v>-3.9563504319354832e-005</v>
+        <v>-3.9563504319355103e-005</v>
       </c>
       <c r="AA6">
-        <v>2.1099303147705569e-005</v>
+        <v>2.1099303147705312e-005</v>
       </c>
       <c r="AB6">
-        <v>5.8517165327780555e-005</v>
+        <v>5.8517165327780013e-005</v>
       </c>
       <c r="AC6">
-        <v>6.1187453167548282e-005</v>
+        <v>6.1187453167544758e-005</v>
       </c>
       <c r="AD6">
-        <v>6.5405406941513786e-005</v>
+        <v>6.5405406941513393e-005</v>
       </c>
       <c r="AE6">
-        <v>-2.4563141838224883e-005</v>
+        <v>-2.456314183822575e-005</v>
       </c>
       <c r="AF6">
-        <v>4.3059488357400921e-005</v>
+        <v>4.3059488357399403e-005</v>
       </c>
       <c r="AG6">
-        <v>6.2684186318883307e-005</v>
+        <v>6.2684186318882968e-005</v>
       </c>
       <c r="AH6">
-        <v>5.2049254081877014e-005</v>
+        <v>5.2049254081875157e-005</v>
       </c>
       <c r="AI6">
-        <v>7.8461982076474362e-005</v>
+        <v>7.8461982076473725e-005</v>
       </c>
       <c r="AJ6">
-        <v>-1.1715212806015348e-005</v>
+        <v>-1.1715212806017266e-005</v>
       </c>
       <c r="AK6">
-        <v>3.7137573823124481e-005</v>
+        <v>3.7137573823123885e-005</v>
       </c>
       <c r="AL6">
-        <v>-2.5129145492207836e-006</v>
+        <v>-2.5129145492206752e-006</v>
       </c>
       <c r="AM6">
-        <v>1.5017072349810152e-005</v>
+        <v>1.5017072349809529e-005</v>
       </c>
       <c r="AN6">
-        <v>1.8928164114159063e-005</v>
+        <v>1.8928164114159605e-005</v>
       </c>
       <c r="AO6">
-        <v>6.1895639545434694e-005</v>
+        <v>6.1895639545434748e-005</v>
       </c>
       <c r="AP6">
-        <v>7.8146814757587942e-005</v>
+        <v>7.814681475758702e-005</v>
       </c>
       <c r="AQ6">
-        <v>-1.7705123841352098e-005</v>
+        <v>-1.77051238413518e-005</v>
       </c>
       <c r="AR6">
-        <v>-0.00085379951980207804</v>
+        <v>-0.00085379951980205484</v>
       </c>
     </row>
     <row r="7">
@@ -1290,130 +1416,130 @@
         <v>0.012414359701786516</v>
       </c>
       <c r="C7">
-        <v>-1.9110215114272185e-005</v>
+        <v>-1.9110215114272259e-005</v>
       </c>
       <c r="D7">
-        <v>-5.0654465609007045e-008</v>
+        <v>-5.0654465608383629e-008</v>
       </c>
       <c r="E7">
-        <v>2.7106495169775076e-008</v>
+        <v>2.7106495169768829e-008</v>
       </c>
       <c r="F7">
-        <v>0.00085818404736183115</v>
+        <v>0.00085818404736183332</v>
       </c>
       <c r="G7">
-        <v>0.0007597631061267813</v>
+        <v>0.00075976310612678195</v>
       </c>
       <c r="H7">
-        <v>0.0016770422236972282</v>
+        <v>0.0016770422236972286</v>
       </c>
       <c r="I7">
-        <v>0.00078821475415920197</v>
+        <v>0.00078821475415919893</v>
       </c>
       <c r="J7">
-        <v>0.00082766250663657336</v>
+        <v>0.0008276625066365701</v>
       </c>
       <c r="K7">
-        <v>0.00076439104703266379</v>
+        <v>0.00076439104703266249</v>
       </c>
       <c r="L7">
-        <v>0.00077525916244256823</v>
+        <v>0.00077525916244256389</v>
       </c>
       <c r="M7">
-        <v>9.4830053936788411e-005</v>
+        <v>9.483005393678528e-005</v>
       </c>
       <c r="N7">
-        <v>4.0645165692777256e-005</v>
+        <v>4.0645165692773956e-005</v>
       </c>
       <c r="O7">
-        <v>-4.8580811496723205e-005</v>
+        <v>-4.8580811496725129e-005</v>
       </c>
       <c r="P7">
-        <v>-4.6168277448304263e-006</v>
+        <v>-4.6168277448317815e-006</v>
       </c>
       <c r="Q7">
-        <v>1.8229716450658245e-005</v>
+        <v>1.822971645065735e-005</v>
       </c>
       <c r="R7">
-        <v>2.8842976648460516e-005</v>
+        <v>2.884297664846122e-005</v>
       </c>
       <c r="S7">
-        <v>5.0390719465660914e-007</v>
+        <v>5.0390719465656679e-007</v>
       </c>
       <c r="T7">
-        <v>-1.3200867165801667e-006</v>
+        <v>-1.3200867165802218e-006</v>
       </c>
       <c r="U7">
-        <v>-4.4419594255488008e-005</v>
+        <v>-4.4419594255488645e-005</v>
       </c>
       <c r="V7">
-        <v>-3.9700452207297517e-005</v>
+        <v>-3.9700452207296283e-005</v>
       </c>
       <c r="W7">
-        <v>-2.4618417597373687e-006</v>
+        <v>-2.4618417597330319e-006</v>
       </c>
       <c r="X7">
-        <v>0.00021564468405084914</v>
+        <v>0.00021564468405084404</v>
       </c>
       <c r="Y7">
-        <v>1.1453377564667509e-005</v>
+        <v>1.1453377564667655e-005</v>
       </c>
       <c r="Z7">
-        <v>-5.1553080450806416e-005</v>
+        <v>-5.1553080450806796e-005</v>
       </c>
       <c r="AA7">
-        <v>-3.0852490993212906e-005</v>
+        <v>-3.0852490993213083e-005</v>
       </c>
       <c r="AB7">
-        <v>-7.1957525722399739e-006</v>
+        <v>-7.1957525722406515e-006</v>
       </c>
       <c r="AC7">
-        <v>1.1450031033868049e-005</v>
+        <v>1.145003103386485e-005</v>
       </c>
       <c r="AD7">
-        <v>1.4892552454762322e-005</v>
+        <v>1.4892552454762054e-005</v>
       </c>
       <c r="AE7">
-        <v>7.7127984679595263e-006</v>
+        <v>7.7127984679586047e-006</v>
       </c>
       <c r="AF7">
-        <v>-2.2166076240639593e-006</v>
+        <v>-2.21660762406545e-006</v>
       </c>
       <c r="AG7">
-        <v>8.2950318306736807e-006</v>
+        <v>8.2950318306732403e-006</v>
       </c>
       <c r="AH7">
-        <v>1.7039702809658626e-005</v>
+        <v>1.7039702809656728e-005</v>
       </c>
       <c r="AI7">
-        <v>7.3917316703664762e-005</v>
+        <v>7.3917316703664274e-005</v>
       </c>
       <c r="AJ7">
-        <v>-5.2956930014984375e-005</v>
+        <v>-5.2956930014986205e-005</v>
       </c>
       <c r="AK7">
-        <v>8.9075732955111897e-006</v>
+        <v>8.9075732955107019e-006</v>
       </c>
       <c r="AL7">
-        <v>5.3365881955915622e-006</v>
+        <v>5.3365881955916571e-006</v>
       </c>
       <c r="AM7">
-        <v>-3.2755924613270802e-006</v>
+        <v>-3.2755924613277849e-006</v>
       </c>
       <c r="AN7">
-        <v>-2.3311382286742011e-005</v>
+        <v>-2.3311382286741712e-005</v>
       </c>
       <c r="AO7">
-        <v>-7.9006280705703699e-005</v>
+        <v>-7.9006280705703509e-005</v>
       </c>
       <c r="AP7">
-        <v>0.00048721441514155874</v>
+        <v>0.00048721441514155777</v>
       </c>
       <c r="AQ7">
-        <v>-2.1844161501035204e-005</v>
+        <v>-2.1844161501035042e-005</v>
       </c>
       <c r="AR7">
-        <v>-0.00089514177615652828</v>
+        <v>-0.00089514177615650464</v>
       </c>
     </row>
     <row r="8">
@@ -1424,130 +1550,130 @@
         <v>-0.2264272683971198</v>
       </c>
       <c r="C8">
-        <v>-6.2288857945440437e-005</v>
+        <v>-6.228885794544064e-005</v>
       </c>
       <c r="D8">
-        <v>3.186356349573391e-006</v>
+        <v>3.1863563495735485e-006</v>
       </c>
       <c r="E8">
-        <v>8.0513292386083072e-009</v>
+        <v>8.0513292386062293e-009</v>
       </c>
       <c r="F8">
-        <v>0.00097166672394532756</v>
+        <v>0.00097166672394532431</v>
       </c>
       <c r="G8">
-        <v>0.00087727131993849399</v>
+        <v>0.00087727131993849084</v>
       </c>
       <c r="H8">
-        <v>0.00078821475415920197</v>
+        <v>0.00078821475415919893</v>
       </c>
       <c r="I8">
-        <v>0.023989217829248261</v>
+        <v>0.02398921782924825</v>
       </c>
       <c r="J8">
-        <v>0.00098388636142415927</v>
+        <v>0.00098388636142415537</v>
       </c>
       <c r="K8">
-        <v>0.0008828953847017549</v>
+        <v>0.00088289538470175295</v>
       </c>
       <c r="L8">
-        <v>0.00096970569210961784</v>
+        <v>0.00096970569210961253</v>
       </c>
       <c r="M8">
-        <v>0.00019825386725749576</v>
+        <v>0.00019825386725749505</v>
       </c>
       <c r="N8">
-        <v>0.00014575623749065256</v>
+        <v>0.00014575623749064971</v>
       </c>
       <c r="O8">
-        <v>3.0273762155107641e-005</v>
+        <v>3.0273762155106763e-005</v>
       </c>
       <c r="P8">
-        <v>0.00010510891435513628</v>
+        <v>0.00010510891435513444</v>
       </c>
       <c r="Q8">
-        <v>0.00011701139869537612</v>
+        <v>0.00011701139869537536</v>
       </c>
       <c r="R8">
-        <v>0.00019329162416323298</v>
+        <v>0.00019329162416323407</v>
       </c>
       <c r="S8">
-        <v>5.3943887649995809e-007</v>
+        <v>5.3943887649991023e-007</v>
       </c>
       <c r="T8">
-        <v>1.4953105196428771e-006</v>
+        <v>1.4953105196428426e-006</v>
       </c>
       <c r="U8">
-        <v>-6.0305337685957077e-005</v>
+        <v>-6.0305337685956996e-005</v>
       </c>
       <c r="V8">
-        <v>3.0375240113230724e-005</v>
+        <v>3.0375240113234058e-005</v>
       </c>
       <c r="W8">
-        <v>0.00025648664510740732</v>
+        <v>0.00025648664510741453</v>
       </c>
       <c r="X8">
-        <v>0.00055756887930067658</v>
+        <v>0.00055756887930067116</v>
       </c>
       <c r="Y8">
-        <v>5.334721430239551e-006</v>
+        <v>5.3347214302397408e-006</v>
       </c>
       <c r="Z8">
-        <v>-2.1069270456002345e-005</v>
+        <v>-2.1069270456002616e-005</v>
       </c>
       <c r="AA8">
-        <v>-3.8454813066869875e-005</v>
+        <v>-3.8454813066869631e-005</v>
       </c>
       <c r="AB8">
-        <v>-1.7163599744755864e-005</v>
+        <v>-1.7163599744756406e-005</v>
       </c>
       <c r="AC8">
-        <v>9.8732372083621119e-005</v>
+        <v>9.8732372083617785e-005</v>
       </c>
       <c r="AD8">
-        <v>0.00019982728928884206</v>
+        <v>0.00019982728928884149</v>
       </c>
       <c r="AE8">
-        <v>-1.7878381275420043e-005</v>
+        <v>-1.7878381275420721e-005</v>
       </c>
       <c r="AF8">
-        <v>3.4066532533534111e-005</v>
+        <v>3.4066532533532946e-005</v>
       </c>
       <c r="AG8">
-        <v>2.9277263107849511e-005</v>
+        <v>2.9277263107849517e-005</v>
       </c>
       <c r="AH8">
-        <v>7.0805307919838198e-005</v>
+        <v>7.0805307919836395e-005</v>
       </c>
       <c r="AI8">
-        <v>3.4602105039228893e-005</v>
+        <v>3.4602105039228446e-005</v>
       </c>
       <c r="AJ8">
-        <v>-4.7534915596808612e-005</v>
+        <v>-4.7534915596810814e-005</v>
       </c>
       <c r="AK8">
-        <v>5.601103958479401e-005</v>
+        <v>5.6011039584793901e-005</v>
       </c>
       <c r="AL8">
-        <v>6.0198201151925109e-007</v>
+        <v>6.0198201151937306e-007</v>
       </c>
       <c r="AM8">
-        <v>-2.4857347083338994e-005</v>
+        <v>-2.4857347083339699e-005</v>
       </c>
       <c r="AN8">
-        <v>1.6333941158872402e-005</v>
+        <v>1.6333941158872618e-005</v>
       </c>
       <c r="AO8">
-        <v>-4.2336294477487665e-005</v>
+        <v>-4.2336294477487285e-005</v>
       </c>
       <c r="AP8">
-        <v>-0.00031563404324402215</v>
+        <v>-0.00031563404324402302</v>
       </c>
       <c r="AQ8">
-        <v>9.3065147360806531e-005</v>
+        <v>9.3065147360807128e-005</v>
       </c>
       <c r="AR8">
-        <v>-0.0013819365227629179</v>
+        <v>-0.0013819365227628949</v>
       </c>
     </row>
     <row r="9">
@@ -1558,130 +1684,130 @@
         <v>-0.16850602105957024</v>
       </c>
       <c r="C9">
-        <v>-4.1743773505625406e-005</v>
+        <v>-4.1743773505625596e-005</v>
       </c>
       <c r="D9">
-        <v>-4.9463363931125027e-006</v>
+        <v>-4.9463363931119656e-006</v>
       </c>
       <c r="E9">
-        <v>7.0411545695360501e-008</v>
+        <v>7.0411545695354214e-008</v>
       </c>
       <c r="F9">
-        <v>0.00094351453921162241</v>
+        <v>0.00094351453921161937</v>
       </c>
       <c r="G9">
-        <v>0.00087949587512627678</v>
+        <v>0.00087949587512627353</v>
       </c>
       <c r="H9">
-        <v>0.00082766250663657336</v>
+        <v>0.0008276625066365701</v>
       </c>
       <c r="I9">
-        <v>0.00098388636142415927</v>
+        <v>0.00098388636142415537</v>
       </c>
       <c r="J9">
-        <v>0.0019820990701685751</v>
+        <v>0.0019820990701685712</v>
       </c>
       <c r="K9">
-        <v>0.00088083670407906748</v>
+        <v>0.00088083670407906487</v>
       </c>
       <c r="L9">
-        <v>0.00096664489063724712</v>
+        <v>0.00096664489063724159</v>
       </c>
       <c r="M9">
-        <v>0.00017306320451280366</v>
+        <v>0.00017306320451280138</v>
       </c>
       <c r="N9">
-        <v>9.8447465793736089e-005</v>
+        <v>9.8447465793732674e-005</v>
       </c>
       <c r="O9">
-        <v>7.5955953665694741e-005</v>
+        <v>7.595595366569325e-005</v>
       </c>
       <c r="P9">
-        <v>3.0591208644005019e-005</v>
+        <v>3.0591208644003502e-005</v>
       </c>
       <c r="Q9">
-        <v>3.1416036478610807e-005</v>
+        <v>3.1416036478609994e-005</v>
       </c>
       <c r="R9">
-        <v>9.9815567753607209e-005</v>
+        <v>9.9815567753608293e-005</v>
       </c>
       <c r="S9">
-        <v>-6.3318059620109478e-007</v>
+        <v>-6.3318059620113713e-007</v>
       </c>
       <c r="T9">
-        <v>-1.1332049925488468e-006</v>
+        <v>-1.1332049925488955e-006</v>
       </c>
       <c r="U9">
-        <v>-2.5999556811430208e-005</v>
+        <v>-2.5999556811430262e-005</v>
       </c>
       <c r="V9">
-        <v>6.3707855740123353e-005</v>
+        <v>6.3707855740125874e-005</v>
       </c>
       <c r="W9">
-        <v>0.00029381187277655962</v>
+        <v>0.00029381187277656624</v>
       </c>
       <c r="X9">
-        <v>0.00053990245059271037</v>
+        <v>0.00053990245059270343</v>
       </c>
       <c r="Y9">
-        <v>2.8737524549438014e-006</v>
+        <v>2.8737524549439623e-006</v>
       </c>
       <c r="Z9">
-        <v>-2.9279214136346786e-005</v>
+        <v>-2.9279214136346949e-005</v>
       </c>
       <c r="AA9">
-        <v>2.8316877733636889e-005</v>
+        <v>2.8316877733636781e-005</v>
       </c>
       <c r="AB9">
-        <v>-2.4321333586669518e-005</v>
+        <v>-2.4321333586669843e-005</v>
       </c>
       <c r="AC9">
-        <v>8.7419944024424398e-005</v>
+        <v>8.7419944024420495e-005</v>
       </c>
       <c r="AD9">
-        <v>8.5762330607335748e-005</v>
+        <v>8.576233060733545e-005</v>
       </c>
       <c r="AE9">
-        <v>4.6440425210770724e-005</v>
+        <v>4.644042521076991e-005</v>
       </c>
       <c r="AF9">
-        <v>7.8426301734844681e-005</v>
+        <v>7.8426301734843421e-005</v>
       </c>
       <c r="AG9">
-        <v>6.6898236795609375e-005</v>
+        <v>6.6898236795609036e-005</v>
       </c>
       <c r="AH9">
-        <v>9.3364765904528245e-005</v>
+        <v>9.3364765904526618e-005</v>
       </c>
       <c r="AI9">
-        <v>8.0771753064403008e-005</v>
+        <v>8.0771753064402371e-005</v>
       </c>
       <c r="AJ9">
-        <v>4.7496736955574955e-006</v>
+        <v>4.7496736955553745e-006</v>
       </c>
       <c r="AK9">
-        <v>4.4931155737837401e-005</v>
+        <v>4.4931155737837239e-005</v>
       </c>
       <c r="AL9">
-        <v>-2.1481505128037657e-006</v>
+        <v>-2.1481505128036302e-006</v>
       </c>
       <c r="AM9">
-        <v>4.9999387739772805e-005</v>
+        <v>4.9999387739771992e-005</v>
       </c>
       <c r="AN9">
-        <v>3.2302692425942542e-005</v>
+        <v>3.2302692425942786e-005</v>
       </c>
       <c r="AO9">
-        <v>-0.0001402046376901985</v>
+        <v>-0.0001402046376901979</v>
       </c>
       <c r="AP9">
-        <v>4.9981873358811508e-005</v>
+        <v>4.9981873358810749e-005</v>
       </c>
       <c r="AQ9">
-        <v>-1.9265200884426091e-005</v>
+        <v>-1.9265200884425549e-005</v>
       </c>
       <c r="AR9">
-        <v>-0.0009244285236165294</v>
+        <v>-0.00092442852361650511</v>
       </c>
     </row>
     <row r="10">
@@ -1692,130 +1818,130 @@
         <v>-0.23309014993139543</v>
       </c>
       <c r="C10">
-        <v>5.7119741304956337e-005</v>
+        <v>5.7119741304956229e-005</v>
       </c>
       <c r="D10">
-        <v>7.8714309045590841e-006</v>
+        <v>7.8714309045609815e-006</v>
       </c>
       <c r="E10">
-        <v>-6.9200346870263668e-008</v>
+        <v>-6.9200346870282197e-008</v>
       </c>
       <c r="F10">
-        <v>0.00092851519052453732</v>
+        <v>0.0009285151905245397</v>
       </c>
       <c r="G10">
-        <v>0.00093465699626598883</v>
+        <v>0.00093465699626598731</v>
       </c>
       <c r="H10">
-        <v>0.00076439104703266379</v>
+        <v>0.00076439104703266249</v>
       </c>
       <c r="I10">
-        <v>0.0008828953847017549</v>
+        <v>0.00088289538470175295</v>
       </c>
       <c r="J10">
-        <v>0.00088083670407906748</v>
+        <v>0.00088083670407906487</v>
       </c>
       <c r="K10">
-        <v>0.001054228864298862</v>
+        <v>0.0010542288642988642</v>
       </c>
       <c r="L10">
-        <v>0.00096731272085377957</v>
+        <v>0.00096731272085377816</v>
       </c>
       <c r="M10">
-        <v>-3.9133337825911308e-005</v>
+        <v>-3.9133337825907418e-005</v>
       </c>
       <c r="N10">
-        <v>-4.8176425429376129e-005</v>
+        <v>-4.8176425429377918e-005</v>
       </c>
       <c r="O10">
-        <v>-6.677903870580838e-005</v>
+        <v>-6.6779038705809518e-005</v>
       </c>
       <c r="P10">
-        <v>2.4550854414299593e-005</v>
+        <v>2.4550854414297316e-005</v>
       </c>
       <c r="Q10">
-        <v>4.2911078734865656e-005</v>
+        <v>4.2911078734865764e-005</v>
       </c>
       <c r="R10">
-        <v>5.4183267296301378e-005</v>
+        <v>5.4183267296302679e-005</v>
       </c>
       <c r="S10">
-        <v>7.1070514033530672e-008</v>
+        <v>7.1070514033515001e-008</v>
       </c>
       <c r="T10">
-        <v>6.5177634143807304e-007</v>
+        <v>6.5177634143804552e-007</v>
       </c>
       <c r="U10">
-        <v>4.0904890860921788e-006</v>
+        <v>4.090489086095052e-006</v>
       </c>
       <c r="V10">
-        <v>4.7744001122612537e-005</v>
+        <v>4.7744001122618527e-005</v>
       </c>
       <c r="W10">
-        <v>0.00016013198282030923</v>
+        <v>0.00016013198282031633</v>
       </c>
       <c r="X10">
-        <v>0.00034642341845914537</v>
+        <v>0.00034642341845914732</v>
       </c>
       <c r="Y10">
-        <v>-4.8224622873501432e-007</v>
+        <v>-4.8224622873499907e-007</v>
       </c>
       <c r="Z10">
         <v>-3.4067901259253897e-005</v>
       </c>
       <c r="AA10">
-        <v>5.4067773522827763e-005</v>
+        <v>5.4067773522828183e-005</v>
       </c>
       <c r="AB10">
-        <v>7.6244204832872503e-005</v>
+        <v>7.6244204832872611e-005</v>
       </c>
       <c r="AC10">
-        <v>0.0001075158168526052</v>
+        <v>0.0001075158168526039</v>
       </c>
       <c r="AD10">
-        <v>9.6352853455409658e-005</v>
+        <v>9.6352853455408167e-005</v>
       </c>
       <c r="AE10">
-        <v>6.154551878967922e-005</v>
+        <v>6.1545518789679436e-005</v>
       </c>
       <c r="AF10">
-        <v>7.5388672424806392e-005</v>
+        <v>7.5388672424805552e-005</v>
       </c>
       <c r="AG10">
-        <v>7.6854999545582188e-005</v>
+        <v>7.6854999545582675e-005</v>
       </c>
       <c r="AH10">
-        <v>8.7393877995467327e-005</v>
+        <v>8.739387799546524e-005</v>
       </c>
       <c r="AI10">
-        <v>0.00012436222096174531</v>
+        <v>0.00012436222096174563</v>
       </c>
       <c r="AJ10">
-        <v>2.3603331651853174e-005</v>
+        <v>2.3603331651851074e-005</v>
       </c>
       <c r="AK10">
-        <v>4.8177857676390951e-005</v>
+        <v>4.8177857676390897e-005</v>
       </c>
       <c r="AL10">
-        <v>1.4487326934295051e-006</v>
+        <v>1.4487326934294509e-006</v>
       </c>
       <c r="AM10">
-        <v>-4.5809783189185117e-006</v>
+        <v>-4.5809783189190538e-006</v>
       </c>
       <c r="AN10">
-        <v>3.1529328078946472e-006</v>
+        <v>3.1529328078952435e-006</v>
       </c>
       <c r="AO10">
-        <v>5.1034847559638941e-005</v>
+        <v>5.103484755963867e-005</v>
       </c>
       <c r="AP10">
-        <v>2.6819045759125467e-005</v>
+        <v>2.6819045759124275e-005</v>
       </c>
       <c r="AQ10">
-        <v>-3.3611662745310089e-005</v>
+        <v>-3.3611662745309655e-005</v>
       </c>
       <c r="AR10">
-        <v>-0.0013257180498786228</v>
+        <v>-0.001325718049878608</v>
       </c>
     </row>
     <row r="11">
@@ -1826,130 +1952,130 @@
         <v>-0.30553247476495521</v>
       </c>
       <c r="C11">
-        <v>0.00014079346106052565</v>
+        <v>0.00014079346106052486</v>
       </c>
       <c r="D11">
-        <v>4.5199294331551765e-007</v>
+        <v>4.5199294331752681e-007</v>
       </c>
       <c r="E11">
-        <v>2.599409488113338e-008</v>
+        <v>2.5994094881113011e-008</v>
       </c>
       <c r="F11">
-        <v>0.00095200092260827466</v>
+        <v>0.00095200092260827422</v>
       </c>
       <c r="G11">
-        <v>0.0009025298862893929</v>
+        <v>0.00090252988628938802</v>
       </c>
       <c r="H11">
-        <v>0.00077525916244256823</v>
+        <v>0.00077525916244256389</v>
       </c>
       <c r="I11">
-        <v>0.00096970569210961784</v>
+        <v>0.00096970569210961253</v>
       </c>
       <c r="J11">
-        <v>0.00096664489063724712</v>
+        <v>0.00096664489063724159</v>
       </c>
       <c r="K11">
-        <v>0.00096731272085377957</v>
+        <v>0.00096731272085377816</v>
       </c>
       <c r="L11">
-        <v>0.0019971724888173071</v>
+        <v>0.0019971724888173011</v>
       </c>
       <c r="M11">
-        <v>0.00010595274845782678</v>
+        <v>0.00010595274845782773</v>
       </c>
       <c r="N11">
-        <v>9.486593289753504e-006</v>
+        <v>9.4865932897497229e-006</v>
       </c>
       <c r="O11">
-        <v>8.9400994553342952e-005</v>
+        <v>8.9400994553341624e-005</v>
       </c>
       <c r="P11">
-        <v>-1.3276604256051282e-005</v>
+        <v>-1.3276604256053396e-005</v>
       </c>
       <c r="Q11">
-        <v>7.4329532209340223e-006</v>
+        <v>7.4329532209332634e-006</v>
       </c>
       <c r="R11">
-        <v>0.00013607179998894052</v>
+        <v>0.00013607179998894215</v>
       </c>
       <c r="S11">
-        <v>1.787361506892389e-009</v>
+        <v>1.7873615068729072e-009</v>
       </c>
       <c r="T11">
-        <v>-2.3101791425125704e-007</v>
+        <v>-2.3101791425129304e-007</v>
       </c>
       <c r="U11">
-        <v>-1.330778390749244e-005</v>
+        <v>-1.3307783907490353e-005</v>
       </c>
       <c r="V11">
-        <v>0.00017941140256331299</v>
+        <v>0.00017941140256331751</v>
       </c>
       <c r="W11">
-        <v>0.00031256187880037832</v>
+        <v>0.00031256187880038689</v>
       </c>
       <c r="X11">
-        <v>0.00053061406795338717</v>
+        <v>0.00053061406795337979</v>
       </c>
       <c r="Y11">
-        <v>-1.5698585313602546e-005</v>
+        <v>-1.569858531360243e-005</v>
       </c>
       <c r="Z11">
-        <v>9.4514353176459185e-006</v>
+        <v>9.4514353176456474e-006</v>
       </c>
       <c r="AA11">
-        <v>2.8939937073308044e-005</v>
+        <v>2.8939937073308017e-005</v>
       </c>
       <c r="AB11">
         <v>3.6558440500630341e-005</v>
       </c>
       <c r="AC11">
-        <v>5.2709697111056895e-005</v>
+        <v>5.27096971110531e-005</v>
       </c>
       <c r="AD11">
-        <v>0.00011795259458065728</v>
+        <v>0.00011795259458065665</v>
       </c>
       <c r="AE11">
-        <v>1.3167178215708593e-007</v>
+        <v>1.3167178215648962e-007</v>
       </c>
       <c r="AF11">
-        <v>0.00010383663614040038</v>
+        <v>0.00010383663614039923</v>
       </c>
       <c r="AG11">
-        <v>5.4381361092423086e-005</v>
+        <v>5.4381361092422998e-005</v>
       </c>
       <c r="AH11">
-        <v>5.7208549644156969e-005</v>
+        <v>5.7208549644155438e-005</v>
       </c>
       <c r="AI11">
-        <v>8.0325162247492243e-005</v>
+        <v>8.032516224749185e-005</v>
       </c>
       <c r="AJ11">
-        <v>-1.3812228128396513e-005</v>
+        <v>-1.3812228128398858e-005</v>
       </c>
       <c r="AK11">
-        <v>1.2930378904404786e-005</v>
+        <v>1.2930378904405329e-005</v>
       </c>
       <c r="AL11">
-        <v>3.6238143179959982e-006</v>
+        <v>3.6238143179961066e-006</v>
       </c>
       <c r="AM11">
-        <v>2.688945968248158e-005</v>
+        <v>2.6889459682480658e-005</v>
       </c>
       <c r="AN11">
-        <v>1.6892956007167486e-005</v>
+        <v>1.6892956007167757e-005</v>
       </c>
       <c r="AO11">
-        <v>-6.3235109826288336e-005</v>
+        <v>-6.3235109826288065e-005</v>
       </c>
       <c r="AP11">
-        <v>-0.00012291969029934509</v>
+        <v>-0.00012291969029934623</v>
       </c>
       <c r="AQ11">
-        <v>-0.00010893720246602911</v>
+        <v>-0.00010893720246602835</v>
       </c>
       <c r="AR11">
-        <v>-0.0013669345585731907</v>
+        <v>-0.0013669345585731719</v>
       </c>
     </row>
     <row r="12">
@@ -1960,130 +2086,130 @@
         <v>0.16220851386968813</v>
       </c>
       <c r="C12">
-        <v>-2.1015395207162641e-005</v>
+        <v>-2.1015395207162895e-005</v>
       </c>
       <c r="D12">
-        <v>3.1221000919189724e-005</v>
+        <v>3.1221000919193119e-005</v>
       </c>
       <c r="E12">
-        <v>-1.9242184619714848e-007</v>
+        <v>-1.9242184619718053e-007</v>
       </c>
       <c r="F12">
-        <v>-0.00024001513471835423</v>
+        <v>-0.00024001513471834761</v>
       </c>
       <c r="G12">
-        <v>-4.2371897196805881e-005</v>
+        <v>-4.2371897196808524e-005</v>
       </c>
       <c r="H12">
-        <v>9.4830053936788411e-005</v>
+        <v>9.483005393678528e-005</v>
       </c>
       <c r="I12">
-        <v>0.00019825386725749576</v>
+        <v>0.00019825386725749505</v>
       </c>
       <c r="J12">
-        <v>0.00017306320451280366</v>
+        <v>0.00017306320451280138</v>
       </c>
       <c r="K12">
-        <v>-3.9133337825911308e-005</v>
+        <v>-3.9133337825907418e-005</v>
       </c>
       <c r="L12">
-        <v>0.00010595274845782678</v>
+        <v>0.00010595274845782773</v>
       </c>
       <c r="M12">
-        <v>0.0042349404892102968</v>
+        <v>0.0042349404892103272</v>
       </c>
       <c r="N12">
-        <v>0.0011525240865150673</v>
+        <v>0.0011525240865150742</v>
       </c>
       <c r="O12">
-        <v>0.00074301703871835914</v>
+        <v>0.0007430170387183727</v>
       </c>
       <c r="P12">
-        <v>5.299914436657574e-005</v>
+        <v>5.2999144366572596e-005</v>
       </c>
       <c r="Q12">
-        <v>8.1600316665843102e-005</v>
+        <v>8.1600316665846897e-005</v>
       </c>
       <c r="R12">
-        <v>-0.0027479995940856016</v>
+        <v>-0.0027479995940855977</v>
       </c>
       <c r="S12">
-        <v>7.6559243139081178e-007</v>
+        <v>7.6559243139099135e-007</v>
       </c>
       <c r="T12">
-        <v>-4.8698238867935072e-007</v>
+        <v>-4.8698238867911864e-007</v>
       </c>
       <c r="U12">
-        <v>0.00073880584348539734</v>
+        <v>0.00073880584348541372</v>
       </c>
       <c r="V12">
-        <v>0.0012232715306503108</v>
+        <v>0.0012232715306503311</v>
       </c>
       <c r="W12">
-        <v>0.001244540787666532</v>
+        <v>0.00124454078766655</v>
       </c>
       <c r="X12">
-        <v>0.0012435844642963705</v>
+        <v>0.0012435844642963826</v>
       </c>
       <c r="Y12">
-        <v>-7.7535588980698084e-005</v>
+        <v>-7.7535588980698355e-005</v>
       </c>
       <c r="Z12">
-        <v>-0.0001127040533805369</v>
+        <v>-0.00011270405338053647</v>
       </c>
       <c r="AA12">
-        <v>-4.5786824760092062e-005</v>
+        <v>-4.5786824760088809e-005</v>
       </c>
       <c r="AB12">
-        <v>-7.5309339545896032e-005</v>
+        <v>-7.5309339545891044e-005</v>
       </c>
       <c r="AC12">
-        <v>-2.1817353218621572e-005</v>
+        <v>-2.1817353218613956e-005</v>
       </c>
       <c r="AD12">
-        <v>-2.2707777568890011e-005</v>
+        <v>-2.270777756889348e-005</v>
       </c>
       <c r="AE12">
-        <v>-1.5651849468180466e-005</v>
+        <v>-1.5651849468175045e-005</v>
       </c>
       <c r="AF12">
-        <v>-5.1192621658569003e-005</v>
+        <v>-5.1192621658566347e-005</v>
       </c>
       <c r="AG12">
-        <v>-6.4028010656713336e-005</v>
+        <v>-6.4028010656706926e-005</v>
       </c>
       <c r="AH12">
-        <v>-5.1584734982397039e-005</v>
+        <v>-5.1584734982394546e-005</v>
       </c>
       <c r="AI12">
-        <v>-6.5751063532627009e-005</v>
+        <v>-6.5751063532624163e-005</v>
       </c>
       <c r="AJ12">
-        <v>-0.00012834369175097082</v>
+        <v>-0.00012834369175097074</v>
       </c>
       <c r="AK12">
-        <v>-8.5507285691666579e-006</v>
+        <v>-8.5507285691612369e-006</v>
       </c>
       <c r="AL12">
-        <v>-3.0699328490907461e-006</v>
+        <v>-3.0699328490908545e-006</v>
       </c>
       <c r="AM12">
-        <v>-1.0022660543728161e-005</v>
+        <v>-1.0022660543727185e-005</v>
       </c>
       <c r="AN12">
-        <v>4.3089916938325568e-005</v>
+        <v>4.3089916938325134e-005</v>
       </c>
       <c r="AO12">
         <v>-0.00010603247255646357</v>
       </c>
       <c r="AP12">
-        <v>-0.00017162079197778911</v>
+        <v>-0.00017162079197778943</v>
       </c>
       <c r="AQ12">
-        <v>1.1566786474190099e-005</v>
+        <v>1.1566786474192701e-005</v>
       </c>
       <c r="AR12">
-        <v>-0.0021289784604977893</v>
+        <v>-0.0021289784604978557</v>
       </c>
     </row>
     <row r="13">
@@ -2094,130 +2220,130 @@
         <v>-0.02378683159474285</v>
       </c>
       <c r="C13">
-        <v>-5.6043360543491884e-005</v>
+        <v>-5.6043360543492277e-005</v>
       </c>
       <c r="D13">
-        <v>-4.8451324346025912e-006</v>
+        <v>-4.8451324346013546e-006</v>
       </c>
       <c r="E13">
-        <v>8.3548624238436732e-008</v>
+        <v>8.3548624238424848e-008</v>
       </c>
       <c r="F13">
-        <v>-6.4290986453170934e-005</v>
+        <v>-6.4290986453171802e-005</v>
       </c>
       <c r="G13">
-        <v>-4.96573528976194e-005</v>
+        <v>-4.9657352897623452e-005</v>
       </c>
       <c r="H13">
-        <v>4.0645165692777256e-005</v>
+        <v>4.0645165692773956e-005</v>
       </c>
       <c r="I13">
-        <v>0.00014575623749065256</v>
+        <v>0.00014575623749064971</v>
       </c>
       <c r="J13">
-        <v>9.8447465793736089e-005</v>
+        <v>9.8447465793732674e-005</v>
       </c>
       <c r="K13">
-        <v>-4.8176425429376129e-005</v>
+        <v>-4.8176425429377918e-005</v>
       </c>
       <c r="L13">
-        <v>9.486593289753504e-006</v>
+        <v>9.4865932897497229e-006</v>
       </c>
       <c r="M13">
-        <v>0.0011525240865150673</v>
+        <v>0.0011525240865150742</v>
       </c>
       <c r="N13">
-        <v>0.00154101564131226</v>
+        <v>0.0015410156413122628</v>
       </c>
       <c r="O13">
-        <v>0.00084420989299218362</v>
+        <v>0.00084420989299219501</v>
       </c>
       <c r="P13">
-        <v>3.5294004281916569e-005</v>
+        <v>3.5294004281914075e-005</v>
       </c>
       <c r="Q13">
-        <v>3.6156786155918546e-005</v>
+        <v>3.6156786155920389e-005</v>
       </c>
       <c r="R13">
-        <v>7.1267337531774524e-006</v>
+        <v>7.1267337531804881e-006</v>
       </c>
       <c r="S13">
-        <v>3.1652204422735849e-006</v>
+        <v>3.1652204422737204e-006</v>
       </c>
       <c r="T13">
-        <v>2.5271800298096919e-006</v>
+        <v>2.5271800298098245e-006</v>
       </c>
       <c r="U13">
-        <v>0.00068206398847657946</v>
+        <v>0.00068206398847658889</v>
       </c>
       <c r="V13">
-        <v>0.0011391809011316698</v>
+        <v>0.0011391809011316823</v>
       </c>
       <c r="W13">
-        <v>0.0012113199633241381</v>
+        <v>0.0012113199633241544</v>
       </c>
       <c r="X13">
-        <v>0.0012343293384560815</v>
+        <v>0.0012343293384560789</v>
       </c>
       <c r="Y13">
-        <v>-7.2422524511325288e-005</v>
+        <v>-7.2422524511325234e-005</v>
       </c>
       <c r="Z13">
-        <v>-1.5189057460102194e-005</v>
+        <v>-1.518905746010176e-005</v>
       </c>
       <c r="AA13">
-        <v>-2.381389980264713e-005</v>
+        <v>-2.3813899802646154e-005</v>
       </c>
       <c r="AB13">
-        <v>-6.7511640797502e-005</v>
+        <v>-6.7511640797498964e-005</v>
       </c>
       <c r="AC13">
-        <v>2.4144081687174011e-005</v>
+        <v>2.4144081687175881e-005</v>
       </c>
       <c r="AD13">
-        <v>-6.8561985376150185e-006</v>
+        <v>-6.8561985376162721e-006</v>
       </c>
       <c r="AE13">
-        <v>5.0829659946405098e-005</v>
+        <v>5.0829659946407374e-005</v>
       </c>
       <c r="AF13">
-        <v>-3.0389947216074046e-005</v>
+        <v>-3.0389947216072908e-005</v>
       </c>
       <c r="AG13">
-        <v>3.3971703979008487e-006</v>
+        <v>3.3971703979050771e-006</v>
       </c>
       <c r="AH13">
-        <v>1.3344986052519672e-005</v>
+        <v>1.334498605252228e-005</v>
       </c>
       <c r="AI13">
-        <v>-3.5526186225770751e-005</v>
+        <v>-3.5526186225770073e-005</v>
       </c>
       <c r="AJ13">
-        <v>-4.2131290468233024e-005</v>
+        <v>-4.2131290468233728e-005</v>
       </c>
       <c r="AK13">
-        <v>-3.932946520510724e-005</v>
+        <v>-3.9329465205102795e-005</v>
       </c>
       <c r="AL13">
-        <v>-2.8486466540738318e-006</v>
+        <v>-2.8486466540735608e-006</v>
       </c>
       <c r="AM13">
-        <v>-8.9782770100952898e-006</v>
+        <v>-8.9782770100955067e-006</v>
       </c>
       <c r="AN13">
-        <v>2.8764268275706362e-005</v>
+        <v>2.876426827570517e-005</v>
       </c>
       <c r="AO13">
-        <v>-5.4573577878855588e-005</v>
+        <v>-5.4573577878854666e-005</v>
       </c>
       <c r="AP13">
-        <v>-7.8984974460211783e-005</v>
+        <v>-7.8984974460212108e-005</v>
       </c>
       <c r="AQ13">
-        <v>0.00011508895384840147</v>
+        <v>0.00011508895384840348</v>
       </c>
       <c r="AR13">
-        <v>-0.0013618450006663604</v>
+        <v>-0.0013618450006664066</v>
       </c>
     </row>
     <row r="14">
@@ -2228,130 +2354,130 @@
         <v>0.13362879746806683</v>
       </c>
       <c r="C14">
-        <v>-3.6913905125721386e-005</v>
+        <v>-3.6913905125722748e-005</v>
       </c>
       <c r="D14">
-        <v>8.3856789702572369e-006</v>
+        <v>8.3856789702581483e-006</v>
       </c>
       <c r="E14">
-        <v>-1.7869038228465474e-007</v>
+        <v>-1.7869038228466205e-007</v>
       </c>
       <c r="F14">
-        <v>-7.2448380436126701e-005</v>
+        <v>-7.2448380436126485e-005</v>
       </c>
       <c r="G14">
-        <v>-4.8942203627644646e-005</v>
+        <v>-4.8942203627647296e-005</v>
       </c>
       <c r="H14">
-        <v>-4.8580811496723205e-005</v>
+        <v>-4.8580811496725129e-005</v>
       </c>
       <c r="I14">
-        <v>3.0273762155107641e-005</v>
+        <v>3.0273762155106763e-005</v>
       </c>
       <c r="J14">
-        <v>7.5955953665694741e-005</v>
+        <v>7.595595366569325e-005</v>
       </c>
       <c r="K14">
-        <v>-6.677903870580838e-005</v>
+        <v>-6.6779038705809518e-005</v>
       </c>
       <c r="L14">
-        <v>8.9400994553342952e-005</v>
+        <v>8.9400994553341624e-005</v>
       </c>
       <c r="M14">
-        <v>0.00074301703871835914</v>
+        <v>0.0007430170387183727</v>
       </c>
       <c r="N14">
-        <v>0.00084420989299218362</v>
+        <v>0.00084420989299219501</v>
       </c>
       <c r="O14">
-        <v>0.0013841823088598683</v>
+        <v>0.0013841823088598761</v>
       </c>
       <c r="P14">
-        <v>5.9570786866506957e-005</v>
+        <v>5.9570786866505277e-005</v>
       </c>
       <c r="Q14">
-        <v>5.8382311306116028e-005</v>
+        <v>5.8382311306119389e-005</v>
       </c>
       <c r="R14">
-        <v>8.6535164948743355e-005</v>
+        <v>8.6535164948744981e-005</v>
       </c>
       <c r="S14">
-        <v>1.3109694415009711e-006</v>
+        <v>1.3109694415011456e-006</v>
       </c>
       <c r="T14">
-        <v>-7.5551999660274686e-007</v>
+        <v>-7.5551999660253595e-007</v>
       </c>
       <c r="U14">
-        <v>0.00048116415972502646</v>
+        <v>0.00048116415972503871</v>
       </c>
       <c r="V14">
-        <v>0.00083688150539680084</v>
+        <v>0.00083688150539681515</v>
       </c>
       <c r="W14">
-        <v>0.00098183880766435929</v>
+        <v>0.00098183880766437122</v>
       </c>
       <c r="X14">
-        <v>0.0010281791198004781</v>
+        <v>0.001028179119800495</v>
       </c>
       <c r="Y14">
-        <v>-8.3327383696171092e-005</v>
+        <v>-8.3327383696171349e-005</v>
       </c>
       <c r="Z14">
-        <v>1.1081674890348709e-005</v>
+        <v>1.108167489034936e-005</v>
       </c>
       <c r="AA14">
-        <v>-6.393419503143149e-005</v>
+        <v>-6.3934195031429376e-005</v>
       </c>
       <c r="AB14">
-        <v>-8.0433865819956455e-005</v>
+        <v>-8.0433865819952986e-005</v>
       </c>
       <c r="AC14">
-        <v>-2.6517319736276779e-005</v>
+        <v>-2.6517319736269379e-005</v>
       </c>
       <c r="AD14">
-        <v>-5.4597090472370632e-006</v>
+        <v>-5.4597090472407309e-006</v>
       </c>
       <c r="AE14">
-        <v>-1.6961982026322906e-005</v>
+        <v>-1.6961982026318624e-005</v>
       </c>
       <c r="AF14">
-        <v>-4.8780497296978476e-005</v>
+        <v>-4.878049729697628e-005</v>
       </c>
       <c r="AG14">
-        <v>-6.374754304186153e-006</v>
+        <v>-6.3747543041801832e-006</v>
       </c>
       <c r="AH14">
-        <v>1.7637862802154376e-005</v>
+        <v>1.7637862802156388e-005</v>
       </c>
       <c r="AI14">
-        <v>-3.6003823550613231e-005</v>
+        <v>-3.6003823550611713e-005</v>
       </c>
       <c r="AJ14">
-        <v>-7.8927664947620185e-005</v>
+        <v>-7.8927664947619426e-005</v>
       </c>
       <c r="AK14">
-        <v>-2.2218754609247874e-005</v>
+        <v>-2.2218754609244296e-005</v>
       </c>
       <c r="AL14">
-        <v>1.7658887970857962e-006</v>
+        <v>1.7658887970856336e-006</v>
       </c>
       <c r="AM14">
-        <v>-3.0443866844916275e-005</v>
+        <v>-3.0443866844915191e-005</v>
       </c>
       <c r="AN14">
-        <v>-5.4718112438425582e-006</v>
+        <v>-5.4718112438428834e-006</v>
       </c>
       <c r="AO14">
-        <v>-8.0930963355587522e-005</v>
+        <v>-8.0930963355588118e-005</v>
       </c>
       <c r="AP14">
-        <v>5.6097868507115959e-005</v>
+        <v>5.6097868507114983e-005</v>
       </c>
       <c r="AQ14">
-        <v>-2.9974449459499724e-005</v>
+        <v>-2.9974449459498585e-005</v>
       </c>
       <c r="AR14">
-        <v>-0.00093452285064598022</v>
+        <v>-0.00093452285064605405</v>
       </c>
     </row>
     <row r="15">
@@ -2362,130 +2488,130 @@
         <v>-0.16466634537223668</v>
       </c>
       <c r="C15">
-        <v>-2.5296856216310698e-005</v>
+        <v>-2.529685621631081e-005</v>
       </c>
       <c r="D15">
-        <v>7.679434612894412e-007</v>
+        <v>7.6794346128919726e-007</v>
       </c>
       <c r="E15">
-        <v>-1.270894148361265e-008</v>
+        <v>-1.2708941483610426e-008</v>
       </c>
       <c r="F15">
-        <v>0.0001973315521787865</v>
+        <v>0.000197331552178784</v>
       </c>
       <c r="G15">
-        <v>2.5948394020186381e-005</v>
+        <v>2.5948394020184674e-005</v>
       </c>
       <c r="H15">
-        <v>-4.6168277448304263e-006</v>
+        <v>-4.6168277448317815e-006</v>
       </c>
       <c r="I15">
-        <v>0.00010510891435513628</v>
+        <v>0.00010510891435513444</v>
       </c>
       <c r="J15">
-        <v>3.0591208644005019e-005</v>
+        <v>3.0591208644003502e-005</v>
       </c>
       <c r="K15">
-        <v>2.4550854414299593e-005</v>
+        <v>2.4550854414297316e-005</v>
       </c>
       <c r="L15">
-        <v>-1.3276604256051282e-005</v>
+        <v>-1.3276604256053396e-005</v>
       </c>
       <c r="M15">
-        <v>5.299914436657574e-005</v>
+        <v>5.2999144366572596e-005</v>
       </c>
       <c r="N15">
-        <v>3.5294004281916569e-005</v>
+        <v>3.5294004281914075e-005</v>
       </c>
       <c r="O15">
-        <v>5.9570786866506957e-005</v>
+        <v>5.9570786866505277e-005</v>
       </c>
       <c r="P15">
-        <v>0.00046160590175671739</v>
+        <v>0.00046160590175671674</v>
       </c>
       <c r="Q15">
         <v>0.00035950621854139949</v>
       </c>
       <c r="R15">
-        <v>0.0003452210129737648</v>
+        <v>0.00034522101297376501</v>
       </c>
       <c r="S15">
-        <v>5.4188540166182362e-007</v>
+        <v>5.4188540166178254e-007</v>
       </c>
       <c r="T15">
-        <v>3.0913841740410465e-008</v>
+        <v>3.0913841740402207e-008</v>
       </c>
       <c r="U15">
-        <v>3.0494360210134313e-005</v>
+        <v>3.0494360210134164e-005</v>
       </c>
       <c r="V15">
-        <v>2.829871391237196e-005</v>
+        <v>2.8298713912373058e-005</v>
       </c>
       <c r="W15">
-        <v>0.00010391853954084038</v>
+        <v>0.00010391853954084165</v>
       </c>
       <c r="X15">
-        <v>0.00016776162462602139</v>
+        <v>0.00016776162462602009</v>
       </c>
       <c r="Y15">
-        <v>-5.759060063784046e-007</v>
+        <v>-5.7590600637830762e-007</v>
       </c>
       <c r="Z15">
-        <v>-3.0115007396594559e-006</v>
+        <v>-3.0115007396596728e-006</v>
       </c>
       <c r="AA15">
-        <v>-2.799545736193258e-005</v>
+        <v>-2.7995457361932376e-005</v>
       </c>
       <c r="AB15">
-        <v>-3.5894578389401049e-005</v>
+        <v>-3.5894578389401266e-005</v>
       </c>
       <c r="AC15">
-        <v>-2.113688565160433e-005</v>
+        <v>-2.1136885651604577e-005</v>
       </c>
       <c r="AD15">
-        <v>-4.7830291953542181e-005</v>
+        <v>-4.7830291953543048e-005</v>
       </c>
       <c r="AE15">
-        <v>-3.3215351931366393e-005</v>
+        <v>-3.3215351931366624e-005</v>
       </c>
       <c r="AF15">
-        <v>-4.4925466177820861e-005</v>
+        <v>-4.4925466177821146e-005</v>
       </c>
       <c r="AG15">
-        <v>-2.7841507683270559e-005</v>
+        <v>-2.7841507683270233e-005</v>
       </c>
       <c r="AH15">
-        <v>-3.1691635280815236e-005</v>
+        <v>-3.1691635280815785e-005</v>
       </c>
       <c r="AI15">
-        <v>-7.7012783928613973e-005</v>
+        <v>-7.7012783928614366e-005</v>
       </c>
       <c r="AJ15">
-        <v>-5.3016544937652357e-005</v>
+        <v>-5.3016544937652845e-005</v>
       </c>
       <c r="AK15">
-        <v>-8.4943755631748826e-006</v>
+        <v>-8.494375563174747e-006</v>
       </c>
       <c r="AL15">
-        <v>-7.0892045033260566e-007</v>
+        <v>-7.0892045033263277e-007</v>
       </c>
       <c r="AM15">
-        <v>-1.7533332889775854e-005</v>
+        <v>-1.75333328897758e-005</v>
       </c>
       <c r="AN15">
-        <v>4.0653882754113316e-005</v>
+        <v>4.0653882754113234e-005</v>
       </c>
       <c r="AO15">
-        <v>0.00012373135501357198</v>
+        <v>0.00012373135501357209</v>
       </c>
       <c r="AP15">
-        <v>-4.9457782564098861e-005</v>
+        <v>-4.9457782564099199e-005</v>
       </c>
       <c r="AQ15">
-        <v>2.7124900873592216e-005</v>
+        <v>2.7124900873592311e-005</v>
       </c>
       <c r="AR15">
-        <v>-0.00041412722166980738</v>
+        <v>-0.00041412722166980429</v>
       </c>
     </row>
     <row r="16">
@@ -2496,130 +2622,130 @@
         <v>-0.29662049717465033</v>
       </c>
       <c r="C16">
-        <v>-2.4638573741358446e-005</v>
+        <v>-2.4638573741358636e-005</v>
       </c>
       <c r="D16">
-        <v>2.0142446136799905e-006</v>
+        <v>2.0142446136804784e-006</v>
       </c>
       <c r="E16">
-        <v>-6.2086123423845401e-008</v>
+        <v>-6.2086123423850218e-008</v>
       </c>
       <c r="F16">
-        <v>0.0001761194141308896</v>
+        <v>0.00017611941413088987</v>
       </c>
       <c r="G16">
-        <v>3.6032988772732931e-005</v>
+        <v>3.6032988772732226e-005</v>
       </c>
       <c r="H16">
-        <v>1.8229716450658245e-005</v>
+        <v>1.822971645065735e-005</v>
       </c>
       <c r="I16">
-        <v>0.00011701139869537612</v>
+        <v>0.00011701139869537536</v>
       </c>
       <c r="J16">
-        <v>3.1416036478610807e-005</v>
+        <v>3.1416036478609994e-005</v>
       </c>
       <c r="K16">
-        <v>4.2911078734865656e-005</v>
+        <v>4.2911078734865764e-005</v>
       </c>
       <c r="L16">
-        <v>7.4329532209340223e-006</v>
+        <v>7.4329532209332634e-006</v>
       </c>
       <c r="M16">
-        <v>8.1600316665843102e-005</v>
+        <v>8.1600316665846897e-005</v>
       </c>
       <c r="N16">
-        <v>3.6156786155918546e-005</v>
+        <v>3.6156786155920389e-005</v>
       </c>
       <c r="O16">
-        <v>5.8382311306116028e-005</v>
+        <v>5.8382311306119389e-005</v>
       </c>
       <c r="P16">
         <v>0.00035950621854139949</v>
       </c>
       <c r="Q16">
-        <v>0.0006398669833342041</v>
+        <v>0.00063986698333420421</v>
       </c>
       <c r="R16">
-        <v>0.00028052649422890662</v>
+        <v>0.0002805264942289069</v>
       </c>
       <c r="S16">
-        <v>1.5764463137921975e-006</v>
+        <v>1.5764463137921603e-006</v>
       </c>
       <c r="T16">
-        <v>2.3245001786483499e-007</v>
+        <v>2.3245001786484303e-007</v>
       </c>
       <c r="U16">
-        <v>3.2004572896313668e-005</v>
+        <v>3.2004572896313817e-005</v>
       </c>
       <c r="V16">
-        <v>7.6224857291609969e-005</v>
+        <v>7.6224857291612097e-005</v>
       </c>
       <c r="W16">
-        <v>0.0001373108598322086</v>
+        <v>0.00013731085983221175</v>
       </c>
       <c r="X16">
-        <v>0.00023342728825639616</v>
+        <v>0.0002334272882563967</v>
       </c>
       <c r="Y16">
-        <v>7.5993245916347912e-006</v>
+        <v>7.5993245916349217e-006</v>
       </c>
       <c r="Z16">
-        <v>1.9829827945221025e-005</v>
+        <v>1.9829827945220862e-005</v>
       </c>
       <c r="AA16">
-        <v>-1.4529425622065881e-006</v>
+        <v>-1.4529425622061408e-006</v>
       </c>
       <c r="AB16">
-        <v>-3.1162968217501695e-005</v>
+        <v>-3.1162968217501966e-005</v>
       </c>
       <c r="AC16">
-        <v>-3.374909157595717e-005</v>
+        <v>-3.3749091575957224e-005</v>
       </c>
       <c r="AD16">
-        <v>-5.8310482600679141e-005</v>
+        <v>-5.8310482600680341e-005</v>
       </c>
       <c r="AE16">
-        <v>-3.6232512181531211e-006</v>
+        <v>-3.6232512181532159e-006</v>
       </c>
       <c r="AF16">
-        <v>-3.3158693346604675e-005</v>
+        <v>-3.3158693346604824e-005</v>
       </c>
       <c r="AG16">
-        <v>-1.8845789235205042e-005</v>
+        <v>-1.8845789235204249e-005</v>
       </c>
       <c r="AH16">
-        <v>-6.8509161631558018e-006</v>
+        <v>-6.8509161631561973e-006</v>
       </c>
       <c r="AI16">
-        <v>-6.0803425415086148e-005</v>
+        <v>-6.0803425415086662e-005</v>
       </c>
       <c r="AJ16">
-        <v>-3.6247264831092393e-005</v>
+        <v>-3.624726483109303e-005</v>
       </c>
       <c r="AK16">
-        <v>-2.9757842378926318e-005</v>
+        <v>-2.9757842378926155e-005</v>
       </c>
       <c r="AL16">
-        <v>3.6657020293479569e-006</v>
+        <v>3.6657020293479298e-006</v>
       </c>
       <c r="AM16">
-        <v>-2.6417359465770262e-005</v>
+        <v>-2.6417359465770126e-005</v>
       </c>
       <c r="AN16">
         <v>4.794313342363256e-005</v>
       </c>
       <c r="AO16">
-        <v>6.4535690093456695e-005</v>
+        <v>6.453569009345683e-005</v>
       </c>
       <c r="AP16">
-        <v>1.312708388221305e-005</v>
+        <v>1.3127083882212616e-005</v>
       </c>
       <c r="AQ16">
-        <v>6.0124255663574305e-005</v>
+        <v>6.0124255663574291e-005</v>
       </c>
       <c r="AR16">
-        <v>-0.00056085186551675008</v>
+        <v>-0.00056085186551675117</v>
       </c>
     </row>
     <row r="17">
@@ -2630,130 +2756,130 @@
         <v>-0.12765543741736268</v>
       </c>
       <c r="C17">
-        <v>-2.3444387672616781e-005</v>
+        <v>-2.3444387672616835e-005</v>
       </c>
       <c r="D17">
-        <v>-2.3064223972200535e-007</v>
+        <v>-2.3064223972178851e-007</v>
       </c>
       <c r="E17">
-        <v>-2.2778854145536958e-009</v>
+        <v>-2.2778854145554957e-009</v>
       </c>
       <c r="F17">
-        <v>0.00034406786427301512</v>
+        <v>0.00034406786427301658</v>
       </c>
       <c r="G17">
-        <v>7.7544270617507923e-005</v>
+        <v>7.7544270617508737e-005</v>
       </c>
       <c r="H17">
-        <v>2.8842976648460516e-005</v>
+        <v>2.884297664846122e-005</v>
       </c>
       <c r="I17">
-        <v>0.00019329162416323298</v>
+        <v>0.00019329162416323407</v>
       </c>
       <c r="J17">
-        <v>9.9815567753607209e-005</v>
+        <v>9.9815567753608293e-005</v>
       </c>
       <c r="K17">
-        <v>5.4183267296301378e-005</v>
+        <v>5.4183267296302679e-005</v>
       </c>
       <c r="L17">
-        <v>0.00013607179998894052</v>
+        <v>0.00013607179998894215</v>
       </c>
       <c r="M17">
-        <v>-0.0027479995940856016</v>
+        <v>-0.0027479995940855977</v>
       </c>
       <c r="N17">
-        <v>7.1267337531774524e-006</v>
+        <v>7.1267337531804881e-006</v>
       </c>
       <c r="O17">
-        <v>8.6535164948743355e-005</v>
+        <v>8.6535164948744981e-005</v>
       </c>
       <c r="P17">
-        <v>0.0003452210129737648</v>
+        <v>0.00034522101297376501</v>
       </c>
       <c r="Q17">
-        <v>0.00028052649422890662</v>
+        <v>0.0002805264942289069</v>
       </c>
       <c r="R17">
-        <v>0.005430014561984677</v>
+        <v>0.0054300145619846762</v>
       </c>
       <c r="S17">
-        <v>3.573773554275586e-008</v>
+        <v>3.573773554273966e-008</v>
       </c>
       <c r="T17">
-        <v>-2.5801178212606264e-006</v>
+        <v>-2.5801178212606014e-006</v>
       </c>
       <c r="U17">
-        <v>3.8415631755004705e-005</v>
+        <v>3.8415631755006412e-005</v>
       </c>
       <c r="V17">
-        <v>6.4316863125706458e-005</v>
+        <v>6.4316863125709426e-005</v>
       </c>
       <c r="W17">
-        <v>0.00014302277872261276</v>
+        <v>0.00014302277872261436</v>
       </c>
       <c r="X17">
-        <v>0.00019563666315527669</v>
+        <v>0.0001956366631552807</v>
       </c>
       <c r="Y17">
-        <v>-9.6685720339629898e-006</v>
+        <v>-9.6685720339630135e-006</v>
       </c>
       <c r="Z17">
-        <v>4.6467771264812718e-006</v>
+        <v>4.6467771264813531e-006</v>
       </c>
       <c r="AA17">
-        <v>4.2708286761512158e-007</v>
+        <v>4.2708286761595506e-007</v>
       </c>
       <c r="AB17">
-        <v>1.5711229592522443e-005</v>
+        <v>1.5711229592522849e-005</v>
       </c>
       <c r="AC17">
-        <v>-2.1759828669103873e-005</v>
+        <v>-2.1759828669102155e-005</v>
       </c>
       <c r="AD17">
-        <v>-1.7816854081849041e-005</v>
+        <v>-1.7816854081850257e-005</v>
       </c>
       <c r="AE17">
-        <v>-4.9939853678547934e-005</v>
+        <v>-4.9939853678547493e-005</v>
       </c>
       <c r="AF17">
-        <v>-2.3288915060881721e-005</v>
+        <v>-2.3288915060881653e-005</v>
       </c>
       <c r="AG17">
-        <v>7.9766340056744047e-006</v>
+        <v>7.976634005675416e-006</v>
       </c>
       <c r="AH17">
-        <v>1.4208835870225412e-005</v>
+        <v>1.4208835870225103e-005</v>
       </c>
       <c r="AI17">
-        <v>2.8726732420323639e-005</v>
+        <v>2.8726732420324194e-005</v>
       </c>
       <c r="AJ17">
-        <v>1.416153316204855e-005</v>
+        <v>1.4161533162048418e-005</v>
       </c>
       <c r="AK17">
-        <v>-4.5502479570227658e-005</v>
+        <v>-4.5502479570227333e-005</v>
       </c>
       <c r="AL17">
-        <v>3.1260469260903907e-006</v>
+        <v>3.1260469260902958e-006</v>
       </c>
       <c r="AM17">
-        <v>-8.740134791834287e-005</v>
+        <v>-8.7401347918342545e-005</v>
       </c>
       <c r="AN17">
-        <v>-2.6548707415788414e-005</v>
+        <v>-2.6548707415788156e-005</v>
       </c>
       <c r="AO17">
-        <v>-3.5504609063952509e-005</v>
+        <v>-3.5504609063952617e-005</v>
       </c>
       <c r="AP17">
-        <v>1.6338125590001227e-005</v>
+        <v>1.6338125590000901e-005</v>
       </c>
       <c r="AQ17">
-        <v>0.00031194683469120505</v>
+        <v>0.00031194683469120538</v>
       </c>
       <c r="AR17">
-        <v>-0.00028553703677698086</v>
+        <v>-0.00028553703677698601</v>
       </c>
     </row>
     <row r="18">
@@ -2764,130 +2890,130 @@
         <v>0.0065675531684875662</v>
       </c>
       <c r="C18">
-        <v>-5.2859634024004762e-007</v>
+        <v>-5.2859634024005546e-007</v>
       </c>
       <c r="D18">
-        <v>1.5294151081129712e-007</v>
+        <v>1.5294151081130877e-007</v>
       </c>
       <c r="E18">
-        <v>-3.0239205225700207e-010</v>
+        <v>-3.0239205225712532e-010</v>
       </c>
       <c r="F18">
-        <v>-1.8289953009510864e-006</v>
+        <v>-1.8289953009511215e-006</v>
       </c>
       <c r="G18">
-        <v>-9.2089538807322488e-007</v>
+        <v>-9.2089538807325622e-007</v>
       </c>
       <c r="H18">
-        <v>5.0390719465660914e-007</v>
+        <v>5.0390719465656679e-007</v>
       </c>
       <c r="I18">
-        <v>5.3943887649995809e-007</v>
+        <v>5.3943887649991023e-007</v>
       </c>
       <c r="J18">
-        <v>-6.3318059620109478e-007</v>
+        <v>-6.3318059620113713e-007</v>
       </c>
       <c r="K18">
-        <v>7.1070514033530672e-008</v>
+        <v>7.1070514033515001e-008</v>
       </c>
       <c r="L18">
-        <v>1.787361506892389e-009</v>
+        <v>1.7873615068729072e-009</v>
       </c>
       <c r="M18">
-        <v>7.6559243139081178e-007</v>
+        <v>7.6559243139099135e-007</v>
       </c>
       <c r="N18">
-        <v>3.1652204422735849e-006</v>
+        <v>3.1652204422737204e-006</v>
       </c>
       <c r="O18">
-        <v>1.3109694415009711e-006</v>
+        <v>1.3109694415011456e-006</v>
       </c>
       <c r="P18">
-        <v>5.4188540166182362e-007</v>
+        <v>5.4188540166178254e-007</v>
       </c>
       <c r="Q18">
-        <v>1.5764463137921975e-006</v>
+        <v>1.5764463137921603e-006</v>
       </c>
       <c r="R18">
-        <v>3.573773554275586e-008</v>
+        <v>3.573773554273966e-008</v>
       </c>
       <c r="S18">
-        <v>5.4062229809190631e-007</v>
+        <v>5.4062229809190599e-007</v>
       </c>
       <c r="T18">
-        <v>-2.7093950796788721e-009</v>
+        <v>-2.709395079678528e-009</v>
       </c>
       <c r="U18">
-        <v>8.0835086648017708e-007</v>
+        <v>8.0835086648031938e-007</v>
       </c>
       <c r="V18">
-        <v>-8.8829618239509296e-007</v>
+        <v>-8.8829618239468384e-007</v>
       </c>
       <c r="W18">
-        <v>-1.2560250109220201e-006</v>
+        <v>-1.2560250109215018e-006</v>
       </c>
       <c r="X18">
-        <v>-1.457738535931683e-006</v>
+        <v>-1.4577385359316356e-006</v>
       </c>
       <c r="Y18">
-        <v>-2.6198855942942262e-008</v>
+        <v>-2.6198855942942579e-008</v>
       </c>
       <c r="Z18">
-        <v>-7.2403600792762224e-007</v>
+        <v>-7.2403600792760869e-007</v>
       </c>
       <c r="AA18">
-        <v>1.9879628997550427e-006</v>
+        <v>1.9879628997550588e-006</v>
       </c>
       <c r="AB18">
-        <v>4.7712506940220115e-007</v>
+        <v>4.7712506940221131e-007</v>
       </c>
       <c r="AC18">
-        <v>1.3741449696128293e-006</v>
+        <v>1.374144969612853e-006</v>
       </c>
       <c r="AD18">
-        <v>1.3792963263199738e-006</v>
+        <v>1.3792963263199096e-006</v>
       </c>
       <c r="AE18">
-        <v>3.005024940018818e-006</v>
+        <v>3.0050249400188264e-006</v>
       </c>
       <c r="AF18">
-        <v>1.1013059060450647e-006</v>
+        <v>1.1013059060450714e-006</v>
       </c>
       <c r="AG18">
-        <v>9.1854783113393936e-007</v>
+        <v>9.1854783113400267e-007</v>
       </c>
       <c r="AH18">
-        <v>1.9811368500926468e-006</v>
+        <v>1.9811368500926447e-006</v>
       </c>
       <c r="AI18">
-        <v>1.872351147270361e-006</v>
+        <v>1.8723511472703058e-006</v>
       </c>
       <c r="AJ18">
-        <v>1.1257162621809847e-006</v>
+        <v>1.1257162621809245e-006</v>
       </c>
       <c r="AK18">
-        <v>1.8739130171534807e-006</v>
+        <v>1.8739130171535417e-006</v>
       </c>
       <c r="AL18">
-        <v>1.0809047784141537e-007</v>
+        <v>1.0809047784141452e-007</v>
       </c>
       <c r="AM18">
-        <v>-4.3537703964380468e-007</v>
+        <v>-4.353770396437979e-007</v>
       </c>
       <c r="AN18">
-        <v>-8.5843833960773721e-007</v>
+        <v>-8.5843833960775076e-007</v>
       </c>
       <c r="AO18">
-        <v>1.1665665695757725e-006</v>
+        <v>1.1665665695757759e-006</v>
       </c>
       <c r="AP18">
-        <v>1.1815582784634849e-006</v>
+        <v>1.18155827846349e-006</v>
       </c>
       <c r="AQ18">
-        <v>5.7822382418539757e-007</v>
+        <v>5.7822382418543145e-007</v>
       </c>
       <c r="AR18">
-        <v>-3.6233586246106934e-005</v>
+        <v>-3.6233586246106866e-005</v>
       </c>
     </row>
     <row r="19">
@@ -2898,130 +3024,130 @@
         <v>0.0035464628721402439</v>
       </c>
       <c r="C19">
-        <v>-2.111075240515896e-006</v>
+        <v>-2.1110752405158985e-006</v>
       </c>
       <c r="D19">
-        <v>8.1297443753781934e-008</v>
+        <v>8.1297443753801257e-008</v>
       </c>
       <c r="E19">
-        <v>-1.4676985848761628e-009</v>
+        <v>-1.4676985848763547e-009</v>
       </c>
       <c r="F19">
-        <v>2.5130255296876655e-006</v>
+        <v>2.5130255296876511e-006</v>
       </c>
       <c r="G19">
-        <v>-6.63481251449356e-007</v>
+        <v>-6.6348125144941911e-007</v>
       </c>
       <c r="H19">
-        <v>-1.3200867165801667e-006</v>
+        <v>-1.3200867165802218e-006</v>
       </c>
       <c r="I19">
-        <v>1.4953105196428771e-006</v>
+        <v>1.4953105196428426e-006</v>
       </c>
       <c r="J19">
-        <v>-1.1332049925488468e-006</v>
+        <v>-1.1332049925488955e-006</v>
       </c>
       <c r="K19">
-        <v>6.5177634143807304e-007</v>
+        <v>6.5177634143804552e-007</v>
       </c>
       <c r="L19">
-        <v>-2.3101791425125704e-007</v>
+        <v>-2.3101791425129304e-007</v>
       </c>
       <c r="M19">
-        <v>-4.8698238867935072e-007</v>
+        <v>-4.8698238867911864e-007</v>
       </c>
       <c r="N19">
-        <v>2.5271800298096919e-006</v>
+        <v>2.5271800298098245e-006</v>
       </c>
       <c r="O19">
-        <v>-7.5551999660274686e-007</v>
+        <v>-7.5551999660253595e-007</v>
       </c>
       <c r="P19">
-        <v>3.0913841740410465e-008</v>
+        <v>3.0913841740402207e-008</v>
       </c>
       <c r="Q19">
-        <v>2.3245001786483499e-007</v>
+        <v>2.3245001786484303e-007</v>
       </c>
       <c r="R19">
-        <v>-2.5801178212606264e-006</v>
+        <v>-2.5801178212606014e-006</v>
       </c>
       <c r="S19">
-        <v>-2.7093950796788721e-009</v>
+        <v>-2.709395079678528e-009</v>
       </c>
       <c r="T19">
-        <v>6.8947674577144812e-007</v>
+        <v>6.8947674577144675e-007</v>
       </c>
       <c r="U19">
-        <v>3.8428482826233996e-007</v>
+        <v>3.8428482826243144e-007</v>
       </c>
       <c r="V19">
-        <v>-1.1354298054468393e-006</v>
+        <v>-1.1354298054466258e-006</v>
       </c>
       <c r="W19">
-        <v>-1.7398437729270858e-006</v>
+        <v>-1.7398437729268825e-006</v>
       </c>
       <c r="X19">
-        <v>-1.9782017643194653e-006</v>
+        <v>-1.9782017643192688e-006</v>
       </c>
       <c r="Y19">
-        <v>4.9522192939229459e-008</v>
+        <v>4.9522192939231471e-008</v>
       </c>
       <c r="Z19">
-        <v>-4.0966996353986499e-007</v>
+        <v>-4.096699635398599e-007</v>
       </c>
       <c r="AA19">
-        <v>1.5652263061771817e-006</v>
+        <v>1.5652263061771334e-006</v>
       </c>
       <c r="AB19">
-        <v>1.8042953125036854e-006</v>
+        <v>1.804295312503687e-006</v>
       </c>
       <c r="AC19">
-        <v>1.7997576982976277e-006</v>
+        <v>1.7997576982976438e-006</v>
       </c>
       <c r="AD19">
-        <v>9.7846385221225734e-007</v>
+        <v>9.7846385221220016e-007</v>
       </c>
       <c r="AE19">
-        <v>2.2906799369046227e-006</v>
+        <v>2.2906799369046295e-006</v>
       </c>
       <c r="AF19">
-        <v>1.6814927442265341e-006</v>
+        <v>1.6814927442265422e-006</v>
       </c>
       <c r="AG19">
-        <v>1.3992193814255076e-006</v>
+        <v>1.3992193814255042e-006</v>
       </c>
       <c r="AH19">
-        <v>2.7700938297861094e-007</v>
+        <v>2.770093829786085e-007</v>
       </c>
       <c r="AI19">
-        <v>-9.0919938225552548e-008</v>
+        <v>-9.0919938225550007e-008</v>
       </c>
       <c r="AJ19">
-        <v>6.5432913302823684e-007</v>
+        <v>6.5432913302812694e-007</v>
       </c>
       <c r="AK19">
-        <v>6.7862422894459416e-007</v>
+        <v>6.7862422894464498e-007</v>
       </c>
       <c r="AL19">
-        <v>1.7875692451641683e-007</v>
+        <v>1.7875692451642361e-007</v>
       </c>
       <c r="AM19">
-        <v>4.588815820395906e-007</v>
+        <v>4.5888158203956349e-007</v>
       </c>
       <c r="AN19">
-        <v>1.6034020641304969e-006</v>
+        <v>1.6034020641304698e-006</v>
       </c>
       <c r="AO19">
-        <v>4.3872289432178702e-006</v>
+        <v>4.3872289432178736e-006</v>
       </c>
       <c r="AP19">
-        <v>-3.4976686572818025e-006</v>
+        <v>-3.4976686572818457e-006</v>
       </c>
       <c r="AQ19">
-        <v>1.7125742510849635e-006</v>
+        <v>1.7125742510849551e-006</v>
       </c>
       <c r="AR19">
-        <v>-3.5586229727230072e-005</v>
+        <v>-3.5586229727230167e-005</v>
       </c>
     </row>
     <row r="20">
@@ -3032,130 +3158,130 @@
         <v>0.077809490571521533</v>
       </c>
       <c r="C20">
-        <v>-4.1802062486350442e-005</v>
+        <v>-4.1802062486350557e-005</v>
       </c>
       <c r="D20">
-        <v>9.1431235299073356e-008</v>
+        <v>9.1431235300760646e-008</v>
       </c>
       <c r="E20">
-        <v>1.8363534191056456e-008</v>
+        <v>1.8363534191040468e-008</v>
       </c>
       <c r="F20">
-        <v>-0.00013568252562926625</v>
+        <v>-0.00013568252562926153</v>
       </c>
       <c r="G20">
-        <v>-2.6616280561899129e-005</v>
+        <v>-2.6616280561899563e-005</v>
       </c>
       <c r="H20">
-        <v>-4.4419594255488008e-005</v>
+        <v>-4.4419594255488645e-005</v>
       </c>
       <c r="I20">
-        <v>-6.0305337685957077e-005</v>
+        <v>-6.0305337685956996e-005</v>
       </c>
       <c r="J20">
-        <v>-2.5999556811430208e-005</v>
+        <v>-2.5999556811430262e-005</v>
       </c>
       <c r="K20">
-        <v>4.0904890860921788e-006</v>
+        <v>4.090489086095052e-006</v>
       </c>
       <c r="L20">
-        <v>-1.330778390749244e-005</v>
+        <v>-1.3307783907490353e-005</v>
       </c>
       <c r="M20">
-        <v>0.00073880584348539734</v>
+        <v>0.00073880584348541372</v>
       </c>
       <c r="N20">
-        <v>0.00068206398847657946</v>
+        <v>0.00068206398847658889</v>
       </c>
       <c r="O20">
-        <v>0.00048116415972502646</v>
+        <v>0.00048116415972503871</v>
       </c>
       <c r="P20">
-        <v>3.0494360210134313e-005</v>
+        <v>3.0494360210134164e-005</v>
       </c>
       <c r="Q20">
-        <v>3.2004572896313668e-005</v>
+        <v>3.2004572896313817e-005</v>
       </c>
       <c r="R20">
-        <v>3.8415631755004705e-005</v>
+        <v>3.8415631755006412e-005</v>
       </c>
       <c r="S20">
-        <v>8.0835086648017708e-007</v>
+        <v>8.0835086648031938e-007</v>
       </c>
       <c r="T20">
-        <v>3.8428482826233996e-007</v>
+        <v>3.8428482826243144e-007</v>
       </c>
       <c r="U20">
-        <v>0.0009583411319834252</v>
+        <v>0.00095834113198343322</v>
       </c>
       <c r="V20">
-        <v>0.00093366656729831346</v>
+        <v>0.00093366656729832105</v>
       </c>
       <c r="W20">
-        <v>0.00093434169697037832</v>
+        <v>0.0009343416969703883</v>
       </c>
       <c r="X20">
-        <v>0.00090304424419730732</v>
+        <v>0.00090304424419730689</v>
       </c>
       <c r="Y20">
-        <v>-7.9295951572697855e-005</v>
+        <v>-7.9295951572697719e-005</v>
       </c>
       <c r="Z20">
-        <v>-2.483725332290659e-005</v>
+        <v>-2.4837253322906373e-005</v>
       </c>
       <c r="AA20">
-        <v>-3.076897877102392e-005</v>
+        <v>-3.07689787710227e-005</v>
       </c>
       <c r="AB20">
-        <v>-2.4992711963683965e-005</v>
+        <v>-2.4992711963681363e-005</v>
       </c>
       <c r="AC20">
-        <v>6.0764066150467282e-006</v>
+        <v>6.0764066150489508e-006</v>
       </c>
       <c r="AD20">
-        <v>-2.2832336034873248e-005</v>
+        <v>-2.2832336034874244e-005</v>
       </c>
       <c r="AE20">
-        <v>2.7210759183189572e-005</v>
+        <v>2.7210759183191849e-005</v>
       </c>
       <c r="AF20">
-        <v>-4.9719309572991146e-005</v>
+        <v>-4.9719309572990306e-005</v>
       </c>
       <c r="AG20">
-        <v>-3.7684588234171212e-006</v>
+        <v>-3.7684588234136992e-006</v>
       </c>
       <c r="AH20">
-        <v>-4.0022951393980047e-005</v>
+        <v>-4.0022951393978062e-005</v>
       </c>
       <c r="AI20">
-        <v>-3.9412224871447141e-005</v>
+        <v>-3.9412224871446111e-005</v>
       </c>
       <c r="AJ20">
-        <v>-4.861101136781027e-005</v>
+        <v>-4.8611011367810094e-005</v>
       </c>
       <c r="AK20">
-        <v>-2.237748137005717e-005</v>
+        <v>-2.2377481370053917e-005</v>
       </c>
       <c r="AL20">
-        <v>4.2542319785726667e-006</v>
+        <v>4.2542319785727751e-006</v>
       </c>
       <c r="AM20">
-        <v>-6.2428407644931814e-005</v>
+        <v>-6.2428407644931705e-005</v>
       </c>
       <c r="AN20">
-        <v>-3.197922235086267e-005</v>
+        <v>-3.1979222350863212e-005</v>
       </c>
       <c r="AO20">
-        <v>3.8012649383127161e-005</v>
+        <v>3.8012649383127703e-005</v>
       </c>
       <c r="AP20">
-        <v>-6.4855753695447336e-005</v>
+        <v>-6.4855753695447445e-005</v>
       </c>
       <c r="AQ20">
-        <v>4.4192741894875313e-005</v>
+        <v>4.4192741894876939e-005</v>
       </c>
       <c r="AR20">
-        <v>-0.0010013012718396745</v>
+        <v>-0.0010013012718397172</v>
       </c>
     </row>
     <row r="21">
@@ -3166,130 +3292,130 @@
         <v>0.23735009390516218</v>
       </c>
       <c r="C21">
-        <v>-4.226846860645582e-005</v>
+        <v>-4.2268468606455867e-005</v>
       </c>
       <c r="D21">
-        <v>-4.1640705650681992e-006</v>
+        <v>-4.164070565066024e-006</v>
       </c>
       <c r="E21">
-        <v>7.5860138125306047e-008</v>
+        <v>7.586013812528601e-008</v>
       </c>
       <c r="F21">
-        <v>-0.0001106587141544848</v>
+        <v>-0.00011065871415447729</v>
       </c>
       <c r="G21">
-        <v>3.3974872992910529e-005</v>
+        <v>3.3974872992911695e-005</v>
       </c>
       <c r="H21">
-        <v>-3.9700452207297517e-005</v>
+        <v>-3.9700452207296283e-005</v>
       </c>
       <c r="I21">
-        <v>3.0375240113230724e-005</v>
+        <v>3.0375240113234058e-005</v>
       </c>
       <c r="J21">
-        <v>6.3707855740123353e-005</v>
+        <v>6.3707855740125874e-005</v>
       </c>
       <c r="K21">
-        <v>4.7744001122612537e-005</v>
+        <v>4.7744001122618527e-005</v>
       </c>
       <c r="L21">
-        <v>0.00017941140256331299</v>
+        <v>0.00017941140256331751</v>
       </c>
       <c r="M21">
-        <v>0.0012232715306503108</v>
+        <v>0.0012232715306503311</v>
       </c>
       <c r="N21">
-        <v>0.0011391809011316698</v>
+        <v>0.0011391809011316823</v>
       </c>
       <c r="O21">
-        <v>0.00083688150539680084</v>
+        <v>0.00083688150539681515</v>
       </c>
       <c r="P21">
-        <v>2.829871391237196e-005</v>
+        <v>2.8298713912373058e-005</v>
       </c>
       <c r="Q21">
-        <v>7.6224857291609969e-005</v>
+        <v>7.6224857291612097e-005</v>
       </c>
       <c r="R21">
-        <v>6.4316863125706458e-005</v>
+        <v>6.4316863125709426e-005</v>
       </c>
       <c r="S21">
-        <v>-8.8829618239509296e-007</v>
+        <v>-8.8829618239468384e-007</v>
       </c>
       <c r="T21">
-        <v>-1.1354298054468393e-006</v>
+        <v>-1.1354298054466258e-006</v>
       </c>
       <c r="U21">
-        <v>0.00093366656729831346</v>
+        <v>0.00093366656729832105</v>
       </c>
       <c r="V21">
-        <v>0.0016262165864250561</v>
+        <v>0.0016262165864250667</v>
       </c>
       <c r="W21">
-        <v>0.0014253922371825095</v>
+        <v>0.0014253922371825225</v>
       </c>
       <c r="X21">
-        <v>0.001438249099318946</v>
+        <v>0.0014382490993189421</v>
       </c>
       <c r="Y21">
-        <v>-0.00010321457883615811</v>
+        <v>-0.00010321457883615798</v>
       </c>
       <c r="Z21">
-        <v>-3.2659898003095807e-005</v>
+        <v>-3.2659898003095373e-005</v>
       </c>
       <c r="AA21">
-        <v>-4.288569286322138e-005</v>
+        <v>-4.2885692863219753e-005</v>
       </c>
       <c r="AB21">
-        <v>-7.0892266513092978e-005</v>
+        <v>-7.0892266513089509e-005</v>
       </c>
       <c r="AC21">
-        <v>-1.0337927216232375e-005</v>
+        <v>-1.0337927216230302e-005</v>
       </c>
       <c r="AD21">
-        <v>-2.4616680539874497e-005</v>
+        <v>-2.4616680539875578e-005</v>
       </c>
       <c r="AE21">
-        <v>-1.2420097785560322e-005</v>
+        <v>-1.2420097785557449e-005</v>
       </c>
       <c r="AF21">
-        <v>-6.7972506729304749e-005</v>
+        <v>-6.7972506729303502e-005</v>
       </c>
       <c r="AG21">
-        <v>-3.6431199264291717e-005</v>
+        <v>-3.6431199264287183e-005</v>
       </c>
       <c r="AH21">
-        <v>-4.3945520463039664e-005</v>
+        <v>-4.3945520463036899e-005</v>
       </c>
       <c r="AI21">
-        <v>-6.192092835186396e-005</v>
+        <v>-6.192092835186274e-005</v>
       </c>
       <c r="AJ21">
-        <v>-8.5252838608095932e-005</v>
+        <v>-8.5252838608095566e-005</v>
       </c>
       <c r="AK21">
-        <v>-4.6697600736223953e-005</v>
+        <v>-4.6697600736219291e-005</v>
       </c>
       <c r="AL21">
-        <v>-1.6294092022376403e-006</v>
+        <v>-1.6294092022374777e-006</v>
       </c>
       <c r="AM21">
-        <v>-3.0082986885877992e-005</v>
+        <v>-3.00829868858781e-005</v>
       </c>
       <c r="AN21">
-        <v>3.1343774996907443e-005</v>
+        <v>3.1343774996906576e-005</v>
       </c>
       <c r="AO21">
-        <v>-7.1002114972978209e-006</v>
+        <v>-7.1002114972968993e-006</v>
       </c>
       <c r="AP21">
-        <v>-0.00012735181070724398</v>
+        <v>-0.00012735181070724447</v>
       </c>
       <c r="AQ21">
-        <v>6.7146047269941132e-005</v>
+        <v>6.7146047269943301e-005</v>
       </c>
       <c r="AR21">
-        <v>-0.0011898007594459165</v>
+        <v>-0.0011898007594459677</v>
       </c>
     </row>
     <row r="22">
@@ -3300,130 +3426,130 @@
         <v>0.33836189777750852</v>
       </c>
       <c r="C22">
-        <v>-5.0666231693518638e-005</v>
+        <v>-5.0666231693519519e-005</v>
       </c>
       <c r="D22">
-        <v>-1.1421700110895525e-005</v>
+        <v>-1.1421700110894563e-005</v>
       </c>
       <c r="E22">
-        <v>1.2814808475640945e-007</v>
+        <v>1.2814808475640156e-007</v>
       </c>
       <c r="F22">
-        <v>-5.5988895563068345e-005</v>
+        <v>-5.5988895563060105e-005</v>
       </c>
       <c r="G22">
-        <v>0.00015747990045400582</v>
+        <v>0.00015747990045401059</v>
       </c>
       <c r="H22">
-        <v>-2.4618417597373687e-006</v>
+        <v>-2.4618417597330319e-006</v>
       </c>
       <c r="I22">
-        <v>0.00025648664510740732</v>
+        <v>0.00025648664510741453</v>
       </c>
       <c r="J22">
-        <v>0.00029381187277655962</v>
+        <v>0.00029381187277656624</v>
       </c>
       <c r="K22">
-        <v>0.00016013198282030923</v>
+        <v>0.00016013198282031633</v>
       </c>
       <c r="L22">
-        <v>0.00031256187880037832</v>
+        <v>0.00031256187880038689</v>
       </c>
       <c r="M22">
-        <v>0.001244540787666532</v>
+        <v>0.00124454078766655</v>
       </c>
       <c r="N22">
-        <v>0.0012113199633241381</v>
+        <v>0.0012113199633241544</v>
       </c>
       <c r="O22">
-        <v>0.00098183880766435929</v>
+        <v>0.00098183880766437122</v>
       </c>
       <c r="P22">
-        <v>0.00010391853954084038</v>
+        <v>0.00010391853954084165</v>
       </c>
       <c r="Q22">
-        <v>0.0001373108598322086</v>
+        <v>0.00013731085983221175</v>
       </c>
       <c r="R22">
-        <v>0.00014302277872261276</v>
+        <v>0.00014302277872261436</v>
       </c>
       <c r="S22">
-        <v>-1.2560250109220201e-006</v>
+        <v>-1.2560250109215018e-006</v>
       </c>
       <c r="T22">
-        <v>-1.7398437729270858e-006</v>
+        <v>-1.7398437729268825e-006</v>
       </c>
       <c r="U22">
-        <v>0.00093434169697037832</v>
+        <v>0.0009343416969703883</v>
       </c>
       <c r="V22">
-        <v>0.0014253922371825095</v>
+        <v>0.0014253922371825225</v>
       </c>
       <c r="W22">
-        <v>0.0019145285500977293</v>
+        <v>0.0019145285500977451</v>
       </c>
       <c r="X22">
-        <v>0.0016191610611042309</v>
+        <v>0.0016191610611042257</v>
       </c>
       <c r="Y22">
-        <v>-9.9254478770523832e-005</v>
+        <v>-9.9254478770523778e-005</v>
       </c>
       <c r="Z22">
-        <v>-3.994251917640722e-005</v>
+        <v>-3.9942519176406461e-005</v>
       </c>
       <c r="AA22">
-        <v>7.6307758992014488e-008</v>
+        <v>7.6307758993640791e-008</v>
       </c>
       <c r="AB22">
-        <v>-4.2100027117227077e-006</v>
+        <v>-4.2100027117191298e-006</v>
       </c>
       <c r="AC22">
-        <v>5.5323966355177572e-005</v>
+        <v>5.5323966355179171e-005</v>
       </c>
       <c r="AD22">
-        <v>4.1041610294057716e-006</v>
+        <v>4.1041610294050719e-006</v>
       </c>
       <c r="AE22">
-        <v>3.5000378968972398e-005</v>
+        <v>3.5000378968975325e-005</v>
       </c>
       <c r="AF22">
-        <v>-3.2886693973134529e-005</v>
+        <v>-3.2886693973133336e-005</v>
       </c>
       <c r="AG22">
-        <v>1.6235610702650704e-005</v>
+        <v>1.6235610702655556e-005</v>
       </c>
       <c r="AH22">
-        <v>-3.6662179746308565e-006</v>
+        <v>-3.6662179746277394e-006</v>
       </c>
       <c r="AI22">
-        <v>1.3189982189747e-007</v>
+        <v>1.3189982189860841e-007</v>
       </c>
       <c r="AJ22">
-        <v>-6.4705955962645644e-005</v>
+        <v>-6.4705955962645372e-005</v>
       </c>
       <c r="AK22">
-        <v>2.5606344078588821e-005</v>
+        <v>2.5606344078593483e-005</v>
       </c>
       <c r="AL22">
-        <v>1.223786904663973e-006</v>
+        <v>1.2237869046642712e-006</v>
       </c>
       <c r="AM22">
-        <v>-3.3545968427638596e-005</v>
+        <v>-3.3545968427638813e-005</v>
       </c>
       <c r="AN22">
-        <v>2.479204403048709e-005</v>
+        <v>2.4792044030486006e-005</v>
       </c>
       <c r="AO22">
-        <v>7.7262241716620278e-006</v>
+        <v>7.7262241716632204e-006</v>
       </c>
       <c r="AP22">
-        <v>-0.0001907798999700902</v>
+        <v>-0.00019077989997009064</v>
       </c>
       <c r="AQ22">
-        <v>5.9091613669990414e-005</v>
+        <v>5.9091613669992799e-005</v>
       </c>
       <c r="AR22">
-        <v>-0.0013060491489696115</v>
+        <v>-0.001306049148969667</v>
       </c>
     </row>
     <row r="23">
@@ -3434,130 +3560,130 @@
         <v>0.57821775478908677</v>
       </c>
       <c r="C23">
-        <v>-6.7680688689462028e-005</v>
+        <v>-6.7680688689462909e-005</v>
       </c>
       <c r="D23">
-        <v>-1.4565289128997498e-005</v>
+        <v>-1.4565289128993405e-005</v>
       </c>
       <c r="E23">
-        <v>1.4559625400088673e-007</v>
+        <v>1.4559625400084534e-007</v>
       </c>
       <c r="F23">
-        <v>0.00028316271886620701</v>
+        <v>0.00028316271886621048</v>
       </c>
       <c r="G23">
-        <v>0.00037065696543726846</v>
+        <v>0.00037065696543726379</v>
       </c>
       <c r="H23">
-        <v>0.00021564468405084914</v>
+        <v>0.00021564468405084404</v>
       </c>
       <c r="I23">
-        <v>0.00055756887930067658</v>
+        <v>0.00055756887930067116</v>
       </c>
       <c r="J23">
-        <v>0.00053990245059271037</v>
+        <v>0.00053990245059270343</v>
       </c>
       <c r="K23">
-        <v>0.00034642341845914537</v>
+        <v>0.00034642341845914732</v>
       </c>
       <c r="L23">
-        <v>0.00053061406795338717</v>
+        <v>0.00053061406795337979</v>
       </c>
       <c r="M23">
-        <v>0.0012435844642963705</v>
+        <v>0.0012435844642963826</v>
       </c>
       <c r="N23">
-        <v>0.0012343293384560815</v>
+        <v>0.0012343293384560789</v>
       </c>
       <c r="O23">
-        <v>0.0010281791198004781</v>
+        <v>0.001028179119800495</v>
       </c>
       <c r="P23">
-        <v>0.00016776162462602139</v>
+        <v>0.00016776162462602009</v>
       </c>
       <c r="Q23">
-        <v>0.00023342728825639616</v>
+        <v>0.0002334272882563967</v>
       </c>
       <c r="R23">
-        <v>0.00019563666315527669</v>
+        <v>0.0001956366631552807</v>
       </c>
       <c r="S23">
-        <v>-1.457738535931683e-006</v>
+        <v>-1.4577385359316356e-006</v>
       </c>
       <c r="T23">
-        <v>-1.9782017643194653e-006</v>
+        <v>-1.9782017643192688e-006</v>
       </c>
       <c r="U23">
-        <v>0.00090304424419730732</v>
+        <v>0.00090304424419730689</v>
       </c>
       <c r="V23">
-        <v>0.001438249099318946</v>
+        <v>0.0014382490993189421</v>
       </c>
       <c r="W23">
-        <v>0.0016191610611042309</v>
+        <v>0.0016191610611042257</v>
       </c>
       <c r="X23">
-        <v>0.0022590495903486267</v>
+        <v>0.0022590495903486172</v>
       </c>
       <c r="Y23">
-        <v>-9.2499615380287224e-005</v>
+        <v>-9.2499615380287062e-005</v>
       </c>
       <c r="Z23">
-        <v>-1.9718108388979707e-005</v>
+        <v>-1.9718108388979382e-005</v>
       </c>
       <c r="AA23">
-        <v>2.7106839798559084e-005</v>
+        <v>2.7106839798560277e-005</v>
       </c>
       <c r="AB23">
-        <v>-1.9083401742996217e-005</v>
+        <v>-1.9083401742992856e-005</v>
       </c>
       <c r="AC23">
-        <v>8.0001062442423501e-005</v>
+        <v>8.0001062442423419e-005</v>
       </c>
       <c r="AD23">
-        <v>6.6266146997782997e-005</v>
+        <v>6.6266146997782089e-005</v>
       </c>
       <c r="AE23">
-        <v>6.3438348941717289e-005</v>
+        <v>6.3438348941719782e-005</v>
       </c>
       <c r="AF23">
-        <v>3.0704801696259721e-005</v>
+        <v>3.070480169626029e-005</v>
       </c>
       <c r="AG23">
-        <v>6.1770233905072218e-005</v>
+        <v>6.1770233905076568e-005</v>
       </c>
       <c r="AH23">
-        <v>7.2494043269069968e-005</v>
+        <v>7.2494043269072327e-005</v>
       </c>
       <c r="AI23">
-        <v>5.9057308561918869e-005</v>
+        <v>5.9057308561919519e-005</v>
       </c>
       <c r="AJ23">
-        <v>-3.990600052266723e-005</v>
+        <v>-3.9906000522667718e-005</v>
       </c>
       <c r="AK23">
-        <v>6.1921404085622648e-005</v>
+        <v>6.1921404085626985e-005</v>
       </c>
       <c r="AL23">
-        <v>3.233796564268025e-006</v>
+        <v>3.2337965642682961e-006</v>
       </c>
       <c r="AM23">
-        <v>-3.6071372926431856e-005</v>
+        <v>-3.6071372926432289e-005</v>
       </c>
       <c r="AN23">
-        <v>3.1095124272513151e-005</v>
+        <v>3.1095124272512067e-005</v>
       </c>
       <c r="AO23">
-        <v>3.6381671166443971e-006</v>
+        <v>3.6381671166456982e-006</v>
       </c>
       <c r="AP23">
-        <v>0.00011680430192955864</v>
+        <v>0.0001168043019295581</v>
       </c>
       <c r="AQ23">
-        <v>1.847634351199339e-005</v>
+        <v>1.8476343511995667e-005</v>
       </c>
       <c r="AR23">
-        <v>-0.0015469890464635779</v>
+        <v>-0.0015469890464636269</v>
       </c>
     </row>
     <row r="24">
@@ -3568,130 +3694,130 @@
         <v>0.025332245207594532</v>
       </c>
       <c r="C24">
-        <v>1.9172472073785821e-006</v>
+        <v>1.917247207378602e-006</v>
       </c>
       <c r="D24">
-        <v>-4.0173526973749299e-007</v>
+        <v>-4.017352697375687e-007</v>
       </c>
       <c r="E24">
-        <v>-1.8348439949019265e-009</v>
+        <v>-1.8348439949012003e-009</v>
       </c>
       <c r="F24">
-        <v>3.8247655731721304e-006</v>
+        <v>3.8247655731720796e-006</v>
       </c>
       <c r="G24">
-        <v>-7.8086964854894302e-006</v>
+        <v>-7.8086964854892676e-006</v>
       </c>
       <c r="H24">
-        <v>1.1453377564667509e-005</v>
+        <v>1.1453377564667655e-005</v>
       </c>
       <c r="I24">
-        <v>5.334721430239551e-006</v>
+        <v>5.3347214302397408e-006</v>
       </c>
       <c r="J24">
-        <v>2.8737524549438014e-006</v>
+        <v>2.8737524549439623e-006</v>
       </c>
       <c r="K24">
-        <v>-4.8224622873501432e-007</v>
+        <v>-4.8224622873499907e-007</v>
       </c>
       <c r="L24">
-        <v>-1.5698585313602546e-005</v>
+        <v>-1.569858531360243e-005</v>
       </c>
       <c r="M24">
-        <v>-7.7535588980698084e-005</v>
+        <v>-7.7535588980698355e-005</v>
       </c>
       <c r="N24">
-        <v>-7.2422524511325288e-005</v>
+        <v>-7.2422524511325234e-005</v>
       </c>
       <c r="O24">
-        <v>-8.3327383696171092e-005</v>
+        <v>-8.3327383696171349e-005</v>
       </c>
       <c r="P24">
-        <v>-5.759060063784046e-007</v>
+        <v>-5.7590600637830762e-007</v>
       </c>
       <c r="Q24">
-        <v>7.5993245916347912e-006</v>
+        <v>7.5993245916349217e-006</v>
       </c>
       <c r="R24">
-        <v>-9.6685720339629898e-006</v>
+        <v>-9.6685720339630135e-006</v>
       </c>
       <c r="S24">
-        <v>-2.6198855942942262e-008</v>
+        <v>-2.6198855942942579e-008</v>
       </c>
       <c r="T24">
-        <v>4.9522192939229459e-008</v>
+        <v>4.9522192939231471e-008</v>
       </c>
       <c r="U24">
-        <v>-7.9295951572697855e-005</v>
+        <v>-7.9295951572697719e-005</v>
       </c>
       <c r="V24">
-        <v>-0.00010321457883615811</v>
+        <v>-0.00010321457883615798</v>
       </c>
       <c r="W24">
-        <v>-9.9254478770523832e-005</v>
+        <v>-9.9254478770523778e-005</v>
       </c>
       <c r="X24">
-        <v>-9.2499615380287224e-005</v>
+        <v>-9.2499615380287062e-005</v>
       </c>
       <c r="Y24">
-        <v>1.8384296100941413e-005</v>
+        <v>1.8384296100941399e-005</v>
       </c>
       <c r="Z24">
-        <v>-3.8476829746095646e-006</v>
+        <v>-3.8476829746095917e-006</v>
       </c>
       <c r="AA24">
-        <v>5.492820011553154e-006</v>
+        <v>5.4928200115530185e-006</v>
       </c>
       <c r="AB24">
-        <v>6.3134423785058351e-006</v>
+        <v>6.3134423785055166e-006</v>
       </c>
       <c r="AC24">
-        <v>1.8377217868794636e-006</v>
+        <v>1.8377217868792552e-006</v>
       </c>
       <c r="AD24">
-        <v>1.6504408618961196e-006</v>
+        <v>1.6504408618962091e-006</v>
       </c>
       <c r="AE24">
-        <v>5.0821490929837811e-006</v>
+        <v>5.0821490929835541e-006</v>
       </c>
       <c r="AF24">
-        <v>6.9324461777779794e-006</v>
+        <v>6.9324461777778812e-006</v>
       </c>
       <c r="AG24">
-        <v>9.4406532682533979e-007</v>
+        <v>9.440653268250175e-007</v>
       </c>
       <c r="AH24">
-        <v>2.543888677239866e-006</v>
+        <v>2.5438886772396737e-006</v>
       </c>
       <c r="AI24">
-        <v>5.5325639065215473e-006</v>
+        <v>5.5325639065214609e-006</v>
       </c>
       <c r="AJ24">
         <v>7.6531177090155907e-006</v>
       </c>
       <c r="AK24">
-        <v>9.3274257843658481e-006</v>
+        <v>9.3274257843655161e-006</v>
       </c>
       <c r="AL24">
-        <v>8.1572801357504765e-008</v>
+        <v>8.1572801357501377e-008</v>
       </c>
       <c r="AM24">
         <v>6.7178253239322673e-006</v>
       </c>
       <c r="AN24">
-        <v>3.1385165109328633e-006</v>
+        <v>3.138516510932931e-006</v>
       </c>
       <c r="AO24">
-        <v>2.6593975610107229e-006</v>
+        <v>2.6593975610106822e-006</v>
       </c>
       <c r="AP24">
-        <v>9.2676325506488142e-006</v>
+        <v>9.2676325506488447e-006</v>
       </c>
       <c r="AQ24">
-        <v>1.4885622350689095e-005</v>
+        <v>1.4885622350688898e-005</v>
       </c>
       <c r="AR24">
-        <v>9.6391757175422248e-005</v>
+        <v>9.6391757175425853e-005</v>
       </c>
     </row>
     <row r="25">
@@ -3702,130 +3828,130 @@
         <v>3.7629327198538025</v>
       </c>
       <c r="C25">
-        <v>4.9133748646457759e-006</v>
+        <v>4.9133748646456811e-006</v>
       </c>
       <c r="D25">
-        <v>1.6528686182612116e-006</v>
+        <v>1.6528686182612793e-006</v>
       </c>
       <c r="E25">
-        <v>-3.1040478989826164e-008</v>
+        <v>-3.1040478989826905e-008</v>
       </c>
       <c r="F25">
-        <v>7.7175228406035532e-005</v>
+        <v>7.7175228406035478e-005</v>
       </c>
       <c r="G25">
-        <v>-3.9563504319354832e-005</v>
+        <v>-3.9563504319355103e-005</v>
       </c>
       <c r="H25">
-        <v>-5.1553080450806416e-005</v>
+        <v>-5.1553080450806796e-005</v>
       </c>
       <c r="I25">
-        <v>-2.1069270456002345e-005</v>
+        <v>-2.1069270456002616e-005</v>
       </c>
       <c r="J25">
-        <v>-2.9279214136346786e-005</v>
+        <v>-2.9279214136346949e-005</v>
       </c>
       <c r="K25">
         <v>-3.4067901259253897e-005</v>
       </c>
       <c r="L25">
-        <v>9.4514353176459185e-006</v>
+        <v>9.4514353176456474e-006</v>
       </c>
       <c r="M25">
-        <v>-0.0001127040533805369</v>
+        <v>-0.00011270405338053647</v>
       </c>
       <c r="N25">
-        <v>-1.5189057460102194e-005</v>
+        <v>-1.518905746010176e-005</v>
       </c>
       <c r="O25">
-        <v>1.1081674890348709e-005</v>
+        <v>1.108167489034936e-005</v>
       </c>
       <c r="P25">
-        <v>-3.0115007396594559e-006</v>
+        <v>-3.0115007396596728e-006</v>
       </c>
       <c r="Q25">
-        <v>1.9829827945221025e-005</v>
+        <v>1.9829827945220862e-005</v>
       </c>
       <c r="R25">
-        <v>4.6467771264812718e-006</v>
+        <v>4.6467771264813531e-006</v>
       </c>
       <c r="S25">
-        <v>-7.2403600792762224e-007</v>
+        <v>-7.2403600792760869e-007</v>
       </c>
       <c r="T25">
-        <v>-4.0966996353986499e-007</v>
+        <v>-4.096699635398599e-007</v>
       </c>
       <c r="U25">
-        <v>-2.483725332290659e-005</v>
+        <v>-2.4837253322906373e-005</v>
       </c>
       <c r="V25">
-        <v>-3.2659898003095807e-005</v>
+        <v>-3.2659898003095373e-005</v>
       </c>
       <c r="W25">
-        <v>-3.994251917640722e-005</v>
+        <v>-3.9942519176406461e-005</v>
       </c>
       <c r="X25">
-        <v>-1.9718108388979707e-005</v>
+        <v>-1.9718108388979382e-005</v>
       </c>
       <c r="Y25">
-        <v>-3.8476829746095646e-006</v>
+        <v>-3.8476829746095917e-006</v>
       </c>
       <c r="Z25">
-        <v>0.00036115170827494958</v>
+        <v>0.00036115170827494953</v>
       </c>
       <c r="AA25">
-        <v>1.8867667497290179e-005</v>
+        <v>1.8867667497290433e-005</v>
       </c>
       <c r="AB25">
-        <v>3.2410306295986387e-005</v>
+        <v>3.2410306295986455e-005</v>
       </c>
       <c r="AC25">
-        <v>1.2464750887375996e-005</v>
+        <v>1.2464750887376206e-005</v>
       </c>
       <c r="AD25">
-        <v>-3.8485784119720351e-006</v>
+        <v>-3.8485784119723595e-006</v>
       </c>
       <c r="AE25">
-        <v>-1.4497062607255772e-005</v>
+        <v>-1.4497062607255691e-005</v>
       </c>
       <c r="AF25">
-        <v>1.8674528758030312e-005</v>
+        <v>1.8674528758030681e-005</v>
       </c>
       <c r="AG25">
-        <v>1.0898978086052061e-005</v>
+        <v>1.0898978086052437e-005</v>
       </c>
       <c r="AH25">
-        <v>3.6729566786976938e-005</v>
+        <v>3.6729566786976999e-005</v>
       </c>
       <c r="AI25">
-        <v>1.1208741863025789e-005</v>
+        <v>1.1208741863025836e-005</v>
       </c>
       <c r="AJ25">
-        <v>2.7192284001170244e-005</v>
+        <v>2.7192284001170135e-005</v>
       </c>
       <c r="AK25">
-        <v>3.8810514857990052e-005</v>
+        <v>3.8810514857990357e-005</v>
       </c>
       <c r="AL25">
-        <v>-2.2410219462174139e-006</v>
+        <v>-2.2410219462174207e-006</v>
       </c>
       <c r="AM25">
-        <v>2.0566109562185455e-005</v>
+        <v>2.0566109562185522e-005</v>
       </c>
       <c r="AN25">
-        <v>8.5543599476870262e-006</v>
+        <v>8.5543599476870397e-006</v>
       </c>
       <c r="AO25">
-        <v>1.7994488680800379e-005</v>
+        <v>1.7994488680800515e-005</v>
       </c>
       <c r="AP25">
-        <v>5.6032212269172835e-005</v>
+        <v>5.6032212269172822e-005</v>
       </c>
       <c r="AQ25">
-        <v>3.2310732276846345e-006</v>
+        <v>3.2310732276847633e-006</v>
       </c>
       <c r="AR25">
-        <v>-6.246885734528862e-005</v>
+        <v>-6.2468857345290775e-005</v>
       </c>
     </row>
     <row r="26">
@@ -3836,130 +3962,130 @@
         <v>0.12817871214002283</v>
       </c>
       <c r="C26">
-        <v>1.4586778808205605e-005</v>
+        <v>1.4586778808205727e-005</v>
       </c>
       <c r="D26">
-        <v>1.1045635412607635e-006</v>
+        <v>1.1045635412611802e-006</v>
       </c>
       <c r="E26">
-        <v>-5.1573874919431026e-009</v>
+        <v>-5.1573874919470466e-009</v>
       </c>
       <c r="F26">
-        <v>-2.09485669032236e-005</v>
+        <v>-2.0948566903222733e-005</v>
       </c>
       <c r="G26">
-        <v>2.1099303147705569e-005</v>
+        <v>2.1099303147705312e-005</v>
       </c>
       <c r="H26">
-        <v>-3.0852490993212906e-005</v>
+        <v>-3.0852490993213083e-005</v>
       </c>
       <c r="I26">
-        <v>-3.8454813066869875e-005</v>
+        <v>-3.8454813066869631e-005</v>
       </c>
       <c r="J26">
-        <v>2.8316877733636889e-005</v>
+        <v>2.8316877733636781e-005</v>
       </c>
       <c r="K26">
-        <v>5.4067773522827763e-005</v>
+        <v>5.4067773522828183e-005</v>
       </c>
       <c r="L26">
-        <v>2.8939937073308044e-005</v>
+        <v>2.8939937073308017e-005</v>
       </c>
       <c r="M26">
-        <v>-4.5786824760092062e-005</v>
+        <v>-4.5786824760088809e-005</v>
       </c>
       <c r="N26">
-        <v>-2.381389980264713e-005</v>
+        <v>-2.3813899802646154e-005</v>
       </c>
       <c r="O26">
-        <v>-6.393419503143149e-005</v>
+        <v>-6.3934195031429376e-005</v>
       </c>
       <c r="P26">
-        <v>-2.799545736193258e-005</v>
+        <v>-2.7995457361932376e-005</v>
       </c>
       <c r="Q26">
-        <v>-1.4529425622065881e-006</v>
+        <v>-1.4529425622061408e-006</v>
       </c>
       <c r="R26">
-        <v>4.2708286761512158e-007</v>
+        <v>4.2708286761595506e-007</v>
       </c>
       <c r="S26">
-        <v>1.9879628997550427e-006</v>
+        <v>1.9879628997550588e-006</v>
       </c>
       <c r="T26">
-        <v>1.5652263061771817e-006</v>
+        <v>1.5652263061771334e-006</v>
       </c>
       <c r="U26">
-        <v>-3.076897877102392e-005</v>
+        <v>-3.07689787710227e-005</v>
       </c>
       <c r="V26">
-        <v>-4.288569286322138e-005</v>
+        <v>-4.2885692863219753e-005</v>
       </c>
       <c r="W26">
-        <v>7.6307758992014488e-008</v>
+        <v>7.6307758993640791e-008</v>
       </c>
       <c r="X26">
-        <v>2.7106839798559084e-005</v>
+        <v>2.7106839798560277e-005</v>
       </c>
       <c r="Y26">
-        <v>5.492820011553154e-006</v>
+        <v>5.4928200115530185e-006</v>
       </c>
       <c r="Z26">
-        <v>1.8867667497290179e-005</v>
+        <v>1.8867667497290433e-005</v>
       </c>
       <c r="AA26">
-        <v>0.0017520960258131846</v>
+        <v>0.0017520960258131844</v>
       </c>
       <c r="AB26">
-        <v>0.00076582610333398042</v>
+        <v>0.00076582610333397977</v>
       </c>
       <c r="AC26">
-        <v>0.0007416764676055485</v>
+        <v>0.00074167646760554785</v>
       </c>
       <c r="AD26">
-        <v>0.00074161030818948844</v>
+        <v>0.00074161030818948757</v>
       </c>
       <c r="AE26">
-        <v>0.00071419180411844835</v>
+        <v>0.00071419180411844813</v>
       </c>
       <c r="AF26">
         <v>0.0007538483389272657</v>
       </c>
       <c r="AG26">
-        <v>0.00077345142835916268</v>
+        <v>0.00077345142835916366</v>
       </c>
       <c r="AH26">
-        <v>0.00076783116940227374</v>
+        <v>0.00076783116940227385</v>
       </c>
       <c r="AI26">
-        <v>0.00075508385658314625</v>
+        <v>0.00075508385658314549</v>
       </c>
       <c r="AJ26">
-        <v>0.0007535264710489748</v>
+        <v>0.00075352647104897361</v>
       </c>
       <c r="AK26">
-        <v>0.00076262389974661329</v>
+        <v>0.00076262389974661427</v>
       </c>
       <c r="AL26">
-        <v>-4.185880501603325e-007</v>
+        <v>-4.1858805016029184e-007</v>
       </c>
       <c r="AM26">
-        <v>1.0153964018569367e-005</v>
+        <v>1.0153964018569205e-005</v>
       </c>
       <c r="AN26">
-        <v>-2.9249240436185031e-005</v>
+        <v>-2.9249240436185139e-005</v>
       </c>
       <c r="AO26">
-        <v>0.00040667310985996778</v>
+        <v>0.00040667310985996799</v>
       </c>
       <c r="AP26">
-        <v>0.00042653613757206023</v>
+        <v>0.00042653613757206001</v>
       </c>
       <c r="AQ26">
-        <v>0.0001801290143543884</v>
+        <v>0.00018012901435438886</v>
       </c>
       <c r="AR26">
-        <v>-0.00097135406621512844</v>
+        <v>-0.00097135406621512649</v>
       </c>
     </row>
     <row r="27">
@@ -3970,130 +4096,130 @@
         <v>0.21540611465986548</v>
       </c>
       <c r="C27">
-        <v>4.8348325666041706e-005</v>
+        <v>4.8348325666041652e-005</v>
       </c>
       <c r="D27">
-        <v>1.9078451432136867e-006</v>
+        <v>1.9078451432141203e-006</v>
       </c>
       <c r="E27">
-        <v>-2.1319695933760214e-008</v>
+        <v>-2.1319695933764132e-008</v>
       </c>
       <c r="F27">
-        <v>7.4816698394393651e-005</v>
+        <v>7.4816698394393976e-005</v>
       </c>
       <c r="G27">
-        <v>5.8517165327780555e-005</v>
+        <v>5.8517165327780013e-005</v>
       </c>
       <c r="H27">
-        <v>-7.1957525722399739e-006</v>
+        <v>-7.1957525722406515e-006</v>
       </c>
       <c r="I27">
-        <v>-1.7163599744755864e-005</v>
+        <v>-1.7163599744756406e-005</v>
       </c>
       <c r="J27">
-        <v>-2.4321333586669518e-005</v>
+        <v>-2.4321333586669843e-005</v>
       </c>
       <c r="K27">
-        <v>7.6244204832872503e-005</v>
+        <v>7.6244204832872611e-005</v>
       </c>
       <c r="L27">
         <v>3.6558440500630341e-005</v>
       </c>
       <c r="M27">
-        <v>-7.5309339545896032e-005</v>
+        <v>-7.5309339545891044e-005</v>
       </c>
       <c r="N27">
-        <v>-6.7511640797502e-005</v>
+        <v>-6.7511640797498964e-005</v>
       </c>
       <c r="O27">
-        <v>-8.0433865819956455e-005</v>
+        <v>-8.0433865819952986e-005</v>
       </c>
       <c r="P27">
-        <v>-3.5894578389401049e-005</v>
+        <v>-3.5894578389401266e-005</v>
       </c>
       <c r="Q27">
-        <v>-3.1162968217501695e-005</v>
+        <v>-3.1162968217501966e-005</v>
       </c>
       <c r="R27">
-        <v>1.5711229592522443e-005</v>
+        <v>1.5711229592522849e-005</v>
       </c>
       <c r="S27">
-        <v>4.7712506940220115e-007</v>
+        <v>4.7712506940221131e-007</v>
       </c>
       <c r="T27">
-        <v>1.8042953125036854e-006</v>
+        <v>1.804295312503687e-006</v>
       </c>
       <c r="U27">
-        <v>-2.4992711963683965e-005</v>
+        <v>-2.4992711963681363e-005</v>
       </c>
       <c r="V27">
-        <v>-7.0892266513092978e-005</v>
+        <v>-7.0892266513089509e-005</v>
       </c>
       <c r="W27">
-        <v>-4.2100027117227077e-006</v>
+        <v>-4.2100027117191298e-006</v>
       </c>
       <c r="X27">
-        <v>-1.9083401742996217e-005</v>
+        <v>-1.9083401742992856e-005</v>
       </c>
       <c r="Y27">
-        <v>6.3134423785058351e-006</v>
+        <v>6.3134423785055166e-006</v>
       </c>
       <c r="Z27">
-        <v>3.2410306295986387e-005</v>
+        <v>3.2410306295986455e-005</v>
       </c>
       <c r="AA27">
-        <v>0.00076582610333398042</v>
+        <v>0.00076582610333397977</v>
       </c>
       <c r="AB27">
-        <v>0.0014817686315319303</v>
+        <v>0.0014817686315319297</v>
       </c>
       <c r="AC27">
-        <v>0.00074430609589742241</v>
+        <v>0.0007443060958974223</v>
       </c>
       <c r="AD27">
-        <v>0.00075207796468486202</v>
+        <v>0.00075207796468486062</v>
       </c>
       <c r="AE27">
-        <v>0.0007105221784815337</v>
+        <v>0.00071052217848153348</v>
       </c>
       <c r="AF27">
-        <v>0.0007629490986268265</v>
+        <v>0.00076294909862682661</v>
       </c>
       <c r="AG27">
-        <v>0.00077085599380908307</v>
+        <v>0.00077085599380908394</v>
       </c>
       <c r="AH27">
         <v>0.00077824357656879723</v>
       </c>
       <c r="AI27">
-        <v>0.00076365159117512628</v>
+        <v>0.00076365159117512584</v>
       </c>
       <c r="AJ27">
-        <v>0.00075392067678132406</v>
+        <v>0.00075392067678132298</v>
       </c>
       <c r="AK27">
-        <v>0.00076775634214041276</v>
+        <v>0.00076775634214041352</v>
       </c>
       <c r="AL27">
-        <v>8.2812427561535824e-006</v>
+        <v>8.2812427561536095e-006</v>
       </c>
       <c r="AM27">
-        <v>-2.7424139002368332e-006</v>
+        <v>-2.7424139002368603e-006</v>
       </c>
       <c r="AN27">
-        <v>-3.7753771744656071e-005</v>
+        <v>-3.775377174465618e-005</v>
       </c>
       <c r="AO27">
         <v>0.00056897941243370031</v>
       </c>
       <c r="AP27">
-        <v>0.00034086033844387586</v>
+        <v>0.00034086033844387569</v>
       </c>
       <c r="AQ27">
-        <v>0.00019285211886811151</v>
+        <v>0.00019285211886811186</v>
       </c>
       <c r="AR27">
-        <v>-0.0010810131861802076</v>
+        <v>-0.0010810131861802047</v>
       </c>
     </row>
     <row r="28">
@@ -4104,88 +4230,88 @@
         <v>0.18614353591487351</v>
       </c>
       <c r="C28">
-        <v>4.1662813292447448e-006</v>
+        <v>4.1662813292441722e-006</v>
       </c>
       <c r="D28">
-        <v>-1.5330894462409858e-006</v>
+        <v>-1.533089446239556e-006</v>
       </c>
       <c r="E28">
-        <v>2.0522970470851614e-008</v>
+        <v>2.052297047083744e-008</v>
       </c>
       <c r="F28">
-        <v>7.9931594919426674e-005</v>
+        <v>7.993159491942662e-005</v>
       </c>
       <c r="G28">
-        <v>6.1187453167548282e-005</v>
+        <v>6.1187453167544758e-005</v>
       </c>
       <c r="H28">
-        <v>1.1450031033868049e-005</v>
+        <v>1.145003103386485e-005</v>
       </c>
       <c r="I28">
-        <v>9.8732372083621119e-005</v>
+        <v>9.8732372083617785e-005</v>
       </c>
       <c r="J28">
-        <v>8.7419944024424398e-005</v>
+        <v>8.7419944024420495e-005</v>
       </c>
       <c r="K28">
-        <v>0.0001075158168526052</v>
+        <v>0.0001075158168526039</v>
       </c>
       <c r="L28">
-        <v>5.2709697111056895e-005</v>
+        <v>5.27096971110531e-005</v>
       </c>
       <c r="M28">
-        <v>-2.1817353218621572e-005</v>
+        <v>-2.1817353218613956e-005</v>
       </c>
       <c r="N28">
-        <v>2.4144081687174011e-005</v>
+        <v>2.4144081687175881e-005</v>
       </c>
       <c r="O28">
-        <v>-2.6517319736276779e-005</v>
+        <v>-2.6517319736269379e-005</v>
       </c>
       <c r="P28">
-        <v>-2.113688565160433e-005</v>
+        <v>-2.1136885651604577e-005</v>
       </c>
       <c r="Q28">
-        <v>-3.374909157595717e-005</v>
+        <v>-3.3749091575957224e-005</v>
       </c>
       <c r="R28">
-        <v>-2.1759828669103873e-005</v>
+        <v>-2.1759828669102155e-005</v>
       </c>
       <c r="S28">
-        <v>1.3741449696128293e-006</v>
+        <v>1.374144969612853e-006</v>
       </c>
       <c r="T28">
-        <v>1.7997576982976277e-006</v>
+        <v>1.7997576982976438e-006</v>
       </c>
       <c r="U28">
-        <v>6.0764066150467282e-006</v>
+        <v>6.0764066150489508e-006</v>
       </c>
       <c r="V28">
-        <v>-1.0337927216232375e-005</v>
+        <v>-1.0337927216230302e-005</v>
       </c>
       <c r="W28">
-        <v>5.5323966355177572e-005</v>
+        <v>5.5323966355179171e-005</v>
       </c>
       <c r="X28">
-        <v>8.0001062442423501e-005</v>
+        <v>8.0001062442423419e-005</v>
       </c>
       <c r="Y28">
-        <v>1.8377217868794636e-006</v>
+        <v>1.8377217868792552e-006</v>
       </c>
       <c r="Z28">
-        <v>1.2464750887375996e-005</v>
+        <v>1.2464750887376206e-005</v>
       </c>
       <c r="AA28">
-        <v>0.0007416764676055485</v>
+        <v>0.00074167646760554785</v>
       </c>
       <c r="AB28">
-        <v>0.00074430609589742241</v>
+        <v>0.0007443060958974223</v>
       </c>
       <c r="AC28">
         <v>0.0014255880896480672</v>
       </c>
       <c r="AD28">
-        <v>0.00073421016262355818</v>
+        <v>0.0007342101626235572</v>
       </c>
       <c r="AE28">
         <v>0.00070152838912274085</v>
@@ -4194,40 +4320,40 @@
         <v>0.00074112676630128224</v>
       </c>
       <c r="AG28">
-        <v>0.00075674723407687875</v>
+        <v>0.00075674723407687995</v>
       </c>
       <c r="AH28">
         <v>0.00075773118476117531</v>
       </c>
       <c r="AI28">
-        <v>0.00075415647031044268</v>
+        <v>0.00075415647031044225</v>
       </c>
       <c r="AJ28">
-        <v>0.00073417708710036113</v>
+        <v>0.00073417708710036016</v>
       </c>
       <c r="AK28">
-        <v>0.00074810463871088516</v>
+        <v>0.00074810463871088613</v>
       </c>
       <c r="AL28">
-        <v>-1.3054637036469474e-006</v>
+        <v>-1.3054637036469203e-006</v>
       </c>
       <c r="AM28">
-        <v>6.3257219955537448e-005</v>
+        <v>6.3257219955537421e-005</v>
       </c>
       <c r="AN28">
-        <v>3.9561312607833414e-005</v>
+        <v>3.956131260783336e-005</v>
       </c>
       <c r="AO28">
-        <v>0.00036911767534070157</v>
+        <v>0.00036911767534070179</v>
       </c>
       <c r="AP28">
-        <v>0.0003493078803809193</v>
+        <v>0.00034930788038091919</v>
       </c>
       <c r="AQ28">
-        <v>0.00014827495259978966</v>
+        <v>0.00014827495259979014</v>
       </c>
       <c r="AR28">
-        <v>-0.00095530970503672149</v>
+        <v>-0.00095530970503672659</v>
       </c>
     </row>
     <row r="29">
@@ -4238,130 +4364,130 @@
         <v>0.2343467889093348</v>
       </c>
       <c r="C29">
-        <v>1.7452870443351564e-005</v>
+        <v>1.7452870443351544e-005</v>
       </c>
       <c r="D29">
-        <v>1.6505894576776775e-006</v>
+        <v>1.6505894576770522e-006</v>
       </c>
       <c r="E29">
-        <v>-1.163196309365136e-008</v>
+        <v>-1.1631963093645107e-008</v>
       </c>
       <c r="F29">
-        <v>0.00013480050484371357</v>
+        <v>0.00013480050484371132</v>
       </c>
       <c r="G29">
-        <v>6.5405406941513786e-005</v>
+        <v>6.5405406941513393e-005</v>
       </c>
       <c r="H29">
-        <v>1.4892552454762322e-005</v>
+        <v>1.4892552454762054e-005</v>
       </c>
       <c r="I29">
-        <v>0.00019982728928884206</v>
+        <v>0.00019982728928884149</v>
       </c>
       <c r="J29">
-        <v>8.5762330607335748e-005</v>
+        <v>8.576233060733545e-005</v>
       </c>
       <c r="K29">
-        <v>9.6352853455409658e-005</v>
+        <v>9.6352853455408167e-005</v>
       </c>
       <c r="L29">
-        <v>0.00011795259458065728</v>
+        <v>0.00011795259458065665</v>
       </c>
       <c r="M29">
-        <v>-2.2707777568890011e-005</v>
+        <v>-2.270777756889348e-005</v>
       </c>
       <c r="N29">
-        <v>-6.8561985376150185e-006</v>
+        <v>-6.8561985376162721e-006</v>
       </c>
       <c r="O29">
-        <v>-5.4597090472370632e-006</v>
+        <v>-5.4597090472407309e-006</v>
       </c>
       <c r="P29">
-        <v>-4.7830291953542181e-005</v>
+        <v>-4.7830291953543048e-005</v>
       </c>
       <c r="Q29">
-        <v>-5.8310482600679141e-005</v>
+        <v>-5.8310482600680341e-005</v>
       </c>
       <c r="R29">
-        <v>-1.7816854081849041e-005</v>
+        <v>-1.7816854081850257e-005</v>
       </c>
       <c r="S29">
-        <v>1.3792963263199738e-006</v>
+        <v>1.3792963263199096e-006</v>
       </c>
       <c r="T29">
-        <v>9.7846385221225734e-007</v>
+        <v>9.7846385221220016e-007</v>
       </c>
       <c r="U29">
-        <v>-2.2832336034873248e-005</v>
+        <v>-2.2832336034874244e-005</v>
       </c>
       <c r="V29">
-        <v>-2.4616680539874497e-005</v>
+        <v>-2.4616680539875578e-005</v>
       </c>
       <c r="W29">
-        <v>4.1041610294057716e-006</v>
+        <v>4.1041610294050719e-006</v>
       </c>
       <c r="X29">
-        <v>6.6266146997782997e-005</v>
+        <v>6.6266146997782089e-005</v>
       </c>
       <c r="Y29">
-        <v>1.6504408618961196e-006</v>
+        <v>1.6504408618962091e-006</v>
       </c>
       <c r="Z29">
-        <v>-3.8485784119720351e-006</v>
+        <v>-3.8485784119723595e-006</v>
       </c>
       <c r="AA29">
-        <v>0.00074161030818948844</v>
+        <v>0.00074161030818948757</v>
       </c>
       <c r="AB29">
-        <v>0.00075207796468486202</v>
+        <v>0.00075207796468486062</v>
       </c>
       <c r="AC29">
-        <v>0.00073421016262355818</v>
+        <v>0.0007342101626235572</v>
       </c>
       <c r="AD29">
-        <v>0.0014781135402534521</v>
+        <v>0.0014781135402534508</v>
       </c>
       <c r="AE29">
         <v>0.00070369050325878326</v>
       </c>
       <c r="AF29">
-        <v>0.00073306539195586444</v>
+        <v>0.00073306539195586433</v>
       </c>
       <c r="AG29">
-        <v>0.0007549982872926609</v>
+        <v>0.00075499828729266155</v>
       </c>
       <c r="AH29">
-        <v>0.00075190355026618445</v>
+        <v>0.00075190355026618456</v>
       </c>
       <c r="AI29">
-        <v>0.00075452145079943692</v>
+        <v>0.00075452145079943648</v>
       </c>
       <c r="AJ29">
-        <v>0.00072410759392834572</v>
+        <v>0.00072410759392834475</v>
       </c>
       <c r="AK29">
-        <v>0.00074700902868599886</v>
+        <v>0.00074700902868599984</v>
       </c>
       <c r="AL29">
-        <v>-2.0205520996701917e-007</v>
+        <v>-2.0205520996700562e-007</v>
       </c>
       <c r="AM29">
-        <v>3.8669777341555943e-005</v>
+        <v>3.8669777341555862e-005</v>
       </c>
       <c r="AN29">
-        <v>-1.3648641224538855e-006</v>
+        <v>-1.3648641224538584e-006</v>
       </c>
       <c r="AO29">
         <v>0.00034527432085628524</v>
       </c>
       <c r="AP29">
-        <v>0.00035063666474183312</v>
+        <v>0.00035063666474183301</v>
       </c>
       <c r="AQ29">
-        <v>0.00013240843373502206</v>
+        <v>0.00013240843373502254</v>
       </c>
       <c r="AR29">
-        <v>-0.00094956294404000907</v>
+        <v>-0.00094956294404000864</v>
       </c>
     </row>
     <row r="30">
@@ -4372,82 +4498,82 @@
         <v>0.25168116116828909</v>
       </c>
       <c r="C30">
-        <v>6.6743433041048662e-006</v>
+        <v>6.6743433041047443e-006</v>
       </c>
       <c r="D30">
-        <v>-1.7110537181407257e-006</v>
+        <v>-1.7110537181401226e-006</v>
       </c>
       <c r="E30">
-        <v>3.1711804310644824e-008</v>
+        <v>3.1711804310638842e-008</v>
       </c>
       <c r="F30">
-        <v>0.00015314337615946578</v>
+        <v>0.00015314337615946654</v>
       </c>
       <c r="G30">
-        <v>-2.4563141838224883e-005</v>
+        <v>-2.456314183822575e-005</v>
       </c>
       <c r="H30">
-        <v>7.7127984679595263e-006</v>
+        <v>7.7127984679586047e-006</v>
       </c>
       <c r="I30">
-        <v>-1.7878381275420043e-005</v>
+        <v>-1.7878381275420721e-005</v>
       </c>
       <c r="J30">
-        <v>4.6440425210770724e-005</v>
+        <v>4.644042521076991e-005</v>
       </c>
       <c r="K30">
-        <v>6.154551878967922e-005</v>
+        <v>6.1545518789679436e-005</v>
       </c>
       <c r="L30">
-        <v>1.3167178215708593e-007</v>
+        <v>1.3167178215648962e-007</v>
       </c>
       <c r="M30">
-        <v>-1.5651849468180466e-005</v>
+        <v>-1.5651849468175045e-005</v>
       </c>
       <c r="N30">
-        <v>5.0829659946405098e-005</v>
+        <v>5.0829659946407374e-005</v>
       </c>
       <c r="O30">
-        <v>-1.6961982026322906e-005</v>
+        <v>-1.6961982026318624e-005</v>
       </c>
       <c r="P30">
-        <v>-3.3215351931366393e-005</v>
+        <v>-3.3215351931366624e-005</v>
       </c>
       <c r="Q30">
-        <v>-3.6232512181531211e-006</v>
+        <v>-3.6232512181532159e-006</v>
       </c>
       <c r="R30">
-        <v>-4.9939853678547934e-005</v>
+        <v>-4.9939853678547493e-005</v>
       </c>
       <c r="S30">
-        <v>3.005024940018818e-006</v>
+        <v>3.0050249400188264e-006</v>
       </c>
       <c r="T30">
-        <v>2.2906799369046227e-006</v>
+        <v>2.2906799369046295e-006</v>
       </c>
       <c r="U30">
-        <v>2.7210759183189572e-005</v>
+        <v>2.7210759183191849e-005</v>
       </c>
       <c r="V30">
-        <v>-1.2420097785560322e-005</v>
+        <v>-1.2420097785557449e-005</v>
       </c>
       <c r="W30">
-        <v>3.5000378968972398e-005</v>
+        <v>3.5000378968975325e-005</v>
       </c>
       <c r="X30">
-        <v>6.3438348941717289e-005</v>
+        <v>6.3438348941719782e-005</v>
       </c>
       <c r="Y30">
-        <v>5.0821490929837811e-006</v>
+        <v>5.0821490929835541e-006</v>
       </c>
       <c r="Z30">
-        <v>-1.4497062607255772e-005</v>
+        <v>-1.4497062607255691e-005</v>
       </c>
       <c r="AA30">
-        <v>0.00071419180411844835</v>
+        <v>0.00071419180411844813</v>
       </c>
       <c r="AB30">
-        <v>0.0007105221784815337</v>
+        <v>0.00071052217848153348</v>
       </c>
       <c r="AC30">
         <v>0.00070152838912274085</v>
@@ -4462,40 +4588,40 @@
         <v>0.00071016430929977232</v>
       </c>
       <c r="AG30">
-        <v>0.00072391009447585338</v>
+        <v>0.00072391009447585447</v>
       </c>
       <c r="AH30">
-        <v>0.00071948789598513276</v>
+        <v>0.00071948789598513287</v>
       </c>
       <c r="AI30">
-        <v>0.00072592186689537464</v>
+        <v>0.00072592186689537442</v>
       </c>
       <c r="AJ30">
-        <v>0.00070256217106079574</v>
+        <v>0.00070256217106079476</v>
       </c>
       <c r="AK30">
-        <v>0.00071566647326955527</v>
+        <v>0.00071566647326955614</v>
       </c>
       <c r="AL30">
-        <v>5.2159778893596945e-006</v>
+        <v>5.2159778893597081e-006</v>
       </c>
       <c r="AM30">
-        <v>1.9976263603420775e-005</v>
+        <v>1.9976263603420721e-005</v>
       </c>
       <c r="AN30">
         <v>-1.3142188213072952e-005</v>
       </c>
       <c r="AO30">
-        <v>0.00025121291813554785</v>
+        <v>0.00025121291813554796</v>
       </c>
       <c r="AP30">
-        <v>0.00025745556175778983</v>
+        <v>0.00025745556175778972</v>
       </c>
       <c r="AQ30">
-        <v>9.7964694079839826e-005</v>
+        <v>9.7964694079840286e-005</v>
       </c>
       <c r="AR30">
-        <v>-0.0011091362621227568</v>
+        <v>-0.0011091362621227566</v>
       </c>
     </row>
     <row r="31">
@@ -4506,88 +4632,88 @@
         <v>0.17543179604188527</v>
       </c>
       <c r="C31">
-        <v>-9.2457802703926466e-007</v>
+        <v>-9.2457802703931549e-007</v>
       </c>
       <c r="D31">
-        <v>-7.9883507211689906e-008</v>
+        <v>-7.9883507211378198e-008</v>
       </c>
       <c r="E31">
-        <v>3.714190287959945e-009</v>
+        <v>3.7141902879569274e-009</v>
       </c>
       <c r="F31">
-        <v>5.7110204037460566e-005</v>
+        <v>5.7110204037459875e-005</v>
       </c>
       <c r="G31">
-        <v>4.3059488357400921e-005</v>
+        <v>4.3059488357399403e-005</v>
       </c>
       <c r="H31">
-        <v>-2.2166076240639593e-006</v>
+        <v>-2.21660762406545e-006</v>
       </c>
       <c r="I31">
-        <v>3.4066532533534111e-005</v>
+        <v>3.4066532533532946e-005</v>
       </c>
       <c r="J31">
-        <v>7.8426301734844681e-005</v>
+        <v>7.8426301734843421e-005</v>
       </c>
       <c r="K31">
-        <v>7.5388672424806392e-005</v>
+        <v>7.5388672424805552e-005</v>
       </c>
       <c r="L31">
-        <v>0.00010383663614040038</v>
+        <v>0.00010383663614039923</v>
       </c>
       <c r="M31">
-        <v>-5.1192621658569003e-005</v>
+        <v>-5.1192621658566347e-005</v>
       </c>
       <c r="N31">
-        <v>-3.0389947216074046e-005</v>
+        <v>-3.0389947216072908e-005</v>
       </c>
       <c r="O31">
-        <v>-4.8780497296978476e-005</v>
+        <v>-4.878049729697628e-005</v>
       </c>
       <c r="P31">
-        <v>-4.4925466177820861e-005</v>
+        <v>-4.4925466177821146e-005</v>
       </c>
       <c r="Q31">
-        <v>-3.3158693346604675e-005</v>
+        <v>-3.3158693346604824e-005</v>
       </c>
       <c r="R31">
-        <v>-2.3288915060881721e-005</v>
+        <v>-2.3288915060881653e-005</v>
       </c>
       <c r="S31">
-        <v>1.1013059060450647e-006</v>
+        <v>1.1013059060450714e-006</v>
       </c>
       <c r="T31">
-        <v>1.6814927442265341e-006</v>
+        <v>1.6814927442265422e-006</v>
       </c>
       <c r="U31">
-        <v>-4.9719309572991146e-005</v>
+        <v>-4.9719309572990306e-005</v>
       </c>
       <c r="V31">
-        <v>-6.7972506729304749e-005</v>
+        <v>-6.7972506729303502e-005</v>
       </c>
       <c r="W31">
-        <v>-3.2886693973134529e-005</v>
+        <v>-3.2886693973133336e-005</v>
       </c>
       <c r="X31">
-        <v>3.0704801696259721e-005</v>
+        <v>3.070480169626029e-005</v>
       </c>
       <c r="Y31">
-        <v>6.9324461777779794e-006</v>
+        <v>6.9324461777778812e-006</v>
       </c>
       <c r="Z31">
-        <v>1.8674528758030312e-005</v>
+        <v>1.8674528758030681e-005</v>
       </c>
       <c r="AA31">
         <v>0.0007538483389272657</v>
       </c>
       <c r="AB31">
-        <v>0.0007629490986268265</v>
+        <v>0.00076294909862682661</v>
       </c>
       <c r="AC31">
         <v>0.00074112676630128224</v>
       </c>
       <c r="AD31">
-        <v>0.00073306539195586444</v>
+        <v>0.00073306539195586433</v>
       </c>
       <c r="AE31">
         <v>0.00071016430929977232</v>
@@ -4596,40 +4722,40 @@
         <v>0.0013251436527656631</v>
       </c>
       <c r="AG31">
-        <v>0.00076759852390409153</v>
+        <v>0.0007675985239040924</v>
       </c>
       <c r="AH31">
-        <v>0.00076497387433915182</v>
+        <v>0.00076497387433915203</v>
       </c>
       <c r="AI31">
-        <v>0.00075925104225068023</v>
+        <v>0.0007592510422506798</v>
       </c>
       <c r="AJ31">
-        <v>0.0007458866854992204</v>
+        <v>0.00074588668549921953</v>
       </c>
       <c r="AK31">
-        <v>0.00075799814901674454</v>
+        <v>0.0007579981490167453</v>
       </c>
       <c r="AL31">
-        <v>-1.7176370339405016e-006</v>
+        <v>-1.7176370339404881e-006</v>
       </c>
       <c r="AM31">
-        <v>2.8469741865013473e-005</v>
+        <v>2.8469741865013446e-005</v>
       </c>
       <c r="AN31">
         <v>6.804480587293307e-006</v>
       </c>
       <c r="AO31">
-        <v>0.00038515508749997448</v>
+        <v>0.00038515508749997459</v>
       </c>
       <c r="AP31">
-        <v>0.00033555524927157611</v>
+        <v>0.00033555524927157606</v>
       </c>
       <c r="AQ31">
-        <v>8.1334805588733787e-005</v>
+        <v>8.1334805588734071e-005</v>
       </c>
       <c r="AR31">
-        <v>-0.0008715863496420365</v>
+        <v>-0.00087158634964203921</v>
       </c>
     </row>
     <row r="32">
@@ -4640,130 +4766,130 @@
         <v>0.17901918267980349</v>
       </c>
       <c r="C32">
-        <v>1.4919103126229899e-005</v>
+        <v>1.4919103126229465e-005</v>
       </c>
       <c r="D32">
-        <v>-7.8844860095415302e-007</v>
+        <v>-7.8844860095354485e-007</v>
       </c>
       <c r="E32">
-        <v>4.3192795793339746e-009</v>
+        <v>4.3192795793279792e-009</v>
       </c>
       <c r="F32">
-        <v>8.7040917421662192e-005</v>
+        <v>8.7040917421663222e-005</v>
       </c>
       <c r="G32">
-        <v>6.2684186318883307e-005</v>
+        <v>6.2684186318882968e-005</v>
       </c>
       <c r="H32">
-        <v>8.2950318306736807e-006</v>
+        <v>8.2950318306732403e-006</v>
       </c>
       <c r="I32">
-        <v>2.9277263107849511e-005</v>
+        <v>2.9277263107849517e-005</v>
       </c>
       <c r="J32">
-        <v>6.6898236795609375e-005</v>
+        <v>6.6898236795609036e-005</v>
       </c>
       <c r="K32">
-        <v>7.6854999545582188e-005</v>
+        <v>7.6854999545582675e-005</v>
       </c>
       <c r="L32">
-        <v>5.4381361092423086e-005</v>
+        <v>5.4381361092422998e-005</v>
       </c>
       <c r="M32">
-        <v>-6.4028010656713336e-005</v>
+        <v>-6.4028010656706926e-005</v>
       </c>
       <c r="N32">
-        <v>3.3971703979008487e-006</v>
+        <v>3.3971703979050771e-006</v>
       </c>
       <c r="O32">
-        <v>-6.374754304186153e-006</v>
+        <v>-6.3747543041801832e-006</v>
       </c>
       <c r="P32">
-        <v>-2.7841507683270559e-005</v>
+        <v>-2.7841507683270233e-005</v>
       </c>
       <c r="Q32">
-        <v>-1.8845789235205042e-005</v>
+        <v>-1.8845789235204249e-005</v>
       </c>
       <c r="R32">
-        <v>7.9766340056744047e-006</v>
+        <v>7.976634005675416e-006</v>
       </c>
       <c r="S32">
-        <v>9.1854783113393936e-007</v>
+        <v>9.1854783113400267e-007</v>
       </c>
       <c r="T32">
-        <v>1.3992193814255076e-006</v>
+        <v>1.3992193814255042e-006</v>
       </c>
       <c r="U32">
-        <v>-3.7684588234171212e-006</v>
+        <v>-3.7684588234136992e-006</v>
       </c>
       <c r="V32">
-        <v>-3.6431199264291717e-005</v>
+        <v>-3.6431199264287183e-005</v>
       </c>
       <c r="W32">
-        <v>1.6235610702650704e-005</v>
+        <v>1.6235610702655556e-005</v>
       </c>
       <c r="X32">
-        <v>6.1770233905072218e-005</v>
+        <v>6.1770233905076568e-005</v>
       </c>
       <c r="Y32">
-        <v>9.4406532682533979e-007</v>
+        <v>9.440653268250175e-007</v>
       </c>
       <c r="Z32">
-        <v>1.0898978086052061e-005</v>
+        <v>1.0898978086052437e-005</v>
       </c>
       <c r="AA32">
-        <v>0.00077345142835916268</v>
+        <v>0.00077345142835916366</v>
       </c>
       <c r="AB32">
-        <v>0.00077085599380908307</v>
+        <v>0.00077085599380908394</v>
       </c>
       <c r="AC32">
-        <v>0.00075674723407687875</v>
+        <v>0.00075674723407687995</v>
       </c>
       <c r="AD32">
-        <v>0.0007549982872926609</v>
+        <v>0.00075499828729266155</v>
       </c>
       <c r="AE32">
-        <v>0.00072391009447585338</v>
+        <v>0.00072391009447585447</v>
       </c>
       <c r="AF32">
-        <v>0.00076759852390409153</v>
+        <v>0.0007675985239040924</v>
       </c>
       <c r="AG32">
-        <v>0.0012522381586096861</v>
+        <v>0.0012522381586096869</v>
       </c>
       <c r="AH32">
         <v>0.00077917967158550809</v>
       </c>
       <c r="AI32">
-        <v>0.0007748577284809122</v>
+        <v>0.00077485772848091188</v>
       </c>
       <c r="AJ32">
-        <v>0.00075931960699552529</v>
+        <v>0.00075931960699552443</v>
       </c>
       <c r="AK32">
-        <v>0.00077346783161252419</v>
+        <v>0.00077346783161252506</v>
       </c>
       <c r="AL32">
-        <v>-3.6478814823989421e-007</v>
+        <v>-3.6478814823990777e-007</v>
       </c>
       <c r="AM32">
-        <v>1.2150099578316103e-005</v>
+        <v>1.2150099578316212e-005</v>
       </c>
       <c r="AN32">
-        <v>-3.153996104924661e-006</v>
+        <v>-3.1539961049245797e-006</v>
       </c>
       <c r="AO32">
-        <v>0.0004016707033665921</v>
+        <v>0.0004016707033665922</v>
       </c>
       <c r="AP32">
         <v>0.00043844491449865309</v>
       </c>
       <c r="AQ32">
-        <v>0.00013302587577027587</v>
+        <v>0.00013302587577027623</v>
       </c>
       <c r="AR32">
-        <v>-0.00090903362570042296</v>
+        <v>-0.00090903362570042188</v>
       </c>
     </row>
     <row r="33">
@@ -4774,79 +4900,79 @@
         <v>0.17682617604489581</v>
       </c>
       <c r="C33">
-        <v>1.3612597189542542e-005</v>
+        <v>1.3612597189542371e-005</v>
       </c>
       <c r="D33">
-        <v>2.2295222118078913e-006</v>
+        <v>2.229522211807871e-006</v>
       </c>
       <c r="E33">
-        <v>-2.6741717379863864e-008</v>
+        <v>-2.6741717379863639e-008</v>
       </c>
       <c r="F33">
-        <v>0.00010997163232206887</v>
+        <v>0.0001099716323220667</v>
       </c>
       <c r="G33">
-        <v>5.2049254081877014e-005</v>
+        <v>5.2049254081875157e-005</v>
       </c>
       <c r="H33">
-        <v>1.7039702809658626e-005</v>
+        <v>1.7039702809656728e-005</v>
       </c>
       <c r="I33">
-        <v>7.0805307919838198e-005</v>
+        <v>7.0805307919836395e-005</v>
       </c>
       <c r="J33">
-        <v>9.3364765904528245e-005</v>
+        <v>9.3364765904526618e-005</v>
       </c>
       <c r="K33">
-        <v>8.7393877995467327e-005</v>
+        <v>8.739387799546524e-005</v>
       </c>
       <c r="L33">
-        <v>5.7208549644156969e-005</v>
+        <v>5.7208549644155438e-005</v>
       </c>
       <c r="M33">
-        <v>-5.1584734982397039e-005</v>
+        <v>-5.1584734982394546e-005</v>
       </c>
       <c r="N33">
-        <v>1.3344986052519672e-005</v>
+        <v>1.334498605252228e-005</v>
       </c>
       <c r="O33">
-        <v>1.7637862802154376e-005</v>
+        <v>1.7637862802156388e-005</v>
       </c>
       <c r="P33">
-        <v>-3.1691635280815236e-005</v>
+        <v>-3.1691635280815785e-005</v>
       </c>
       <c r="Q33">
-        <v>-6.8509161631558018e-006</v>
+        <v>-6.8509161631561973e-006</v>
       </c>
       <c r="R33">
-        <v>1.4208835870225412e-005</v>
+        <v>1.4208835870225103e-005</v>
       </c>
       <c r="S33">
-        <v>1.9811368500926468e-006</v>
+        <v>1.9811368500926447e-006</v>
       </c>
       <c r="T33">
-        <v>2.7700938297861094e-007</v>
+        <v>2.770093829786085e-007</v>
       </c>
       <c r="U33">
-        <v>-4.0022951393980047e-005</v>
+        <v>-4.0022951393978062e-005</v>
       </c>
       <c r="V33">
-        <v>-4.3945520463039664e-005</v>
+        <v>-4.3945520463036899e-005</v>
       </c>
       <c r="W33">
-        <v>-3.6662179746308565e-006</v>
+        <v>-3.6662179746277394e-006</v>
       </c>
       <c r="X33">
-        <v>7.2494043269069968e-005</v>
+        <v>7.2494043269072327e-005</v>
       </c>
       <c r="Y33">
-        <v>2.543888677239866e-006</v>
+        <v>2.5438886772396737e-006</v>
       </c>
       <c r="Z33">
-        <v>3.6729566786976938e-005</v>
+        <v>3.6729566786976999e-005</v>
       </c>
       <c r="AA33">
-        <v>0.00076783116940227374</v>
+        <v>0.00076783116940227385</v>
       </c>
       <c r="AB33">
         <v>0.00077824357656879723</v>
@@ -4855,49 +4981,49 @@
         <v>0.00075773118476117531</v>
       </c>
       <c r="AD33">
-        <v>0.00075190355026618445</v>
+        <v>0.00075190355026618456</v>
       </c>
       <c r="AE33">
-        <v>0.00071948789598513276</v>
+        <v>0.00071948789598513287</v>
       </c>
       <c r="AF33">
-        <v>0.00076497387433915182</v>
+        <v>0.00076497387433915203</v>
       </c>
       <c r="AG33">
         <v>0.00077917967158550809</v>
       </c>
       <c r="AH33">
-        <v>0.0014557699200025346</v>
+        <v>0.0014557699200025353</v>
       </c>
       <c r="AI33">
-        <v>0.00076899962649758897</v>
+        <v>0.00076899962649758886</v>
       </c>
       <c r="AJ33">
-        <v>0.00075920868665692233</v>
+        <v>0.00075920868665692147</v>
       </c>
       <c r="AK33">
-        <v>0.00077569916809100403</v>
+        <v>0.00077569916809100523</v>
       </c>
       <c r="AL33">
-        <v>1.1857755812136285e-006</v>
+        <v>1.1857755812136556e-006</v>
       </c>
       <c r="AM33">
-        <v>3.5195521248497454e-005</v>
+        <v>3.5195521248497399e-005</v>
       </c>
       <c r="AN33">
-        <v>7.249235149254233e-006</v>
+        <v>7.2492351492541246e-006</v>
       </c>
       <c r="AO33">
-        <v>0.0004122811006228266</v>
+        <v>0.00041228110062282693</v>
       </c>
       <c r="AP33">
         <v>0.00040746498305542402</v>
       </c>
       <c r="AQ33">
-        <v>0.00016470006754011466</v>
+        <v>0.00016470006754011523</v>
       </c>
       <c r="AR33">
-        <v>-0.0010129733688989428</v>
+        <v>-0.0010129733688989456</v>
       </c>
     </row>
     <row r="34">
@@ -4908,130 +5034,130 @@
         <v>0.23917005253266202</v>
       </c>
       <c r="C34">
-        <v>5.8301133889744733e-005</v>
+        <v>5.8301133889744801e-005</v>
       </c>
       <c r="D34">
-        <v>3.5810226884147745e-007</v>
+        <v>3.5810226884189927e-007</v>
       </c>
       <c r="E34">
-        <v>-2.2986567658487526e-009</v>
+        <v>-2.2986567658527628e-009</v>
       </c>
       <c r="F34">
-        <v>8.963330669920557e-005</v>
+        <v>8.963330669920599e-005</v>
       </c>
       <c r="G34">
-        <v>7.8461982076474362e-005</v>
+        <v>7.8461982076473725e-005</v>
       </c>
       <c r="H34">
-        <v>7.3917316703664762e-005</v>
+        <v>7.3917316703664274e-005</v>
       </c>
       <c r="I34">
-        <v>3.4602105039228893e-005</v>
+        <v>3.4602105039228446e-005</v>
       </c>
       <c r="J34">
-        <v>8.0771753064403008e-005</v>
+        <v>8.0771753064402371e-005</v>
       </c>
       <c r="K34">
-        <v>0.00012436222096174531</v>
+        <v>0.00012436222096174563</v>
       </c>
       <c r="L34">
-        <v>8.0325162247492243e-005</v>
+        <v>8.032516224749185e-005</v>
       </c>
       <c r="M34">
-        <v>-6.5751063532627009e-005</v>
+        <v>-6.5751063532624163e-005</v>
       </c>
       <c r="N34">
-        <v>-3.5526186225770751e-005</v>
+        <v>-3.5526186225770073e-005</v>
       </c>
       <c r="O34">
-        <v>-3.6003823550613231e-005</v>
+        <v>-3.6003823550611713e-005</v>
       </c>
       <c r="P34">
-        <v>-7.7012783928613973e-005</v>
+        <v>-7.7012783928614366e-005</v>
       </c>
       <c r="Q34">
-        <v>-6.0803425415086148e-005</v>
+        <v>-6.0803425415086662e-005</v>
       </c>
       <c r="R34">
-        <v>2.8726732420323639e-005</v>
+        <v>2.8726732420324194e-005</v>
       </c>
       <c r="S34">
-        <v>1.872351147270361e-006</v>
+        <v>1.8723511472703058e-006</v>
       </c>
       <c r="T34">
-        <v>-9.0919938225552548e-008</v>
+        <v>-9.0919938225550007e-008</v>
       </c>
       <c r="U34">
-        <v>-3.9412224871447141e-005</v>
+        <v>-3.9412224871446111e-005</v>
       </c>
       <c r="V34">
-        <v>-6.192092835186396e-005</v>
+        <v>-6.192092835186274e-005</v>
       </c>
       <c r="W34">
-        <v>1.3189982189747e-007</v>
+        <v>1.3189982189860841e-007</v>
       </c>
       <c r="X34">
-        <v>5.9057308561918869e-005</v>
+        <v>5.9057308561919519e-005</v>
       </c>
       <c r="Y34">
-        <v>5.5325639065215473e-006</v>
+        <v>5.5325639065214609e-006</v>
       </c>
       <c r="Z34">
-        <v>1.1208741863025789e-005</v>
+        <v>1.1208741863025836e-005</v>
       </c>
       <c r="AA34">
-        <v>0.00075508385658314625</v>
+        <v>0.00075508385658314549</v>
       </c>
       <c r="AB34">
-        <v>0.00076365159117512628</v>
+        <v>0.00076365159117512584</v>
       </c>
       <c r="AC34">
-        <v>0.00075415647031044268</v>
+        <v>0.00075415647031044225</v>
       </c>
       <c r="AD34">
-        <v>0.00075452145079943692</v>
+        <v>0.00075452145079943648</v>
       </c>
       <c r="AE34">
-        <v>0.00072592186689537464</v>
+        <v>0.00072592186689537442</v>
       </c>
       <c r="AF34">
-        <v>0.00075925104225068023</v>
+        <v>0.0007592510422506798</v>
       </c>
       <c r="AG34">
-        <v>0.0007748577284809122</v>
+        <v>0.00077485772848091188</v>
       </c>
       <c r="AH34">
-        <v>0.00076899962649758897</v>
+        <v>0.00076899962649758886</v>
       </c>
       <c r="AI34">
-        <v>0.0018150990965600607</v>
+        <v>0.0018150990965600598</v>
       </c>
       <c r="AJ34">
-        <v>0.00075580073571676469</v>
+        <v>0.0007558007357167636</v>
       </c>
       <c r="AK34">
-        <v>0.00078004191764674655</v>
+        <v>0.00078004191764674742</v>
       </c>
       <c r="AL34">
-        <v>3.9421135921308836e-006</v>
+        <v>3.9421135921309243e-006</v>
       </c>
       <c r="AM34">
-        <v>-7.0821478250976465e-007</v>
+        <v>-7.0821478250990017e-007</v>
       </c>
       <c r="AN34">
-        <v>-4.0288353086371614e-005</v>
+        <v>-4.0288353086371696e-005</v>
       </c>
       <c r="AO34">
-        <v>0.00037346088621774333</v>
+        <v>0.00037346088621774344</v>
       </c>
       <c r="AP34">
-        <v>0.00040064684333281704</v>
+        <v>0.00040064684333281694</v>
       </c>
       <c r="AQ34">
-        <v>0.0001333008981011423</v>
+        <v>0.00013330089810114281</v>
       </c>
       <c r="AR34">
-        <v>-0.000991779301602816</v>
+        <v>-0.00099177930160281773</v>
       </c>
     </row>
     <row r="35">
@@ -5042,109 +5168,109 @@
         <v>0.15030017715138966</v>
       </c>
       <c r="C35">
-        <v>5.0434960393527338e-005</v>
+        <v>5.0434960393527263e-005</v>
       </c>
       <c r="D35">
-        <v>-2.3689269384005123e-006</v>
+        <v>-2.368926938400453e-006</v>
       </c>
       <c r="E35">
-        <v>2.0044812961463735e-008</v>
+        <v>2.0044812961462967e-008</v>
       </c>
       <c r="F35">
-        <v>2.0457253425828246e-005</v>
+        <v>2.0457253425826186e-005</v>
       </c>
       <c r="G35">
-        <v>-1.1715212806015348e-005</v>
+        <v>-1.1715212806017266e-005</v>
       </c>
       <c r="H35">
-        <v>-5.2956930014984375e-005</v>
+        <v>-5.2956930014986205e-005</v>
       </c>
       <c r="I35">
-        <v>-4.7534915596808612e-005</v>
+        <v>-4.7534915596810814e-005</v>
       </c>
       <c r="J35">
-        <v>4.7496736955574955e-006</v>
+        <v>4.7496736955553745e-006</v>
       </c>
       <c r="K35">
-        <v>2.3603331651853174e-005</v>
+        <v>2.3603331651851074e-005</v>
       </c>
       <c r="L35">
-        <v>-1.3812228128396513e-005</v>
+        <v>-1.3812228128398858e-005</v>
       </c>
       <c r="M35">
-        <v>-0.00012834369175097082</v>
+        <v>-0.00012834369175097074</v>
       </c>
       <c r="N35">
-        <v>-4.2131290468233024e-005</v>
+        <v>-4.2131290468233728e-005</v>
       </c>
       <c r="O35">
-        <v>-7.8927664947620185e-005</v>
+        <v>-7.8927664947619426e-005</v>
       </c>
       <c r="P35">
-        <v>-5.3016544937652357e-005</v>
+        <v>-5.3016544937652845e-005</v>
       </c>
       <c r="Q35">
-        <v>-3.6247264831092393e-005</v>
+        <v>-3.624726483109303e-005</v>
       </c>
       <c r="R35">
-        <v>1.416153316204855e-005</v>
+        <v>1.4161533162048418e-005</v>
       </c>
       <c r="S35">
-        <v>1.1257162621809847e-006</v>
+        <v>1.1257162621809245e-006</v>
       </c>
       <c r="T35">
-        <v>6.5432913302823684e-007</v>
+        <v>6.5432913302812694e-007</v>
       </c>
       <c r="U35">
-        <v>-4.861101136781027e-005</v>
+        <v>-4.8611011367810094e-005</v>
       </c>
       <c r="V35">
-        <v>-8.5252838608095932e-005</v>
+        <v>-8.5252838608095566e-005</v>
       </c>
       <c r="W35">
-        <v>-6.4705955962645644e-005</v>
+        <v>-6.4705955962645372e-005</v>
       </c>
       <c r="X35">
-        <v>-3.990600052266723e-005</v>
+        <v>-3.9906000522667718e-005</v>
       </c>
       <c r="Y35">
         <v>7.6531177090155907e-006</v>
       </c>
       <c r="Z35">
-        <v>2.7192284001170244e-005</v>
+        <v>2.7192284001170135e-005</v>
       </c>
       <c r="AA35">
-        <v>0.0007535264710489748</v>
+        <v>0.00075352647104897361</v>
       </c>
       <c r="AB35">
-        <v>0.00075392067678132406</v>
+        <v>0.00075392067678132298</v>
       </c>
       <c r="AC35">
-        <v>0.00073417708710036113</v>
+        <v>0.00073417708710036016</v>
       </c>
       <c r="AD35">
-        <v>0.00072410759392834572</v>
+        <v>0.00072410759392834475</v>
       </c>
       <c r="AE35">
-        <v>0.00070256217106079574</v>
+        <v>0.00070256217106079476</v>
       </c>
       <c r="AF35">
-        <v>0.0007458866854992204</v>
+        <v>0.00074588668549921953</v>
       </c>
       <c r="AG35">
-        <v>0.00075931960699552529</v>
+        <v>0.00075931960699552443</v>
       </c>
       <c r="AH35">
-        <v>0.00075920868665692233</v>
+        <v>0.00075920868665692147</v>
       </c>
       <c r="AI35">
-        <v>0.00075580073571676469</v>
+        <v>0.0007558007357167636</v>
       </c>
       <c r="AJ35">
-        <v>0.0013554452834347794</v>
+        <v>0.0013554452834347785</v>
       </c>
       <c r="AK35">
-        <v>0.0007556620152195764</v>
+        <v>0.00075566201521957727</v>
       </c>
       <c r="AL35">
         <v>2.6997776408038785e-007</v>
@@ -5153,19 +5279,19 @@
         <v>2.1656733642858348e-005</v>
       </c>
       <c r="AN35">
-        <v>-2.1057852117538313e-005</v>
+        <v>-2.1057852117538258e-005</v>
       </c>
       <c r="AO35">
-        <v>0.00038026104349897245</v>
+        <v>0.00038026104349897277</v>
       </c>
       <c r="AP35">
-        <v>0.00036953671517060899</v>
+        <v>0.00036953671517060905</v>
       </c>
       <c r="AQ35">
-        <v>0.00015484823302541241</v>
+        <v>0.00015484823302541281</v>
       </c>
       <c r="AR35">
-        <v>-0.00072346021065076169</v>
+        <v>-0.00072346021065076071</v>
       </c>
     </row>
     <row r="36">
@@ -5176,130 +5302,130 @@
         <v>0.31709786514647736</v>
       </c>
       <c r="C36">
-        <v>1.4316850098585939e-005</v>
+        <v>1.431685009858595e-005</v>
       </c>
       <c r="D36">
-        <v>1.3747387937357601e-006</v>
+        <v>1.3747387937359905e-006</v>
       </c>
       <c r="E36">
-        <v>-1.1317478305566059e-008</v>
+        <v>-1.1317478305567859e-008</v>
       </c>
       <c r="F36">
-        <v>0.0001295253426587838</v>
+        <v>0.00012952534265878396</v>
       </c>
       <c r="G36">
-        <v>3.7137573823124481e-005</v>
+        <v>3.7137573823123885e-005</v>
       </c>
       <c r="H36">
-        <v>8.9075732955111897e-006</v>
+        <v>8.9075732955107019e-006</v>
       </c>
       <c r="I36">
-        <v>5.601103958479401e-005</v>
+        <v>5.6011039584793901e-005</v>
       </c>
       <c r="J36">
-        <v>4.4931155737837401e-005</v>
+        <v>4.4931155737837239e-005</v>
       </c>
       <c r="K36">
-        <v>4.8177857676390951e-005</v>
+        <v>4.8177857676390897e-005</v>
       </c>
       <c r="L36">
-        <v>1.2930378904404786e-005</v>
+        <v>1.2930378904405329e-005</v>
       </c>
       <c r="M36">
-        <v>-8.5507285691666579e-006</v>
+        <v>-8.5507285691612369e-006</v>
       </c>
       <c r="N36">
-        <v>-3.932946520510724e-005</v>
+        <v>-3.9329465205102795e-005</v>
       </c>
       <c r="O36">
-        <v>-2.2218754609247874e-005</v>
+        <v>-2.2218754609244296e-005</v>
       </c>
       <c r="P36">
-        <v>-8.4943755631748826e-006</v>
+        <v>-8.494375563174747e-006</v>
       </c>
       <c r="Q36">
-        <v>-2.9757842378926318e-005</v>
+        <v>-2.9757842378926155e-005</v>
       </c>
       <c r="R36">
-        <v>-4.5502479570227658e-005</v>
+        <v>-4.5502479570227333e-005</v>
       </c>
       <c r="S36">
-        <v>1.8739130171534807e-006</v>
+        <v>1.8739130171535417e-006</v>
       </c>
       <c r="T36">
-        <v>6.7862422894459416e-007</v>
+        <v>6.7862422894464498e-007</v>
       </c>
       <c r="U36">
-        <v>-2.237748137005717e-005</v>
+        <v>-2.2377481370053917e-005</v>
       </c>
       <c r="V36">
-        <v>-4.6697600736223953e-005</v>
+        <v>-4.6697600736219291e-005</v>
       </c>
       <c r="W36">
-        <v>2.5606344078588821e-005</v>
+        <v>2.5606344078593483e-005</v>
       </c>
       <c r="X36">
-        <v>6.1921404085622648e-005</v>
+        <v>6.1921404085626985e-005</v>
       </c>
       <c r="Y36">
-        <v>9.3274257843658481e-006</v>
+        <v>9.3274257843655161e-006</v>
       </c>
       <c r="Z36">
-        <v>3.8810514857990052e-005</v>
+        <v>3.8810514857990357e-005</v>
       </c>
       <c r="AA36">
-        <v>0.00076262389974661329</v>
+        <v>0.00076262389974661427</v>
       </c>
       <c r="AB36">
-        <v>0.00076775634214041276</v>
+        <v>0.00076775634214041352</v>
       </c>
       <c r="AC36">
-        <v>0.00074810463871088516</v>
+        <v>0.00074810463871088613</v>
       </c>
       <c r="AD36">
-        <v>0.00074700902868599886</v>
+        <v>0.00074700902868599984</v>
       </c>
       <c r="AE36">
-        <v>0.00071566647326955527</v>
+        <v>0.00071566647326955614</v>
       </c>
       <c r="AF36">
-        <v>0.00075799814901674454</v>
+        <v>0.0007579981490167453</v>
       </c>
       <c r="AG36">
-        <v>0.00077346783161252419</v>
+        <v>0.00077346783161252506</v>
       </c>
       <c r="AH36">
-        <v>0.00077569916809100403</v>
+        <v>0.00077569916809100523</v>
       </c>
       <c r="AI36">
-        <v>0.00078004191764674655</v>
+        <v>0.00078004191764674742</v>
       </c>
       <c r="AJ36">
-        <v>0.0007556620152195764</v>
+        <v>0.00075566201521957727</v>
       </c>
       <c r="AK36">
-        <v>0.0017035240196553196</v>
+        <v>0.0017035240196553204</v>
       </c>
       <c r="AL36">
-        <v>-4.1361853284710372e-007</v>
+        <v>-4.1361853284707661e-007</v>
       </c>
       <c r="AM36">
-        <v>2.2917204746696876e-005</v>
+        <v>2.2917204746696903e-005</v>
       </c>
       <c r="AN36">
-        <v>-3.5590691236426743e-005</v>
+        <v>-3.559069123642677e-005</v>
       </c>
       <c r="AO36">
-        <v>0.00050836871260555761</v>
+        <v>0.00050836871260555782</v>
       </c>
       <c r="AP36">
         <v>0.00043259280791338786</v>
       </c>
       <c r="AQ36">
-        <v>0.00018508197948161365</v>
+        <v>0.00018508197948161414</v>
       </c>
       <c r="AR36">
-        <v>-0.00097377242397340264</v>
+        <v>-0.00097377242397340166</v>
       </c>
     </row>
     <row r="37">
@@ -5310,109 +5436,109 @@
         <v>0.0094379697399259582</v>
       </c>
       <c r="C37">
-        <v>6.9577425603410914e-007</v>
+        <v>6.9577425603409474e-007</v>
       </c>
       <c r="D37">
-        <v>-1.2111370772023238e-007</v>
+        <v>-1.211137077203137e-007</v>
       </c>
       <c r="E37">
-        <v>-2.9702376529953202e-011</v>
+        <v>-2.9702376529185578e-011</v>
       </c>
       <c r="F37">
-        <v>2.454494799653033e-006</v>
+        <v>2.4544947996529246e-006</v>
       </c>
       <c r="G37">
-        <v>-2.5129145492207836e-006</v>
+        <v>-2.5129145492206752e-006</v>
       </c>
       <c r="H37">
-        <v>5.3365881955915622e-006</v>
+        <v>5.3365881955916571e-006</v>
       </c>
       <c r="I37">
-        <v>6.0198201151925109e-007</v>
+        <v>6.0198201151937306e-007</v>
       </c>
       <c r="J37">
-        <v>-2.1481505128037657e-006</v>
+        <v>-2.1481505128036302e-006</v>
       </c>
       <c r="K37">
-        <v>1.4487326934295051e-006</v>
+        <v>1.4487326934294509e-006</v>
       </c>
       <c r="L37">
-        <v>3.6238143179959982e-006</v>
+        <v>3.6238143179961066e-006</v>
       </c>
       <c r="M37">
-        <v>-3.0699328490907461e-006</v>
+        <v>-3.0699328490908545e-006</v>
       </c>
       <c r="N37">
-        <v>-2.8486466540738318e-006</v>
+        <v>-2.8486466540735608e-006</v>
       </c>
       <c r="O37">
-        <v>1.7658887970857962e-006</v>
+        <v>1.7658887970856336e-006</v>
       </c>
       <c r="P37">
-        <v>-7.0892045033260566e-007</v>
+        <v>-7.0892045033263277e-007</v>
       </c>
       <c r="Q37">
-        <v>3.6657020293479569e-006</v>
+        <v>3.6657020293479298e-006</v>
       </c>
       <c r="R37">
-        <v>3.1260469260903907e-006</v>
+        <v>3.1260469260902958e-006</v>
       </c>
       <c r="S37">
-        <v>1.0809047784141537e-007</v>
+        <v>1.0809047784141452e-007</v>
       </c>
       <c r="T37">
-        <v>1.7875692451641683e-007</v>
+        <v>1.7875692451642361e-007</v>
       </c>
       <c r="U37">
-        <v>4.2542319785726667e-006</v>
+        <v>4.2542319785727751e-006</v>
       </c>
       <c r="V37">
-        <v>-1.6294092022376403e-006</v>
+        <v>-1.6294092022374777e-006</v>
       </c>
       <c r="W37">
-        <v>1.223786904663973e-006</v>
+        <v>1.2237869046642712e-006</v>
       </c>
       <c r="X37">
-        <v>3.233796564268025e-006</v>
+        <v>3.2337965642682961e-006</v>
       </c>
       <c r="Y37">
-        <v>8.1572801357504765e-008</v>
+        <v>8.1572801357501377e-008</v>
       </c>
       <c r="Z37">
-        <v>-2.2410219462174139e-006</v>
+        <v>-2.2410219462174207e-006</v>
       </c>
       <c r="AA37">
-        <v>-4.185880501603325e-007</v>
+        <v>-4.1858805016029184e-007</v>
       </c>
       <c r="AB37">
-        <v>8.2812427561535824e-006</v>
+        <v>8.2812427561536095e-006</v>
       </c>
       <c r="AC37">
-        <v>-1.3054637036469474e-006</v>
+        <v>-1.3054637036469203e-006</v>
       </c>
       <c r="AD37">
-        <v>-2.0205520996701917e-007</v>
+        <v>-2.0205520996700562e-007</v>
       </c>
       <c r="AE37">
-        <v>5.2159778893596945e-006</v>
+        <v>5.2159778893597081e-006</v>
       </c>
       <c r="AF37">
-        <v>-1.7176370339405016e-006</v>
+        <v>-1.7176370339404881e-006</v>
       </c>
       <c r="AG37">
-        <v>-3.6478814823989421e-007</v>
+        <v>-3.6478814823990777e-007</v>
       </c>
       <c r="AH37">
-        <v>1.1857755812136285e-006</v>
+        <v>1.1857755812136556e-006</v>
       </c>
       <c r="AI37">
-        <v>3.9421135921308836e-006</v>
+        <v>3.9421135921309243e-006</v>
       </c>
       <c r="AJ37">
         <v>2.6997776408038785e-007</v>
       </c>
       <c r="AK37">
-        <v>-4.1361853284710372e-007</v>
+        <v>-4.1361853284707661e-007</v>
       </c>
       <c r="AL37">
         <v>5.2557270910892523e-006</v>
@@ -5424,16 +5550,16 @@
         <v>-2.7346966961911284e-005</v>
       </c>
       <c r="AO37">
-        <v>1.0737892507111869e-005</v>
+        <v>1.0737892507111977e-005</v>
       </c>
       <c r="AP37">
-        <v>1.1331890824418911e-005</v>
+        <v>1.133189082441885e-005</v>
       </c>
       <c r="AQ37">
-        <v>-4.8508973518122782e-006</v>
+        <v>-4.8508973518122239e-006</v>
       </c>
       <c r="AR37">
-        <v>-9.4484547373245226e-005</v>
+        <v>-9.4484547373245266e-005</v>
       </c>
     </row>
     <row r="38">
@@ -5444,109 +5570,109 @@
         <v>0.021556552585683102</v>
       </c>
       <c r="C38">
-        <v>2.3552594679521088e-006</v>
+        <v>2.355259467952119e-006</v>
       </c>
       <c r="D38">
-        <v>-1.4510760285588929e-006</v>
+        <v>-1.45107602855871e-006</v>
       </c>
       <c r="E38">
-        <v>1.2819615368578351e-008</v>
+        <v>1.2819615368576234e-008</v>
       </c>
       <c r="F38">
-        <v>3.8627978727757322e-005</v>
+        <v>3.8627978727757051e-005</v>
       </c>
       <c r="G38">
-        <v>1.5017072349810152e-005</v>
+        <v>1.5017072349809529e-005</v>
       </c>
       <c r="H38">
-        <v>-3.2755924613270802e-006</v>
+        <v>-3.2755924613277849e-006</v>
       </c>
       <c r="I38">
-        <v>-2.4857347083338994e-005</v>
+        <v>-2.4857347083339699e-005</v>
       </c>
       <c r="J38">
-        <v>4.9999387739772805e-005</v>
+        <v>4.9999387739771992e-005</v>
       </c>
       <c r="K38">
-        <v>-4.5809783189185117e-006</v>
+        <v>-4.5809783189190538e-006</v>
       </c>
       <c r="L38">
-        <v>2.688945968248158e-005</v>
+        <v>2.6889459682480658e-005</v>
       </c>
       <c r="M38">
-        <v>-1.0022660543728161e-005</v>
+        <v>-1.0022660543727185e-005</v>
       </c>
       <c r="N38">
-        <v>-8.9782770100952898e-006</v>
+        <v>-8.9782770100955067e-006</v>
       </c>
       <c r="O38">
-        <v>-3.0443866844916275e-005</v>
+        <v>-3.0443866844915191e-005</v>
       </c>
       <c r="P38">
-        <v>-1.7533332889775854e-005</v>
+        <v>-1.75333328897758e-005</v>
       </c>
       <c r="Q38">
-        <v>-2.6417359465770262e-005</v>
+        <v>-2.6417359465770126e-005</v>
       </c>
       <c r="R38">
-        <v>-8.740134791834287e-005</v>
+        <v>-8.7401347918342545e-005</v>
       </c>
       <c r="S38">
-        <v>-4.3537703964380468e-007</v>
+        <v>-4.353770396437979e-007</v>
       </c>
       <c r="T38">
-        <v>4.588815820395906e-007</v>
+        <v>4.5888158203956349e-007</v>
       </c>
       <c r="U38">
-        <v>-6.2428407644931814e-005</v>
+        <v>-6.2428407644931705e-005</v>
       </c>
       <c r="V38">
-        <v>-3.0082986885877992e-005</v>
+        <v>-3.00829868858781e-005</v>
       </c>
       <c r="W38">
-        <v>-3.3545968427638596e-005</v>
+        <v>-3.3545968427638813e-005</v>
       </c>
       <c r="X38">
-        <v>-3.6071372926431856e-005</v>
+        <v>-3.6071372926432289e-005</v>
       </c>
       <c r="Y38">
         <v>6.7178253239322673e-006</v>
       </c>
       <c r="Z38">
-        <v>2.0566109562185455e-005</v>
+        <v>2.0566109562185522e-005</v>
       </c>
       <c r="AA38">
-        <v>1.0153964018569367e-005</v>
+        <v>1.0153964018569205e-005</v>
       </c>
       <c r="AB38">
-        <v>-2.7424139002368332e-006</v>
+        <v>-2.7424139002368603e-006</v>
       </c>
       <c r="AC38">
-        <v>6.3257219955537448e-005</v>
+        <v>6.3257219955537421e-005</v>
       </c>
       <c r="AD38">
-        <v>3.8669777341555943e-005</v>
+        <v>3.8669777341555862e-005</v>
       </c>
       <c r="AE38">
-        <v>1.9976263603420775e-005</v>
+        <v>1.9976263603420721e-005</v>
       </c>
       <c r="AF38">
-        <v>2.8469741865013473e-005</v>
+        <v>2.8469741865013446e-005</v>
       </c>
       <c r="AG38">
-        <v>1.2150099578316103e-005</v>
+        <v>1.2150099578316212e-005</v>
       </c>
       <c r="AH38">
-        <v>3.5195521248497454e-005</v>
+        <v>3.5195521248497399e-005</v>
       </c>
       <c r="AI38">
-        <v>-7.0821478250976465e-007</v>
+        <v>-7.0821478250990017e-007</v>
       </c>
       <c r="AJ38">
         <v>2.1656733642858348e-005</v>
       </c>
       <c r="AK38">
-        <v>2.2917204746696876e-005</v>
+        <v>2.2917204746696903e-005</v>
       </c>
       <c r="AL38">
         <v>-2.5447366411689566e-005</v>
@@ -5555,16 +5681,16 @@
         <v>0.0010128292213331396</v>
       </c>
       <c r="AN38">
-        <v>0.00012717129607673562</v>
+        <v>0.00012717129607673559</v>
       </c>
       <c r="AO38">
-        <v>-6.405161412790436e-005</v>
+        <v>-6.4051614127904645e-005</v>
       </c>
       <c r="AP38">
-        <v>-3.3860108883625265e-005</v>
+        <v>-3.3860108883625157e-005</v>
       </c>
       <c r="AQ38">
-        <v>7.3037320864195699e-006</v>
+        <v>7.3037320864194818e-006</v>
       </c>
       <c r="AR38">
         <v>0.0003942342501973724</v>
@@ -5578,88 +5704,88 @@
         <v>-0.022453996442778876</v>
       </c>
       <c r="C39">
-        <v>-4.6263798001906424e-006</v>
+        <v>-4.6263798001905069e-006</v>
       </c>
       <c r="D39">
-        <v>-4.1721003046750409e-006</v>
+        <v>-4.172100304674885e-006</v>
       </c>
       <c r="E39">
-        <v>3.7193788054851373e-008</v>
+        <v>3.7193788054849785e-008</v>
       </c>
       <c r="F39">
-        <v>-5.2194278313286786e-006</v>
+        <v>-5.2194278313278113e-006</v>
       </c>
       <c r="G39">
-        <v>1.8928164114159063e-005</v>
+        <v>1.8928164114159605e-005</v>
       </c>
       <c r="H39">
-        <v>-2.3311382286742011e-005</v>
+        <v>-2.3311382286741712e-005</v>
       </c>
       <c r="I39">
-        <v>1.6333941158872402e-005</v>
+        <v>1.6333941158872618e-005</v>
       </c>
       <c r="J39">
-        <v>3.2302692425942542e-005</v>
+        <v>3.2302692425942786e-005</v>
       </c>
       <c r="K39">
-        <v>3.1529328078946472e-006</v>
+        <v>3.1529328078952435e-006</v>
       </c>
       <c r="L39">
-        <v>1.6892956007167486e-005</v>
+        <v>1.6892956007167757e-005</v>
       </c>
       <c r="M39">
-        <v>4.3089916938325568e-005</v>
+        <v>4.3089916938325134e-005</v>
       </c>
       <c r="N39">
-        <v>2.8764268275706362e-005</v>
+        <v>2.876426827570517e-005</v>
       </c>
       <c r="O39">
-        <v>-5.4718112438425582e-006</v>
+        <v>-5.4718112438428834e-006</v>
       </c>
       <c r="P39">
-        <v>4.0653882754113316e-005</v>
+        <v>4.0653882754113234e-005</v>
       </c>
       <c r="Q39">
         <v>4.794313342363256e-005</v>
       </c>
       <c r="R39">
-        <v>-2.6548707415788414e-005</v>
+        <v>-2.6548707415788156e-005</v>
       </c>
       <c r="S39">
-        <v>-8.5843833960773721e-007</v>
+        <v>-8.5843833960775076e-007</v>
       </c>
       <c r="T39">
-        <v>1.6034020641304969e-006</v>
+        <v>1.6034020641304698e-006</v>
       </c>
       <c r="U39">
-        <v>-3.197922235086267e-005</v>
+        <v>-3.1979222350863212e-005</v>
       </c>
       <c r="V39">
-        <v>3.1343774996907443e-005</v>
+        <v>3.1343774996906576e-005</v>
       </c>
       <c r="W39">
-        <v>2.479204403048709e-005</v>
+        <v>2.4792044030486006e-005</v>
       </c>
       <c r="X39">
-        <v>3.1095124272513151e-005</v>
+        <v>3.1095124272512067e-005</v>
       </c>
       <c r="Y39">
-        <v>3.1385165109328633e-006</v>
+        <v>3.138516510932931e-006</v>
       </c>
       <c r="Z39">
-        <v>8.5543599476870262e-006</v>
+        <v>8.5543599476870397e-006</v>
       </c>
       <c r="AA39">
-        <v>-2.9249240436185031e-005</v>
+        <v>-2.9249240436185139e-005</v>
       </c>
       <c r="AB39">
-        <v>-3.7753771744656071e-005</v>
+        <v>-3.775377174465618e-005</v>
       </c>
       <c r="AC39">
-        <v>3.9561312607833414e-005</v>
+        <v>3.956131260783336e-005</v>
       </c>
       <c r="AD39">
-        <v>-1.3648641224538855e-006</v>
+        <v>-1.3648641224538584e-006</v>
       </c>
       <c r="AE39">
         <v>-1.3142188213072952e-005</v>
@@ -5668,40 +5794,40 @@
         <v>6.804480587293307e-006</v>
       </c>
       <c r="AG39">
-        <v>-3.153996104924661e-006</v>
+        <v>-3.1539961049245797e-006</v>
       </c>
       <c r="AH39">
-        <v>7.249235149254233e-006</v>
+        <v>7.2492351492541246e-006</v>
       </c>
       <c r="AI39">
-        <v>-4.0288353086371614e-005</v>
+        <v>-4.0288353086371696e-005</v>
       </c>
       <c r="AJ39">
-        <v>-2.1057852117538313e-005</v>
+        <v>-2.1057852117538258e-005</v>
       </c>
       <c r="AK39">
-        <v>-3.5590691236426743e-005</v>
+        <v>-3.559069123642677e-005</v>
       </c>
       <c r="AL39">
         <v>-2.7346966961911284e-005</v>
       </c>
       <c r="AM39">
-        <v>0.00012717129607673562</v>
+        <v>0.00012717129607673559</v>
       </c>
       <c r="AN39">
         <v>0.0010914491018651341</v>
       </c>
       <c r="AO39">
-        <v>-9.4842263013269459e-005</v>
+        <v>-9.4842263013269812e-005</v>
       </c>
       <c r="AP39">
-        <v>-8.2896844308442808e-005</v>
+        <v>-8.2896844308442564e-005</v>
       </c>
       <c r="AQ39">
-        <v>-2.0048302954905257e-005</v>
+        <v>-2.0048302954905434e-005</v>
       </c>
       <c r="AR39">
-        <v>0.00040090222642198009</v>
+        <v>0.00040090222642198296</v>
       </c>
     </row>
     <row r="40">
@@ -5712,130 +5838,130 @@
         <v>0.13590542833970337</v>
       </c>
       <c r="C40">
-        <v>-1.5382763588456706e-005</v>
+        <v>-1.5382763588456804e-005</v>
       </c>
       <c r="D40">
-        <v>4.3760362831400668e-006</v>
+        <v>4.3760362831398635e-006</v>
       </c>
       <c r="E40">
-        <v>-3.1435677844151087e-008</v>
+        <v>-3.1435677844148917e-008</v>
       </c>
       <c r="F40">
-        <v>0.00010029161839558622</v>
+        <v>0.00010029161839558601</v>
       </c>
       <c r="G40">
-        <v>6.1895639545434694e-005</v>
+        <v>6.1895639545434748e-005</v>
       </c>
       <c r="H40">
-        <v>-7.9006280705703699e-005</v>
+        <v>-7.9006280705703509e-005</v>
       </c>
       <c r="I40">
-        <v>-4.2336294477487665e-005</v>
+        <v>-4.2336294477487285e-005</v>
       </c>
       <c r="J40">
-        <v>-0.0001402046376901985</v>
+        <v>-0.0001402046376901979</v>
       </c>
       <c r="K40">
-        <v>5.1034847559638941e-005</v>
+        <v>5.103484755963867e-005</v>
       </c>
       <c r="L40">
-        <v>-6.3235109826288336e-005</v>
+        <v>-6.3235109826288065e-005</v>
       </c>
       <c r="M40">
         <v>-0.00010603247255646357</v>
       </c>
       <c r="N40">
-        <v>-5.4573577878855588e-005</v>
+        <v>-5.4573577878854666e-005</v>
       </c>
       <c r="O40">
-        <v>-8.0930963355587522e-005</v>
+        <v>-8.0930963355588118e-005</v>
       </c>
       <c r="P40">
-        <v>0.00012373135501357198</v>
+        <v>0.00012373135501357209</v>
       </c>
       <c r="Q40">
-        <v>6.4535690093456695e-005</v>
+        <v>6.453569009345683e-005</v>
       </c>
       <c r="R40">
-        <v>-3.5504609063952509e-005</v>
+        <v>-3.5504609063952617e-005</v>
       </c>
       <c r="S40">
-        <v>1.1665665695757725e-006</v>
+        <v>1.1665665695757759e-006</v>
       </c>
       <c r="T40">
-        <v>4.3872289432178702e-006</v>
+        <v>4.3872289432178736e-006</v>
       </c>
       <c r="U40">
-        <v>3.8012649383127161e-005</v>
+        <v>3.8012649383127703e-005</v>
       </c>
       <c r="V40">
-        <v>-7.1002114972978209e-006</v>
+        <v>-7.1002114972968993e-006</v>
       </c>
       <c r="W40">
-        <v>7.7262241716620278e-006</v>
+        <v>7.7262241716632204e-006</v>
       </c>
       <c r="X40">
-        <v>3.6381671166443971e-006</v>
+        <v>3.6381671166456982e-006</v>
       </c>
       <c r="Y40">
-        <v>2.6593975610107229e-006</v>
+        <v>2.6593975610106822e-006</v>
       </c>
       <c r="Z40">
-        <v>1.7994488680800379e-005</v>
+        <v>1.7994488680800515e-005</v>
       </c>
       <c r="AA40">
-        <v>0.00040667310985996778</v>
+        <v>0.00040667310985996799</v>
       </c>
       <c r="AB40">
         <v>0.00056897941243370031</v>
       </c>
       <c r="AC40">
-        <v>0.00036911767534070157</v>
+        <v>0.00036911767534070179</v>
       </c>
       <c r="AD40">
         <v>0.00034527432085628524</v>
       </c>
       <c r="AE40">
-        <v>0.00025121291813554785</v>
+        <v>0.00025121291813554796</v>
       </c>
       <c r="AF40">
-        <v>0.00038515508749997448</v>
+        <v>0.00038515508749997459</v>
       </c>
       <c r="AG40">
-        <v>0.0004016707033665921</v>
+        <v>0.0004016707033665922</v>
       </c>
       <c r="AH40">
-        <v>0.0004122811006228266</v>
+        <v>0.00041228110062282693</v>
       </c>
       <c r="AI40">
-        <v>0.00037346088621774333</v>
+        <v>0.00037346088621774344</v>
       </c>
       <c r="AJ40">
-        <v>0.00038026104349897245</v>
+        <v>0.00038026104349897277</v>
       </c>
       <c r="AK40">
-        <v>0.00050836871260555761</v>
+        <v>0.00050836871260555782</v>
       </c>
       <c r="AL40">
-        <v>1.0737892507111869e-005</v>
+        <v>1.0737892507111977e-005</v>
       </c>
       <c r="AM40">
-        <v>-6.405161412790436e-005</v>
+        <v>-6.4051614127904645e-005</v>
       </c>
       <c r="AN40">
-        <v>-9.4842263013269459e-005</v>
+        <v>-9.4842263013269812e-005</v>
       </c>
       <c r="AO40">
         <v>0.0020467706838353883</v>
       </c>
       <c r="AP40">
-        <v>0.00017511916118460944</v>
+        <v>0.0001751191611846095</v>
       </c>
       <c r="AQ40">
-        <v>0.00017546481009309901</v>
+        <v>0.00017546481009309922</v>
       </c>
       <c r="AR40">
-        <v>-0.0010999821206434924</v>
+        <v>-0.0010999821206434956</v>
       </c>
     </row>
     <row r="41">
@@ -5846,94 +5972,94 @@
         <v>-0.098354706674296799</v>
       </c>
       <c r="C41">
-        <v>8.8093084096739987e-005</v>
+        <v>8.809308409673996e-005</v>
       </c>
       <c r="D41">
-        <v>-1.2946571286714252e-006</v>
+        <v>-1.2946571286715336e-006</v>
       </c>
       <c r="E41">
-        <v>-4.4613305539511652e-009</v>
+        <v>-4.4613305539501064e-009</v>
       </c>
       <c r="F41">
-        <v>0.00016719960752428005</v>
+        <v>0.00016719960752427902</v>
       </c>
       <c r="G41">
-        <v>7.8146814757587942e-005</v>
+        <v>7.814681475758702e-005</v>
       </c>
       <c r="H41">
-        <v>0.00048721441514155874</v>
+        <v>0.00048721441514155777</v>
       </c>
       <c r="I41">
-        <v>-0.00031563404324402215</v>
+        <v>-0.00031563404324402302</v>
       </c>
       <c r="J41">
-        <v>4.9981873358811508e-005</v>
+        <v>4.9981873358810749e-005</v>
       </c>
       <c r="K41">
-        <v>2.6819045759125467e-005</v>
+        <v>2.6819045759124275e-005</v>
       </c>
       <c r="L41">
-        <v>-0.00012291969029934509</v>
+        <v>-0.00012291969029934623</v>
       </c>
       <c r="M41">
-        <v>-0.00017162079197778911</v>
+        <v>-0.00017162079197778943</v>
       </c>
       <c r="N41">
-        <v>-7.8984974460211783e-005</v>
+        <v>-7.8984974460212108e-005</v>
       </c>
       <c r="O41">
-        <v>5.6097868507115959e-005</v>
+        <v>5.6097868507114983e-005</v>
       </c>
       <c r="P41">
-        <v>-4.9457782564098861e-005</v>
+        <v>-4.9457782564099199e-005</v>
       </c>
       <c r="Q41">
-        <v>1.312708388221305e-005</v>
+        <v>1.3127083882212616e-005</v>
       </c>
       <c r="R41">
-        <v>1.6338125590001227e-005</v>
+        <v>1.6338125590000901e-005</v>
       </c>
       <c r="S41">
-        <v>1.1815582784634849e-006</v>
+        <v>1.18155827846349e-006</v>
       </c>
       <c r="T41">
-        <v>-3.4976686572818025e-006</v>
+        <v>-3.4976686572818457e-006</v>
       </c>
       <c r="U41">
-        <v>-6.4855753695447336e-005</v>
+        <v>-6.4855753695447445e-005</v>
       </c>
       <c r="V41">
-        <v>-0.00012735181070724398</v>
+        <v>-0.00012735181070724447</v>
       </c>
       <c r="W41">
-        <v>-0.0001907798999700902</v>
+        <v>-0.00019077989997009064</v>
       </c>
       <c r="X41">
-        <v>0.00011680430192955864</v>
+        <v>0.0001168043019295581</v>
       </c>
       <c r="Y41">
-        <v>9.2676325506488142e-006</v>
+        <v>9.2676325506488447e-006</v>
       </c>
       <c r="Z41">
-        <v>5.6032212269172835e-005</v>
+        <v>5.6032212269172822e-005</v>
       </c>
       <c r="AA41">
-        <v>0.00042653613757206023</v>
+        <v>0.00042653613757206001</v>
       </c>
       <c r="AB41">
-        <v>0.00034086033844387586</v>
+        <v>0.00034086033844387569</v>
       </c>
       <c r="AC41">
-        <v>0.0003493078803809193</v>
+        <v>0.00034930788038091919</v>
       </c>
       <c r="AD41">
-        <v>0.00035063666474183312</v>
+        <v>0.00035063666474183301</v>
       </c>
       <c r="AE41">
-        <v>0.00025745556175778983</v>
+        <v>0.00025745556175778972</v>
       </c>
       <c r="AF41">
-        <v>0.00033555524927157611</v>
+        <v>0.00033555524927157606</v>
       </c>
       <c r="AG41">
         <v>0.00043844491449865309</v>
@@ -5942,34 +6068,34 @@
         <v>0.00040746498305542402</v>
       </c>
       <c r="AI41">
-        <v>0.00040064684333281704</v>
+        <v>0.00040064684333281694</v>
       </c>
       <c r="AJ41">
-        <v>0.00036953671517060899</v>
+        <v>0.00036953671517060905</v>
       </c>
       <c r="AK41">
         <v>0.00043259280791338786</v>
       </c>
       <c r="AL41">
-        <v>1.1331890824418911e-005</v>
+        <v>1.133189082441885e-005</v>
       </c>
       <c r="AM41">
-        <v>-3.3860108883625265e-005</v>
+        <v>-3.3860108883625157e-005</v>
       </c>
       <c r="AN41">
-        <v>-8.2896844308442808e-005</v>
+        <v>-8.2896844308442564e-005</v>
       </c>
       <c r="AO41">
-        <v>0.00017511916118460944</v>
+        <v>0.0001751191611846095</v>
       </c>
       <c r="AP41">
         <v>0.004091670375793389</v>
       </c>
       <c r="AQ41">
-        <v>0.00013001197998526646</v>
+        <v>0.0001300119799852666</v>
       </c>
       <c r="AR41">
-        <v>-0.00049472177749748127</v>
+        <v>-0.0004947217774974714</v>
       </c>
     </row>
     <row r="42">
@@ -5980,130 +6106,130 @@
         <v>-0.040950088925950673</v>
       </c>
       <c r="C42">
-        <v>-3.256565125021845e-005</v>
+        <v>-3.2565651250218376e-005</v>
       </c>
       <c r="D42">
-        <v>2.9664197279297112e-006</v>
+        <v>2.9664197279297925e-006</v>
       </c>
       <c r="E42">
-        <v>-1.9718864686090522e-008</v>
+        <v>-1.971886468609084e-008</v>
       </c>
       <c r="F42">
-        <v>0.00039851319441228247</v>
+        <v>0.0003985131944122829</v>
       </c>
       <c r="G42">
-        <v>-1.7705123841352098e-005</v>
+        <v>-1.77051238413518e-005</v>
       </c>
       <c r="H42">
-        <v>-2.1844161501035204e-005</v>
+        <v>-2.1844161501035042e-005</v>
       </c>
       <c r="I42">
-        <v>9.3065147360806531e-005</v>
+        <v>9.3065147360807128e-005</v>
       </c>
       <c r="J42">
-        <v>-1.9265200884426091e-005</v>
+        <v>-1.9265200884425549e-005</v>
       </c>
       <c r="K42">
-        <v>-3.3611662745310089e-005</v>
+        <v>-3.3611662745309655e-005</v>
       </c>
       <c r="L42">
-        <v>-0.00010893720246602911</v>
+        <v>-0.00010893720246602835</v>
       </c>
       <c r="M42">
-        <v>1.1566786474190099e-005</v>
+        <v>1.1566786474192701e-005</v>
       </c>
       <c r="N42">
-        <v>0.00011508895384840147</v>
+        <v>0.00011508895384840348</v>
       </c>
       <c r="O42">
-        <v>-2.9974449459499724e-005</v>
+        <v>-2.9974449459498585e-005</v>
       </c>
       <c r="P42">
-        <v>2.7124900873592216e-005</v>
+        <v>2.7124900873592311e-005</v>
       </c>
       <c r="Q42">
-        <v>6.0124255663574305e-005</v>
+        <v>6.0124255663574291e-005</v>
       </c>
       <c r="R42">
-        <v>0.00031194683469120505</v>
+        <v>0.00031194683469120538</v>
       </c>
       <c r="S42">
-        <v>5.7822382418539757e-007</v>
+        <v>5.7822382418543145e-007</v>
       </c>
       <c r="T42">
-        <v>1.7125742510849635e-006</v>
+        <v>1.7125742510849551e-006</v>
       </c>
       <c r="U42">
-        <v>4.4192741894875313e-005</v>
+        <v>4.4192741894876939e-005</v>
       </c>
       <c r="V42">
-        <v>6.7146047269941132e-005</v>
+        <v>6.7146047269943301e-005</v>
       </c>
       <c r="W42">
-        <v>5.9091613669990414e-005</v>
+        <v>5.9091613669992799e-005</v>
       </c>
       <c r="X42">
-        <v>1.847634351199339e-005</v>
+        <v>1.8476343511995667e-005</v>
       </c>
       <c r="Y42">
-        <v>1.4885622350689095e-005</v>
+        <v>1.4885622350688898e-005</v>
       </c>
       <c r="Z42">
-        <v>3.2310732276846345e-006</v>
+        <v>3.2310732276847633e-006</v>
       </c>
       <c r="AA42">
-        <v>0.0001801290143543884</v>
+        <v>0.00018012901435438886</v>
       </c>
       <c r="AB42">
-        <v>0.00019285211886811151</v>
+        <v>0.00019285211886811186</v>
       </c>
       <c r="AC42">
-        <v>0.00014827495259978966</v>
+        <v>0.00014827495259979014</v>
       </c>
       <c r="AD42">
-        <v>0.00013240843373502206</v>
+        <v>0.00013240843373502254</v>
       </c>
       <c r="AE42">
-        <v>9.7964694079839826e-005</v>
+        <v>9.7964694079840286e-005</v>
       </c>
       <c r="AF42">
-        <v>8.1334805588733787e-005</v>
+        <v>8.1334805588734071e-005</v>
       </c>
       <c r="AG42">
-        <v>0.00013302587577027587</v>
+        <v>0.00013302587577027623</v>
       </c>
       <c r="AH42">
-        <v>0.00016470006754011466</v>
+        <v>0.00016470006754011523</v>
       </c>
       <c r="AI42">
-        <v>0.0001333008981011423</v>
+        <v>0.00013330089810114281</v>
       </c>
       <c r="AJ42">
-        <v>0.00015484823302541241</v>
+        <v>0.00015484823302541281</v>
       </c>
       <c r="AK42">
-        <v>0.00018508197948161365</v>
+        <v>0.00018508197948161414</v>
       </c>
       <c r="AL42">
-        <v>-4.8508973518122782e-006</v>
+        <v>-4.8508973518122239e-006</v>
       </c>
       <c r="AM42">
-        <v>7.3037320864195699e-006</v>
+        <v>7.3037320864194818e-006</v>
       </c>
       <c r="AN42">
-        <v>-2.0048302954905257e-005</v>
+        <v>-2.0048302954905434e-005</v>
       </c>
       <c r="AO42">
-        <v>0.00017546481009309901</v>
+        <v>0.00017546481009309922</v>
       </c>
       <c r="AP42">
-        <v>0.00013001197998526646</v>
+        <v>0.0001300119799852666</v>
       </c>
       <c r="AQ42">
-        <v>0.0023562015541280161</v>
+        <v>0.0023562015541280165</v>
       </c>
       <c r="AR42">
-        <v>-0.00039015444207898229</v>
+        <v>-0.0003901544420789838</v>
       </c>
     </row>
     <row r="43">
@@ -6114,130 +6240,130 @@
         <v>-2.6415002227624624</v>
       </c>
       <c r="C43">
-        <v>-6.9261250709546818e-005</v>
+        <v>-6.9261250709543417e-005</v>
       </c>
       <c r="D43">
-        <v>-0.00014875875697339168</v>
+        <v>-0.0001487587569733977</v>
       </c>
       <c r="E43">
-        <v>1.2858923047636232e-006</v>
+        <v>1.2858923047636871e-006</v>
       </c>
       <c r="F43">
-        <v>-0.001642070453253288</v>
+        <v>-0.0016420704532532754</v>
       </c>
       <c r="G43">
-        <v>-0.00085379951980207804</v>
+        <v>-0.00085379951980205484</v>
       </c>
       <c r="H43">
-        <v>-0.00089514177615652828</v>
+        <v>-0.00089514177615650464</v>
       </c>
       <c r="I43">
-        <v>-0.0013819365227629179</v>
+        <v>-0.0013819365227628949</v>
       </c>
       <c r="J43">
-        <v>-0.0009244285236165294</v>
+        <v>-0.00092442852361650511</v>
       </c>
       <c r="K43">
-        <v>-0.0013257180498786228</v>
+        <v>-0.001325718049878608</v>
       </c>
       <c r="L43">
-        <v>-0.0013669345585731907</v>
+        <v>-0.0013669345585731719</v>
       </c>
       <c r="M43">
-        <v>-0.0021289784604977893</v>
+        <v>-0.0021289784604978557</v>
       </c>
       <c r="N43">
-        <v>-0.0013618450006663604</v>
+        <v>-0.0013618450006664066</v>
       </c>
       <c r="O43">
-        <v>-0.00093452285064598022</v>
+        <v>-0.00093452285064605405</v>
       </c>
       <c r="P43">
-        <v>-0.00041412722166980738</v>
+        <v>-0.00041412722166980429</v>
       </c>
       <c r="Q43">
-        <v>-0.00056085186551675008</v>
+        <v>-0.00056085186551675117</v>
       </c>
       <c r="R43">
-        <v>-0.00028553703677698086</v>
+        <v>-0.00028553703677698601</v>
       </c>
       <c r="S43">
-        <v>-3.6233586246106934e-005</v>
+        <v>-3.6233586246106866e-005</v>
       </c>
       <c r="T43">
-        <v>-3.5586229727230072e-005</v>
+        <v>-3.5586229727230167e-005</v>
       </c>
       <c r="U43">
-        <v>-0.0010013012718396745</v>
+        <v>-0.0010013012718397172</v>
       </c>
       <c r="V43">
-        <v>-0.0011898007594459165</v>
+        <v>-0.0011898007594459677</v>
       </c>
       <c r="W43">
-        <v>-0.0013060491489696115</v>
+        <v>-0.001306049148969667</v>
       </c>
       <c r="X43">
-        <v>-0.0015469890464635779</v>
+        <v>-0.0015469890464636269</v>
       </c>
       <c r="Y43">
-        <v>9.6391757175422248e-005</v>
+        <v>9.6391757175425853e-005</v>
       </c>
       <c r="Z43">
-        <v>-6.246885734528862e-005</v>
+        <v>-6.2468857345290775e-005</v>
       </c>
       <c r="AA43">
-        <v>-0.00097135406621512844</v>
+        <v>-0.00097135406621512649</v>
       </c>
       <c r="AB43">
-        <v>-0.0010810131861802076</v>
+        <v>-0.0010810131861802047</v>
       </c>
       <c r="AC43">
-        <v>-0.00095530970503672149</v>
+        <v>-0.00095530970503672659</v>
       </c>
       <c r="AD43">
-        <v>-0.00094956294404000907</v>
+        <v>-0.00094956294404000864</v>
       </c>
       <c r="AE43">
-        <v>-0.0011091362621227568</v>
+        <v>-0.0011091362621227566</v>
       </c>
       <c r="AF43">
-        <v>-0.0008715863496420365</v>
+        <v>-0.00087158634964203921</v>
       </c>
       <c r="AG43">
-        <v>-0.00090903362570042296</v>
+        <v>-0.00090903362570042188</v>
       </c>
       <c r="AH43">
-        <v>-0.0010129733688989428</v>
+        <v>-0.0010129733688989456</v>
       </c>
       <c r="AI43">
-        <v>-0.000991779301602816</v>
+        <v>-0.00099177930160281773</v>
       </c>
       <c r="AJ43">
-        <v>-0.00072346021065076169</v>
+        <v>-0.00072346021065076071</v>
       </c>
       <c r="AK43">
-        <v>-0.00097377242397340264</v>
+        <v>-0.00097377242397340166</v>
       </c>
       <c r="AL43">
-        <v>-9.4484547373245226e-005</v>
+        <v>-9.4484547373245266e-005</v>
       </c>
       <c r="AM43">
         <v>0.0003942342501973724</v>
       </c>
       <c r="AN43">
-        <v>0.00040090222642198009</v>
+        <v>0.00040090222642198296</v>
       </c>
       <c r="AO43">
-        <v>-0.0010999821206434924</v>
+        <v>-0.0010999821206434956</v>
       </c>
       <c r="AP43">
-        <v>-0.00049472177749748127</v>
+        <v>-0.0004947217774974714</v>
       </c>
       <c r="AQ43">
-        <v>-0.00039015444207898229</v>
+        <v>-0.0003901544420789838</v>
       </c>
       <c r="AR43">
-        <v>0.012569363274011472</v>
+        <v>0.012569363274011629</v>
       </c>
     </row>
   </sheetData>
